--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27470,7 +27470,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>293.41</v>
+        <v>219.9</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
@@ -27550,7 +27550,7 @@
         <v>2.661398770219695e-05</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>293.411</v>
+        <v>219.901</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>0.1112857237805481</v>
@@ -27630,7 +27630,7 @@
         <v>5.261538975502517e-05</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>279.532</v>
+        <v>206.022</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.1154668076100317</v>
@@ -27710,7 +27710,7 @@
         <v>7.810692926740683e-05</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>271.571</v>
+        <v>198.061</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.1176226100741688</v>
@@ -27790,7 +27790,7 @@
         <v>0.0001031913293482641</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>265.851</v>
+        <v>192.341</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0.1190558697427829</v>
@@ -27855,7 +27855,7 @@
         <v>0.0001279713131065191</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>261.483</v>
+        <v>187.973</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0.1200895057210479</v>
@@ -27900,7 +27900,7 @@
         <v>0.0001525496036510941</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>258.055</v>
+        <v>184.545</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0.1208797211170362</v>
@@ -27934,7 +27934,7 @@
         <v>0.0001770289240909113</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>255.317</v>
+        <v>181.807</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.1215268809056527</v>
@@ -27964,7 +27964,7 @@
         <v>0.0002015119975348927</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>253.099</v>
+        <v>179.589</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.1221030145613062</v>
@@ -27989,7 +27989,7 @@
         <v>0.0002260726832141147</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>251.279</v>
+        <v>177.769</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.1226465337943992</v>
@@ -28006,7 +28006,7 @@
         <v>0.0002506693848482696</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>249.769</v>
+        <v>176.259</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0.1231313538342954</v>
@@ -28023,7 +28023,7 @@
         <v>0.0002752316422792043</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>248.503</v>
+        <v>174.993</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>0.1235321314044198</v>
@@ -28040,7 +28040,7 @@
         <v>0.0002996889953487651</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>247.432</v>
+        <v>173.922</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.1238339079555154</v>
@@ -28057,7 +28057,7 @@
         <v>0.0003239640399071632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>246.518</v>
+        <v>173.008</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.1240254217468656</v>
@@ -28074,7 +28074,7 @@
         <v>0.0003479515958380678</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>245.732</v>
+        <v>172.222</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>0.1240894832507529</v>
@@ -28091,7 +28091,7 @@
         <v>0.0003715395390335124</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>245.051</v>
+        <v>171.541</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>0.1240118522378651</v>
@@ -28108,7 +28108,7 @@
         <v>0.0003946157453855307</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>244.457</v>
+        <v>170.947</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>0.1237820992815037</v>
@@ -28125,7 +28125,7 @@
         <v>0.0004170775537410905</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>243.935</v>
+        <v>170.425</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0.1233955996827052</v>
@@ -28142,7 +28142,7 @@
         <v>0.0004388601547668969</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>243.475</v>
+        <v>169.965</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0.1228584881388688</v>
@@ -28159,7 +28159,7 @@
         <v>0.0004599082020845885</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>243.068</v>
+        <v>169.558</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>0.1221787452775384</v>
@@ -28176,7 +28176,7 @@
         <v>0.0004801663493158043</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>242.705</v>
+        <v>169.195</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0.1213637245757375</v>
@@ -28193,7 +28193,7 @@
         <v>0.0004996144084749656</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>242.38</v>
+        <v>168.87</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.1204272510841864</v>
@@ -28210,7 +28210,7 @@
         <v>0.0005183728251476213</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>242.088</v>
+        <v>168.578</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>0.1194131562024102</v>
@@ -28227,7 +28227,7 @@
         <v>0.0005365972033121028</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>241.825</v>
+        <v>168.315</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0.1183655353721301</v>
@@ -28244,7 +28244,7 @@
         <v>0.0005544431469467415</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>241.587</v>
+        <v>168.077</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>0.1173216363539563</v>
@@ -28261,7 +28261,7 @@
         <v>0.0005720440726142114</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>241.371</v>
+        <v>167.861</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>0.1163081869633094</v>
@@ -28278,7 +28278,7 @@
         <v>0.0005894446472145586</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>241.175</v>
+        <v>167.665</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>0.1153302643339966</v>
@@ -28295,7 +28295,7 @@
         <v>0.0006066673502321717</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>240.996</v>
+        <v>167.486</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>0.114388645785176</v>
@@ -28312,7 +28312,7 @@
         <v>0.0006237346611514396</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>240.832</v>
+        <v>167.322</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>0.1134837162942553</v>
@@ -28329,7 +28329,7 @@
         <v>0.0006406799617838726</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>240.681</v>
+        <v>167.171</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>0.1126178495617659</v>
@@ -28346,7 +28346,7 @@
         <v>0.0006575802432494677</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>240.543</v>
+        <v>167.033</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>0.1117997089875733</v>
@@ -28363,7 +28363,7 @@
         <v>0.0006745233989953432</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>240.415</v>
+        <v>166.905</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>0.1110400528034714</v>
@@ -28380,7 +28380,7 @@
         <v>0.0006915973224686174</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>240.298</v>
+        <v>166.788</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>0.1103466271593397</v>
@@ -28397,7 +28397,7 @@
         <v>0.0007088418133964745</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>240.189</v>
+        <v>166.679</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>0.1097205986317153</v>
@@ -28414,7 +28414,7 @@
         <v>0.0007261042966263634</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>240.088</v>
+        <v>166.578</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>0.1091328583492951</v>
@@ -28431,7 +28431,7 @@
         <v>0.0007431841032857985</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>239.994</v>
+        <v>166.484</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>0.1085510121743906</v>
@@ -28448,7 +28448,7 @@
         <v>0.0007598805645022946</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>239.907</v>
+        <v>166.397</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>0.1079458151702543</v>
@@ -28465,7 +28465,7 @@
         <v>0.0007760517094351554</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>239.825</v>
+        <v>166.315</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>0.1073001618543659</v>
@@ -28482,7 +28482,7 @@
         <v>0.0007917903593708433</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>239.749</v>
+        <v>166.239</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>0.1066290900331442</v>
@@ -28499,7 +28499,7 @@
         <v>0.0008072480336276096</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>239.678</v>
+        <v>166.168</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>0.1059546719306844</v>
@@ -28516,7 +28516,7 @@
         <v>0.0008225762515237059</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>239.612</v>
+        <v>166.102</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>0.1052963957719576</v>
@@ -28533,7 +28533,7 @@
         <v>0.0008379002154167179</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>239.549</v>
+        <v>166.039</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>0.1046694585321525</v>
@@ -28550,7 +28550,7 @@
         <v>0.0008532398598215696</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>239.49</v>
+        <v>165.98</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>0.1040735468549181</v>
@@ -28567,7 +28567,7 @@
         <v>0.0008685888022925192</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>239.434</v>
+        <v>165.924</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>0.1035060759143579</v>
@@ -28584,7 +28584,7 @@
         <v>0.0008839406603838247</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>239.382</v>
+        <v>165.872</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>0.1029638654141289</v>
@@ -28601,7 +28601,7 @@
         <v>0.0008992686264573183</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>239.332</v>
+        <v>165.822</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>0.1024429444577545</v>
@@ -28618,7 +28618,7 @@
         <v>0.0009144641921051261</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>239.286</v>
+        <v>165.776</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>0.1019289328018456</v>
@@ -28635,7 +28635,7 @@
         <v>0.0009293984237269484</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>239.242</v>
+        <v>165.732</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>0.1014080761625971</v>
@@ -28652,7 +28652,7 @@
         <v>0.0009439423877224854</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>239.2</v>
+        <v>165.69</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>0.1008669688875111</v>
@@ -28669,7 +28669,7 @@
         <v>0.0009580248387294006</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>239.161</v>
+        <v>165.651</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>0.1002989122045029</v>
@@ -28686,7 +28686,7 @@
         <v>0.0009718052843372098</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>239.124</v>
+        <v>165.614</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>0.09972222949425953</v>
@@ -28703,7 +28703,7 @@
         <v>0.0009855009203733921</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>239.089</v>
+        <v>165.579</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>0.09915923256847266</v>
@@ -28720,7 +28720,7 @@
         <v>0.0009993289426654271</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>239.055</v>
+        <v>165.545</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>0.098630942852046</v>
@@ -28737,7 +28737,7 @@
         <v>0.001013457143978018</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>239.024</v>
+        <v>165.514</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>0.0981508134539094</v>
@@ -28754,7 +28754,7 @@
         <v>0.001027855704824765</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>238.994</v>
+        <v>165.484</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>0.09771411145470539</v>
@@ -28771,7 +28771,7 @@
         <v>0.001042445402656492</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>238.966</v>
+        <v>165.456</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>0.0973106579992216</v>
@@ -28788,7 +28788,7 @@
         <v>0.001057147014924023</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>238.939</v>
+        <v>165.429</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>0.09693178568761178</v>
@@ -28805,7 +28805,7 @@
         <v>0.001071878193075125</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>238.913</v>
+        <v>165.403</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>0.09656876836882189</v>
@@ -28822,7 +28822,7 @@
         <v>0.001086544084545324</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>238.889</v>
+        <v>165.379</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>0.09621196842422147</v>
@@ -28839,7 +28839,7 @@
         <v>0.00110104671076709</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>238.866</v>
+        <v>165.356</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>0.0958529072251585</v>
@@ -28856,7 +28856,7 @@
         <v>0.001115288093172891</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>238.843</v>
+        <v>165.333</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>0.09548368957349142</v>
@@ -28873,7 +28873,7 @@
         <v>0.001129204542136493</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>238.821</v>
+        <v>165.311</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>0.09509904665700883</v>
@@ -28890,7 +28890,7 @@
         <v>0.001142869523796845</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>238.8</v>
+        <v>165.29</v>
       </c>
       <c r="E68" s="1" t="n">
         <v>0.09470579067421878</v>
@@ -28907,7 +28907,7 @@
         <v>0.00115639079323419</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>238.78</v>
+        <v>165.27</v>
       </c>
       <c r="E69" s="1" t="n">
         <v>0.09431310051574124</v>
@@ -28924,7 +28924,7 @@
         <v>0.001169876105528773</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>238.76</v>
+        <v>165.25</v>
       </c>
       <c r="E70" s="1" t="n">
         <v>0.09392997805670734</v>
@@ -28941,7 +28941,7 @@
         <v>0.001183398583241379</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>238.741</v>
+        <v>165.231</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>0.09356137035534468</v>
@@ -28958,7 +28958,7 @@
         <v>0.001196892818854963</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>238.723</v>
+        <v>165.213</v>
       </c>
       <c r="E72" s="1" t="n">
         <v>0.09320151171390739</v>
@@ -28975,7 +28975,7 @@
         <v>0.001210258772333016</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>238.705</v>
+        <v>165.195</v>
       </c>
       <c r="E73" s="1" t="n">
         <v>0.09284271134072715</v>
@@ -28992,7 +28992,7 @@
         <v>0.001223396403639034</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>238.688</v>
+        <v>165.178</v>
       </c>
       <c r="E74" s="1" t="n">
         <v>0.09247697085479535</v>
@@ -29009,7 +29009,7 @@
         <v>0.001236233964005328</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>238.671</v>
+        <v>165.161</v>
       </c>
       <c r="E75" s="1" t="n">
         <v>0.09209961654602945</v>
@@ -29026,7 +29026,7 @@
         <v>0.001248812869739474</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>238.655</v>
+        <v>165.145</v>
       </c>
       <c r="E76" s="1" t="n">
         <v>0.09171379883304261</v>
@@ -29043,7 +29043,7 @@
         <v>0.001261202828417863</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>238.64</v>
+        <v>165.13</v>
       </c>
       <c r="E77" s="1" t="n">
         <v>0.09132490757534896</v>
@@ -29060,7 +29060,7 @@
         <v>0.001273473547616889</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>238.626</v>
+        <v>165.116</v>
       </c>
       <c r="E78" s="1" t="n">
         <v>0.09093803483082658</v>
@@ -29077,7 +29077,7 @@
         <v>0.001285695902402913</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>238.612</v>
+        <v>165.102</v>
       </c>
       <c r="E79" s="1" t="n">
         <v>0.09055845680085915</v>
@@ -29094,7 +29094,7 @@
         <v>0.001297945437802176</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>238.598</v>
+        <v>165.088</v>
       </c>
       <c r="E80" s="1" t="n">
         <v>0.09019112662327873</v>
@@ -29111,7 +29111,7 @@
         <v>0.001310298866330885</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>238.585</v>
+        <v>165.075</v>
       </c>
       <c r="E81" s="1" t="n">
         <v>0.08984043797640451</v>
@@ -29128,7 +29128,7 @@
         <v>0.001322832900505251</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>238.573</v>
+        <v>165.063</v>
       </c>
       <c r="E82" s="1" t="n">
         <v>0.08951091532630005</v>
@@ -29145,7 +29145,7 @@
         <v>0.001335586209595795</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>238.561</v>
+        <v>165.051</v>
       </c>
       <c r="E83" s="1" t="n">
         <v>0.08920468188120592</v>
@@ -29162,7 +29162,7 @@
         <v>0.001348445289890304</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>238.549</v>
+        <v>165.039</v>
       </c>
       <c r="E84" s="1" t="n">
         <v>0.08891335992498277</v>
@@ -29179,7 +29179,7 @@
         <v>0.001361258594430875</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>238.538</v>
+        <v>165.028</v>
       </c>
       <c r="E85" s="1" t="n">
         <v>0.08862614604751046</v>
@@ -29196,7 +29196,7 @@
         <v>0.00137387457625961</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>238.526</v>
+        <v>165.016</v>
       </c>
       <c r="E86" s="1" t="n">
         <v>0.08833387229966326</v>
@@ -29213,7 +29213,7 @@
         <v>0.001386167395906253</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>238.515</v>
+        <v>165.005</v>
       </c>
       <c r="E87" s="1" t="n">
         <v>0.08802800479848273</v>
@@ -29230,7 +29230,7 @@
         <v>0.001398114043851136</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>238.505</v>
+        <v>164.995</v>
       </c>
       <c r="E88" s="1" t="n">
         <v>0.08770758483141153</v>
@@ -29247,7 +29247,7 @@
         <v>0.001409717218062237</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>238.494</v>
+        <v>164.984</v>
       </c>
       <c r="E89" s="1" t="n">
         <v>0.08737402622344086</v>
@@ -29264,7 +29264,7 @@
         <v>0.001420979616507535</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>238.484</v>
+        <v>164.974</v>
       </c>
       <c r="E90" s="1" t="n">
         <v>0.08702723974231855</v>
@@ -29281,7 +29281,7 @@
         <v>0.001431931678207736</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>238.474</v>
+        <v>164.964</v>
       </c>
       <c r="E91" s="1" t="n">
         <v>0.08666988679736835</v>
@@ -29298,7 +29298,7 @@
         <v>0.001442714806394464</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>238.464</v>
+        <v>164.954</v>
       </c>
       <c r="E92" s="1" t="n">
         <v>0.08631079314327535</v>
@@ -29315,7 +29315,7 @@
         <v>0.00145349814535207</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>238.455</v>
+        <v>164.945</v>
       </c>
       <c r="E93" s="1" t="n">
         <v>0.08595966027640642</v>
@@ -29332,7 +29332,7 @@
         <v>0.001464450839364906</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>238.446</v>
+        <v>164.936</v>
       </c>
       <c r="E94" s="1" t="n">
         <v>0.08562645772838749</v>
@@ -29349,7 +29349,7 @@
         <v>0.001475680364579871</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>238.438</v>
+        <v>164.928</v>
       </c>
       <c r="E95" s="1" t="n">
         <v>0.08531643816295487</v>
@@ -29366,7 +29366,7 @@
         <v>0.00148704752459405</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>238.429</v>
+        <v>164.919</v>
       </c>
       <c r="E96" s="1" t="n">
         <v>0.0850215769850417</v>
@@ -29383,7 +29383,7 @@
         <v>0.001498351454867077</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>238.421</v>
+        <v>164.911</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>0.08472931410638661</v>
@@ -29400,7 +29400,7 @@
         <v>0.001509391290858582</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>238.413</v>
+        <v>164.903</v>
       </c>
       <c r="E98" s="1" t="n">
         <v>0.08442867512139254</v>
@@ -29417,7 +29417,7 @@
         <v>0.001520018269174404</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>238.405</v>
+        <v>164.895</v>
       </c>
       <c r="E99" s="1" t="n">
         <v>0.08411169679232629</v>
@@ -29434,7 +29434,7 @@
         <v>0.001530292031005206</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>238.397</v>
+        <v>164.887</v>
       </c>
       <c r="E100" s="1" t="n">
         <v>0.08378216361978076</v>
@@ -29451,7 +29451,7 @@
         <v>0.001540324318687857</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>238.389</v>
+        <v>164.879</v>
       </c>
       <c r="E101" s="1" t="n">
         <v>0.0834465237514761</v>
@@ -29468,7 +29468,7 @@
         <v>0.001550226874559223</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>238.381</v>
+        <v>164.871</v>
       </c>
       <c r="E102" s="1" t="n">
         <v>0.0831109574662191</v>
@@ -29485,7 +29485,7 @@
         <v>0.001560110856307789</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>238.373</v>
+        <v>164.863</v>
       </c>
       <c r="E103" s="1" t="n">
         <v>0.08278135995956597</v>
@@ -29502,7 +29502,7 @@
         <v>0.001570085083028485</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>238.366</v>
+        <v>164.856</v>
       </c>
       <c r="E104" s="1" t="n">
         <v>0.08246291781169843</v>
@@ -29519,7 +29519,7 @@
         <v>0.001580257789167853</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>238.358</v>
+        <v>164.848</v>
       </c>
       <c r="E105" s="1" t="n">
         <v>0.08216160353758246</v>
@@ -29536,7 +29536,7 @@
         <v>0.001590737209172439</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>238.351</v>
+        <v>164.841</v>
       </c>
       <c r="E106" s="1" t="n">
         <v>0.08188179523644272</v>
@@ -29553,7 +29553,7 @@
         <v>0.001601567094611052</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>238.344</v>
+        <v>164.834</v>
       </c>
       <c r="E107" s="1" t="n">
         <v>0.0816254210145958</v>
@@ -29570,7 +29570,7 @@
         <v>0.001612533265541569</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>238.336</v>
+        <v>164.826</v>
       </c>
       <c r="E108" s="1" t="n">
         <v>0.08138132546288539</v>
@@ -29587,7 +29587,7 @@
         <v>0.00162335705914413</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>238.329</v>
+        <v>164.819</v>
       </c>
       <c r="E109" s="1" t="n">
         <v>0.08113455019743158</v>
@@ -29604,7 +29604,7 @@
         <v>0.001633759812598878</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>238.323</v>
+        <v>164.813</v>
       </c>
       <c r="E110" s="1" t="n">
         <v>0.08087137124245822</v>
@@ -29621,7 +29621,7 @@
         <v>0.001643545611554173</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>238.316</v>
+        <v>164.806</v>
       </c>
       <c r="E111" s="1" t="n">
         <v>0.08058331988090196</v>
@@ -29638,7 +29638,7 @@
         <v>0.001652849535531249</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>238.309</v>
+        <v>164.799</v>
       </c>
       <c r="E112" s="1" t="n">
         <v>0.08027732729997705</v>
@@ -29655,7 +29655,7 @@
         <v>0.001661889412519558</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>238.302</v>
+        <v>164.792</v>
       </c>
       <c r="E113" s="1" t="n">
         <v>0.07996437561390424</v>
@@ -29672,7 +29672,7 @@
         <v>0.001670883070508552</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>238.295</v>
+        <v>164.785</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>0.07965504141184</v>
@@ -29689,7 +29689,7 @@
         <v>0.001680002981852637</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>238.288</v>
+        <v>164.778</v>
       </c>
       <c r="E115" s="1" t="n">
         <v>0.07935737192106723</v>
@@ -29706,7 +29706,7 @@
         <v>0.001689240196366028</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>238.281</v>
+        <v>164.771</v>
       </c>
       <c r="E116" s="1" t="n">
         <v>0.07907063059222802</v>
@@ -29723,7 +29723,7 @@
         <v>0.001698540408227893</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>238.274</v>
+        <v>164.764</v>
       </c>
       <c r="E117" s="1" t="n">
         <v>0.07879200340939584</v>
@@ -29740,7 +29740,7 @@
         <v>0.0017078493116174</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>238.267</v>
+        <v>164.757</v>
       </c>
       <c r="E118" s="1" t="n">
         <v>0.07851877656387476</v>
@@ -29757,7 +29757,7 @@
         <v>0.001717111562107486</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>238.261</v>
+        <v>164.751</v>
       </c>
       <c r="E119" s="1" t="n">
         <v>0.07824795627706468</v>
@@ -29774,7 +29774,7 @@
         <v>0.001726267660846155</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>238.254</v>
+        <v>164.744</v>
       </c>
       <c r="E120" s="1" t="n">
         <v>0.0779774407055526</v>
@@ -29791,7 +29791,7 @@
         <v>0.001735257070375183</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>238.248</v>
+        <v>164.738</v>
       </c>
       <c r="E121" s="1" t="n">
         <v>0.07770386354634869</v>
@@ -29808,7 +29808,7 @@
         <v>0.001744019253236343</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>238.241</v>
+        <v>164.731</v>
       </c>
       <c r="E122" s="1" t="n">
         <v>0.07742526079464357</v>
@@ -29825,7 +29825,7 @@
         <v>0.001752515844284814</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>238.235</v>
+        <v>164.725</v>
       </c>
       <c r="E123" s="1" t="n">
         <v>0.07713942903919103</v>
@@ -29842,7 +29842,7 @@
         <v>0.001760797167629392</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>238.229</v>
+        <v>164.719</v>
       </c>
       <c r="E124" s="1" t="n">
         <v>0.07684906541954119</v>
@@ -29859,7 +29859,7 @@
         <v>0.001768935719692276</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>238.223</v>
+        <v>164.713</v>
       </c>
       <c r="E125" s="1" t="n">
         <v>0.07655742104023924</v>
@@ -29876,7 +29876,7 @@
         <v>0.001777003996895664</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>238.217</v>
+        <v>164.707</v>
       </c>
       <c r="E126" s="1" t="n">
         <v>0.07626763894907877</v>
@@ -29893,7 +29893,7 @@
         <v>0.00178506885825409</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>238.211</v>
+        <v>164.701</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>0.07598251864268254</v>
@@ -29910,7 +29910,7 @@
         <v>0.001793174613151416</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>238.205</v>
+        <v>164.695</v>
       </c>
       <c r="E128" s="1" t="n">
         <v>0.07570381612035583</v>
@@ -29927,7 +29927,7 @@
         <v>0.001801359933563841</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>238.199</v>
+        <v>164.689</v>
       </c>
       <c r="E129" s="1" t="n">
         <v>0.07543299439295768</v>
@@ -29944,7 +29944,7 @@
         <v>0.001809663491467559</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>238.193</v>
+        <v>164.683</v>
       </c>
       <c r="E130" s="1" t="n">
         <v>0.07517146943931527</v>
@@ -29961,7 +29961,7 @@
         <v>0.001818106811959512</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>238.188</v>
+        <v>164.678</v>
       </c>
       <c r="E131" s="1" t="n">
         <v>0.07491959096390317</v>
@@ -29978,7 +29978,7 @@
         <v>0.001826642832619614</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>238.182</v>
+        <v>164.672</v>
       </c>
       <c r="E132" s="1" t="n">
         <v>0.07467582834172752</v>
@@ -29995,7 +29995,7 @@
         <v>0.001835207344148521</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>238.176</v>
+        <v>164.666</v>
       </c>
       <c r="E133" s="1" t="n">
         <v>0.07443707764424058</v>
@@ -30012,7 +30012,7 @@
         <v>0.001843736137246892</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>238.171</v>
+        <v>164.661</v>
       </c>
       <c r="E134" s="1" t="n">
         <v>0.07420032586385963</v>
@@ -30029,7 +30029,7 @@
         <v>0.001852171233657576</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>238.165</v>
+        <v>164.655</v>
       </c>
       <c r="E135" s="1" t="n">
         <v>0.07396382794560923</v>
@@ -30046,7 +30046,7 @@
         <v>0.001860479579292194</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>238.16</v>
+        <v>164.65</v>
       </c>
       <c r="E136" s="1" t="n">
         <v>0.07372565302328093</v>
@@ -30063,7 +30063,7 @@
         <v>0.001868634351104557</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>238.154</v>
+        <v>164.644</v>
       </c>
       <c r="E137" s="1" t="n">
         <v>0.07348539732740578</v>
@@ -30080,7 +30080,7 @@
         <v>0.00187660872604848</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>238.149</v>
+        <v>164.639</v>
       </c>
       <c r="E138" s="1" t="n">
         <v>0.073241449781997</v>
@@ -30097,7 +30097,7 @@
         <v>0.001884384226049059</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>238.143</v>
+        <v>164.633</v>
       </c>
       <c r="E139" s="1" t="n">
         <v>0.07299378654942464</v>
@@ -30114,7 +30114,7 @@
         <v>0.001891975752916537</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>238.138</v>
+        <v>164.628</v>
       </c>
       <c r="E140" s="1" t="n">
         <v>0.07274245606748407</v>
@@ -30131,7 +30131,7 @@
         <v>0.001899406553432437</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>238.132</v>
+        <v>164.622</v>
       </c>
       <c r="E141" s="1" t="n">
         <v>0.07248903169380341</v>
@@ -30148,7 +30148,7 @@
         <v>0.001906699874378286</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>238.127</v>
+        <v>164.617</v>
       </c>
       <c r="E142" s="1" t="n">
         <v>0.0722338367551119</v>
@@ -30165,7 +30165,7 @@
         <v>0.001913874049517385</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>238.122</v>
+        <v>164.612</v>
       </c>
       <c r="E143" s="1" t="n">
         <v>0.07197789797869525</v>
@@ -30182,7 +30182,7 @@
         <v>0.001920927760540145</v>
       </c>
       <c r="D144" s="1" t="n">
-        <v>238.116</v>
+        <v>164.606</v>
       </c>
       <c r="E144" s="1" t="n">
         <v>0.07172148323675412</v>
@@ -30199,7 +30199,7 @@
         <v>0.00192785477611875</v>
       </c>
       <c r="D145" s="1" t="n">
-        <v>238.111</v>
+        <v>164.601</v>
       </c>
       <c r="E145" s="1" t="n">
         <v>0.07146377455220949</v>
@@ -30216,7 +30216,7 @@
         <v>0.001934648864925388</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>238.105</v>
+        <v>164.595</v>
       </c>
       <c r="E146" s="1" t="n">
         <v>0.07120516486028444</v>
@@ -30233,7 +30233,7 @@
         <v>0.001941318081847259</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>238.1</v>
+        <v>164.59</v>
       </c>
       <c r="E147" s="1" t="n">
         <v>0.07094537457178263</v>
@@ -30250,7 +30250,7 @@
         <v>0.001947927626631631</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>238.094</v>
+        <v>164.584</v>
       </c>
       <c r="E148" s="1" t="n">
         <v>0.07068738501140739</v>
@@ -30267,7 +30267,7 @@
         <v>0.001954556985240787</v>
       </c>
       <c r="D149" s="1" t="n">
-        <v>238.089</v>
+        <v>164.579</v>
       </c>
       <c r="E149" s="1" t="n">
         <v>0.0704334339643997</v>
@@ -30284,7 +30284,7 @@
         <v>0.001961285643637013</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>238.084</v>
+        <v>164.574</v>
       </c>
       <c r="E150" s="1" t="n">
         <v>0.07018657358347999</v>
@@ -30301,7 +30301,7 @@
         <v>0.001968161884976572</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>238.078</v>
+        <v>164.568</v>
       </c>
       <c r="E151" s="1" t="n">
         <v>0.06994866717354301</v>
@@ -30318,7 +30318,7 @@
         <v>0.001975109181191667</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>238.073</v>
+        <v>164.563</v>
       </c>
       <c r="E152" s="1" t="n">
         <v>0.06971624730426294</v>
@@ -30335,7 +30335,7 @@
         <v>0.001982019801408476</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>238.067</v>
+        <v>164.557</v>
       </c>
       <c r="E153" s="1" t="n">
         <v>0.06948600598764205</v>
@@ -30352,7 +30352,7 @@
         <v>0.001988786014753182</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>238.062</v>
+        <v>164.552</v>
       </c>
       <c r="E154" s="1" t="n">
         <v>0.0692535687888145</v>
@@ -30369,7 +30369,7 @@
         <v>0.001995328602121302</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>238.057</v>
+        <v>164.547</v>
       </c>
       <c r="E155" s="1" t="n">
         <v>0.0690165264330737</v>
@@ -30386,7 +30386,7 @@
         <v>0.002001682391485688</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>238.052</v>
+        <v>164.542</v>
       </c>
       <c r="E156" s="1" t="n">
         <v>0.06877616720064846</v>
@@ -30403,7 +30403,7 @@
         <v>0.002007910722588528</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>238.047</v>
+        <v>164.537</v>
       </c>
       <c r="E157" s="1" t="n">
         <v>0.06853471851876157</v>
@@ -30420,7 +30420,7 @@
         <v>0.002014076935172008</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>238.042</v>
+        <v>164.532</v>
       </c>
       <c r="E158" s="1" t="n">
         <v>0.06829434937854423</v>
@@ -30437,7 +30437,7 @@
         <v>0.002020226539476091</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>238.037</v>
+        <v>164.527</v>
       </c>
       <c r="E159" s="1" t="n">
         <v>0.06805657161169748</v>
@@ -30454,7 +30454,7 @@
         <v>0.002026333727731821</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>238.032</v>
+        <v>164.522</v>
       </c>
       <c r="E160" s="1" t="n">
         <v>0.06782047092812034</v>
@@ -30471,7 +30471,7 @@
         <v>0.002032354862668019</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>238.027</v>
+        <v>164.517</v>
       </c>
       <c r="E161" s="1" t="n">
         <v>0.06758456365234446</v>
@@ -30488,7 +30488,7 @@
         <v>0.002038246307013504</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>238.022</v>
+        <v>164.512</v>
       </c>
       <c r="E162" s="1" t="n">
         <v>0.06734740403070419</v>
@@ -30505,7 +30505,7 @@
         <v>0.002043984623523161</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>238.017</v>
+        <v>164.507</v>
       </c>
       <c r="E163" s="1" t="n">
         <v>0.06710824623229301</v>
@@ -30522,7 +30522,7 @@
         <v>0.00204962717505614</v>
       </c>
       <c r="D164" s="1" t="n">
-        <v>238.012</v>
+        <v>164.502</v>
       </c>
       <c r="E164" s="1" t="n">
         <v>0.06686899934368876</v>
@@ -30539,7 +30539,7 @@
         <v>0.002055251524497656</v>
       </c>
       <c r="D165" s="1" t="n">
-        <v>238.007</v>
+        <v>164.497</v>
       </c>
       <c r="E165" s="1" t="n">
         <v>0.06663217947431646</v>
@@ -30556,7 +30556,7 @@
         <v>0.002060935234732921</v>
       </c>
       <c r="D166" s="1" t="n">
-        <v>238.003</v>
+        <v>164.493</v>
       </c>
       <c r="E166" s="1" t="n">
         <v>0.06639996105175112</v>
@@ -30573,7 +30573,7 @@
         <v>0.002066736533294453</v>
       </c>
       <c r="D167" s="1" t="n">
-        <v>237.998</v>
+        <v>164.488</v>
       </c>
       <c r="E167" s="1" t="n">
         <v>0.0661746765660404</v>
@@ -30590,7 +30590,7 @@
         <v>0.002072636306303973</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>237.993</v>
+        <v>164.483</v>
       </c>
       <c r="E168" s="1" t="n">
         <v>0.06595531483318721</v>
@@ -30607,7 +30607,7 @@
         <v>0.002078596104530505</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>237.988</v>
+        <v>164.478</v>
       </c>
       <c r="E169" s="1" t="n">
         <v>0.06574055099377865</v>
@@ -30624,7 +30624,7 @@
         <v>0.00208457747874307</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>237.983</v>
+        <v>164.473</v>
       </c>
       <c r="E170" s="1" t="n">
         <v>0.06552909240048935</v>
@@ -30641,7 +30641,7 @@
         <v>0.002090553558184468</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>237.978</v>
+        <v>164.468</v>
       </c>
       <c r="E171" s="1" t="n">
         <v>0.06532003941520105</v>
@@ -30658,7 +30658,7 @@
         <v>0.002096543785992593</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>237.973</v>
+        <v>164.463</v>
       </c>
       <c r="E172" s="1" t="n">
         <v>0.06511395241349904</v>
@@ -30675,7 +30675,7 @@
         <v>0.002102579183779113</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>237.969</v>
+        <v>164.459</v>
       </c>
       <c r="E173" s="1" t="n">
         <v>0.06491146308099088</v>
@@ -30692,7 +30692,7 @@
         <v>0.002108690773155699</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>237.964</v>
+        <v>164.454</v>
       </c>
       <c r="E174" s="1" t="n">
         <v>0.06471400079436644</v>
@@ -30709,7 +30709,7 @@
         <v>0.002114886102030925</v>
       </c>
       <c r="D175" s="1" t="n">
-        <v>237.959</v>
+        <v>164.449</v>
       </c>
       <c r="E175" s="1" t="n">
         <v>0.06452143797568857</v>
@@ -30726,7 +30726,7 @@
         <v>0.002121078823500985</v>
       </c>
       <c r="D176" s="1" t="n">
-        <v>237.954</v>
+        <v>164.444</v>
       </c>
       <c r="E176" s="1" t="n">
         <v>0.06433106947369424</v>
@@ -30743,7 +30743,7 @@
         <v>0.002127159116958984</v>
       </c>
       <c r="D177" s="1" t="n">
-        <v>237.949</v>
+        <v>164.439</v>
       </c>
       <c r="E177" s="1" t="n">
         <v>0.06413954540166739</v>
@@ -30760,7 +30760,7 @@
         <v>0.00213301716179802</v>
       </c>
       <c r="D178" s="1" t="n">
-        <v>237.945</v>
+        <v>164.435</v>
       </c>
       <c r="E178" s="1" t="n">
         <v>0.06394332476785552</v>
@@ -30777,7 +30777,7 @@
         <v>0.002138565696239664</v>
       </c>
       <c r="D179" s="1" t="n">
-        <v>237.94</v>
+        <v>164.43</v>
       </c>
       <c r="E179" s="1" t="n">
         <v>0.06374042138330177</v>
@@ -30794,7 +30794,7 @@
         <v>0.002143807693819359</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>237.935</v>
+        <v>164.425</v>
       </c>
       <c r="E180" s="1" t="n">
         <v>0.06353077310637087</v>
@@ -30811,7 +30811,7 @@
         <v>0.002148768686901016</v>
       </c>
       <c r="D181" s="1" t="n">
-        <v>237.931</v>
+        <v>164.421</v>
       </c>
       <c r="E181" s="1" t="n">
         <v>0.06331498121943306</v>
@@ -30828,7 +30828,7 @@
         <v>0.002153474207848548</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>237.926</v>
+        <v>164.416</v>
       </c>
       <c r="E182" s="1" t="n">
         <v>0.06309442659848397</v>
@@ -30845,7 +30845,7 @@
         <v>0.002157972926543238</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>237.922</v>
+        <v>164.412</v>
       </c>
       <c r="E183" s="1" t="n">
         <v>0.06287008071645467</v>
@@ -30862,7 +30862,7 @@
         <v>0.002162406062935862</v>
       </c>
       <c r="D184" s="1" t="n">
-        <v>237.917</v>
+        <v>164.407</v>
       </c>
       <c r="E184" s="1" t="n">
         <v>0.06264662334061398</v>
@@ -30879,7 +30879,7 @@
         <v>0.002166937974494568</v>
       </c>
       <c r="D185" s="1" t="n">
-        <v>237.913</v>
+        <v>164.403</v>
       </c>
       <c r="E185" s="1" t="n">
         <v>0.06242825138601774</v>
@@ -30896,7 +30896,7 @@
         <v>0.002171733018687505</v>
       </c>
       <c r="D186" s="1" t="n">
-        <v>237.909</v>
+        <v>164.399</v>
       </c>
       <c r="E186" s="1" t="n">
         <v>0.06221984890078584</v>
@@ -30913,7 +30913,7 @@
         <v>0.002176901077804824</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>237.904</v>
+        <v>164.394</v>
       </c>
       <c r="E187" s="1" t="n">
         <v>0.0620246425073574</v>
@@ -30930,7 +30930,7 @@
         <v>0.002182334133424685</v>
       </c>
       <c r="D188" s="1" t="n">
-        <v>237.9</v>
+        <v>164.39</v>
       </c>
       <c r="E188" s="1" t="n">
         <v>0.06183883651045132</v>
@@ -30947,7 +30947,7 @@
         <v>0.002187869691947251</v>
       </c>
       <c r="D189" s="1" t="n">
-        <v>237.896</v>
+        <v>164.386</v>
       </c>
       <c r="E189" s="1" t="n">
         <v>0.06165795507290891</v>
@@ -30964,7 +30964,7 @@
         <v>0.002193345259772684</v>
       </c>
       <c r="D190" s="1" t="n">
-        <v>237.892</v>
+        <v>164.382</v>
       </c>
       <c r="E190" s="1" t="n">
         <v>0.06147736350846496</v>
@@ -30981,7 +30981,7 @@
         <v>0.002198630832435984</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>237.887</v>
+        <v>164.377</v>
       </c>
       <c r="E191" s="1" t="n">
         <v>0.06129369042552286</v>
@@ -30998,7 +30998,7 @@
         <v>0.002203726362011487</v>
       </c>
       <c r="D192" s="1" t="n">
-        <v>237.883</v>
+        <v>164.373</v>
       </c>
       <c r="E192" s="1" t="n">
         <v>0.06110647198914575</v>
@@ -31015,7 +31015,7 @@
         <v>0.002208664289708364</v>
       </c>
       <c r="D193" s="1" t="n">
-        <v>237.879</v>
+        <v>164.369</v>
       </c>
       <c r="E193" s="1" t="n">
         <v>0.06091691385045522</v>
@@ -31032,7 +31032,7 @@
         <v>0.002213477056735786</v>
       </c>
       <c r="D194" s="1" t="n">
-        <v>237.875</v>
+        <v>164.365</v>
       </c>
       <c r="E194" s="1" t="n">
         <v>0.0607259431401001</v>
@@ -31049,7 +31049,7 @@
         <v>0.002218185060532989</v>
       </c>
       <c r="D195" s="1" t="n">
-        <v>237.87</v>
+        <v>164.36</v>
       </c>
       <c r="E195" s="1" t="n">
         <v>0.06053439323680806</v>
@@ -31066,7 +31066,7 @@
         <v>0.002222760523459464</v>
       </c>
       <c r="D196" s="1" t="n">
-        <v>237.866</v>
+        <v>164.356</v>
       </c>
       <c r="E196" s="1" t="n">
         <v>0.06034101331060278</v>
@@ -31083,7 +31083,7 @@
         <v>0.002227163624104767</v>
       </c>
       <c r="D197" s="1" t="n">
-        <v>237.862</v>
+        <v>164.352</v>
       </c>
       <c r="E197" s="1" t="n">
         <v>0.06014500781608029</v>
@@ -31100,7 +31100,7 @@
         <v>0.002231354541058451</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>237.858</v>
+        <v>164.348</v>
       </c>
       <c r="E198" s="1" t="n">
         <v>0.05994534774201475</v>
@@ -31117,7 +31117,7 @@
         <v>0.002235325085873816</v>
       </c>
       <c r="D199" s="1" t="n">
-        <v>237.854</v>
+        <v>164.344</v>
       </c>
       <c r="E199" s="1" t="n">
         <v>0.05974187076292248</v>
@@ -31134,7 +31134,7 @@
         <v>0.002239193601959133</v>
       </c>
       <c r="D200" s="1" t="n">
-        <v>237.85</v>
+        <v>164.34</v>
       </c>
       <c r="E200" s="1" t="n">
         <v>0.05953778223335349</v>
@@ -31151,7 +31151,7 @@
         <v>0.00224311006568642</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>237.845</v>
+        <v>164.335</v>
       </c>
       <c r="E201" s="1" t="n">
         <v>0.05933730823316435</v>
@@ -31168,7 +31168,7 @@
         <v>0.002247224453427692</v>
       </c>
       <c r="D202" s="1" t="n">
-        <v>237.841</v>
+        <v>164.331</v>
       </c>
       <c r="E202" s="1" t="n">
         <v>0.05914384470982588</v>
@@ -31185,7 +31185,7 @@
         <v>0.002251631134770238</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>237.837</v>
+        <v>164.327</v>
       </c>
       <c r="E203" s="1" t="n">
         <v>0.05896000278338819</v>
@@ -31202,7 +31202,7 @@
         <v>0.002256202052162433</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>237.833</v>
+        <v>164.323</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0.05878230068974353</v>
@@ -31219,7 +31219,7 @@
         <v>0.002260753541267923</v>
       </c>
       <c r="D205" s="1" t="n">
-        <v>237.829</v>
+        <v>164.319</v>
       </c>
       <c r="E205" s="1" t="n">
         <v>0.05860588492288851</v>
@@ -31236,7 +31236,7 @@
         <v>0.002265101937750358</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>237.824</v>
+        <v>164.314</v>
       </c>
       <c r="E206" s="1" t="n">
         <v>0.05842624439730312</v>
@@ -31253,7 +31253,7 @@
         <v>0.002269117332231759</v>
       </c>
       <c r="D207" s="1" t="n">
-        <v>237.82</v>
+        <v>164.31</v>
       </c>
       <c r="E207" s="1" t="n">
         <v>0.05823960426362389</v>
@@ -31270,7 +31270,7 @@
         <v>0.002272884835167656</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>237.816</v>
+        <v>164.306</v>
       </c>
       <c r="E208" s="1" t="n">
         <v>0.05804848449286561</v>
@@ -31287,7 +31287,7 @@
         <v>0.002276543311971955</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>237.812</v>
+        <v>164.302</v>
       </c>
       <c r="E209" s="1" t="n">
         <v>0.05785648011938557</v>
@@ -31304,7 +31304,7 @@
         <v>0.00228023162805856</v>
       </c>
       <c r="D210" s="1" t="n">
-        <v>237.807</v>
+        <v>164.297</v>
       </c>
       <c r="E210" s="1" t="n">
         <v>0.05766735841838327</v>
@@ -31321,7 +31321,7 @@
         <v>0.002284048575570907</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>237.803</v>
+        <v>164.293</v>
       </c>
       <c r="E211" s="1" t="n">
         <v>0.05748308133949132</v>
@@ -31338,7 +31338,7 @@
         <v>0.002287932653570548</v>
       </c>
       <c r="D212" s="1" t="n">
-        <v>237.799</v>
+        <v>164.289</v>
       </c>
       <c r="E212" s="1" t="n">
         <v>0.05730227791930999</v>
@@ -31355,7 +31355,7 @@
         <v>0.002291782287848565</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>237.795</v>
+        <v>164.285</v>
       </c>
       <c r="E213" s="1" t="n">
         <v>0.05712236617602257</v>
@@ -31372,7 +31372,7 @@
         <v>0.002295495904196042</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>237.791</v>
+        <v>164.281</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0.05694081361178396</v>
@@ -31389,7 +31389,7 @@
         <v>0.002299004864902178</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>237.787</v>
+        <v>164.277</v>
       </c>
       <c r="E215" s="1" t="n">
         <v>0.05675594913816879</v>
@@ -31406,7 +31406,7 @@
         <v>0.002302372278248647</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>237.783</v>
+        <v>164.273</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0.05656937038733476</v>
@@ -31423,7 +31423,7 @@
         <v>0.002305694189015241</v>
       </c>
       <c r="D217" s="1" t="n">
-        <v>237.78</v>
+        <v>164.27</v>
       </c>
       <c r="E217" s="1" t="n">
         <v>0.05638321311314566</v>
@@ -31440,7 +31440,7 @@
         <v>0.002309066641981755</v>
       </c>
       <c r="D218" s="1" t="n">
-        <v>237.776</v>
+        <v>164.266</v>
       </c>
       <c r="E218" s="1" t="n">
         <v>0.05620028059415675</v>
@@ -31457,7 +31457,7 @@
         <v>0.00231255639534559</v>
       </c>
       <c r="D219" s="1" t="n">
-        <v>237.772</v>
+        <v>164.262</v>
       </c>
       <c r="E219" s="1" t="n">
         <v>0.05602191014562068</v>
@@ -31474,7 +31474,7 @@
         <v>0.002316113060974595</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>237.768</v>
+        <v>164.258</v>
       </c>
       <c r="E220" s="1" t="n">
         <v>0.05584682298218582</v>
@@ -31491,7 +31491,7 @@
         <v>0.002319656964154227</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>237.765</v>
+        <v>164.255</v>
       </c>
       <c r="E221" s="1" t="n">
         <v>0.05567282698254609</v>
@@ -31508,7 +31508,7 @@
         <v>0.002323108430169946</v>
       </c>
       <c r="D222" s="1" t="n">
-        <v>237.761</v>
+        <v>164.251</v>
       </c>
       <c r="E222" s="1" t="n">
         <v>0.05549846934028149</v>
@@ -31525,7 +31525,7 @@
         <v>0.002326425379775902</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>237.757</v>
+        <v>164.247</v>
       </c>
       <c r="E223" s="1" t="n">
         <v>0.0553225226661764</v>
@@ -31542,7 +31542,7 @@
         <v>0.002329716115601015</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>237.754</v>
+        <v>164.244</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>0.05514734038644178</v>
@@ -31559,7 +31559,7 @@
         <v>0.002333126535742898</v>
       </c>
       <c r="D225" s="1" t="n">
-        <v>237.75</v>
+        <v>164.24</v>
       </c>
       <c r="E225" s="1" t="n">
         <v>0.05497681133509232</v>
@@ -31576,7 +31576,7 @@
         <v>0.002336802538299164</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>237.747</v>
+        <v>164.237</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0.05481383444554529</v>
@@ -31593,7 +31593,7 @@
         <v>0.00234082833310125</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>237.743</v>
+        <v>164.233</v>
       </c>
       <c r="E227" s="1" t="n">
         <v>0.05466073252972457</v>
@@ -31610,7 +31610,7 @@
         <v>0.002345041376915894</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>237.74</v>
+        <v>164.23</v>
       </c>
       <c r="E228" s="1" t="n">
         <v>0.05451313662523762</v>
@@ -31627,7 +31627,7 @@
         <v>0.00234921743824366</v>
       </c>
       <c r="D229" s="1" t="n">
-        <v>237.737</v>
+        <v>164.227</v>
       </c>
       <c r="E229" s="1" t="n">
         <v>0.05436601107339335</v>
@@ -31644,7 +31644,7 @@
         <v>0.002353132285585111</v>
       </c>
       <c r="D230" s="1" t="n">
-        <v>237.734</v>
+        <v>164.224</v>
       </c>
       <c r="E230" s="1" t="n">
         <v>0.05421418343801334</v>
@@ -31661,7 +31661,7 @@
         <v>0.002356629775254825</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>237.73</v>
+        <v>164.22</v>
       </c>
       <c r="E231" s="1" t="n">
         <v>0.05405436208747426</v>
@@ -31678,7 +31678,7 @@
         <v>0.002359826114823439</v>
       </c>
       <c r="D232" s="1" t="n">
-        <v>237.727</v>
+        <v>164.217</v>
       </c>
       <c r="E232" s="1" t="n">
         <v>0.05388885404318669</v>
@@ -31695,7 +31695,7 @@
         <v>0.002362905599675604</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>237.724</v>
+        <v>164.214</v>
       </c>
       <c r="E233" s="1" t="n">
         <v>0.05372214930507026</v>
@@ -31712,7 +31712,7 @@
         <v>0.002366052525195971</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>237.721</v>
+        <v>164.211</v>
       </c>
       <c r="E234" s="1" t="n">
         <v>0.05355843526598324</v>
@@ -31729,7 +31729,7 @@
         <v>0.00236940104541944</v>
       </c>
       <c r="D235" s="1" t="n">
-        <v>237.718</v>
+        <v>164.208</v>
       </c>
       <c r="E235" s="1" t="n">
         <v>0.05340069631876838</v>
@@ -31746,7 +31746,7 @@
         <v>0.002372884748981894</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>237.715</v>
+        <v>164.205</v>
       </c>
       <c r="E236" s="1" t="n">
         <v>0.05324736443251123</v>
@@ -31763,7 +31763,7 @@
         <v>0.002376387083169464</v>
       </c>
       <c r="D237" s="1" t="n">
-        <v>237.712</v>
+        <v>164.202</v>
       </c>
       <c r="E237" s="1" t="n">
         <v>0.05309577834186136</v>
@@ -31780,7 +31780,7 @@
         <v>0.002379791495268283</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>237.709</v>
+        <v>164.199</v>
       </c>
       <c r="E238" s="1" t="n">
         <v>0.05294332253446389</v>
@@ -31797,7 +31797,7 @@
         <v>0.002383016125132892</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>237.706</v>
+        <v>164.196</v>
       </c>
       <c r="E239" s="1" t="n">
         <v>0.05278819477339353</v>
@@ -31814,7 +31814,7 @@
         <v>0.00238611788289149</v>
       </c>
       <c r="D240" s="1" t="n">
-        <v>237.703</v>
+        <v>164.193</v>
       </c>
       <c r="E240" s="1" t="n">
         <v>0.05263168445690758</v>
@@ -31831,7 +31831,7 @@
         <v>0.002389188371240681</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>237.7</v>
+        <v>164.19</v>
       </c>
       <c r="E241" s="1" t="n">
         <v>0.05247582108219135</v>
@@ -31848,7 +31848,7 @@
         <v>0.002392319192877076</v>
       </c>
       <c r="D242" s="1" t="n">
-        <v>237.697</v>
+        <v>164.187</v>
       </c>
       <c r="E242" s="1" t="n">
         <v>0.05232259984930951</v>
@@ -31865,7 +31865,7 @@
         <v>0.002395573604809415</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>237.694</v>
+        <v>164.184</v>
       </c>
       <c r="E243" s="1" t="n">
         <v>0.0521733650420622</v>
@@ -31882,7 +31882,7 @@
         <v>0.002398901481294975</v>
       </c>
       <c r="D244" s="1" t="n">
-        <v>237.691</v>
+        <v>164.181</v>
       </c>
       <c r="E244" s="1" t="n">
         <v>0.05202697939410761</v>
@@ -31899,7 +31899,7 @@
         <v>0.002402224350903167</v>
       </c>
       <c r="D245" s="1" t="n">
-        <v>237.688</v>
+        <v>164.178</v>
       </c>
       <c r="E245" s="1" t="n">
         <v>0.05188171242607691</v>
@@ -31916,7 +31916,7 @@
         <v>0.002405463742203402</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>237.685</v>
+        <v>164.175</v>
       </c>
       <c r="E246" s="1" t="n">
         <v>0.05173586241471949</v>
@@ -31933,7 +31933,7 @@
         <v>0.002408559240228179</v>
       </c>
       <c r="D247" s="1" t="n">
-        <v>237.682</v>
+        <v>164.172</v>
       </c>
       <c r="E247" s="1" t="n">
         <v>0.05158814254177434</v>
@@ -31950,7 +31950,7 @@
         <v>0.002411522655862361</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>237.679</v>
+        <v>164.169</v>
       </c>
       <c r="E248" s="1" t="n">
         <v>0.05143882780250349</v>
@@ -31967,7 +31967,7 @@
         <v>0.002414383856453898</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>237.676</v>
+        <v>164.166</v>
       </c>
       <c r="E249" s="1" t="n">
         <v>0.05128857225022866</v>
@@ -31984,7 +31984,7 @@
         <v>0.002417172709350743</v>
       </c>
       <c r="D250" s="1" t="n">
-        <v>237.674</v>
+        <v>164.164</v>
       </c>
       <c r="E250" s="1" t="n">
         <v>0.05113780408764111</v>
@@ -32001,7 +32001,7 @@
         <v>0.00241992900101967</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>237.671</v>
+        <v>164.161</v>
       </c>
       <c r="E251" s="1" t="n">
         <v>0.05098779615105785</v>
@@ -32018,7 +32018,7 @@
         <v>0.002422732194402755</v>
       </c>
       <c r="D252" s="1" t="n">
-        <v>237.668</v>
+        <v>164.158</v>
       </c>
       <c r="E252" s="1" t="n">
         <v>0.05083999347982419</v>
@@ -32035,7 +32035,7 @@
         <v>0.002425671671560896</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>237.665</v>
+        <v>164.155</v>
       </c>
       <c r="E253" s="1" t="n">
         <v>0.05069623740051465</v>
@@ -32052,7 +32052,7 @@
         <v>0.002428836814554991</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>237.663</v>
+        <v>164.153</v>
       </c>
       <c r="E254" s="1" t="n">
         <v>0.05055812690361336</v>
@@ -32069,7 +32069,7 @@
         <v>0.002432276270978178</v>
       </c>
       <c r="D255" s="1" t="n">
-        <v>237.66</v>
+        <v>164.15</v>
       </c>
       <c r="E255" s="1" t="n">
         <v>0.05042702618328389</v>
@@ -32086,7 +32086,7 @@
         <v>0.002435875750552536</v>
       </c>
       <c r="D256" s="1" t="n">
-        <v>237.658</v>
+        <v>164.148</v>
       </c>
       <c r="E256" s="1" t="n">
         <v>0.05030006886962563</v>
@@ -32103,7 +32103,7 @@
         <v>0.002439480228532388</v>
       </c>
       <c r="D257" s="1" t="n">
-        <v>237.655</v>
+        <v>164.145</v>
       </c>
       <c r="E257" s="1" t="n">
         <v>0.05017443834842027</v>
@@ -32120,7 +32120,7 @@
         <v>0.002442934680172049</v>
       </c>
       <c r="D258" s="1" t="n">
-        <v>237.653</v>
+        <v>164.143</v>
       </c>
       <c r="E258" s="1" t="n">
         <v>0.05004652270049628</v>
@@ -32137,7 +32137,7 @@
         <v>0.002446124769378371</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>237.65</v>
+        <v>164.14</v>
       </c>
       <c r="E259" s="1" t="n">
         <v>0.04991443504061856</v>
@@ -32154,7 +32154,7 @@
         <v>0.002449098914668323</v>
       </c>
       <c r="D260" s="1" t="n">
-        <v>237.648</v>
+        <v>164.138</v>
       </c>
       <c r="E260" s="1" t="n">
         <v>0.0497787904746884</v>
@@ -32171,7 +32171,7 @@
         <v>0.002451946223211407</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>237.645</v>
+        <v>164.135</v>
       </c>
       <c r="E261" s="1" t="n">
         <v>0.04964185178516733</v>
@@ -32188,7 +32188,7 @@
         <v>0.002454755802177124</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>237.643</v>
+        <v>164.133</v>
       </c>
       <c r="E262" s="1" t="n">
         <v>0.04950501518215963</v>
@@ -32205,7 +32205,7 @@
         <v>0.002457612676435201</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>237.64</v>
+        <v>164.13</v>
       </c>
       <c r="E263" s="1" t="n">
         <v>0.04937040226445663</v>
@@ -32222,7 +32222,7 @@
         <v>0.002460585541656275</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>237.638</v>
+        <v>164.128</v>
       </c>
       <c r="E264" s="1" t="n">
         <v>0.04923894822745042</v>
@@ -32239,7 +32239,7 @@
         <v>0.002463739011211209</v>
       </c>
       <c r="D265" s="1" t="n">
-        <v>237.635</v>
+        <v>164.125</v>
       </c>
       <c r="E265" s="1" t="n">
         <v>0.04911231711650424</v>
@@ -32256,7 +32256,7 @@
         <v>0.002467137698470864</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>237.633</v>
+        <v>164.123</v>
       </c>
       <c r="E266" s="1" t="n">
         <v>0.04899132496780554</v>
@@ -32273,7 +32273,7 @@
         <v>0.002470802580736493</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>237.63</v>
+        <v>164.12</v>
       </c>
       <c r="E267" s="1" t="n">
         <v>0.04887673255766622</v>
@@ -32290,7 +32290,7 @@
         <v>0.002474580091030905</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>237.628</v>
+        <v>164.118</v>
       </c>
       <c r="E268" s="1" t="n">
         <v>0.04876503102186772</v>
@@ -32307,7 +32307,7 @@
         <v>0.002478273026307293</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>237.625</v>
+        <v>164.115</v>
       </c>
       <c r="E269" s="1" t="n">
         <v>0.0486527245827438</v>
@@ -32324,7 +32324,7 @@
         <v>0.002481684183518854</v>
       </c>
       <c r="D270" s="1" t="n">
-        <v>237.623</v>
+        <v>164.113</v>
       </c>
       <c r="E270" s="1" t="n">
         <v>0.04853555563411324</v>
@@ -32341,7 +32341,7 @@
         <v>0.002484690366743772</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>237.62</v>
+        <v>164.11</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0.04841158537941274</v>
@@ -32358,7 +32358,7 @@
         <v>0.002487464408560187</v>
       </c>
       <c r="D272" s="1" t="n">
-        <v>237.618</v>
+        <v>164.108</v>
       </c>
       <c r="E272" s="1" t="n">
         <v>0.04828383943556482</v>
@@ -32375,7 +32375,7 @@
         <v>0.002490253148671224</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>237.615</v>
+        <v>164.105</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>0.04815753821008842</v>
@@ -32392,7 +32392,7 @@
         <v>0.002493303426780009</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>237.613</v>
+        <v>164.103</v>
       </c>
       <c r="E274" s="1" t="n">
         <v>0.0480370176579896</v>
@@ -32409,7 +32409,7 @@
         <v>0.00249677967486558</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>237.611</v>
+        <v>164.101</v>
       </c>
       <c r="E275" s="1" t="n">
         <v>0.04792557063592997</v>
@@ -32426,7 +32426,7 @@
         <v>0.002500516694010608</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>237.608</v>
+        <v>164.098</v>
       </c>
       <c r="E276" s="1" t="n">
         <v>0.04782013852042883</v>
@@ -32443,7 +32443,7 @@
         <v>0.002504266877573674</v>
       </c>
       <c r="D277" s="1" t="n">
-        <v>237.606</v>
+        <v>164.096</v>
       </c>
       <c r="E277" s="1" t="n">
         <v>0.04771553632803509</v>
@@ -32460,7 +32460,7 @@
         <v>0.002507782618913359</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>237.604</v>
+        <v>164.094</v>
       </c>
       <c r="E278" s="1" t="n">
         <v>0.04760725386940356</v>
@@ -32477,7 +32477,7 @@
         <v>0.002510883024321127</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>237.601</v>
+        <v>164.091</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0.04749210985543035</v>
@@ -32494,7 +32494,7 @@
         <v>0.002513654051819962</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>237.599</v>
+        <v>164.089</v>
       </c>
       <c r="E280" s="1" t="n">
         <v>0.04737140106177624</v>
@@ -32511,7 +32511,7 @@
         <v>0.002516248372365732</v>
       </c>
       <c r="D281" s="1" t="n">
-        <v>237.597</v>
+        <v>164.087</v>
       </c>
       <c r="E281" s="1" t="n">
         <v>0.0472482529602919</v>
@@ -32528,7 +32528,7 @@
         <v>0.002518818656914302</v>
       </c>
       <c r="D282" s="1" t="n">
-        <v>237.595</v>
+        <v>164.085</v>
       </c>
       <c r="E282" s="1" t="n">
         <v>0.04712554836144092</v>
@@ -32545,7 +32545,7 @@
         <v>0.002521486118649736</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>237.592</v>
+        <v>164.082</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0.04700573994816104</v>
@@ -32562,7 +32562,7 @@
         <v>0.002524246139668868</v>
       </c>
       <c r="D284" s="1" t="n">
-        <v>237.59</v>
+        <v>164.08</v>
       </c>
       <c r="E284" s="1" t="n">
         <v>0.04688831669380352</v>
@@ -32579,7 +32579,7 @@
         <v>0.002527062644296725</v>
       </c>
       <c r="D285" s="1" t="n">
-        <v>237.588</v>
+        <v>164.078</v>
       </c>
       <c r="E285" s="1" t="n">
         <v>0.04677278149109811</v>
@@ -32596,7 +32596,7 @@
         <v>0.002529899556858338</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>237.585</v>
+        <v>164.075</v>
       </c>
       <c r="E286" s="1" t="n">
         <v>0.04665864518688558</v>
@@ -32613,7 +32613,7 @@
         <v>0.002532725244339933</v>
       </c>
       <c r="D287" s="1" t="n">
-        <v>237.583</v>
+        <v>164.073</v>
       </c>
       <c r="E287" s="1" t="n">
         <v>0.04654492037245717</v>
@@ -32630,7 +32630,7 @@
         <v>0.00253552584437254</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>237.581</v>
+        <v>164.071</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0.04643154358355026</v>
@@ -32647,7 +32647,7 @@
         <v>0.002538291937248384</v>
       </c>
       <c r="D289" s="1" t="n">
-        <v>237.578</v>
+        <v>164.068</v>
       </c>
       <c r="E289" s="1" t="n">
         <v>0.04631853419056781</v>
@@ -32664,7 +32664,7 @@
         <v>0.002541014103259693</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>237.576</v>
+        <v>164.066</v>
       </c>
       <c r="E290" s="1" t="n">
         <v>0.04620532867471523</v>
@@ -32681,7 +32681,7 @@
         <v>0.002543692228776573</v>
       </c>
       <c r="D291" s="1" t="n">
-        <v>237.574</v>
+        <v>164.064</v>
       </c>
       <c r="E291" s="1" t="n">
         <v>0.04609212039956135</v>
@@ -32698,7 +32698,7 @@
         <v>0.002546363424480635</v>
       </c>
       <c r="D292" s="1" t="n">
-        <v>237.572</v>
+        <v>164.062</v>
       </c>
       <c r="E292" s="1" t="n">
         <v>0.04597957948003637</v>
@@ -32715,7 +32715,7 @@
         <v>0.002549074107131369</v>
       </c>
       <c r="D293" s="1" t="n">
-        <v>237.569</v>
+        <v>164.059</v>
       </c>
       <c r="E293" s="1" t="n">
         <v>0.04586872724392396</v>
@@ -32732,7 +32732,7 @@
         <v>0.002551870693488263</v>
       </c>
       <c r="D294" s="1" t="n">
-        <v>237.567</v>
+        <v>164.057</v>
       </c>
       <c r="E294" s="1" t="n">
         <v>0.04575999386372017</v>
@@ -32749,7 +32749,7 @@
         <v>0.002554784044390916</v>
       </c>
       <c r="D295" s="1" t="n">
-        <v>237.565</v>
+        <v>164.055</v>
       </c>
       <c r="E295" s="1" t="n">
         <v>0.04565410039900038</v>
@@ -32766,7 +32766,7 @@
         <v>0.002557782796999358</v>
       </c>
       <c r="D296" s="1" t="n">
-        <v>237.563</v>
+        <v>164.053</v>
       </c>
       <c r="E296" s="1" t="n">
         <v>0.04555045899647557</v>
@@ -32783,7 +32783,7 @@
         <v>0.002560820032553728</v>
       </c>
       <c r="D297" s="1" t="n">
-        <v>237.561</v>
+        <v>164.051</v>
       </c>
       <c r="E297" s="1" t="n">
         <v>0.04544821378551758</v>
@@ -32800,7 +32800,7 @@
         <v>0.002563848832294164</v>
       </c>
       <c r="D298" s="1" t="n">
-        <v>237.558</v>
+        <v>164.048</v>
       </c>
       <c r="E298" s="1" t="n">
         <v>0.04534671147791106</v>
@@ -32817,7 +32817,7 @@
         <v>0.002566835940862289</v>
       </c>
       <c r="D299" s="1" t="n">
-        <v>237.556</v>
+        <v>164.046</v>
       </c>
       <c r="E299" s="1" t="n">
         <v>0.04524497803756976</v>
@@ -32834,7 +32834,7 @@
         <v>0.002569802756505658</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>237.554</v>
+        <v>164.044</v>
       </c>
       <c r="E300" s="1" t="n">
         <v>0.04514358106673132</v>
@@ -32851,7 +32851,7 @@
         <v>0.002572784340873312</v>
       </c>
       <c r="D301" s="1" t="n">
-        <v>237.552</v>
+        <v>164.042</v>
       </c>
       <c r="E301" s="1" t="n">
         <v>0.04504313097802874</v>
@@ -32868,7 +32868,7 @@
         <v>0.002575815755614292</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>237.55</v>
+        <v>164.04</v>
       </c>
       <c r="E302" s="1" t="n">
         <v>0.04494422995587797</v>
@@ -32885,7 +32885,7 @@
         <v>0.002578910488888114</v>
       </c>
       <c r="D303" s="1" t="n">
-        <v>237.548</v>
+        <v>164.038</v>
       </c>
       <c r="E303" s="1" t="n">
         <v>0.0448470969333271</v>
@@ -32902,7 +32902,7 @@
         <v>0.002581995734896212</v>
       </c>
       <c r="D304" s="1" t="n">
-        <v>237.546</v>
+        <v>164.036</v>
       </c>
       <c r="E304" s="1" t="n">
         <v>0.04475045228903878</v>
@@ -32919,7 +32919,7 @@
         <v>0.002584977114350495</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>237.544</v>
+        <v>164.034</v>
       </c>
       <c r="E305" s="1" t="n">
         <v>0.04465266081949579</v>
@@ -32936,7 +32936,7 @@
         <v>0.002587760247962873</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>237.542</v>
+        <v>164.032</v>
       </c>
       <c r="E306" s="1" t="n">
         <v>0.04455210906917189</v>
@@ -32953,7 +32953,7 @@
         <v>0.002590286936673096</v>
       </c>
       <c r="D307" s="1" t="n">
-        <v>237.54</v>
+        <v>164.03</v>
       </c>
       <c r="E307" s="1" t="n">
         <v>0.04444782580105264</v>
@@ -32970,7 +32970,7 @@
         <v>0.002592643702332273</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>237.539</v>
+        <v>164.029</v>
       </c>
       <c r="E308" s="1" t="n">
         <v>0.04434114106403567</v>
@@ -32987,7 +32987,7 @@
         <v>0.002594953247019354</v>
       </c>
       <c r="D309" s="1" t="n">
-        <v>237.537</v>
+        <v>164.027</v>
       </c>
       <c r="E309" s="1" t="n">
         <v>0.04423454213449209</v>
@@ -33004,7 +33004,7 @@
         <v>0.002597338272813285</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>237.535</v>
+        <v>164.025</v>
       </c>
       <c r="E310" s="1" t="n">
         <v>0.04412992763816211</v>
@@ -33021,7 +33021,7 @@
         <v>0.002599892614548459</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>237.533</v>
+        <v>164.023</v>
       </c>
       <c r="E311" s="1" t="n">
         <v>0.04402886716991383</v>
@@ -33038,7 +33038,7 @@
         <v>0.00260259463808105</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>237.531</v>
+        <v>164.021</v>
       </c>
       <c r="E312" s="1" t="n">
         <v>0.04393096078115136</v>
@@ -33055,7 +33055,7 @@
         <v>0.002605393842022673</v>
       </c>
       <c r="D313" s="1" t="n">
-        <v>237.529</v>
+        <v>164.019</v>
       </c>
       <c r="E313" s="1" t="n">
         <v>0.0438353280353798</v>
@@ -33072,7 +33072,7 @@
         <v>0.002608239724984948</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>237.527</v>
+        <v>164.017</v>
       </c>
       <c r="E314" s="1" t="n">
         <v>0.04374109990182199</v>
@@ -33089,7 +33089,7 @@
         <v>0.002611090627059857</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>237.525</v>
+        <v>164.015</v>
       </c>
       <c r="E315" s="1" t="n">
         <v>0.04364756636699312</v>
@@ -33106,7 +33106,7 @@
         <v>0.002613940254260855</v>
       </c>
       <c r="D316" s="1" t="n">
-        <v>237.523</v>
+        <v>164.013</v>
       </c>
       <c r="E316" s="1" t="n">
         <v>0.04355461583794608</v>
@@ -33123,7 +33123,7 @@
         <v>0.002616791154081766</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>237.522</v>
+        <v>164.012</v>
       </c>
       <c r="E317" s="1" t="n">
         <v>0.04346210201949714</v>
@@ -33140,7 +33140,7 @@
         <v>0.002619645874016409</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>237.52</v>
+        <v>164.01</v>
       </c>
       <c r="E318" s="1" t="n">
         <v>0.04337042747839819</v>
@@ -33157,7 +33157,7 @@
         <v>0.002622512905061223</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>237.518</v>
+        <v>164.008</v>
       </c>
       <c r="E319" s="1" t="n">
         <v>0.04327954268787869</v>
@@ -33174,7 +33174,7 @@
         <v>0.002625424512223105</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>237.515</v>
+        <v>164.005</v>
       </c>
       <c r="E320" s="1" t="n">
         <v>0.0431901527294298</v>
@@ -33191,7 +33191,7 @@
         <v>0.002628418904011567</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>237.513</v>
+        <v>164.003</v>
       </c>
       <c r="E321" s="1" t="n">
         <v>0.04310250763246569</v>
@@ -33208,7 +33208,7 @@
         <v>0.002631534288936124</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>237.511</v>
+        <v>164.001</v>
       </c>
       <c r="E322" s="1" t="n">
         <v>0.04301739594297883</v>
@@ -33225,7 +33225,7 @@
         <v>0.002634784846871753</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>237.51</v>
+        <v>164</v>
       </c>
       <c r="E323" s="1" t="n">
         <v>0.04293484403144383</v>
@@ -33242,7 +33242,7 @@
         <v>0.002638088643155306</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>237.508</v>
+        <v>163.998</v>
       </c>
       <c r="E324" s="1" t="n">
         <v>0.04285385700604676</v>
@@ -33259,7 +33259,7 @@
         <v>0.002641339714489095</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>237.506</v>
+        <v>163.996</v>
       </c>
       <c r="E325" s="1" t="n">
         <v>0.04277252484209025</v>
@@ -33276,7 +33276,7 @@
         <v>0.002644432097575436</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>237.505</v>
+        <v>163.995</v>
       </c>
       <c r="E326" s="1" t="n">
         <v>0.04268896044537206</v>
@@ -33293,7 +33293,7 @@
         <v>0.00264729707707867</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>237.503</v>
+        <v>163.993</v>
       </c>
       <c r="E327" s="1" t="n">
         <v>0.04260243694910931</v>
@@ -33310,7 +33310,7 @@
         <v>0.002650014929511228</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>237.501</v>
+        <v>163.991</v>
       </c>
       <c r="E328" s="1" t="n">
         <v>0.04251409129184186</v>
@@ -33327,7 +33327,7 @@
         <v>0.00265270317934757</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>237.5</v>
+        <v>163.99</v>
       </c>
       <c r="E329" s="1" t="n">
         <v>0.04242564132254642</v>
@@ -33344,7 +33344,7 @@
         <v>0.002655479351062153</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>237.498</v>
+        <v>163.988</v>
       </c>
       <c r="E330" s="1" t="n">
         <v>0.0423393178069956</v>
@@ -33361,7 +33361,7 @@
         <v>0.002658428708915467</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>237.497</v>
+        <v>163.987</v>
       </c>
       <c r="E331" s="1" t="n">
         <v>0.04225610116866424</v>
@@ -33378,7 +33378,7 @@
         <v>0.002661507476312136</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>237.495</v>
+        <v>163.985</v>
       </c>
       <c r="E332" s="1" t="n">
         <v>0.04217562372339787</v>
@@ -33395,7 +33395,7 @@
         <v>0.002664639616442814</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>237.494</v>
+        <v>163.984</v>
       </c>
       <c r="E333" s="1" t="n">
         <v>0.04209630525983715</v>
@@ -33412,7 +33412,7 @@
         <v>0.002667749092498159</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>237.492</v>
+        <v>163.982</v>
       </c>
       <c r="E334" s="1" t="n">
         <v>0.04201729082274133</v>
@@ -33429,7 +33429,7 @@
         <v>0.00267078366668017</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>237.49</v>
+        <v>163.98</v>
       </c>
       <c r="E335" s="1" t="n">
         <v>0.04193758140939358</v>
@@ -33446,7 +33446,7 @@
         <v>0.002673786297236219</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>237.489</v>
+        <v>163.979</v>
       </c>
       <c r="E336" s="1" t="n">
         <v>0.04185767956343576</v>
@@ -33463,7 +33463,7 @@
         <v>0.002676823741425023</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>237.487</v>
+        <v>163.977</v>
       </c>
       <c r="E337" s="1" t="n">
         <v>0.04177898018199667</v>
@@ -33480,7 +33480,7 @@
         <v>0.0026799627565053</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>237.485</v>
+        <v>163.975</v>
       </c>
       <c r="E338" s="1" t="n">
         <v>0.0417023362184622</v>
@@ -33497,7 +33497,7 @@
         <v>0.00268323748076434</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>237.484</v>
+        <v>163.974</v>
       </c>
       <c r="E339" s="1" t="n">
         <v>0.04162808353460793</v>
@@ -33514,7 +33514,7 @@
         <v>0.002686551576603729</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>237.482</v>
+        <v>163.972</v>
       </c>
       <c r="E340" s="1" t="n">
         <v>0.04155505987626922</v>
@@ -33531,7 +33531,7 @@
         <v>0.002689776087453629</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>237.48</v>
+        <v>163.97</v>
       </c>
       <c r="E341" s="1" t="n">
         <v>0.04148109148824371</v>
@@ -33548,7 +33548,7 @@
         <v>0.0026927820567442</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>237.478</v>
+        <v>163.968</v>
       </c>
       <c r="E342" s="1" t="n">
         <v>0.04140420393524109</v>
@@ -33565,7 +33565,7 @@
         <v>0.002695485344366245</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>237.476</v>
+        <v>163.966</v>
       </c>
       <c r="E343" s="1" t="n">
         <v>0.04132313320947383</v>
@@ -33582,7 +33582,7 @@
         <v>0.002697981076053135</v>
       </c>
       <c r="D344" s="1" t="n">
-        <v>237.474</v>
+        <v>163.964</v>
       </c>
       <c r="E344" s="1" t="n">
         <v>0.0412393703453792</v>
@@ -33599,7 +33599,7 @@
         <v>0.002700409193998884</v>
       </c>
       <c r="D345" s="1" t="n">
-        <v>237.472</v>
+        <v>163.962</v>
       </c>
       <c r="E345" s="1" t="n">
         <v>0.04115507184963291</v>
@@ -33616,7 +33616,7 @@
         <v>0.002702909640397504</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>237.47</v>
+        <v>163.96</v>
       </c>
       <c r="E346" s="1" t="n">
         <v>0.0410723689298793</v>
@@ -33633,7 +33633,7 @@
         <v>0.002705596627527859</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>237.468</v>
+        <v>163.958</v>
       </c>
       <c r="E347" s="1" t="n">
         <v>0.0409929780271454</v>
@@ -33650,7 +33650,7 @@
         <v>0.002708481448008219</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>237.467</v>
+        <v>163.957</v>
       </c>
       <c r="E348" s="1" t="n">
         <v>0.04091686845128338</v>
@@ -33667,7 +33667,7 @@
         <v>0.002711549664541707</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>237.465</v>
+        <v>163.955</v>
       </c>
       <c r="E349" s="1" t="n">
         <v>0.04084413751790485</v>
@@ -33684,7 +33684,7 @@
         <v>0.002714786839831445</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>237.463</v>
+        <v>163.953</v>
       </c>
       <c r="E350" s="1" t="n">
         <v>0.04077436787362581</v>
@@ -33701,7 +33701,7 @@
         <v>0.002718161811461362</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>237.462</v>
+        <v>163.952</v>
       </c>
       <c r="E351" s="1" t="n">
         <v>0.04070689571953433</v>
@@ -33718,7 +33718,7 @@
         <v>0.002721576516538622</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>237.461</v>
+        <v>163.951</v>
       </c>
       <c r="E352" s="1" t="n">
         <v>0.04064040733030442</v>
@@ -33735,7 +33735,7 @@
         <v>0.002724916167051194</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>237.459</v>
+        <v>163.949</v>
       </c>
       <c r="E353" s="1" t="n">
         <v>0.04057335591310763</v>
@@ -33752,7 +33752,7 @@
         <v>0.002728065974987051</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>237.458</v>
+        <v>163.948</v>
       </c>
       <c r="E354" s="1" t="n">
         <v>0.04050370150509663</v>
@@ -33769,7 +33769,7 @@
         <v>0.002730949457716863</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>237.456</v>
+        <v>163.946</v>
       </c>
       <c r="E355" s="1" t="n">
         <v>0.04043067409481046</v>
@@ -33786,7 +33786,7 @@
         <v>0.002733643354142108</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>237.455</v>
+        <v>163.945</v>
       </c>
       <c r="E356" s="1" t="n">
         <v>0.04035509599984082</v>
@@ -33803,7 +33803,7 @@
         <v>0.002736262708546968</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>237.454</v>
+        <v>163.944</v>
       </c>
       <c r="E357" s="1" t="n">
         <v>0.04027885159717454</v>
@@ -33820,7 +33820,7 @@
         <v>0.00273892256521562</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>237.453</v>
+        <v>163.943</v>
       </c>
       <c r="E358" s="1" t="n">
         <v>0.04020363524441288</v>
@@ -33837,7 +33837,7 @@
         <v>0.00274171713171767</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>237.451</v>
+        <v>163.941</v>
       </c>
       <c r="E359" s="1" t="n">
         <v>0.04013098614543645</v>
@@ -33854,7 +33854,7 @@
         <v>0.00274465726876441</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>237.45</v>
+        <v>163.94</v>
       </c>
       <c r="E360" s="1" t="n">
         <v>0.0400607042132638</v>
@@ -33871,7 +33871,7 @@
         <v>0.002747733000352561</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>237.449</v>
+        <v>163.939</v>
       </c>
       <c r="E361" s="1" t="n">
         <v>0.03999279215326177</v>
@@ -33888,7 +33888,7 @@
         <v>0.002750934350478841</v>
       </c>
       <c r="D362" s="1" t="n">
-        <v>237.448</v>
+        <v>163.938</v>
       </c>
       <c r="E362" s="1" t="n">
         <v>0.03992708522766771</v>
@@ -33905,7 +33905,7 @@
         <v>0.002754245213961733</v>
       </c>
       <c r="D363" s="1" t="n">
-        <v>237.446</v>
+        <v>163.936</v>
       </c>
       <c r="E363" s="1" t="n">
         <v>0.03986349971573203</v>
@@ -33922,7 +33922,7 @@
         <v>0.002757624968906782</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>237.445</v>
+        <v>163.935</v>
       </c>
       <c r="E364" s="1" t="n">
         <v>0.03980109693971774</v>
@@ -33939,7 +33939,7 @@
         <v>0.002761026864241299</v>
       </c>
       <c r="D365" s="1" t="n">
-        <v>237.444</v>
+        <v>163.934</v>
       </c>
       <c r="E365" s="1" t="n">
         <v>0.03973936088845491</v>
@@ -33956,7 +33956,7 @@
         <v>0.002764404148892593</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>237.443</v>
+        <v>163.933</v>
       </c>
       <c r="E366" s="1" t="n">
         <v>0.03967761498971051</v>
@@ -33973,7 +33973,7 @@
         <v>0.002767715294805458</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>237.442</v>
+        <v>163.932</v>
       </c>
       <c r="E367" s="1" t="n">
         <v>0.03961526491547717</v>
@@ -33990,7 +33990,7 @@
         <v>0.002770939665994619</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>237.441</v>
+        <v>163.931</v>
       </c>
       <c r="E368" s="1" t="n">
         <v>0.03955202110552562</v>
@@ -34007,7 +34007,7 @@
         <v>0.002774061849492286</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>237.44</v>
+        <v>163.93</v>
       </c>
       <c r="E369" s="1" t="n">
         <v>0.03948767153300912</v>
@@ -34024,7 +34024,7 @@
         <v>0.002777066432330666</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>237.439</v>
+        <v>163.929</v>
       </c>
       <c r="E370" s="1" t="n">
         <v>0.03942200649736012</v>
@@ -34041,7 +34041,7 @@
         <v>0.002779946545831645</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>237.438</v>
+        <v>163.928</v>
       </c>
       <c r="E371" s="1" t="n">
         <v>0.03935493955158495</v>
@@ -34058,7 +34058,7 @@
         <v>0.002782729498475804</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>237.437</v>
+        <v>163.927</v>
       </c>
       <c r="E372" s="1" t="n">
         <v>0.03928686770855263</v>
@@ -34075,7 +34075,7 @@
         <v>0.002785451143033405</v>
       </c>
       <c r="D373" s="1" t="n">
-        <v>237.436</v>
+        <v>163.926</v>
       </c>
       <c r="E373" s="1" t="n">
         <v>0.03921830396149059</v>
@@ -34092,7 +34092,7 @@
         <v>0.002788147332274702</v>
       </c>
       <c r="D374" s="1" t="n">
-        <v>237.435</v>
+        <v>163.925</v>
       </c>
       <c r="E374" s="1" t="n">
         <v>0.03914975573609351</v>
@@ -34109,7 +34109,7 @@
         <v>0.00279084606234751</v>
       </c>
       <c r="D375" s="1" t="n">
-        <v>237.434</v>
+        <v>163.924</v>
       </c>
       <c r="E375" s="1" t="n">
         <v>0.03908161494574626</v>
@@ -34126,7 +34126,7 @@
         <v>0.002793543902909862</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>237.432</v>
+        <v>163.922</v>
       </c>
       <c r="E376" s="1" t="n">
         <v>0.03901399469601056</v>
@@ -34143,7 +34143,7 @@
         <v>0.002796229566997343</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>237.431</v>
+        <v>163.921</v>
       </c>
       <c r="E377" s="1" t="n">
         <v>0.03894640598434541</v>
@@ -34160,7 +34160,7 @@
         <v>0.002798891767645538</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>237.43</v>
+        <v>163.92</v>
       </c>
       <c r="E378" s="1" t="n">
         <v>0.03887885504245432</v>
@@ -34177,7 +34177,7 @@
         <v>0.002801524926377552</v>
       </c>
       <c r="D379" s="1" t="n">
-        <v>237.429</v>
+        <v>163.919</v>
       </c>
       <c r="E379" s="1" t="n">
         <v>0.0388112642803517</v>
@@ -34194,7 +34194,7 @@
         <v>0.002804146298666551</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>237.428</v>
+        <v>163.918</v>
       </c>
       <c r="E380" s="1" t="n">
         <v>0.0387438724249995</v>
@@ -34211,7 +34211,7 @@
         <v>0.002806778848473216</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>237.427</v>
+        <v>163.917</v>
       </c>
       <c r="E381" s="1" t="n">
         <v>0.03867699432305197</v>
@@ -34228,7 +34228,7 @@
         <v>0.002809445539758229</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>237.426</v>
+        <v>163.916</v>
       </c>
       <c r="E382" s="1" t="n">
         <v>0.03861094147704788</v>
@@ -34245,7 +34245,7 @@
         <v>0.002812168378511871</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>237.425</v>
+        <v>163.915</v>
       </c>
       <c r="E383" s="1" t="n">
         <v>0.03854600895899237</v>
@@ -34262,7 +34262,7 @@
         <v>0.002814965538842815</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>237.424</v>
+        <v>163.914</v>
       </c>
       <c r="E384" s="1" t="n">
         <v>0.03848243633915395</v>
@@ -34279,7 +34279,7 @@
         <v>0.00281785423688933</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>237.423</v>
+        <v>163.913</v>
       </c>
       <c r="E385" s="1" t="n">
         <v>0.03842044760194174</v>
@@ -34296,7 +34296,7 @@
         <v>0.00282085168878969</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>237.422</v>
+        <v>163.912</v>
       </c>
       <c r="E386" s="1" t="n">
         <v>0.03836026437797884</v>
@@ -34313,7 +34313,7 @@
         <v>0.002823960266170831</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>237.422</v>
+        <v>163.912</v>
       </c>
       <c r="E387" s="1" t="n">
         <v>0.03830174331193087</v>
@@ -34330,7 +34330,7 @@
         <v>0.002827122962614354</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>237.421</v>
+        <v>163.911</v>
       </c>
       <c r="E388" s="1" t="n">
         <v>0.03824442182335558</v>
@@ -34347,7 +34347,7 @@
         <v>0.002830267927190527</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>237.42</v>
+        <v>163.91</v>
       </c>
       <c r="E389" s="1" t="n">
         <v>0.03818716077873646</v>
@@ -34364,7 +34364,7 @@
         <v>0.002833323308969617</v>
       </c>
       <c r="D390" s="1" t="n">
-        <v>237.419</v>
+        <v>163.909</v>
       </c>
       <c r="E390" s="1" t="n">
         <v>0.03812899278051249</v>
@@ -34381,7 +34381,7 @@
         <v>0.002836239390289215</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>237.418</v>
+        <v>163.908</v>
       </c>
       <c r="E391" s="1" t="n">
         <v>0.0380692575482459</v>
@@ -34398,7 +34398,7 @@
         <v>0.002839054986556198</v>
       </c>
       <c r="D392" s="1" t="n">
-        <v>237.418</v>
+        <v>163.908</v>
       </c>
       <c r="E392" s="1" t="n">
         <v>0.03800832679792949</v>
@@ -34415,7 +34415,7 @@
         <v>0.002841831046444766</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>237.417</v>
+        <v>163.907</v>
       </c>
       <c r="E393" s="1" t="n">
         <v>0.037947342836457</v>
@@ -34432,7 +34432,7 @@
         <v>0.00284462851862912</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>237.416</v>
+        <v>163.906</v>
       </c>
       <c r="E394" s="1" t="n">
         <v>0.03788695872359545</v>
@@ -34449,7 +34449,7 @@
         <v>0.002847490565412407</v>
       </c>
       <c r="D395" s="1" t="n">
-        <v>237.415</v>
+        <v>163.905</v>
       </c>
       <c r="E395" s="1" t="n">
         <v>0.03782774323033996</v>
@@ -34466,7 +34466,7 @@
         <v>0.002850389203613561</v>
       </c>
       <c r="D396" s="1" t="n">
-        <v>237.414</v>
+        <v>163.904</v>
       </c>
       <c r="E396" s="1" t="n">
         <v>0.03776931658468268</v>
@@ -34483,7 +34483,7 @@
         <v>0.002853278663680464</v>
       </c>
       <c r="D397" s="1" t="n">
-        <v>237.414</v>
+        <v>163.904</v>
       </c>
       <c r="E397" s="1" t="n">
         <v>0.03771090897455863</v>
@@ -34500,7 +34500,7 @@
         <v>0.002856113176060995</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>237.413</v>
+        <v>163.903</v>
       </c>
       <c r="E398" s="1" t="n">
         <v>0.03765223358149444</v>
@@ -34517,7 +34517,7 @@
         <v>0.002858863213172433</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>237.412</v>
+        <v>163.902</v>
       </c>
       <c r="E399" s="1" t="n">
         <v>0.03759274629503093</v>
@@ -34534,7 +34534,7 @@
         <v>0.002861564215309643</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>237.411</v>
+        <v>163.901</v>
       </c>
       <c r="E400" s="1" t="n">
         <v>0.03753291812595761</v>
@@ -34551,7 +34551,7 @@
         <v>0.002864267864736888</v>
       </c>
       <c r="D401" s="1" t="n">
-        <v>237.411</v>
+        <v>163.901</v>
       </c>
       <c r="E401" s="1" t="n">
         <v>0.03747326997602723</v>
@@ -34568,7 +34568,7 @@
         <v>0.002867025843718431</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>237.41</v>
+        <v>163.9</v>
       </c>
       <c r="E402" s="1" t="n">
         <v>0.03741478967403043</v>
@@ -34585,7 +34585,7 @@
         <v>0.002869880154792552</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>237.409</v>
+        <v>163.899</v>
       </c>
       <c r="E403" s="1" t="n">
         <v>0.03735785826282902</v>
@@ -34602,7 +34602,7 @@
         <v>0.002872834081593617</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>237.409</v>
+        <v>163.899</v>
       </c>
       <c r="E404" s="1" t="n">
         <v>0.03730234959635792</v>
@@ -34619,7 +34619,7 @@
         <v>0.002875881228030007</v>
       </c>
       <c r="D405" s="1" t="n">
-        <v>237.408</v>
+        <v>163.898</v>
       </c>
       <c r="E405" s="1" t="n">
         <v>0.03724848344254497</v>
@@ -34636,7 +34636,7 @@
         <v>0.002879015198010104</v>
       </c>
       <c r="D406" s="1" t="n">
-        <v>237.407</v>
+        <v>163.897</v>
       </c>
       <c r="E406" s="1" t="n">
         <v>0.03719600868648638</v>
@@ -34653,7 +34653,7 @@
         <v>0.00288222631180793</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>237.406</v>
+        <v>163.896</v>
       </c>
       <c r="E407" s="1" t="n">
         <v>0.03714479018506674</v>
@@ -34670,7 +34670,7 @@
         <v>0.002885491755160053</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>237.406</v>
+        <v>163.896</v>
       </c>
       <c r="E408" s="1" t="n">
         <v>0.03709436903702726</v>
@@ -34687,7 +34687,7 @@
         <v>0.00288878543016868</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>237.405</v>
+        <v>163.895</v>
       </c>
       <c r="E409" s="1" t="n">
         <v>0.03704471618832048</v>
@@ -34704,7 +34704,7 @@
         <v>0.002892081238936018</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>237.404</v>
+        <v>163.894</v>
       </c>
       <c r="E410" s="1" t="n">
         <v>0.03699533679696589</v>
@@ -34721,7 +34721,7 @@
         <v>0.002895362754680313</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>237.404</v>
+        <v>163.894</v>
       </c>
       <c r="E411" s="1" t="n">
         <v>0.03694586360012115</v>
@@ -34738,7 +34738,7 @@
         <v>0.002898652235083972</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>237.403</v>
+        <v>163.893</v>
       </c>
       <c r="E412" s="1" t="n">
         <v>0.03689689091333281</v>
@@ -34755,7 +34755,7 @@
         <v>0.002901981608945441</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>237.402</v>
+        <v>163.892</v>
       </c>
       <c r="E413" s="1" t="n">
         <v>0.03684866578930559</v>
@@ -34772,7 +34772,7 @@
         <v>0.002905382805063169</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>237.402</v>
+        <v>163.892</v>
       </c>
       <c r="E414" s="1" t="n">
         <v>0.03680143215186225</v>
@@ -34789,7 +34789,7 @@
         <v>0.002908868473666604</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>237.401</v>
+        <v>163.891</v>
       </c>
       <c r="E415" s="1" t="n">
         <v>0.03675565167657615</v>
@@ -34806,7 +34806,7 @@
         <v>0.0029123741507092</v>
       </c>
       <c r="D416" s="1" t="n">
-        <v>237.4</v>
+        <v>163.89</v>
       </c>
       <c r="E416" s="1" t="n">
         <v>0.03671034709761771</v>
@@ -34823,7 +34823,7 @@
         <v>0.002915816093575416</v>
       </c>
       <c r="D417" s="1" t="n">
-        <v>237.4</v>
+        <v>163.89</v>
       </c>
       <c r="E417" s="1" t="n">
         <v>0.03666430749467369</v>
@@ -34840,7 +34840,7 @@
         <v>0.002919110559649708</v>
       </c>
       <c r="D418" s="1" t="n">
-        <v>237.399</v>
+        <v>163.889</v>
       </c>
       <c r="E418" s="1" t="n">
         <v>0.03661679571142003</v>
@@ -34857,7 +34857,7 @@
         <v>0.002922203747695932</v>
       </c>
       <c r="D419" s="1" t="n">
-        <v>237.399</v>
+        <v>163.889</v>
       </c>
       <c r="E419" s="1" t="n">
         <v>0.03656684163370246</v>
@@ -34874,7 +34874,7 @@
         <v>0.002925161621995538</v>
       </c>
       <c r="D420" s="1" t="n">
-        <v>237.398</v>
+        <v>163.888</v>
       </c>
       <c r="E420" s="1" t="n">
         <v>0.03651559354387375</v>
@@ -34891,7 +34891,7 @@
         <v>0.002928080088209374</v>
       </c>
       <c r="D421" s="1" t="n">
-        <v>237.397</v>
+        <v>163.887</v>
       </c>
       <c r="E421" s="1" t="n">
         <v>0.03646410198581545</v>
@@ -34908,7 +34908,7 @@
         <v>0.002931055051998289</v>
       </c>
       <c r="D422" s="1" t="n">
-        <v>237.397</v>
+        <v>163.887</v>
       </c>
       <c r="E422" s="1" t="n">
         <v>0.03641340679316579</v>
@@ -34925,7 +34925,7 @@
         <v>0.002934151853618653</v>
       </c>
       <c r="D423" s="1" t="n">
-        <v>237.396</v>
+        <v>163.886</v>
       </c>
       <c r="E423" s="1" t="n">
         <v>0.03636461792293541</v>
@@ -34942,7 +34942,7 @@
         <v>0.002937313571708925</v>
       </c>
       <c r="D424" s="1" t="n">
-        <v>237.395</v>
+        <v>163.885</v>
       </c>
       <c r="E424" s="1" t="n">
         <v>0.03631686544161021</v>
@@ -34959,7 +34959,7 @@
         <v>0.002940452719503088</v>
       </c>
       <c r="D425" s="1" t="n">
-        <v>237.395</v>
+        <v>163.885</v>
       </c>
       <c r="E425" s="1" t="n">
         <v>0.03626891005251308</v>
@@ -34976,7 +34976,7 @@
         <v>0.002943481810235123</v>
       </c>
       <c r="D426" s="1" t="n">
-        <v>237.394</v>
+        <v>163.884</v>
       </c>
       <c r="E426" s="1" t="n">
         <v>0.03621998133224055</v>
@@ -34993,7 +34993,7 @@
         <v>0.002946349249464728</v>
       </c>
       <c r="D427" s="1" t="n">
-        <v>237.394</v>
+        <v>163.884</v>
       </c>
       <c r="E427" s="1" t="n">
         <v>0.03616914857788806</v>
@@ -35010,7 +35010,7 @@
         <v>0.002949147012054461</v>
       </c>
       <c r="D428" s="1" t="n">
-        <v>237.393</v>
+        <v>163.883</v>
       </c>
       <c r="E428" s="1" t="n">
         <v>0.03611785556215387</v>
@@ -35027,7 +35027,7 @@
         <v>0.002952002965192596</v>
       </c>
       <c r="D429" s="1" t="n">
-        <v>237.393</v>
+        <v>163.883</v>
       </c>
       <c r="E429" s="1" t="n">
         <v>0.03606736439519542</v>
@@ -35044,7 +35044,7 @@
         <v>0.002955044976067411</v>
       </c>
       <c r="D430" s="1" t="n">
-        <v>237.392</v>
+        <v>163.882</v>
       </c>
       <c r="E430" s="1" t="n">
         <v>0.0360195310025718</v>
@@ -35061,7 +35061,7 @@
         <v>0.002958353273221817</v>
       </c>
       <c r="D431" s="1" t="n">
-        <v>237.391</v>
+        <v>163.881</v>
       </c>
       <c r="E431" s="1" t="n">
         <v>0.03597516120506233</v>
@@ -35078,7 +35078,7 @@
         <v>0.00296181753061728</v>
       </c>
       <c r="D432" s="1" t="n">
-        <v>237.391</v>
+        <v>163.881</v>
       </c>
       <c r="E432" s="1" t="n">
         <v>0.0359327408060854</v>
@@ -35095,7 +35095,7 @@
         <v>0.002965279783569906</v>
       </c>
       <c r="D433" s="1" t="n">
-        <v>237.39</v>
+        <v>163.88</v>
       </c>
       <c r="E433" s="1" t="n">
         <v>0.03589064602446865</v>
@@ -35112,7 +35112,7 @@
         <v>0.002968582067395803</v>
       </c>
       <c r="D434" s="1" t="n">
-        <v>237.39</v>
+        <v>163.88</v>
       </c>
       <c r="E434" s="1" t="n">
         <v>0.03584666560580482</v>
@@ -35129,7 +35129,7 @@
         <v>0.002971618387875193</v>
       </c>
       <c r="D435" s="1" t="n">
-        <v>237.389</v>
+        <v>163.879</v>
       </c>
       <c r="E435" s="1" t="n">
         <v>0.03579983691597866</v>
@@ -35146,7 +35146,7 @@
         <v>0.002974490632644774</v>
       </c>
       <c r="D436" s="1" t="n">
-        <v>237.389</v>
+        <v>163.879</v>
       </c>
       <c r="E436" s="1" t="n">
         <v>0.03575110366784212</v>
@@ -35163,7 +35163,7 @@
         <v>0.002977352659805366</v>
       </c>
       <c r="D437" s="1" t="n">
-        <v>237.388</v>
+        <v>163.878</v>
       </c>
       <c r="E437" s="1" t="n">
         <v>0.03570262443428618</v>
@@ -35180,7 +35180,7 @@
         <v>0.002980358327457785</v>
       </c>
       <c r="D438" s="1" t="n">
-        <v>237.388</v>
+        <v>163.878</v>
       </c>
       <c r="E438" s="1" t="n">
         <v>0.03565593820020543</v>
@@ -35197,7 +35197,7 @@
         <v>0.002983609550026233</v>
       </c>
       <c r="D439" s="1" t="n">
-        <v>237.387</v>
+        <v>163.877</v>
       </c>
       <c r="E439" s="1" t="n">
         <v>0.03561254857160247</v>
@@ -35214,7 +35214,7 @@
         <v>0.002987000467228455</v>
       </c>
       <c r="D440" s="1" t="n">
-        <v>237.387</v>
+        <v>163.877</v>
       </c>
       <c r="E440" s="1" t="n">
         <v>0.0355708729475139</v>
@@ -35231,7 +35231,7 @@
         <v>0.002990373275105584</v>
       </c>
       <c r="D441" s="1" t="n">
-        <v>237.386</v>
+        <v>163.876</v>
       </c>
       <c r="E441" s="1" t="n">
         <v>0.0355293234436366</v>
@@ -35248,7 +35248,7 @@
         <v>0.002993570169698749</v>
       </c>
       <c r="D442" s="1" t="n">
-        <v>237.386</v>
+        <v>163.876</v>
       </c>
       <c r="E442" s="1" t="n">
         <v>0.03548573010406043</v>
@@ -35265,7 +35265,7 @@
         <v>0.002996483480386401</v>
       </c>
       <c r="D443" s="1" t="n">
-        <v>237.385</v>
+        <v>163.875</v>
       </c>
       <c r="E443" s="1" t="n">
         <v>0.03543913165902259</v>
@@ -35282,7 +35282,7 @@
         <v>0.002999206069896262</v>
       </c>
       <c r="D444" s="1" t="n">
-        <v>237.385</v>
+        <v>163.875</v>
       </c>
       <c r="E444" s="1" t="n">
         <v>0.03539034669709464</v>
@@ -35299,7 +35299,7 @@
         <v>0.003001880934293376</v>
       </c>
       <c r="D445" s="1" t="n">
-        <v>237.384</v>
+        <v>163.874</v>
       </c>
       <c r="E445" s="1" t="n">
         <v>0.03534137099898882</v>
@@ -35316,7 +35316,7 @@
         <v>0.003004651069642785</v>
       </c>
       <c r="D446" s="1" t="n">
-        <v>237.384</v>
+        <v>163.874</v>
       </c>
       <c r="E446" s="1" t="n">
         <v>0.03529358859350266</v>
@@ -35333,7 +35333,7 @@
         <v>0.003007629345905354</v>
       </c>
       <c r="D447" s="1" t="n">
-        <v>237.383</v>
+        <v>163.873</v>
       </c>
       <c r="E447" s="1" t="n">
         <v>0.03524861072149778</v>
@@ -35350,7 +35350,7 @@
         <v>0.003010808128625226</v>
       </c>
       <c r="D448" s="1" t="n">
-        <v>237.383</v>
+        <v>163.873</v>
       </c>
       <c r="E448" s="1" t="n">
         <v>0.03520603292972336</v>
@@ -35367,7 +35367,7 @@
         <v>0.003014149657242367</v>
       </c>
       <c r="D449" s="1" t="n">
-        <v>237.382</v>
+        <v>163.872</v>
       </c>
       <c r="E449" s="1" t="n">
         <v>0.03516569422913823</v>
@@ -35384,7 +35384,7 @@
         <v>0.003017616171196739</v>
       </c>
       <c r="D450" s="1" t="n">
-        <v>237.382</v>
+        <v>163.872</v>
       </c>
       <c r="E450" s="1" t="n">
         <v>0.0351268444964167</v>
@@ -35401,7 +35401,7 @@
         <v>0.003021164576478739</v>
       </c>
       <c r="D451" s="1" t="n">
-        <v>237.381</v>
+        <v>163.871</v>
       </c>
       <c r="E451" s="1" t="n">
         <v>0.03508926830849118</v>
@@ -35418,7 +35418,7 @@
         <v>0.003024730445280483</v>
       </c>
       <c r="D452" s="1" t="n">
-        <v>237.381</v>
+        <v>163.871</v>
       </c>
       <c r="E452" s="1" t="n">
         <v>0.03505191568557497</v>
@@ -35435,7 +35435,7 @@
         <v>0.003028244016344515</v>
       </c>
       <c r="D453" s="1" t="n">
-        <v>237.38</v>
+        <v>163.87</v>
       </c>
       <c r="E453" s="1" t="n">
         <v>0.03501427299738689</v>
@@ -35452,7 +35452,7 @@
         <v>0.003031635528413383</v>
       </c>
       <c r="D454" s="1" t="n">
-        <v>237.379</v>
+        <v>163.869</v>
       </c>
       <c r="E454" s="1" t="n">
         <v>0.03497539052874503</v>
@@ -35469,7 +35469,7 @@
         <v>0.003034853734642631</v>
       </c>
       <c r="D455" s="1" t="n">
-        <v>237.379</v>
+        <v>163.869</v>
       </c>
       <c r="E455" s="1" t="n">
         <v>0.03493453946649071</v>
@@ -35486,7 +35486,7 @@
         <v>0.003037921445839805</v>
       </c>
       <c r="D456" s="1" t="n">
-        <v>237.379</v>
+        <v>163.869</v>
       </c>
       <c r="E456" s="1" t="n">
         <v>0.03489214144913171</v>
@@ -35503,7 +35503,7 @@
         <v>0.003040879987225449</v>
       </c>
       <c r="D457" s="1" t="n">
-        <v>237.378</v>
+        <v>163.868</v>
       </c>
       <c r="E457" s="1" t="n">
         <v>0.03484882716322004</v>
@@ -35520,7 +35520,7 @@
         <v>0.00304377068402011</v>
       </c>
       <c r="D458" s="1" t="n">
-        <v>237.378</v>
+        <v>163.868</v>
       </c>
       <c r="E458" s="1" t="n">
         <v>0.034804782407545</v>
@@ -35537,7 +35537,7 @@
         <v>0.003046633780640474</v>
       </c>
       <c r="D459" s="1" t="n">
-        <v>237.377</v>
+        <v>163.867</v>
       </c>
       <c r="E459" s="1" t="n">
         <v>0.03476076364165121</v>
@@ -35554,7 +35554,7 @@
         <v>0.003049505198287787</v>
       </c>
       <c r="D460" s="1" t="n">
-        <v>237.377</v>
+        <v>163.867</v>
       </c>
       <c r="E460" s="1" t="n">
         <v>0.03471688754472568</v>
@@ -35571,7 +35571,7 @@
         <v>0.003052419777359436</v>
       </c>
       <c r="D461" s="1" t="n">
-        <v>237.376</v>
+        <v>163.866</v>
       </c>
       <c r="E461" s="1" t="n">
         <v>0.03467384066894467</v>
@@ -35588,7 +35588,7 @@
         <v>0.003055412358252812</v>
       </c>
       <c r="D462" s="1" t="n">
-        <v>237.376</v>
+        <v>163.866</v>
       </c>
       <c r="E462" s="1" t="n">
         <v>0.03463172109945254</v>
@@ -35605,7 +35605,7 @@
         <v>0.003058505517829356</v>
       </c>
       <c r="D463" s="1" t="n">
-        <v>237.375</v>
+        <v>163.865</v>
       </c>
       <c r="E463" s="1" t="n">
         <v>0.03459106910282245</v>
@@ -35622,7 +35622,7 @@
         <v>0.003061672778806734</v>
       </c>
       <c r="D464" s="1" t="n">
-        <v>237.375</v>
+        <v>163.865</v>
       </c>
       <c r="E464" s="1" t="n">
         <v>0.03455128561013299</v>
@@ -35639,7 +35639,7 @@
         <v>0.003064875400366671</v>
       </c>
       <c r="D465" s="1" t="n">
-        <v>237.374</v>
+        <v>163.864</v>
       </c>
       <c r="E465" s="1" t="n">
         <v>0.0345122190354735</v>
@@ -35656,7 +35656,7 @@
         <v>0.003068074641690885</v>
       </c>
       <c r="D466" s="1" t="n">
-        <v>237.374</v>
+        <v>163.864</v>
       </c>
       <c r="E466" s="1" t="n">
         <v>0.03447313941141421</v>
@@ -35673,7 +35673,7 @@
         <v>0.003071240539804948</v>
       </c>
       <c r="D467" s="1" t="n">
-        <v>237.373</v>
+        <v>163.863</v>
       </c>
       <c r="E467" s="1" t="n">
         <v>0.03443400055804478</v>
@@ -35690,7 +35690,7 @@
         <v>0.003074378243109818</v>
       </c>
       <c r="D468" s="1" t="n">
-        <v>237.373</v>
+        <v>163.863</v>
       </c>
       <c r="E468" s="1" t="n">
         <v>0.03439457110881074</v>
@@ -35707,7 +35707,7 @@
         <v>0.003077501677850308</v>
       </c>
       <c r="D469" s="1" t="n">
-        <v>237.372</v>
+        <v>163.862</v>
       </c>
       <c r="E469" s="1" t="n">
         <v>0.03435529742782134</v>
@@ -35724,7 +35724,7 @@
         <v>0.003080624770271225</v>
       </c>
       <c r="D470" s="1" t="n">
-        <v>237.372</v>
+        <v>163.862</v>
       </c>
       <c r="E470" s="1" t="n">
         <v>0.03431604494395332</v>
@@ -35741,7 +35741,7 @@
         <v>0.003083761555475374</v>
       </c>
       <c r="D471" s="1" t="n">
-        <v>237.371</v>
+        <v>163.861</v>
       </c>
       <c r="E471" s="1" t="n">
         <v>0.03427725789128176</v>
@@ -35758,7 +35758,7 @@
         <v>0.003086926503997539</v>
       </c>
       <c r="D472" s="1" t="n">
-        <v>237.371</v>
+        <v>163.861</v>
       </c>
       <c r="E472" s="1" t="n">
         <v>0.03423880573487946</v>
@@ -35775,7 +35775,7 @@
         <v>0.003090134195230498</v>
       </c>
       <c r="D473" s="1" t="n">
-        <v>237.37</v>
+        <v>163.86</v>
       </c>
       <c r="E473" s="1" t="n">
         <v>0.03420113540667794</v>
@@ -35792,7 +35792,7 @@
         <v>0.003093399208567031</v>
       </c>
       <c r="D474" s="1" t="n">
-        <v>237.37</v>
+        <v>163.86</v>
       </c>
       <c r="E474" s="1" t="n">
         <v>0.03416411551356069</v>
@@ -35809,7 +35809,7 @@
         <v>0.00309671990044548</v>
       </c>
       <c r="D475" s="1" t="n">
-        <v>237.369</v>
+        <v>163.859</v>
       </c>
       <c r="E475" s="1" t="n">
         <v>0.03412801087711729</v>
@@ -35826,7 +35826,7 @@
         <v>0.003100029735486445</v>
       </c>
       <c r="D476" s="1" t="n">
-        <v>237.369</v>
+        <v>163.859</v>
       </c>
       <c r="E476" s="1" t="n">
         <v>0.03409179716625124</v>
@@ -35843,7 +35843,7 @@
         <v>0.003103245955356087</v>
       </c>
       <c r="D477" s="1" t="n">
-        <v>237.368</v>
+        <v>163.858</v>
       </c>
       <c r="E477" s="1" t="n">
         <v>0.03405485337359269</v>
@@ -35860,7 +35860,7 @@
         <v>0.003106285801720571</v>
       </c>
       <c r="D478" s="1" t="n">
-        <v>237.368</v>
+        <v>163.858</v>
       </c>
       <c r="E478" s="1" t="n">
         <v>0.03401599169412351</v>
@@ -35877,7 +35877,7 @@
         <v>0.003109101157587793</v>
       </c>
       <c r="D479" s="1" t="n">
-        <v>237.367</v>
+        <v>163.857</v>
       </c>
       <c r="E479" s="1" t="n">
         <v>0.03397498433687397</v>
@@ -35894,7 +35894,7 @@
         <v>0.00311178247133258</v>
       </c>
       <c r="D480" s="1" t="n">
-        <v>237.367</v>
+        <v>163.857</v>
       </c>
       <c r="E480" s="1" t="n">
         <v>0.03393254563841257</v>
@@ -35911,7 +35911,7 @@
         <v>0.003114454832671495</v>
       </c>
       <c r="D481" s="1" t="n">
-        <v>237.366</v>
+        <v>163.856</v>
       </c>
       <c r="E481" s="1" t="n">
         <v>0.0338903309889757</v>
@@ -35928,7 +35928,7 @@
         <v>0.0031172433313211</v>
       </c>
       <c r="D482" s="1" t="n">
-        <v>237.365</v>
+        <v>163.855</v>
       </c>
       <c r="E482" s="1" t="n">
         <v>0.03384955507078623</v>
@@ -35945,7 +35945,7 @@
         <v>0.003120240788955578</v>
       </c>
       <c r="D483" s="1" t="n">
-        <v>237.364</v>
+        <v>163.854</v>
       </c>
       <c r="E483" s="1" t="n">
         <v>0.03381121467528279</v>
@@ -35962,7 +35962,7 @@
         <v>0.003123410955079591</v>
       </c>
       <c r="D484" s="1" t="n">
-        <v>237.363</v>
+        <v>163.853</v>
       </c>
       <c r="E484" s="1" t="n">
         <v>0.03377490255176996</v>
@@ -35979,7 +35979,7 @@
         <v>0.003126685311155424</v>
       </c>
       <c r="D485" s="1" t="n">
-        <v>237.363</v>
+        <v>163.853</v>
       </c>
       <c r="E485" s="1" t="n">
         <v>0.03373972449677278</v>
@@ -35996,7 +35996,7 @@
         <v>0.00312999533864536</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>237.362</v>
+        <v>163.852</v>
       </c>
       <c r="E486" s="1" t="n">
         <v>0.03370521914008606</v>
@@ -36013,7 +36013,7 @@
         <v>0.00313328283369617</v>
       </c>
       <c r="D487" s="1" t="n">
-        <v>237.361</v>
+        <v>163.851</v>
       </c>
       <c r="E487" s="1" t="n">
         <v>0.03367061542155308</v>
@@ -36030,7 +36030,7 @@
         <v>0.003136530851192564</v>
       </c>
       <c r="D488" s="1" t="n">
-        <v>237.361</v>
+        <v>163.851</v>
       </c>
       <c r="E488" s="1" t="n">
         <v>0.03363559052614026</v>
@@ -36047,7 +36047,7 @@
         <v>0.003139732760703741</v>
       </c>
       <c r="D489" s="1" t="n">
-        <v>237.36</v>
+        <v>163.85</v>
       </c>
       <c r="E489" s="1" t="n">
         <v>0.03360035878939919</v>
@@ -36064,7 +36064,7 @@
         <v>0.0031428819317989</v>
       </c>
       <c r="D490" s="1" t="n">
-        <v>237.36</v>
+        <v>163.85</v>
       </c>
       <c r="E490" s="1" t="n">
         <v>0.03356456829423139</v>
@@ -36081,7 +36081,7 @@
         <v>0.003145973608353518</v>
       </c>
       <c r="D491" s="1" t="n">
-        <v>237.359</v>
+        <v>163.849</v>
       </c>
       <c r="E491" s="1" t="n">
         <v>0.03352845389456494</v>
@@ -36098,7 +36098,7 @@
         <v>0.003149010531468193</v>
       </c>
       <c r="D492" s="1" t="n">
-        <v>237.359</v>
+        <v>163.849</v>
       </c>
       <c r="E492" s="1" t="n">
         <v>0.03349176494903629</v>
@@ -36115,7 +36115,7 @@
         <v>0.0031519973165498</v>
       </c>
       <c r="D493" s="1" t="n">
-        <v>237.359</v>
+        <v>163.849</v>
       </c>
       <c r="E493" s="1" t="n">
         <v>0.03345469452133577</v>
@@ -36132,7 +36132,7 @@
         <v>0.003154938579005215</v>
       </c>
       <c r="D494" s="1" t="n">
-        <v>237.358</v>
+        <v>163.848</v>
       </c>
       <c r="E494" s="1" t="n">
         <v>0.03341743463187195</v>
@@ -36149,7 +36149,7 @@
         <v>0.003157853892579203</v>
       </c>
       <c r="D495" s="1" t="n">
-        <v>237.358</v>
+        <v>163.848</v>
       </c>
       <c r="E495" s="1" t="n">
         <v>0.03337991247376353</v>
@@ -36166,7 +36166,7 @@
         <v>0.003160822664368089</v>
       </c>
       <c r="D496" s="1" t="n">
-        <v>237.357</v>
+        <v>163.847</v>
       </c>
       <c r="E496" s="1" t="n">
         <v>0.03334324786769326</v>
@@ -36183,7 +36183,7 @@
         <v>0.003163939259806087</v>
       </c>
       <c r="D497" s="1" t="n">
-        <v>237.357</v>
+        <v>163.847</v>
       </c>
       <c r="E497" s="1" t="n">
         <v>0.03330814875255304</v>
@@ -36200,7 +36200,7 @@
         <v>0.003167298044327407</v>
       </c>
       <c r="D498" s="1" t="n">
-        <v>237.357</v>
+        <v>163.847</v>
       </c>
       <c r="E498" s="1" t="n">
         <v>0.03327573676316694</v>
@@ -36217,7 +36217,7 @@
         <v>0.003170949024662984</v>
       </c>
       <c r="D499" s="1" t="n">
-        <v>237.356</v>
+        <v>163.846</v>
       </c>
       <c r="E499" s="1" t="n">
         <v>0.033246659924816</v>
@@ -36234,7 +36234,7 @@
         <v>0.003174764772730618</v>
       </c>
       <c r="D500" s="1" t="n">
-        <v>237.356</v>
+        <v>163.846</v>
       </c>
       <c r="E500" s="1" t="n">
         <v>0.03321928523479678</v>
@@ -36251,7 +36251,7 @@
         <v>0.003178573501744832</v>
       </c>
       <c r="D501" s="1" t="n">
-        <v>237.356</v>
+        <v>163.846</v>
       </c>
       <c r="E501" s="1" t="n">
         <v>0.03319194785379597</v>
@@ -36268,7 +36268,7 @@
         <v>0.003182203424920144</v>
       </c>
       <c r="D502" s="1" t="n">
-        <v>237.355</v>
+        <v>163.845</v>
       </c>
       <c r="E502" s="1" t="n">
         <v>0.03316299702423371</v>
@@ -36285,7 +36285,7 @@
         <v>0.003185523789264427</v>
       </c>
       <c r="D503" s="1" t="n">
-        <v>237.355</v>
+        <v>163.845</v>
       </c>
       <c r="E503" s="1" t="n">
         <v>0.03313080387513771</v>
@@ -36302,7 +36302,7 @@
         <v>0.003188567976958948</v>
       </c>
       <c r="D504" s="1" t="n">
-        <v>237.355</v>
+        <v>163.845</v>
       </c>
       <c r="E504" s="1" t="n">
         <v>0.03309587342881808</v>
@@ -36319,7 +36319,7 @@
         <v>0.003191410403978326</v>
       </c>
       <c r="D505" s="1" t="n">
-        <v>237.355</v>
+        <v>163.845</v>
       </c>
       <c r="E505" s="1" t="n">
         <v>0.0330589929977602</v>
@@ -36336,7 +36336,7 @@
         <v>0.003194125486297179</v>
       </c>
       <c r="D506" s="1" t="n">
-        <v>237.354</v>
+        <v>163.844</v>
       </c>
       <c r="E506" s="1" t="n">
         <v>0.03302108271702439</v>
@@ -36353,7 +36353,7 @@
         <v>0.003196784224084905</v>
       </c>
       <c r="D507" s="1" t="n">
-        <v>237.354</v>
+        <v>163.844</v>
       </c>
       <c r="E507" s="1" t="n">
         <v>0.0329826037185006</v>
@@ -36370,7 +36370,7 @@
         <v>0.003199443954290036</v>
       </c>
       <c r="D508" s="1" t="n">
-        <v>237.354</v>
+        <v>163.844</v>
       </c>
       <c r="E508" s="1" t="n">
         <v>0.03294428824156202</v>
@@ -36387,7 +36387,7 @@
         <v>0.00320215859805588</v>
       </c>
       <c r="D509" s="1" t="n">
-        <v>237.353</v>
+        <v>163.843</v>
       </c>
       <c r="E509" s="1" t="n">
         <v>0.03290682806691216</v>
@@ -36404,7 +36404,7 @@
         <v>0.003204982076525748</v>
       </c>
       <c r="D510" s="1" t="n">
-        <v>237.353</v>
+        <v>163.843</v>
       </c>
       <c r="E510" s="1" t="n">
         <v>0.03287049451129534</v>
@@ -36421,7 +36421,7 @@
         <v>0.003207949176642839</v>
       </c>
       <c r="D511" s="1" t="n">
-        <v>237.353</v>
+        <v>163.843</v>
       </c>
       <c r="E511" s="1" t="n">
         <v>0.03283577492663313</v>
@@ -36438,7 +36438,7 @@
         <v>0.003211018148549895</v>
       </c>
       <c r="D512" s="1" t="n">
-        <v>237.353</v>
+        <v>163.843</v>
       </c>
       <c r="E512" s="1" t="n">
         <v>0.03280223324725524</v>
@@ -36455,7 +36455,7 @@
         <v>0.00321412810818955</v>
       </c>
       <c r="D513" s="1" t="n">
-        <v>237.352</v>
+        <v>163.842</v>
       </c>
       <c r="E513" s="1" t="n">
         <v>0.03276937982929296</v>
@@ -36472,7 +36472,7 @@
         <v>0.003217218171504436</v>
       </c>
       <c r="D514" s="1" t="n">
-        <v>237.352</v>
+        <v>163.842</v>
       </c>
       <c r="E514" s="1" t="n">
         <v>0.03273631564677065</v>
@@ -36489,7 +36489,7 @@
         <v>0.003220244319935379</v>
       </c>
       <c r="D515" s="1" t="n">
-        <v>237.352</v>
+        <v>163.842</v>
       </c>
       <c r="E515" s="1" t="n">
         <v>0.0327027323039548</v>
@@ -36506,7 +36506,7 @@
         <v>0.00322322999691599</v>
       </c>
       <c r="D516" s="1" t="n">
-        <v>237.352</v>
+        <v>163.842</v>
       </c>
       <c r="E516" s="1" t="n">
         <v>0.03266887046436228</v>
@@ -36523,7 +36523,7 @@
         <v>0.003226215511378072</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>237.351</v>
+        <v>163.841</v>
       </c>
       <c r="E517" s="1" t="n">
         <v>0.03263527700983268</v>
@@ -36540,7 +36540,7 @@
         <v>0.00322924117225343</v>
       </c>
       <c r="D518" s="1" t="n">
-        <v>237.351</v>
+        <v>163.841</v>
       </c>
       <c r="E518" s="1" t="n">
         <v>0.03260208299191231</v>
@@ -36557,7 +36557,7 @@
         <v>0.003232332431896556</v>
       </c>
       <c r="D519" s="1" t="n">
-        <v>237.351</v>
+        <v>163.841</v>
       </c>
       <c r="E519" s="1" t="n">
         <v>0.0325696793727132</v>
@@ -36574,7 +36574,7 @@
         <v>0.003235455316352684</v>
       </c>
       <c r="D520" s="1" t="n">
-        <v>237.351</v>
+        <v>163.841</v>
       </c>
       <c r="E520" s="1" t="n">
         <v>0.03253771987612034</v>
@@ -36591,7 +36591,7 @@
         <v>0.003238560995089733</v>
       </c>
       <c r="D521" s="1" t="n">
-        <v>237.35</v>
+        <v>163.84</v>
       </c>
       <c r="E521" s="1" t="n">
         <v>0.0325058487514648</v>
@@ -36608,7 +36608,7 @@
         <v>0.003241600637575623</v>
       </c>
       <c r="D522" s="1" t="n">
-        <v>237.35</v>
+        <v>163.84</v>
       </c>
       <c r="E522" s="1" t="n">
         <v>0.03247330307240877</v>
@@ -36625,7 +36625,7 @@
         <v>0.003244546244085651</v>
       </c>
       <c r="D523" s="1" t="n">
-        <v>237.35</v>
+        <v>163.84</v>
       </c>
       <c r="E523" s="1" t="n">
         <v>0.03243994309560674</v>
@@ -36642,7 +36642,7 @@
         <v>0.003247453138124612</v>
       </c>
       <c r="D524" s="1" t="n">
-        <v>237.35</v>
+        <v>163.84</v>
       </c>
       <c r="E524" s="1" t="n">
         <v>0.03240632561016549</v>
@@ -36659,7 +36659,7 @@
         <v>0.003250397474004677</v>
       </c>
       <c r="D525" s="1" t="n">
-        <v>237.349</v>
+        <v>163.839</v>
       </c>
       <c r="E525" s="1" t="n">
         <v>0.03237334697896601</v>
@@ -36676,7 +36676,7 @@
         <v>0.003253455406038018</v>
       </c>
       <c r="D526" s="1" t="n">
-        <v>237.349</v>
+        <v>163.839</v>
       </c>
       <c r="E526" s="1" t="n">
         <v>0.03234148839983535</v>
@@ -36693,7 +36693,7 @@
         <v>0.0032566770304402</v>
       </c>
       <c r="D527" s="1" t="n">
-        <v>237.349</v>
+        <v>163.839</v>
       </c>
       <c r="E527" s="1" t="n">
         <v>0.03231137620517033</v>
@@ -36710,7 +36710,7 @@
         <v>0.003260008211040364</v>
       </c>
       <c r="D528" s="1" t="n">
-        <v>237.349</v>
+        <v>163.839</v>
       </c>
       <c r="E528" s="1" t="n">
         <v>0.03228246427097808</v>
@@ -36727,7 +36727,7 @@
         <v>0.003263368753571038</v>
       </c>
       <c r="D529" s="1" t="n">
-        <v>237.348</v>
+        <v>163.838</v>
       </c>
       <c r="E529" s="1" t="n">
         <v>0.03225408899443685</v>
@@ -36744,7 +36744,7 @@
         <v>0.003266678463764757</v>
       </c>
       <c r="D530" s="1" t="n">
-        <v>237.348</v>
+        <v>163.838</v>
       </c>
       <c r="E530" s="1" t="n">
         <v>0.03222518507469931</v>
@@ -36761,7 +36761,7 @@
         <v>0.003269877461825629</v>
       </c>
       <c r="D531" s="1" t="n">
-        <v>237.348</v>
+        <v>163.838</v>
       </c>
       <c r="E531" s="1" t="n">
         <v>0.03219530119050279</v>
@@ -36778,7 +36778,7 @@
         <v>0.003272987125844066</v>
       </c>
       <c r="D532" s="1" t="n">
-        <v>237.348</v>
+        <v>163.838</v>
       </c>
       <c r="E532" s="1" t="n">
         <v>0.03216465302008006</v>
@@ -36795,7 +36795,7 @@
         <v>0.003276049148382058</v>
       </c>
       <c r="D533" s="1" t="n">
-        <v>237.347</v>
+        <v>163.837</v>
       </c>
       <c r="E533" s="1" t="n">
         <v>0.0321337892492052</v>
@@ -36812,7 +36812,7 @@
         <v>0.00327910522200159</v>
       </c>
       <c r="D534" s="1" t="n">
-        <v>237.347</v>
+        <v>163.837</v>
       </c>
       <c r="E534" s="1" t="n">
         <v>0.03210284914180341</v>
@@ -36829,7 +36829,7 @@
         <v>0.003282185825208224</v>
       </c>
       <c r="D535" s="1" t="n">
-        <v>237.347</v>
+        <v>163.837</v>
       </c>
       <c r="E535" s="1" t="n">
         <v>0.032072265703985</v>
@@ -36846,7 +36846,7 @@
         <v>0.003285276580281795</v>
       </c>
       <c r="D536" s="1" t="n">
-        <v>237.347</v>
+        <v>163.837</v>
       </c>
       <c r="E536" s="1" t="n">
         <v>0.03204189668836028</v>
@@ -36863,7 +36863,7 @@
         <v>0.003288351895445709</v>
       </c>
       <c r="D537" s="1" t="n">
-        <v>237.346</v>
+        <v>163.836</v>
       </c>
       <c r="E537" s="1" t="n">
         <v>0.03201162662502011</v>
@@ -36880,7 +36880,7 @@
         <v>0.003291386178923372</v>
       </c>
       <c r="D538" s="1" t="n">
-        <v>237.346</v>
+        <v>163.836</v>
       </c>
       <c r="E538" s="1" t="n">
         <v>0.0319809371789803</v>
@@ -36897,7 +36897,7 @@
         <v>0.003294373123433378</v>
       </c>
       <c r="D539" s="1" t="n">
-        <v>237.346</v>
+        <v>163.836</v>
       </c>
       <c r="E539" s="1" t="n">
         <v>0.03194990378160622</v>
@@ -36914,7 +36914,7 @@
         <v>0.003297383559675082</v>
       </c>
       <c r="D540" s="1" t="n">
-        <v>237.346</v>
+        <v>163.836</v>
       </c>
       <c r="E540" s="1" t="n">
         <v>0.03191921401800311</v>
@@ -36931,7 +36931,7 @@
         <v>0.003300507602843026</v>
       </c>
       <c r="D541" s="1" t="n">
-        <v>237.345</v>
+        <v>163.835</v>
       </c>
       <c r="E541" s="1" t="n">
         <v>0.03188987102086537</v>
@@ -36948,7 +36948,7 @@
         <v>0.003303835368131752</v>
       </c>
       <c r="D542" s="1" t="n">
-        <v>237.345</v>
+        <v>163.835</v>
       </c>
       <c r="E542" s="1" t="n">
         <v>0.03186246824326656</v>
@@ -36965,7 +36965,7 @@
         <v>0.003307411550121405</v>
       </c>
       <c r="D543" s="1" t="n">
-        <v>237.345</v>
+        <v>163.835</v>
       </c>
       <c r="E543" s="1" t="n">
         <v>0.03183755881478069</v>
@@ -36982,7 +36982,7 @@
         <v>0.003311099160934539</v>
       </c>
       <c r="D544" s="1" t="n">
-        <v>237.345</v>
+        <v>163.835</v>
       </c>
       <c r="E544" s="1" t="n">
         <v>0.03181381262051296</v>
@@ -36999,7 +36999,7 @@
         <v>0.003314715792079305</v>
       </c>
       <c r="D545" s="1" t="n">
-        <v>237.345</v>
+        <v>163.835</v>
       </c>
       <c r="E545" s="1" t="n">
         <v>0.03178947381436899</v>
@@ -37016,7 +37016,7 @@
         <v>0.003318079035063862</v>
       </c>
       <c r="D546" s="1" t="n">
-        <v>237.344</v>
+        <v>163.834</v>
       </c>
       <c r="E546" s="1" t="n">
         <v>0.03176293338252775</v>
@@ -37033,7 +37033,7 @@
         <v>0.003321074949665413</v>
       </c>
       <c r="D547" s="1" t="n">
-        <v>237.344</v>
+        <v>163.834</v>
       </c>
       <c r="E547" s="1" t="n">
         <v>0.03173284780352627</v>
@@ -37050,7 +37050,7 @@
         <v>0.00332386346873737</v>
       </c>
       <c r="D548" s="1" t="n">
-        <v>237.344</v>
+        <v>163.834</v>
       </c>
       <c r="E548" s="1" t="n">
         <v>0.03170089523479826</v>
@@ -37067,7 +37067,7 @@
         <v>0.003326672993402191</v>
       </c>
       <c r="D549" s="1" t="n">
-        <v>237.344</v>
+        <v>163.834</v>
       </c>
       <c r="E549" s="1" t="n">
         <v>0.03166926032412462</v>
@@ -37084,7 +37084,7 @@
         <v>0.003329731924782338</v>
       </c>
       <c r="D550" s="1" t="n">
-        <v>237.344</v>
+        <v>163.834</v>
       </c>
       <c r="E550" s="1" t="n">
         <v>0.0316401116556997</v>
@@ -37101,7 +37101,7 @@
         <v>0.003333194424467846</v>
       </c>
       <c r="D551" s="1" t="n">
-        <v>237.343</v>
+        <v>163.833</v>
       </c>
       <c r="E551" s="1" t="n">
         <v>0.03161503094900514</v>
@@ -37118,7 +37118,7 @@
         <v>0.003336917695919064</v>
       </c>
       <c r="D552" s="1" t="n">
-        <v>237.343</v>
+        <v>163.833</v>
       </c>
       <c r="E552" s="1" t="n">
         <v>0.03159237815697535</v>
@@ -37135,7 +37135,7 @@
         <v>0.003340684703063917</v>
       </c>
       <c r="D553" s="1" t="n">
-        <v>237.343</v>
+        <v>163.833</v>
       </c>
       <c r="E553" s="1" t="n">
         <v>0.03157022150264815</v>
@@ -37152,7 +37152,7 @@
         <v>0.003344278409830328</v>
       </c>
       <c r="D554" s="1" t="n">
-        <v>237.342</v>
+        <v>163.832</v>
       </c>
       <c r="E554" s="1" t="n">
         <v>0.03154664388887744</v>
@@ -37169,7 +37169,7 @@
         <v>0.003347544140623844</v>
       </c>
       <c r="D555" s="1" t="n">
-        <v>237.342</v>
+        <v>163.832</v>
       </c>
       <c r="E555" s="1" t="n">
         <v>0.03151993146844212</v>
@@ -37186,7 +37186,7 @@
         <v>0.003350576661760504</v>
       </c>
       <c r="D556" s="1" t="n">
-        <v>237.341</v>
+        <v>163.831</v>
       </c>
       <c r="E556" s="1" t="n">
         <v>0.03149125699537735</v>
@@ -37203,7 +37203,7 @@
         <v>0.003353533100033963</v>
       </c>
       <c r="D557" s="1" t="n">
-        <v>237.341</v>
+        <v>163.831</v>
       </c>
       <c r="E557" s="1" t="n">
         <v>0.03146184049494797</v>
@@ -37220,7 +37220,7 @@
         <v>0.003356570582237882</v>
       </c>
       <c r="D558" s="1" t="n">
-        <v>237.34</v>
+        <v>163.83</v>
       </c>
       <c r="E558" s="1" t="n">
         <v>0.0314334219683667</v>
@@ -37237,7 +37237,7 @@
         <v>0.003359802464261758</v>
       </c>
       <c r="D559" s="1" t="n">
-        <v>237.339</v>
+        <v>163.829</v>
       </c>
       <c r="E559" s="1" t="n">
         <v>0.03140692368166999</v>
@@ -37254,7 +37254,7 @@
         <v>0.003363167018378446</v>
       </c>
       <c r="D560" s="1" t="n">
-        <v>237.339</v>
+        <v>163.829</v>
       </c>
       <c r="E560" s="1" t="n">
         <v>0.03138162705372188</v>
@@ -37271,7 +37271,7 @@
         <v>0.003366558745956641</v>
       </c>
       <c r="D561" s="1" t="n">
-        <v>237.339</v>
+        <v>163.829</v>
       </c>
       <c r="E561" s="1" t="n">
         <v>0.03135667468282518</v>
@@ -37288,7 +37288,7 @@
         <v>0.003369872148365033</v>
       </c>
       <c r="D562" s="1" t="n">
-        <v>237.338</v>
+        <v>163.828</v>
       </c>
       <c r="E562" s="1" t="n">
         <v>0.03133121585781993</v>
@@ -37305,7 +37305,7 @@
         <v>0.003373036292194859</v>
       </c>
       <c r="D563" s="1" t="n">
-        <v>237.338</v>
+        <v>163.828</v>
       </c>
       <c r="E563" s="1" t="n">
         <v>0.03130433157041842</v>
@@ -37322,7 +37322,7 @@
         <v>0.0033761185049275</v>
       </c>
       <c r="D564" s="1" t="n">
-        <v>237.338</v>
+        <v>163.828</v>
       </c>
       <c r="E564" s="1" t="n">
         <v>0.03127678462252537</v>
@@ -37339,7 +37339,7 @@
         <v>0.003379220679266879</v>
       </c>
       <c r="D565" s="1" t="n">
-        <v>237.337</v>
+        <v>163.827</v>
       </c>
       <c r="E565" s="1" t="n">
         <v>0.03124965249588798</v>
@@ -37356,7 +37356,7 @@
         <v>0.00338244470791692</v>
       </c>
       <c r="D566" s="1" t="n">
-        <v>237.337</v>
+        <v>163.827</v>
       </c>
       <c r="E566" s="1" t="n">
         <v>0.03122361080482643</v>
@@ -37373,7 +37373,7 @@
         <v>0.003385852318604769</v>
       </c>
       <c r="D567" s="1" t="n">
-        <v>237.337</v>
+        <v>163.827</v>
       </c>
       <c r="E567" s="1" t="n">
         <v>0.03119935359333735</v>
@@ -37390,7 +37390,7 @@
         <v>0.003389344579150461</v>
       </c>
       <c r="D568" s="1" t="n">
-        <v>237.337</v>
+        <v>163.827</v>
       </c>
       <c r="E568" s="1" t="n">
         <v>0.03117596133506514</v>
@@ -37407,7 +37407,7 @@
         <v>0.003392782392397253</v>
       </c>
       <c r="D569" s="1" t="n">
-        <v>237.336</v>
+        <v>163.826</v>
       </c>
       <c r="E569" s="1" t="n">
         <v>0.03115228350392542</v>
@@ -37424,7 +37424,7 @@
         <v>0.003396026661188406</v>
       </c>
       <c r="D570" s="1" t="n">
-        <v>237.336</v>
+        <v>163.826</v>
       </c>
       <c r="E570" s="1" t="n">
         <v>0.03112678478428052</v>
@@ -37441,7 +37441,7 @@
         <v>0.003398986926103126</v>
       </c>
       <c r="D571" s="1" t="n">
-        <v>237.336</v>
+        <v>163.826</v>
       </c>
       <c r="E571" s="1" t="n">
         <v>0.03109877785326449</v>
@@ -37458,7 +37458,7 @@
         <v>0.00340176727866442</v>
       </c>
       <c r="D572" s="1" t="n">
-        <v>237.335</v>
+        <v>163.825</v>
       </c>
       <c r="E572" s="1" t="n">
         <v>0.03106935760902262</v>
@@ -37475,7 +37475,7 @@
         <v>0.003404520448131242</v>
       </c>
       <c r="D573" s="1" t="n">
-        <v>237.335</v>
+        <v>163.825</v>
       </c>
       <c r="E573" s="1" t="n">
         <v>0.03103966273537433</v>
@@ -37492,7 +37492,7 @@
         <v>0.003407399163762548</v>
       </c>
       <c r="D574" s="1" t="n">
-        <v>237.335</v>
+        <v>163.825</v>
       </c>
       <c r="E574" s="1" t="n">
         <v>0.03101121503429373</v>
@@ -37509,7 +37509,7 @@
         <v>0.00341051304749818</v>
       </c>
       <c r="D575" s="1" t="n">
-        <v>237.335</v>
+        <v>163.825</v>
       </c>
       <c r="E575" s="1" t="n">
         <v>0.03098500386134256</v>
@@ -37526,7 +37526,7 @@
         <v>0.003413799292001526</v>
       </c>
       <c r="D576" s="1" t="n">
-        <v>237.334</v>
+        <v>163.824</v>
       </c>
       <c r="E576" s="1" t="n">
         <v>0.03096057828362666</v>
@@ -37543,7 +37543,7 @@
         <v>0.00341715198261686</v>
       </c>
       <c r="D577" s="1" t="n">
-        <v>237.334</v>
+        <v>163.824</v>
       </c>
       <c r="E577" s="1" t="n">
         <v>0.03093670972308062</v>
@@ -37560,7 +37560,7 @@
         <v>0.00342046520468846</v>
       </c>
       <c r="D578" s="1" t="n">
-        <v>237.334</v>
+        <v>163.824</v>
       </c>
       <c r="E578" s="1" t="n">
         <v>0.03091256792076477</v>
@@ -37577,7 +37577,7 @@
         <v>0.003423653091857699</v>
       </c>
       <c r="D579" s="1" t="n">
-        <v>237.333</v>
+        <v>163.823</v>
       </c>
       <c r="E579" s="1" t="n">
         <v>0.03088750978514269</v>
@@ -37594,7 +37594,7 @@
         <v>0.003426709970954357</v>
       </c>
       <c r="D580" s="1" t="n">
-        <v>237.333</v>
+        <v>163.823</v>
       </c>
       <c r="E580" s="1" t="n">
         <v>0.0308612292947832</v>
@@ -37611,7 +37611,7 @@
         <v>0.003429650217105316</v>
       </c>
       <c r="D581" s="1" t="n">
-        <v>237.333</v>
+        <v>163.823</v>
       </c>
       <c r="E581" s="1" t="n">
         <v>0.03083399163580246</v>
@@ -37628,7 +37628,7 @@
         <v>0.003432488205437455</v>
       </c>
       <c r="D582" s="1" t="n">
-        <v>237.332</v>
+        <v>163.822</v>
       </c>
       <c r="E582" s="1" t="n">
         <v>0.03080606060849126</v>
@@ -37645,7 +37645,7 @@
         <v>0.003435260106508675</v>
       </c>
       <c r="D583" s="1" t="n">
-        <v>237.332</v>
+        <v>163.822</v>
       </c>
       <c r="E583" s="1" t="n">
         <v>0.03077750483173348</v>
@@ -37662,7 +37662,7 @@
         <v>0.003438089272600953</v>
       </c>
       <c r="D584" s="1" t="n">
-        <v>237.331</v>
+        <v>163.821</v>
       </c>
       <c r="E584" s="1" t="n">
         <v>0.03074968959443403</v>
@@ -37679,7 +37679,7 @@
         <v>0.003441120851427287</v>
       </c>
       <c r="D585" s="1" t="n">
-        <v>237.331</v>
+        <v>163.821</v>
       </c>
       <c r="E585" s="1" t="n">
         <v>0.03072364842219987</v>
@@ -37696,7 +37696,7 @@
         <v>0.003444499990700675</v>
       </c>
       <c r="D586" s="1" t="n">
-        <v>237.331</v>
+        <v>163.821</v>
       </c>
       <c r="E586" s="1" t="n">
         <v>0.03070079484998892</v>
@@ -37713,7 +37713,7 @@
         <v>0.00344830684142655</v>
       </c>
       <c r="D587" s="1" t="n">
-        <v>237.33</v>
+        <v>163.82</v>
       </c>
       <c r="E587" s="1" t="n">
         <v>0.03068195485331526</v>
@@ -37730,7 +37730,7 @@
         <v>0.003452361567780092</v>
       </c>
       <c r="D588" s="1" t="n">
-        <v>237.33</v>
+        <v>163.82</v>
       </c>
       <c r="E588" s="1" t="n">
         <v>0.03066525241452246</v>
@@ -37747,7 +37747,7 @@
         <v>0.003456419337228916</v>
       </c>
       <c r="D589" s="1" t="n">
-        <v>237.33</v>
+        <v>163.82</v>
       </c>
       <c r="E589" s="1" t="n">
         <v>0.03064863425759837</v>
@@ -37764,7 +37764,7 @@
         <v>0.003460235317240637</v>
       </c>
       <c r="D590" s="1" t="n">
-        <v>237.329</v>
+        <v>163.819</v>
       </c>
       <c r="E590" s="1" t="n">
         <v>0.03063006175804949</v>
@@ -37781,7 +37781,7 @@
         <v>0.003463635160121401</v>
       </c>
       <c r="D591" s="1" t="n">
-        <v>237.329</v>
+        <v>163.819</v>
       </c>
       <c r="E591" s="1" t="n">
         <v>0.030607746699764</v>
@@ -37798,7 +37798,7 @@
         <v>0.003466726457531482</v>
       </c>
       <c r="D592" s="1" t="n">
-        <v>237.329</v>
+        <v>163.819</v>
       </c>
       <c r="E592" s="1" t="n">
         <v>0.0305827858740151</v>
@@ -37815,7 +37815,7 @@
         <v>0.003469687285969676</v>
       </c>
       <c r="D593" s="1" t="n">
-        <v>237.329</v>
+        <v>163.819</v>
       </c>
       <c r="E593" s="1" t="n">
         <v>0.0305567610825698</v>
@@ -37832,7 +37832,7 @@
         <v>0.003472695721934791</v>
       </c>
       <c r="D594" s="1" t="n">
-        <v>237.328</v>
+        <v>163.818</v>
       </c>
       <c r="E594" s="1" t="n">
         <v>0.03053137201240926</v>
@@ -37849,7 +37849,7 @@
         <v>0.00347587867817815</v>
       </c>
       <c r="D595" s="1" t="n">
-        <v>237.328</v>
+        <v>163.818</v>
       </c>
       <c r="E595" s="1" t="n">
         <v>0.03050747258560272</v>
@@ -37866,7 +37866,7 @@
         <v>0.003479158412461188</v>
       </c>
       <c r="D596" s="1" t="n">
-        <v>237.328</v>
+        <v>163.818</v>
       </c>
       <c r="E596" s="1" t="n">
         <v>0.03048450214621648</v>
@@ -37883,7 +37883,7 @@
         <v>0.003482406018797867</v>
       </c>
       <c r="D597" s="1" t="n">
-        <v>237.328</v>
+        <v>163.818</v>
       </c>
       <c r="E597" s="1" t="n">
         <v>0.03046132841115696</v>
@@ -37900,7 +37900,7 @@
         <v>0.003485492591202144</v>
       </c>
       <c r="D598" s="1" t="n">
-        <v>237.327</v>
+        <v>163.817</v>
       </c>
       <c r="E598" s="1" t="n">
         <v>0.03043695499637085</v>
@@ -37917,7 +37917,7 @@
         <v>0.003488331917533506</v>
       </c>
       <c r="D599" s="1" t="n">
-        <v>237.327</v>
+        <v>163.817</v>
       </c>
       <c r="E599" s="1" t="n">
         <v>0.03041038043884439</v>
@@ -37934,7 +37934,7 @@
         <v>0.003491008561033535</v>
       </c>
       <c r="D600" s="1" t="n">
-        <v>237.327</v>
+        <v>163.817</v>
       </c>
       <c r="E600" s="1" t="n">
         <v>0.03038247951844966</v>
@@ -37951,7 +37951,7 @@
         <v>0.003493649778789342</v>
       </c>
       <c r="D601" s="1" t="n">
-        <v>237.326</v>
+        <v>163.816</v>
       </c>
       <c r="E601" s="1" t="n">
         <v>0.03035449248978299</v>
@@ -37968,7 +37968,7 @@
         <v>0.003496382827888034</v>
       </c>
       <c r="D602" s="1" t="n">
-        <v>237.326</v>
+        <v>163.816</v>
       </c>
       <c r="E602" s="1" t="n">
         <v>0.03032726832260561</v>
@@ -37985,7 +37985,7 @@
         <v>0.003499307531055794</v>
       </c>
       <c r="D603" s="1" t="n">
-        <v>237.326</v>
+        <v>163.816</v>
       </c>
       <c r="E603" s="1" t="n">
         <v>0.03030179496196215</v>
@@ -38002,7 +38002,7 @@
         <v>0.003502413973575099</v>
       </c>
       <c r="D604" s="1" t="n">
-        <v>237.325</v>
+        <v>163.815</v>
       </c>
       <c r="E604" s="1" t="n">
         <v>0.03027810549314507</v>
@@ -38019,7 +38019,7 @@
         <v>0.003505664806367504</v>
       </c>
       <c r="D605" s="1" t="n">
-        <v>237.325</v>
+        <v>163.815</v>
       </c>
       <c r="E605" s="1" t="n">
         <v>0.03025561402595645</v>
@@ -38036,7 +38036,7 @@
         <v>0.003509022680354561</v>
       </c>
       <c r="D606" s="1" t="n">
-        <v>237.325</v>
+        <v>163.815</v>
       </c>
       <c r="E606" s="1" t="n">
         <v>0.03023411980886202</v>
@@ -38053,7 +38053,7 @@
         <v>0.003512451223835116</v>
       </c>
       <c r="D607" s="1" t="n">
-        <v>237.324</v>
+        <v>163.814</v>
       </c>
       <c r="E607" s="1" t="n">
         <v>0.03021343231108096</v>
@@ -38070,7 +38070,7 @@
         <v>0.003515917974617204</v>
       </c>
       <c r="D608" s="1" t="n">
-        <v>237.324</v>
+        <v>163.814</v>
       </c>
       <c r="E608" s="1" t="n">
         <v>0.03019301467575908</v>
@@ -38087,7 +38087,7 @@
         <v>0.00351939144788615</v>
       </c>
       <c r="D609" s="1" t="n">
-        <v>237.324</v>
+        <v>163.814</v>
       </c>
       <c r="E609" s="1" t="n">
         <v>0.03017272239437153</v>
@@ -38104,7 +38104,7 @@
         <v>0.003522840158827285</v>
       </c>
       <c r="D610" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E610" s="1" t="n">
         <v>0.03015241241479917</v>
@@ -38121,7 +38121,7 @@
         <v>0.003526239149007052</v>
       </c>
       <c r="D611" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E611" s="1" t="n">
         <v>0.03013161799559376</v>
@@ -38138,7 +38138,7 @@
         <v>0.003529589565516365</v>
       </c>
       <c r="D612" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E612" s="1" t="n">
         <v>0.03011047782905513</v>
@@ -38155,7 +38155,7 @@
         <v>0.003532899081827256</v>
       </c>
       <c r="D613" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E613" s="1" t="n">
         <v>0.03008905897754973</v>
@@ -38172,7 +38172,7 @@
         <v>0.003536175371411757</v>
       </c>
       <c r="D614" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E614" s="1" t="n">
         <v>0.03006742806224422</v>
@@ -38189,7 +38189,7 @@
         <v>0.003539424259683123</v>
       </c>
       <c r="D615" s="1" t="n">
-        <v>237.323</v>
+        <v>163.813</v>
       </c>
       <c r="E615" s="1" t="n">
         <v>0.0300456355788372</v>
@@ -38206,7 +38206,7 @@
         <v>0.003542644179819511</v>
       </c>
       <c r="D616" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E616" s="1" t="n">
         <v>0.03002379555348183</v>
@@ -38223,7 +38223,7 @@
         <v>0.003545831716940305</v>
       </c>
       <c r="D617" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E617" s="1" t="n">
         <v>0.0300016268333155</v>
@@ -38240,7 +38240,7 @@
         <v>0.003548983456164884</v>
       </c>
       <c r="D618" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E618" s="1" t="n">
         <v>0.02997922816538489</v>
@@ -38257,7 +38257,7 @@
         <v>0.003552097374192507</v>
       </c>
       <c r="D619" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E619" s="1" t="n">
         <v>0.02995658361155618</v>
@@ -38274,7 +38274,7 @@
         <v>0.003555177014041948</v>
       </c>
       <c r="D620" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E620" s="1" t="n">
         <v>0.02993372420458104</v>
@@ -38291,7 +38291,7 @@
         <v>0.003558227310311859</v>
       </c>
       <c r="D621" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E621" s="1" t="n">
         <v>0.02991069247308399</v>
@@ -38308,7 +38308,7 @@
         <v>0.00356125319760089</v>
       </c>
       <c r="D622" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E622" s="1" t="n">
         <v>0.0298875306695296</v>
@@ -38325,7 +38325,7 @@
         <v>0.00356426149998984</v>
       </c>
       <c r="D623" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E623" s="1" t="n">
         <v>0.02986429660408655</v>
@@ -38342,7 +38342,7 @@
         <v>0.003567266599488105</v>
       </c>
       <c r="D624" s="1" t="n">
-        <v>237.322</v>
+        <v>163.812</v>
       </c>
       <c r="E624" s="1" t="n">
         <v>0.02984111093678197</v>
@@ -38359,7 +38359,7 @@
         <v>0.003570284767587227</v>
       </c>
       <c r="D625" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E625" s="1" t="n">
         <v>0.02981823497303774</v>
@@ -38376,7 +38376,7 @@
         <v>0.003573332275778752</v>
       </c>
       <c r="D626" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E626" s="1" t="n">
         <v>0.02979555211357533</v>
@@ -38393,7 +38393,7 @@
         <v>0.00357642328048239</v>
       </c>
       <c r="D627" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E627" s="1" t="n">
         <v>0.02977330441016298</v>
@@ -38410,7 +38410,7 @@
         <v>0.003579563477830536</v>
       </c>
       <c r="D628" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E628" s="1" t="n">
         <v>0.02975153710737417</v>
@@ -38427,7 +38427,7 @@
         <v>0.00358275644888375</v>
       </c>
       <c r="D629" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E629" s="1" t="n">
         <v>0.02973027760808813</v>
@@ -38444,7 +38444,7 @@
         <v>0.003586005774702598</v>
       </c>
       <c r="D630" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E630" s="1" t="n">
         <v>0.02970955313952463</v>
@@ -38461,7 +38461,7 @@
         <v>0.003589310742150968</v>
       </c>
       <c r="D631" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E631" s="1" t="n">
         <v>0.02968935523475708</v>
@@ -38478,7 +38478,7 @@
         <v>0.00359265346130607</v>
       </c>
       <c r="D632" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E632" s="1" t="n">
         <v>0.02966953362835626</v>
@@ -38495,7 +38495,7 @@
         <v>0.00359601174804844</v>
       </c>
       <c r="D633" s="1" t="n">
-        <v>237.321</v>
+        <v>163.811</v>
       </c>
       <c r="E633" s="1" t="n">
         <v>0.02964990360693306</v>
@@ -38512,7 +38512,7 @@
         <v>0.003599363418258617</v>
       </c>
       <c r="D634" s="1" t="n">
-        <v>237.32</v>
+        <v>163.81</v>
       </c>
       <c r="E634" s="1" t="n">
         <v>0.02963040648732329</v>
@@ -38529,7 +38529,7 @@
         <v>0.00360269243652826</v>
       </c>
       <c r="D635" s="1" t="n">
-        <v>237.32</v>
+        <v>163.81</v>
       </c>
       <c r="E635" s="1" t="n">
         <v>0.02961066064547442</v>
@@ -38546,7 +38546,7 @@
         <v>0.003606007362293521</v>
       </c>
       <c r="D636" s="1" t="n">
-        <v>237.32</v>
+        <v>163.81</v>
       </c>
       <c r="E636" s="1" t="n">
         <v>0.02959086184588191</v>
@@ -38563,7 +38563,7 @@
         <v>0.003609322903701675</v>
       </c>
       <c r="D637" s="1" t="n">
-        <v>237.319</v>
+        <v>163.809</v>
       </c>
       <c r="E637" s="1" t="n">
         <v>0.02957125544895248</v>
@@ -38580,7 +38580,7 @@
         <v>0.003612653768899996</v>
       </c>
       <c r="D638" s="1" t="n">
-        <v>237.319</v>
+        <v>163.809</v>
       </c>
       <c r="E638" s="1" t="n">
         <v>0.02955171215350788</v>
@@ -38597,7 +38597,7 @@
         <v>0.003616007683777291</v>
       </c>
       <c r="D639" s="1" t="n">
-        <v>237.318</v>
+        <v>163.808</v>
       </c>
       <c r="E639" s="1" t="n">
         <v>0.0295325432984351</v>
@@ -38614,7 +38614,7 @@
         <v>0.003619364445188515</v>
       </c>
       <c r="D640" s="1" t="n">
-        <v>237.318</v>
+        <v>163.808</v>
       </c>
       <c r="E640" s="1" t="n">
         <v>0.0295133339935224</v>
@@ -38631,7 +38631,7 @@
         <v>0.003622696867730154</v>
       </c>
       <c r="D641" s="1" t="n">
-        <v>237.317</v>
+        <v>163.807</v>
       </c>
       <c r="E641" s="1" t="n">
         <v>0.02949411131776148</v>
@@ -38648,7 +38648,7 @@
         <v>0.003625977765998694</v>
       </c>
       <c r="D642" s="1" t="n">
-        <v>237.317</v>
+        <v>163.807</v>
       </c>
       <c r="E642" s="1" t="n">
         <v>0.02947440629501574</v>
@@ -38665,7 +38665,7 @@
         <v>0.003629190344185621</v>
       </c>
       <c r="D643" s="1" t="n">
-        <v>237.316</v>
+        <v>163.806</v>
       </c>
       <c r="E643" s="1" t="n">
         <v>0.02945433277421799</v>
@@ -38682,7 +38682,7 @@
         <v>0.003632359364862405</v>
       </c>
       <c r="D644" s="1" t="n">
-        <v>237.316</v>
+        <v>163.806</v>
       </c>
       <c r="E644" s="1" t="n">
         <v>0.029433845413624</v>
@@ -38699,7 +38699,7 @@
         <v>0.003635519980195511</v>
       </c>
       <c r="D645" s="1" t="n">
-        <v>237.316</v>
+        <v>163.806</v>
       </c>
       <c r="E645" s="1" t="n">
         <v>0.02941335417237571</v>
@@ -38716,7 +38716,7 @@
         <v>0.003638707342351408</v>
       </c>
       <c r="D646" s="1" t="n">
-        <v>237.316</v>
+        <v>163.806</v>
       </c>
       <c r="E646" s="1" t="n">
         <v>0.02939314302462918</v>
@@ -38733,7 +38733,7 @@
         <v>0.003641948664153753</v>
       </c>
       <c r="D647" s="1" t="n">
-        <v>237.315</v>
+        <v>163.805</v>
       </c>
       <c r="E647" s="1" t="n">
         <v>0.02937355391325631</v>
@@ -38750,7 +38750,7 @@
         <v>0.003645239401054959</v>
       </c>
       <c r="D648" s="1" t="n">
-        <v>237.315</v>
+        <v>163.805</v>
       </c>
       <c r="E648" s="1" t="n">
         <v>0.02935430028469507</v>
@@ -38767,7 +38767,7 @@
         <v>0.003648567069164632</v>
       </c>
       <c r="D649" s="1" t="n">
-        <v>237.315</v>
+        <v>163.805</v>
       </c>
       <c r="E649" s="1" t="n">
         <v>0.02933540347927475</v>
@@ -38784,7 +38784,7 @@
         <v>0.003651919184592374</v>
       </c>
       <c r="D650" s="1" t="n">
-        <v>237.315</v>
+        <v>163.805</v>
       </c>
       <c r="E650" s="1" t="n">
         <v>0.02931676161699426</v>
@@ -38801,7 +38801,7 @@
         <v>0.003655278695413185</v>
       </c>
       <c r="D651" s="1" t="n">
-        <v>237.314</v>
+        <v>163.804</v>
       </c>
       <c r="E651" s="1" t="n">
         <v>0.02929836029308094</v>
@@ -38818,7 +38818,7 @@
         <v>0.003658610277563641</v>
       </c>
       <c r="D652" s="1" t="n">
-        <v>237.314</v>
+        <v>163.804</v>
       </c>
       <c r="E652" s="1" t="n">
         <v>0.02927966927422223</v>
@@ -38835,7 +38835,7 @@
         <v>0.003661874038945717</v>
       </c>
       <c r="D653" s="1" t="n">
-        <v>237.314</v>
+        <v>163.804</v>
       </c>
       <c r="E653" s="1" t="n">
         <v>0.02926049410564283</v>
@@ -38852,7 +38852,7 @@
         <v>0.003665030087461379</v>
       </c>
       <c r="D654" s="1" t="n">
-        <v>237.314</v>
+        <v>163.804</v>
       </c>
       <c r="E654" s="1" t="n">
         <v>0.02924051875972748</v>
@@ -38869,7 +38869,7 @@
         <v>0.003668053702250028</v>
       </c>
       <c r="D655" s="1" t="n">
-        <v>237.314</v>
+        <v>163.804</v>
       </c>
       <c r="E655" s="1" t="n">
         <v>0.02921955001003462</v>
@@ -38886,7 +38886,7 @@
         <v>0.003670980847400753</v>
       </c>
       <c r="D656" s="1" t="n">
-        <v>237.313</v>
+        <v>163.803</v>
       </c>
       <c r="E656" s="1" t="n">
         <v>0.02919800152437161</v>
@@ -38903,7 +38903,7 @@
         <v>0.00367386265824007</v>
       </c>
       <c r="D657" s="1" t="n">
-        <v>237.313</v>
+        <v>163.803</v>
       </c>
       <c r="E657" s="1" t="n">
         <v>0.02917603646840524</v>
@@ -38920,7 +38920,7 @@
         <v>0.003676750270094494</v>
       </c>
       <c r="D658" s="1" t="n">
-        <v>237.313</v>
+        <v>163.803</v>
       </c>
       <c r="E658" s="1" t="n">
         <v>0.02915418478810357</v>
@@ -38937,7 +38937,7 @@
         <v>0.003679683212834614</v>
       </c>
       <c r="D659" s="1" t="n">
-        <v>237.313</v>
+        <v>163.803</v>
       </c>
       <c r="E659" s="1" t="n">
         <v>0.02913275892817815</v>
@@ -38954,7 +38954,7 @@
         <v>0.003682654594507305</v>
       </c>
       <c r="D660" s="1" t="n">
-        <v>237.312</v>
+        <v>163.802</v>
       </c>
       <c r="E660" s="1" t="n">
         <v>0.02911182512653455</v>
@@ -38971,7 +38971,7 @@
         <v>0.00368564591770352</v>
       </c>
       <c r="D661" s="1" t="n">
-        <v>237.312</v>
+        <v>163.802</v>
       </c>
       <c r="E661" s="1" t="n">
         <v>0.02909099025777364</v>
@@ -38988,7 +38988,7 @@
         <v>0.003688638685014209</v>
       </c>
       <c r="D662" s="1" t="n">
-        <v>237.312</v>
+        <v>163.802</v>
       </c>
       <c r="E662" s="1" t="n">
         <v>0.0290702302910472</v>
@@ -39005,7 +39005,7 @@
         <v>0.003691618136628069</v>
       </c>
       <c r="D663" s="1" t="n">
-        <v>237.311</v>
+        <v>163.801</v>
       </c>
       <c r="E663" s="1" t="n">
         <v>0.0290495511498367</v>
@@ -39022,7 +39022,7 @@
         <v>0.003694584463124793</v>
       </c>
       <c r="D664" s="1" t="n">
-        <v>237.311</v>
+        <v>163.801</v>
       </c>
       <c r="E664" s="1" t="n">
         <v>0.02902870961171944</v>
@@ -39039,7 +39039,7 @@
         <v>0.003697541592681825</v>
       </c>
       <c r="D665" s="1" t="n">
-        <v>237.31</v>
+        <v>163.8</v>
       </c>
       <c r="E665" s="1" t="n">
         <v>0.02900798141016084</v>
@@ -39056,7 +39056,7 @@
         <v>0.003700493453476603</v>
       </c>
       <c r="D666" s="1" t="n">
-        <v>237.31</v>
+        <v>163.8</v>
       </c>
       <c r="E666" s="1" t="n">
         <v>0.02898715279610252</v>
@@ -39073,7 +39073,7 @@
         <v>0.003703451844237278</v>
       </c>
       <c r="D667" s="1" t="n">
-        <v>237.309</v>
+        <v>163.799</v>
       </c>
       <c r="E667" s="1" t="n">
         <v>0.02896656033961734</v>
@@ -39090,7 +39090,7 @@
         <v>0.003706460045894823</v>
       </c>
       <c r="D668" s="1" t="n">
-        <v>237.309</v>
+        <v>163.799</v>
       </c>
       <c r="E668" s="1" t="n">
         <v>0.02894629732319361</v>
@@ -39107,7 +39107,7 @@
         <v>0.003709569209930919</v>
       </c>
       <c r="D669" s="1" t="n">
-        <v>237.309</v>
+        <v>163.799</v>
       </c>
       <c r="E669" s="1" t="n">
         <v>0.02892688272743742</v>
@@ -39124,7 +39124,7 @@
         <v>0.003712830487827249</v>
       </c>
       <c r="D670" s="1" t="n">
-        <v>237.308</v>
+        <v>163.798</v>
       </c>
       <c r="E670" s="1" t="n">
         <v>0.02890883281237169</v>
@@ -39141,7 +39141,7 @@
         <v>0.003716273830622135</v>
       </c>
       <c r="D671" s="1" t="n">
-        <v>237.308</v>
+        <v>163.798</v>
       </c>
       <c r="E671" s="1" t="n">
         <v>0.02889213111502984</v>
@@ -39158,7 +39158,7 @@
         <v>0.003719844387580464</v>
       </c>
       <c r="D672" s="1" t="n">
-        <v>237.308</v>
+        <v>163.798</v>
       </c>
       <c r="E672" s="1" t="n">
         <v>0.02887646711306443</v>
@@ -39175,7 +39175,7 @@
         <v>0.003723466107523772</v>
       </c>
       <c r="D673" s="1" t="n">
-        <v>237.307</v>
+        <v>163.797</v>
       </c>
       <c r="E673" s="1" t="n">
         <v>0.02886136827286849</v>
@@ -39192,7 +39192,7 @@
         <v>0.003727062939273587</v>
       </c>
       <c r="D674" s="1" t="n">
-        <v>237.307</v>
+        <v>163.797</v>
       </c>
       <c r="E674" s="1" t="n">
         <v>0.02884600069427026</v>
@@ -39209,7 +39209,7 @@
         <v>0.003730558831651444</v>
       </c>
       <c r="D675" s="1" t="n">
-        <v>237.307</v>
+        <v>163.797</v>
       </c>
       <c r="E675" s="1" t="n">
         <v>0.02882989899434722</v>
@@ -39226,7 +39226,7 @@
         <v>0.003733877733478871</v>
       </c>
       <c r="D676" s="1" t="n">
-        <v>237.307</v>
+        <v>163.797</v>
       </c>
       <c r="E676" s="1" t="n">
         <v>0.02881247961104503</v>
@@ -39243,7 +39243,7 @@
         <v>0.003736943593577402</v>
       </c>
       <c r="D677" s="1" t="n">
-        <v>237.306</v>
+        <v>163.796</v>
       </c>
       <c r="E677" s="1" t="n">
         <v>0.02879328379454835</v>
@@ -39260,7 +39260,7 @@
         <v>0.003739680360768567</v>
       </c>
       <c r="D678" s="1" t="n">
-        <v>237.306</v>
+        <v>163.796</v>
       </c>
       <c r="E678" s="1" t="n">
         <v>0.02877149215565401</v>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27470,7 +27470,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>219.9</v>
+        <v>243.571</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
@@ -27550,7 +27550,7 @@
         <v>2.661398770219695e-05</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>219.901</v>
+        <v>243.5695</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>0.1112857237805481</v>
@@ -27630,7 +27630,7 @@
         <v>5.261538975502517e-05</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>206.022</v>
+        <v>243.568</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.1154668076100317</v>
@@ -27710,7 +27710,7 @@
         <v>7.810692926740683e-05</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>198.061</v>
+        <v>243.5665</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.1176226100741688</v>
@@ -27790,7 +27790,7 @@
         <v>0.0001031913293482641</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>192.341</v>
+        <v>243.565</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0.1190558697427829</v>
@@ -27855,7 +27855,7 @@
         <v>0.0001279713131065191</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>187.973</v>
+        <v>243.5648</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0.1200895057210479</v>
@@ -27900,7 +27900,7 @@
         <v>0.0001525496036510941</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>184.545</v>
+        <v>243.5645</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0.1208797211170362</v>
@@ -27934,7 +27934,7 @@
         <v>0.0001770289240909113</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>181.807</v>
+        <v>243.5642</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.1215268809056527</v>
@@ -27964,7 +27964,7 @@
         <v>0.0002015119975348927</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>179.589</v>
+        <v>243.564</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.1221030145613062</v>
@@ -27989,7 +27989,7 @@
         <v>0.0002260726832141147</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>177.769</v>
+        <v>243.5637</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.1226465337943992</v>
@@ -28006,7 +28006,7 @@
         <v>0.0002506693848482696</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>176.259</v>
+        <v>243.5635</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0.1231313538342954</v>
@@ -28023,7 +28023,7 @@
         <v>0.0002752316422792043</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>174.993</v>
+        <v>243.5632</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>0.1235321314044198</v>
@@ -28040,7 +28040,7 @@
         <v>0.0002996889953487651</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>173.922</v>
+        <v>243.563</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.1238339079555154</v>
@@ -28057,7 +28057,7 @@
         <v>0.0003239640399071632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>173.008</v>
+        <v>243.563</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.1240254217468656</v>
@@ -28074,7 +28074,7 @@
         <v>0.0003479515958380678</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>172.222</v>
+        <v>243.563</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>0.1240894832507529</v>
@@ -28091,7 +28091,7 @@
         <v>0.0003715395390335124</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>171.541</v>
+        <v>243.563</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>0.1240118522378651</v>
@@ -28108,7 +28108,7 @@
         <v>0.0003946157453855307</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>170.947</v>
+        <v>243.563</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>0.1237820992815037</v>
@@ -28125,7 +28125,7 @@
         <v>0.0004170775537410905</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>170.425</v>
+        <v>243.563</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0.1233955996827052</v>
@@ -28142,7 +28142,7 @@
         <v>0.0004388601547668969</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>169.965</v>
+        <v>243.563</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0.1228584881388688</v>
@@ -28159,7 +28159,7 @@
         <v>0.0004599082020845885</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>169.558</v>
+        <v>243.563</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>0.1221787452775384</v>
@@ -28176,7 +28176,7 @@
         <v>0.0004801663493158043</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>169.195</v>
+        <v>243.563</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0.1213637245757375</v>
@@ -28193,7 +28193,7 @@
         <v>0.0004996144084749656</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>168.87</v>
+        <v>243.5623</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.1204272510841864</v>
@@ -28210,7 +28210,7 @@
         <v>0.0005183728251476213</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>168.578</v>
+        <v>243.5615</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>0.1194131562024102</v>
@@ -28227,7 +28227,7 @@
         <v>0.0005365972033121028</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>168.315</v>
+        <v>243.5607</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0.1183655353721301</v>
@@ -28244,7 +28244,7 @@
         <v>0.0005544431469467415</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>168.077</v>
+        <v>243.56</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>0.1173216363539563</v>
@@ -28261,7 +28261,7 @@
         <v>0.0005720440726142114</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>167.861</v>
+        <v>243.5592</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>0.1163081869633094</v>
@@ -28278,7 +28278,7 @@
         <v>0.0005894446472145586</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>167.665</v>
+        <v>243.5585</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>0.1153302643339966</v>
@@ -28295,7 +28295,7 @@
         <v>0.0006066673502321717</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>167.486</v>
+        <v>243.5577</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>0.114388645785176</v>
@@ -28312,7 +28312,7 @@
         <v>0.0006237346611514396</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>167.322</v>
+        <v>243.557</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>0.1134837162942553</v>
@@ -28329,7 +28329,7 @@
         <v>0.0006406799617838726</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>167.171</v>
+        <v>243.556</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>0.1126178495617659</v>
@@ -28346,7 +28346,7 @@
         <v>0.0006575802432494677</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>167.033</v>
+        <v>243.555</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>0.1117997089875733</v>
@@ -28363,7 +28363,7 @@
         <v>0.0006745233989953432</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>166.905</v>
+        <v>243.554</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>0.1110400528034714</v>
@@ -28380,7 +28380,7 @@
         <v>0.0006915973224686174</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>166.788</v>
+        <v>243.553</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>0.1103466271593397</v>
@@ -28397,7 +28397,7 @@
         <v>0.0007088418133964745</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>166.679</v>
+        <v>243.5523</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>0.1097205986317153</v>
@@ -28414,7 +28414,7 @@
         <v>0.0007261042966263634</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>166.578</v>
+        <v>243.5515</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>0.1091328583492951</v>
@@ -28431,7 +28431,7 @@
         <v>0.0007431841032857985</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>166.484</v>
+        <v>243.5507</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>0.1085510121743906</v>
@@ -28448,7 +28448,7 @@
         <v>0.0007598805645022946</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>166.397</v>
+        <v>243.55</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>0.1079458151702543</v>
@@ -28465,7 +28465,7 @@
         <v>0.0007760517094351554</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>166.315</v>
+        <v>243.5493</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>0.1073001618543659</v>
@@ -28482,7 +28482,7 @@
         <v>0.0007917903593708433</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>166.239</v>
+        <v>243.5485</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>0.1066290900331442</v>
@@ -28499,7 +28499,7 @@
         <v>0.0008072480336276096</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>166.168</v>
+        <v>243.5478</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>0.1059546719306844</v>
@@ -28516,7 +28516,7 @@
         <v>0.0008225762515237059</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>166.102</v>
+        <v>243.547</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>0.1052963957719576</v>
@@ -28533,7 +28533,7 @@
         <v>0.0008379002154167179</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>166.039</v>
+        <v>243.5462</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>0.1046694585321525</v>
@@ -28550,7 +28550,7 @@
         <v>0.0008532398598215696</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>165.98</v>
+        <v>243.5455</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>0.1040735468549181</v>
@@ -28567,7 +28567,7 @@
         <v>0.0008685888022925192</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>165.924</v>
+        <v>243.5448</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>0.1035060759143579</v>
@@ -28584,7 +28584,7 @@
         <v>0.0008839406603838247</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>165.872</v>
+        <v>243.544</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>0.1029638654141289</v>
@@ -28601,7 +28601,7 @@
         <v>0.0008992686264573183</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>165.822</v>
+        <v>243.5433</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>0.1024429444577545</v>
@@ -28618,7 +28618,7 @@
         <v>0.0009144641921051261</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>165.776</v>
+        <v>243.5425</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>0.1019289328018456</v>
@@ -28635,7 +28635,7 @@
         <v>0.0009293984237269484</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>165.732</v>
+        <v>243.5418</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>0.1014080761625971</v>
@@ -28652,7 +28652,7 @@
         <v>0.0009439423877224854</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>165.69</v>
+        <v>243.541</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>0.1008669688875111</v>
@@ -28669,7 +28669,7 @@
         <v>0.0009580248387294006</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>165.651</v>
+        <v>243.5403</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>0.1002989122045029</v>
@@ -28686,7 +28686,7 @@
         <v>0.0009718052843372098</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>165.614</v>
+        <v>243.5395</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>0.09972222949425953</v>
@@ -28703,7 +28703,7 @@
         <v>0.0009855009203733921</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>165.579</v>
+        <v>243.5387</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>0.09915923256847266</v>
@@ -28720,7 +28720,7 @@
         <v>0.0009993289426654271</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>165.545</v>
+        <v>243.538</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>0.098630942852046</v>
@@ -28737,7 +28737,7 @@
         <v>0.001013457143978018</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>165.514</v>
+        <v>243.5375</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>0.0981508134539094</v>
@@ -28754,7 +28754,7 @@
         <v>0.001027855704824765</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>165.484</v>
+        <v>243.537</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>0.09771411145470539</v>
@@ -28771,7 +28771,7 @@
         <v>0.001042445402656492</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>165.456</v>
+        <v>243.5365</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>0.0973106579992216</v>
@@ -28788,7 +28788,7 @@
         <v>0.001057147014924023</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>165.429</v>
+        <v>243.536</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>0.09693178568761178</v>
@@ -28805,7 +28805,7 @@
         <v>0.001071878193075125</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>165.403</v>
+        <v>243.5352</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>0.09656876836882189</v>
@@ -28822,7 +28822,7 @@
         <v>0.001086544084545324</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>165.379</v>
+        <v>243.5345</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>0.09621196842422147</v>
@@ -28839,7 +28839,7 @@
         <v>0.00110104671076709</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>165.356</v>
+        <v>243.5337</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>0.0958529072251585</v>
@@ -28856,7 +28856,7 @@
         <v>0.001115288093172891</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>165.333</v>
+        <v>243.533</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>0.09548368957349142</v>
@@ -28873,7 +28873,7 @@
         <v>0.001129204542136493</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>165.311</v>
+        <v>243.5325</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>0.09509904665700883</v>
@@ -28890,7 +28890,7 @@
         <v>0.001142869523796845</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>165.29</v>
+        <v>243.532</v>
       </c>
       <c r="E68" s="1" t="n">
         <v>0.09470579067421878</v>
@@ -28907,7 +28907,7 @@
         <v>0.00115639079323419</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>165.27</v>
+        <v>243.5315</v>
       </c>
       <c r="E69" s="1" t="n">
         <v>0.09431310051574124</v>
@@ -28924,7 +28924,7 @@
         <v>0.001169876105528773</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>165.25</v>
+        <v>243.531</v>
       </c>
       <c r="E70" s="1" t="n">
         <v>0.09392997805670734</v>
@@ -28941,7 +28941,7 @@
         <v>0.001183398583241379</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>165.231</v>
+        <v>243.5305</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>0.09356137035534468</v>
@@ -28958,7 +28958,7 @@
         <v>0.001196892818854963</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>165.213</v>
+        <v>243.53</v>
       </c>
       <c r="E72" s="1" t="n">
         <v>0.09320151171390739</v>
@@ -28975,7 +28975,7 @@
         <v>0.001210258772333016</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>165.195</v>
+        <v>243.5295</v>
       </c>
       <c r="E73" s="1" t="n">
         <v>0.09284271134072715</v>
@@ -28992,7 +28992,7 @@
         <v>0.001223396403639034</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>165.178</v>
+        <v>243.529</v>
       </c>
       <c r="E74" s="1" t="n">
         <v>0.09247697085479535</v>
@@ -29009,7 +29009,7 @@
         <v>0.001236233964005328</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>165.161</v>
+        <v>243.5283</v>
       </c>
       <c r="E75" s="1" t="n">
         <v>0.09209961654602945</v>
@@ -29026,7 +29026,7 @@
         <v>0.001248812869739474</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>165.145</v>
+        <v>243.5275</v>
       </c>
       <c r="E76" s="1" t="n">
         <v>0.09171379883304261</v>
@@ -29043,7 +29043,7 @@
         <v>0.001261202828417863</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>165.13</v>
+        <v>243.5267</v>
       </c>
       <c r="E77" s="1" t="n">
         <v>0.09132490757534896</v>
@@ -29060,7 +29060,7 @@
         <v>0.001273473547616889</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>165.116</v>
+        <v>243.526</v>
       </c>
       <c r="E78" s="1" t="n">
         <v>0.09093803483082658</v>
@@ -29077,7 +29077,7 @@
         <v>0.001285695902402913</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>165.102</v>
+        <v>243.5258</v>
       </c>
       <c r="E79" s="1" t="n">
         <v>0.09055845680085915</v>
@@ -29094,7 +29094,7 @@
         <v>0.001297945437802176</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>165.088</v>
+        <v>243.5255</v>
       </c>
       <c r="E80" s="1" t="n">
         <v>0.09019112662327873</v>
@@ -29111,7 +29111,7 @@
         <v>0.001310298866330885</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>165.075</v>
+        <v>243.5252</v>
       </c>
       <c r="E81" s="1" t="n">
         <v>0.08984043797640451</v>
@@ -29128,7 +29128,7 @@
         <v>0.001322832900505251</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>165.063</v>
+        <v>243.525</v>
       </c>
       <c r="E82" s="1" t="n">
         <v>0.08951091532630005</v>
@@ -29145,7 +29145,7 @@
         <v>0.001335586209595795</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>165.051</v>
+        <v>243.5245</v>
       </c>
       <c r="E83" s="1" t="n">
         <v>0.08920468188120592</v>
@@ -29162,7 +29162,7 @@
         <v>0.001348445289890304</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>165.039</v>
+        <v>243.524</v>
       </c>
       <c r="E84" s="1" t="n">
         <v>0.08891335992498277</v>
@@ -29179,7 +29179,7 @@
         <v>0.001361258594430875</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>165.028</v>
+        <v>243.5235</v>
       </c>
       <c r="E85" s="1" t="n">
         <v>0.08862614604751046</v>
@@ -29196,7 +29196,7 @@
         <v>0.00137387457625961</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>165.016</v>
+        <v>243.523</v>
       </c>
       <c r="E86" s="1" t="n">
         <v>0.08833387229966326</v>
@@ -29213,7 +29213,7 @@
         <v>0.001386167395906253</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>165.005</v>
+        <v>243.5225</v>
       </c>
       <c r="E87" s="1" t="n">
         <v>0.08802800479848273</v>
@@ -29230,7 +29230,7 @@
         <v>0.001398114043851136</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>164.995</v>
+        <v>243.522</v>
       </c>
       <c r="E88" s="1" t="n">
         <v>0.08770758483141153</v>
@@ -29247,7 +29247,7 @@
         <v>0.001409717218062237</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>164.984</v>
+        <v>243.5215</v>
       </c>
       <c r="E89" s="1" t="n">
         <v>0.08737402622344086</v>
@@ -29264,7 +29264,7 @@
         <v>0.001420979616507535</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>164.974</v>
+        <v>243.521</v>
       </c>
       <c r="E90" s="1" t="n">
         <v>0.08702723974231855</v>
@@ -29281,7 +29281,7 @@
         <v>0.001431931678207736</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>164.964</v>
+        <v>243.5207</v>
       </c>
       <c r="E91" s="1" t="n">
         <v>0.08666988679736835</v>
@@ -29298,7 +29298,7 @@
         <v>0.001442714806394464</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>164.954</v>
+        <v>243.5205</v>
       </c>
       <c r="E92" s="1" t="n">
         <v>0.08631079314327535</v>
@@ -29315,7 +29315,7 @@
         <v>0.00145349814535207</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>164.945</v>
+        <v>243.5203</v>
       </c>
       <c r="E93" s="1" t="n">
         <v>0.08595966027640642</v>
@@ -29332,7 +29332,7 @@
         <v>0.001464450839364906</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>164.936</v>
+        <v>243.52</v>
       </c>
       <c r="E94" s="1" t="n">
         <v>0.08562645772838749</v>
@@ -29349,7 +29349,7 @@
         <v>0.001475680364579871</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>164.928</v>
+        <v>243.5195</v>
       </c>
       <c r="E95" s="1" t="n">
         <v>0.08531643816295487</v>
@@ -29366,7 +29366,7 @@
         <v>0.00148704752459405</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>164.919</v>
+        <v>243.519</v>
       </c>
       <c r="E96" s="1" t="n">
         <v>0.0850215769850417</v>
@@ -29383,7 +29383,7 @@
         <v>0.001498351454867077</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>164.911</v>
+        <v>243.5185</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>0.08472931410638661</v>
@@ -29400,7 +29400,7 @@
         <v>0.001509391290858582</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>164.903</v>
+        <v>243.518</v>
       </c>
       <c r="E98" s="1" t="n">
         <v>0.08442867512139254</v>
@@ -29417,7 +29417,7 @@
         <v>0.001520018269174404</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>164.895</v>
+        <v>243.5178</v>
       </c>
       <c r="E99" s="1" t="n">
         <v>0.08411169679232629</v>
@@ -29434,7 +29434,7 @@
         <v>0.001530292031005206</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>164.887</v>
+        <v>243.5175</v>
       </c>
       <c r="E100" s="1" t="n">
         <v>0.08378216361978076</v>
@@ -29451,7 +29451,7 @@
         <v>0.001540324318687857</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>164.879</v>
+        <v>243.5172</v>
       </c>
       <c r="E101" s="1" t="n">
         <v>0.0834465237514761</v>
@@ -29468,7 +29468,7 @@
         <v>0.001550226874559223</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>164.871</v>
+        <v>243.517</v>
       </c>
       <c r="E102" s="1" t="n">
         <v>0.0831109574662191</v>
@@ -29485,7 +29485,7 @@
         <v>0.001560110856307789</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>164.863</v>
+        <v>243.5168</v>
       </c>
       <c r="E103" s="1" t="n">
         <v>0.08278135995956597</v>
@@ -29502,7 +29502,7 @@
         <v>0.001570085083028485</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>164.856</v>
+        <v>243.5165</v>
       </c>
       <c r="E104" s="1" t="n">
         <v>0.08246291781169843</v>
@@ -29519,7 +29519,7 @@
         <v>0.001580257789167853</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>164.848</v>
+        <v>243.5162</v>
       </c>
       <c r="E105" s="1" t="n">
         <v>0.08216160353758246</v>
@@ -29536,7 +29536,7 @@
         <v>0.001590737209172439</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>164.841</v>
+        <v>243.516</v>
       </c>
       <c r="E106" s="1" t="n">
         <v>0.08188179523644272</v>
@@ -29553,7 +29553,7 @@
         <v>0.001601567094611052</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>164.834</v>
+        <v>243.5157</v>
       </c>
       <c r="E107" s="1" t="n">
         <v>0.0816254210145958</v>
@@ -29570,7 +29570,7 @@
         <v>0.001612533265541569</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>164.826</v>
+        <v>243.5155</v>
       </c>
       <c r="E108" s="1" t="n">
         <v>0.08138132546288539</v>
@@ -29587,7 +29587,7 @@
         <v>0.00162335705914413</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>164.819</v>
+        <v>243.5152</v>
       </c>
       <c r="E109" s="1" t="n">
         <v>0.08113455019743158</v>
@@ -29604,7 +29604,7 @@
         <v>0.001633759812598878</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>164.813</v>
+        <v>243.515</v>
       </c>
       <c r="E110" s="1" t="n">
         <v>0.08087137124245822</v>
@@ -29621,7 +29621,7 @@
         <v>0.001643545611554173</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>164.806</v>
+        <v>243.5147</v>
       </c>
       <c r="E111" s="1" t="n">
         <v>0.08058331988090196</v>
@@ -29638,7 +29638,7 @@
         <v>0.001652849535531249</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>164.799</v>
+        <v>243.5145</v>
       </c>
       <c r="E112" s="1" t="n">
         <v>0.08027732729997705</v>
@@ -29655,7 +29655,7 @@
         <v>0.001661889412519558</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>164.792</v>
+        <v>243.5143</v>
       </c>
       <c r="E113" s="1" t="n">
         <v>0.07996437561390424</v>
@@ -29672,7 +29672,7 @@
         <v>0.001670883070508552</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>164.785</v>
+        <v>243.514</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>0.07965504141184</v>
@@ -29689,7 +29689,7 @@
         <v>0.001680002981852637</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>164.778</v>
+        <v>243.5138</v>
       </c>
       <c r="E115" s="1" t="n">
         <v>0.07935737192106723</v>
@@ -29706,7 +29706,7 @@
         <v>0.001689240196366028</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>164.771</v>
+        <v>243.5135</v>
       </c>
       <c r="E116" s="1" t="n">
         <v>0.07907063059222802</v>
@@ -29723,7 +29723,7 @@
         <v>0.001698540408227893</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>164.764</v>
+        <v>243.5132</v>
       </c>
       <c r="E117" s="1" t="n">
         <v>0.07879200340939584</v>
@@ -29740,7 +29740,7 @@
         <v>0.0017078493116174</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>164.757</v>
+        <v>243.513</v>
       </c>
       <c r="E118" s="1" t="n">
         <v>0.07851877656387476</v>
@@ -29757,7 +29757,7 @@
         <v>0.001717111562107486</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>164.751</v>
+        <v>243.5128</v>
       </c>
       <c r="E119" s="1" t="n">
         <v>0.07824795627706468</v>
@@ -29774,7 +29774,7 @@
         <v>0.001726267660846155</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>164.744</v>
+        <v>243.5125</v>
       </c>
       <c r="E120" s="1" t="n">
         <v>0.0779774407055526</v>
@@ -29791,7 +29791,7 @@
         <v>0.001735257070375183</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>164.738</v>
+        <v>243.5122</v>
       </c>
       <c r="E121" s="1" t="n">
         <v>0.07770386354634869</v>
@@ -29808,7 +29808,7 @@
         <v>0.001744019253236343</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>164.731</v>
+        <v>243.512</v>
       </c>
       <c r="E122" s="1" t="n">
         <v>0.07742526079464357</v>
@@ -29825,7 +29825,7 @@
         <v>0.001752515844284814</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>164.725</v>
+        <v>243.512</v>
       </c>
       <c r="E123" s="1" t="n">
         <v>0.07713942903919103</v>
@@ -29842,7 +29842,7 @@
         <v>0.001760797167629392</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>164.719</v>
+        <v>243.512</v>
       </c>
       <c r="E124" s="1" t="n">
         <v>0.07684906541954119</v>
@@ -29859,7 +29859,7 @@
         <v>0.001768935719692276</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>164.713</v>
+        <v>243.512</v>
       </c>
       <c r="E125" s="1" t="n">
         <v>0.07655742104023924</v>
@@ -29876,7 +29876,7 @@
         <v>0.001777003996895664</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>164.707</v>
+        <v>243.512</v>
       </c>
       <c r="E126" s="1" t="n">
         <v>0.07626763894907877</v>
@@ -29893,7 +29893,7 @@
         <v>0.00178506885825409</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>164.701</v>
+        <v>243.5118</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>0.07598251864268254</v>
@@ -29910,7 +29910,7 @@
         <v>0.001793174613151416</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>164.695</v>
+        <v>243.5115</v>
       </c>
       <c r="E128" s="1" t="n">
         <v>0.07570381612035583</v>
@@ -29927,7 +29927,7 @@
         <v>0.001801359933563841</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>164.689</v>
+        <v>243.5112</v>
       </c>
       <c r="E129" s="1" t="n">
         <v>0.07543299439295768</v>
@@ -29944,7 +29944,7 @@
         <v>0.001809663491467559</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>164.683</v>
+        <v>243.511</v>
       </c>
       <c r="E130" s="1" t="n">
         <v>0.07517146943931527</v>
@@ -29961,7 +29961,7 @@
         <v>0.001818106811959512</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>164.678</v>
+        <v>243.511</v>
       </c>
       <c r="E131" s="1" t="n">
         <v>0.07491959096390317</v>
@@ -29978,7 +29978,7 @@
         <v>0.001826642832619614</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>164.672</v>
+        <v>243.511</v>
       </c>
       <c r="E132" s="1" t="n">
         <v>0.07467582834172752</v>
@@ -29995,7 +29995,7 @@
         <v>0.001835207344148521</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>164.666</v>
+        <v>243.511</v>
       </c>
       <c r="E133" s="1" t="n">
         <v>0.07443707764424058</v>
@@ -30012,7 +30012,7 @@
         <v>0.001843736137246892</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>164.661</v>
+        <v>243.511</v>
       </c>
       <c r="E134" s="1" t="n">
         <v>0.07420032586385963</v>
@@ -30029,7 +30029,7 @@
         <v>0.001852171233657576</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>164.655</v>
+        <v>243.511</v>
       </c>
       <c r="E135" s="1" t="n">
         <v>0.07396382794560923</v>
@@ -30046,7 +30046,7 @@
         <v>0.001860479579292194</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>164.65</v>
+        <v>243.511</v>
       </c>
       <c r="E136" s="1" t="n">
         <v>0.07372565302328093</v>
@@ -30063,7 +30063,7 @@
         <v>0.001868634351104557</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>164.644</v>
+        <v>243.511</v>
       </c>
       <c r="E137" s="1" t="n">
         <v>0.07348539732740578</v>
@@ -30080,7 +30080,7 @@
         <v>0.00187660872604848</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>164.639</v>
+        <v>243.511</v>
       </c>
       <c r="E138" s="1" t="n">
         <v>0.073241449781997</v>
@@ -30097,7 +30097,7 @@
         <v>0.001884384226049059</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>164.633</v>
+        <v>243.511</v>
       </c>
       <c r="E139" s="1" t="n">
         <v>0.07299378654942464</v>
@@ -30114,7 +30114,7 @@
         <v>0.001891975752916537</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>164.628</v>
+        <v>243.511</v>
       </c>
       <c r="E140" s="1" t="n">
         <v>0.07274245606748407</v>
@@ -30131,7 +30131,7 @@
         <v>0.001899406553432437</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>164.622</v>
+        <v>243.511</v>
       </c>
       <c r="E141" s="1" t="n">
         <v>0.07248903169380341</v>
@@ -30148,7 +30148,7 @@
         <v>0.001906699874378286</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>164.617</v>
+        <v>243.511</v>
       </c>
       <c r="E142" s="1" t="n">
         <v>0.0722338367551119</v>
@@ -30165,7 +30165,7 @@
         <v>0.001913874049517385</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>164.612</v>
+        <v>243.511</v>
       </c>
       <c r="E143" s="1" t="n">
         <v>0.07197789797869525</v>
@@ -30182,7 +30182,7 @@
         <v>0.001920927760540145</v>
       </c>
       <c r="D144" s="1" t="n">
-        <v>164.606</v>
+        <v>243.511</v>
       </c>
       <c r="E144" s="1" t="n">
         <v>0.07172148323675412</v>
@@ -30199,7 +30199,7 @@
         <v>0.00192785477611875</v>
       </c>
       <c r="D145" s="1" t="n">
-        <v>164.601</v>
+        <v>243.511</v>
       </c>
       <c r="E145" s="1" t="n">
         <v>0.07146377455220949</v>
@@ -30216,7 +30216,7 @@
         <v>0.001934648864925388</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>164.595</v>
+        <v>243.511</v>
       </c>
       <c r="E146" s="1" t="n">
         <v>0.07120516486028444</v>
@@ -30233,7 +30233,7 @@
         <v>0.001941318081847259</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>164.59</v>
+        <v>243.511</v>
       </c>
       <c r="E147" s="1" t="n">
         <v>0.07094537457178263</v>
@@ -30250,7 +30250,7 @@
         <v>0.001947927626631631</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>164.584</v>
+        <v>243.511</v>
       </c>
       <c r="E148" s="1" t="n">
         <v>0.07068738501140739</v>
@@ -30267,7 +30267,7 @@
         <v>0.001954556985240787</v>
       </c>
       <c r="D149" s="1" t="n">
-        <v>164.579</v>
+        <v>243.511</v>
       </c>
       <c r="E149" s="1" t="n">
         <v>0.0704334339643997</v>
@@ -30284,7 +30284,7 @@
         <v>0.001961285643637013</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>164.574</v>
+        <v>243.511</v>
       </c>
       <c r="E150" s="1" t="n">
         <v>0.07018657358347999</v>
@@ -30301,7 +30301,7 @@
         <v>0.001968161884976572</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>164.568</v>
+        <v>243.511</v>
       </c>
       <c r="E151" s="1" t="n">
         <v>0.06994866717354301</v>
@@ -30318,7 +30318,7 @@
         <v>0.001975109181191667</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>164.563</v>
+        <v>243.511</v>
       </c>
       <c r="E152" s="1" t="n">
         <v>0.06971624730426294</v>
@@ -30335,7 +30335,7 @@
         <v>0.001982019801408476</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>164.557</v>
+        <v>243.511</v>
       </c>
       <c r="E153" s="1" t="n">
         <v>0.06948600598764205</v>
@@ -30352,7 +30352,7 @@
         <v>0.001988786014753182</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>164.552</v>
+        <v>243.511</v>
       </c>
       <c r="E154" s="1" t="n">
         <v>0.0692535687888145</v>
@@ -30369,7 +30369,7 @@
         <v>0.001995328602121302</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>164.547</v>
+        <v>243.511</v>
       </c>
       <c r="E155" s="1" t="n">
         <v>0.0690165264330737</v>
@@ -30386,7 +30386,7 @@
         <v>0.002001682391485688</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>164.542</v>
+        <v>243.511</v>
       </c>
       <c r="E156" s="1" t="n">
         <v>0.06877616720064846</v>
@@ -30403,7 +30403,7 @@
         <v>0.002007910722588528</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>164.537</v>
+        <v>243.511</v>
       </c>
       <c r="E157" s="1" t="n">
         <v>0.06853471851876157</v>
@@ -30420,7 +30420,7 @@
         <v>0.002014076935172008</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>164.532</v>
+        <v>243.511</v>
       </c>
       <c r="E158" s="1" t="n">
         <v>0.06829434937854423</v>
@@ -30437,7 +30437,7 @@
         <v>0.002020226539476091</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>164.527</v>
+        <v>243.5112</v>
       </c>
       <c r="E159" s="1" t="n">
         <v>0.06805657161169748</v>
@@ -30454,7 +30454,7 @@
         <v>0.002026333727731821</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>164.522</v>
+        <v>243.5115</v>
       </c>
       <c r="E160" s="1" t="n">
         <v>0.06782047092812034</v>
@@ -30471,7 +30471,7 @@
         <v>0.002032354862668019</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>164.517</v>
+        <v>243.5118</v>
       </c>
       <c r="E161" s="1" t="n">
         <v>0.06758456365234446</v>
@@ -30488,7 +30488,7 @@
         <v>0.002038246307013504</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>164.512</v>
+        <v>243.512</v>
       </c>
       <c r="E162" s="1" t="n">
         <v>0.06734740403070419</v>
@@ -30505,7 +30505,7 @@
         <v>0.002043984623523161</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>164.507</v>
+        <v>243.512</v>
       </c>
       <c r="E163" s="1" t="n">
         <v>0.06710824623229301</v>
@@ -30522,7 +30522,7 @@
         <v>0.00204962717505614</v>
       </c>
       <c r="D164" s="1" t="n">
-        <v>164.502</v>
+        <v>243.512</v>
       </c>
       <c r="E164" s="1" t="n">
         <v>0.06686899934368876</v>
@@ -30539,7 +30539,7 @@
         <v>0.002055251524497656</v>
       </c>
       <c r="D165" s="1" t="n">
-        <v>164.497</v>
+        <v>243.512</v>
       </c>
       <c r="E165" s="1" t="n">
         <v>0.06663217947431646</v>
@@ -30556,7 +30556,7 @@
         <v>0.002060935234732921</v>
       </c>
       <c r="D166" s="1" t="n">
-        <v>164.493</v>
+        <v>243.512</v>
       </c>
       <c r="E166" s="1" t="n">
         <v>0.06639996105175112</v>
@@ -30573,7 +30573,7 @@
         <v>0.002066736533294453</v>
       </c>
       <c r="D167" s="1" t="n">
-        <v>164.488</v>
+        <v>243.5122</v>
       </c>
       <c r="E167" s="1" t="n">
         <v>0.0661746765660404</v>
@@ -30590,7 +30590,7 @@
         <v>0.002072636306303973</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>164.483</v>
+        <v>243.5125</v>
       </c>
       <c r="E168" s="1" t="n">
         <v>0.06595531483318721</v>
@@ -30607,7 +30607,7 @@
         <v>0.002078596104530505</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>164.478</v>
+        <v>243.5128</v>
       </c>
       <c r="E169" s="1" t="n">
         <v>0.06574055099377865</v>
@@ -30624,7 +30624,7 @@
         <v>0.00208457747874307</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>164.473</v>
+        <v>243.513</v>
       </c>
       <c r="E170" s="1" t="n">
         <v>0.06552909240048935</v>
@@ -30641,7 +30641,7 @@
         <v>0.002090553558184468</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>164.468</v>
+        <v>243.513</v>
       </c>
       <c r="E171" s="1" t="n">
         <v>0.06532003941520105</v>
@@ -30658,7 +30658,7 @@
         <v>0.002096543785992593</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>164.463</v>
+        <v>243.513</v>
       </c>
       <c r="E172" s="1" t="n">
         <v>0.06511395241349904</v>
@@ -30675,7 +30675,7 @@
         <v>0.002102579183779113</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>164.459</v>
+        <v>243.513</v>
       </c>
       <c r="E173" s="1" t="n">
         <v>0.06491146308099088</v>
@@ -30692,7 +30692,7 @@
         <v>0.002108690773155699</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>164.454</v>
+        <v>243.513</v>
       </c>
       <c r="E174" s="1" t="n">
         <v>0.06471400079436644</v>
@@ -30709,7 +30709,7 @@
         <v>0.002114886102030925</v>
       </c>
       <c r="D175" s="1" t="n">
-        <v>164.449</v>
+        <v>243.5132</v>
       </c>
       <c r="E175" s="1" t="n">
         <v>0.06452143797568857</v>
@@ -30726,7 +30726,7 @@
         <v>0.002121078823500985</v>
       </c>
       <c r="D176" s="1" t="n">
-        <v>164.444</v>
+        <v>243.5135</v>
       </c>
       <c r="E176" s="1" t="n">
         <v>0.06433106947369424</v>
@@ -30743,7 +30743,7 @@
         <v>0.002127159116958984</v>
       </c>
       <c r="D177" s="1" t="n">
-        <v>164.439</v>
+        <v>243.5138</v>
       </c>
       <c r="E177" s="1" t="n">
         <v>0.06413954540166739</v>
@@ -30760,7 +30760,7 @@
         <v>0.00213301716179802</v>
       </c>
       <c r="D178" s="1" t="n">
-        <v>164.435</v>
+        <v>243.514</v>
       </c>
       <c r="E178" s="1" t="n">
         <v>0.06394332476785552</v>
@@ -30777,7 +30777,7 @@
         <v>0.002138565696239664</v>
       </c>
       <c r="D179" s="1" t="n">
-        <v>164.43</v>
+        <v>243.514</v>
       </c>
       <c r="E179" s="1" t="n">
         <v>0.06374042138330177</v>
@@ -30794,7 +30794,7 @@
         <v>0.002143807693819359</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>164.425</v>
+        <v>243.514</v>
       </c>
       <c r="E180" s="1" t="n">
         <v>0.06353077310637087</v>
@@ -30811,7 +30811,7 @@
         <v>0.002148768686901016</v>
       </c>
       <c r="D181" s="1" t="n">
-        <v>164.421</v>
+        <v>243.514</v>
       </c>
       <c r="E181" s="1" t="n">
         <v>0.06331498121943306</v>
@@ -30828,7 +30828,7 @@
         <v>0.002153474207848548</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>164.416</v>
+        <v>243.514</v>
       </c>
       <c r="E182" s="1" t="n">
         <v>0.06309442659848397</v>
@@ -30845,7 +30845,7 @@
         <v>0.002157972926543238</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>164.412</v>
+        <v>243.5143</v>
       </c>
       <c r="E183" s="1" t="n">
         <v>0.06287008071645467</v>
@@ -30862,7 +30862,7 @@
         <v>0.002162406062935862</v>
       </c>
       <c r="D184" s="1" t="n">
-        <v>164.407</v>
+        <v>243.5145</v>
       </c>
       <c r="E184" s="1" t="n">
         <v>0.06264662334061398</v>
@@ -30879,7 +30879,7 @@
         <v>0.002166937974494568</v>
       </c>
       <c r="D185" s="1" t="n">
-        <v>164.403</v>
+        <v>243.5147</v>
       </c>
       <c r="E185" s="1" t="n">
         <v>0.06242825138601774</v>
@@ -30896,7 +30896,7 @@
         <v>0.002171733018687505</v>
       </c>
       <c r="D186" s="1" t="n">
-        <v>164.399</v>
+        <v>243.515</v>
       </c>
       <c r="E186" s="1" t="n">
         <v>0.06221984890078584</v>
@@ -30913,7 +30913,7 @@
         <v>0.002176901077804824</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>164.394</v>
+        <v>243.5152</v>
       </c>
       <c r="E187" s="1" t="n">
         <v>0.0620246425073574</v>
@@ -30930,7 +30930,7 @@
         <v>0.002182334133424685</v>
       </c>
       <c r="D188" s="1" t="n">
-        <v>164.39</v>
+        <v>243.5155</v>
       </c>
       <c r="E188" s="1" t="n">
         <v>0.06183883651045132</v>
@@ -30947,7 +30947,7 @@
         <v>0.002187869691947251</v>
       </c>
       <c r="D189" s="1" t="n">
-        <v>164.386</v>
+        <v>243.5157</v>
       </c>
       <c r="E189" s="1" t="n">
         <v>0.06165795507290891</v>
@@ -30964,7 +30964,7 @@
         <v>0.002193345259772684</v>
       </c>
       <c r="D190" s="1" t="n">
-        <v>164.382</v>
+        <v>243.516</v>
       </c>
       <c r="E190" s="1" t="n">
         <v>0.06147736350846496</v>
@@ -30981,7 +30981,7 @@
         <v>0.002198630832435984</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>164.377</v>
+        <v>243.5162</v>
       </c>
       <c r="E191" s="1" t="n">
         <v>0.06129369042552286</v>
@@ -30998,7 +30998,7 @@
         <v>0.002203726362011487</v>
       </c>
       <c r="D192" s="1" t="n">
-        <v>164.373</v>
+        <v>243.5165</v>
       </c>
       <c r="E192" s="1" t="n">
         <v>0.06110647198914575</v>
@@ -31015,7 +31015,7 @@
         <v>0.002208664289708364</v>
       </c>
       <c r="D193" s="1" t="n">
-        <v>164.369</v>
+        <v>243.5168</v>
       </c>
       <c r="E193" s="1" t="n">
         <v>0.06091691385045522</v>
@@ -31032,7 +31032,7 @@
         <v>0.002213477056735786</v>
       </c>
       <c r="D194" s="1" t="n">
-        <v>164.365</v>
+        <v>243.517</v>
       </c>
       <c r="E194" s="1" t="n">
         <v>0.0607259431401001</v>
@@ -31049,7 +31049,7 @@
         <v>0.002218185060532989</v>
       </c>
       <c r="D195" s="1" t="n">
-        <v>164.36</v>
+        <v>243.5172</v>
       </c>
       <c r="E195" s="1" t="n">
         <v>0.06053439323680806</v>
@@ -31066,7 +31066,7 @@
         <v>0.002222760523459464</v>
       </c>
       <c r="D196" s="1" t="n">
-        <v>164.356</v>
+        <v>243.5175</v>
       </c>
       <c r="E196" s="1" t="n">
         <v>0.06034101331060278</v>
@@ -31083,7 +31083,7 @@
         <v>0.002227163624104767</v>
       </c>
       <c r="D197" s="1" t="n">
-        <v>164.352</v>
+        <v>243.5178</v>
       </c>
       <c r="E197" s="1" t="n">
         <v>0.06014500781608029</v>
@@ -31100,7 +31100,7 @@
         <v>0.002231354541058451</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>164.348</v>
+        <v>243.518</v>
       </c>
       <c r="E198" s="1" t="n">
         <v>0.05994534774201475</v>
@@ -31117,7 +31117,7 @@
         <v>0.002235325085873816</v>
       </c>
       <c r="D199" s="1" t="n">
-        <v>164.344</v>
+        <v>243.5182</v>
       </c>
       <c r="E199" s="1" t="n">
         <v>0.05974187076292248</v>
@@ -31134,7 +31134,7 @@
         <v>0.002239193601959133</v>
       </c>
       <c r="D200" s="1" t="n">
-        <v>164.34</v>
+        <v>243.5185</v>
       </c>
       <c r="E200" s="1" t="n">
         <v>0.05953778223335349</v>
@@ -31151,7 +31151,7 @@
         <v>0.00224311006568642</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>164.335</v>
+        <v>243.5188</v>
       </c>
       <c r="E201" s="1" t="n">
         <v>0.05933730823316435</v>
@@ -31168,7 +31168,7 @@
         <v>0.002247224453427692</v>
       </c>
       <c r="D202" s="1" t="n">
-        <v>164.331</v>
+        <v>243.519</v>
       </c>
       <c r="E202" s="1" t="n">
         <v>0.05914384470982588</v>
@@ -31185,7 +31185,7 @@
         <v>0.002251631134770238</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>164.327</v>
+        <v>243.5192</v>
       </c>
       <c r="E203" s="1" t="n">
         <v>0.05896000278338819</v>
@@ -31202,7 +31202,7 @@
         <v>0.002256202052162433</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>164.323</v>
+        <v>243.5195</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0.05878230068974353</v>
@@ -31219,7 +31219,7 @@
         <v>0.002260753541267923</v>
       </c>
       <c r="D205" s="1" t="n">
-        <v>164.319</v>
+        <v>243.5198</v>
       </c>
       <c r="E205" s="1" t="n">
         <v>0.05860588492288851</v>
@@ -31236,7 +31236,7 @@
         <v>0.002265101937750358</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>164.314</v>
+        <v>243.52</v>
       </c>
       <c r="E206" s="1" t="n">
         <v>0.05842624439730312</v>
@@ -31253,7 +31253,7 @@
         <v>0.002269117332231759</v>
       </c>
       <c r="D207" s="1" t="n">
-        <v>164.31</v>
+        <v>243.5203</v>
       </c>
       <c r="E207" s="1" t="n">
         <v>0.05823960426362389</v>
@@ -31270,7 +31270,7 @@
         <v>0.002272884835167656</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>164.306</v>
+        <v>243.5205</v>
       </c>
       <c r="E208" s="1" t="n">
         <v>0.05804848449286561</v>
@@ -31287,7 +31287,7 @@
         <v>0.002276543311971955</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>164.302</v>
+        <v>243.5207</v>
       </c>
       <c r="E209" s="1" t="n">
         <v>0.05785648011938557</v>
@@ -31304,7 +31304,7 @@
         <v>0.00228023162805856</v>
       </c>
       <c r="D210" s="1" t="n">
-        <v>164.297</v>
+        <v>243.521</v>
       </c>
       <c r="E210" s="1" t="n">
         <v>0.05766735841838327</v>
@@ -31321,7 +31321,7 @@
         <v>0.002284048575570907</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>164.293</v>
+        <v>243.5212</v>
       </c>
       <c r="E211" s="1" t="n">
         <v>0.05748308133949132</v>
@@ -31338,7 +31338,7 @@
         <v>0.002287932653570548</v>
       </c>
       <c r="D212" s="1" t="n">
-        <v>164.289</v>
+        <v>243.5215</v>
       </c>
       <c r="E212" s="1" t="n">
         <v>0.05730227791930999</v>
@@ -31355,7 +31355,7 @@
         <v>0.002291782287848565</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>164.285</v>
+        <v>243.5217</v>
       </c>
       <c r="E213" s="1" t="n">
         <v>0.05712236617602257</v>
@@ -31372,7 +31372,7 @@
         <v>0.002295495904196042</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>164.281</v>
+        <v>243.522</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0.05694081361178396</v>
@@ -31389,7 +31389,7 @@
         <v>0.002299004864902178</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>164.277</v>
+        <v>243.5222</v>
       </c>
       <c r="E215" s="1" t="n">
         <v>0.05675594913816879</v>
@@ -31406,7 +31406,7 @@
         <v>0.002302372278248647</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>164.273</v>
+        <v>243.5225</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0.05656937038733476</v>
@@ -31423,7 +31423,7 @@
         <v>0.002305694189015241</v>
       </c>
       <c r="D217" s="1" t="n">
-        <v>164.27</v>
+        <v>243.5228</v>
       </c>
       <c r="E217" s="1" t="n">
         <v>0.05638321311314566</v>
@@ -31440,7 +31440,7 @@
         <v>0.002309066641981755</v>
       </c>
       <c r="D218" s="1" t="n">
-        <v>164.266</v>
+        <v>243.523</v>
       </c>
       <c r="E218" s="1" t="n">
         <v>0.05620028059415675</v>
@@ -31457,7 +31457,7 @@
         <v>0.00231255639534559</v>
       </c>
       <c r="D219" s="1" t="n">
-        <v>164.262</v>
+        <v>243.5232</v>
       </c>
       <c r="E219" s="1" t="n">
         <v>0.05602191014562068</v>
@@ -31474,7 +31474,7 @@
         <v>0.002316113060974595</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>164.258</v>
+        <v>243.5235</v>
       </c>
       <c r="E220" s="1" t="n">
         <v>0.05584682298218582</v>
@@ -31491,7 +31491,7 @@
         <v>0.002319656964154227</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>164.255</v>
+        <v>243.5238</v>
       </c>
       <c r="E221" s="1" t="n">
         <v>0.05567282698254609</v>
@@ -31508,7 +31508,7 @@
         <v>0.002323108430169946</v>
       </c>
       <c r="D222" s="1" t="n">
-        <v>164.251</v>
+        <v>243.524</v>
       </c>
       <c r="E222" s="1" t="n">
         <v>0.05549846934028149</v>
@@ -31525,7 +31525,7 @@
         <v>0.002326425379775902</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>164.247</v>
+        <v>243.5242</v>
       </c>
       <c r="E223" s="1" t="n">
         <v>0.0553225226661764</v>
@@ -31542,7 +31542,7 @@
         <v>0.002329716115601015</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>164.244</v>
+        <v>243.5245</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>0.05514734038644178</v>
@@ -31559,7 +31559,7 @@
         <v>0.002333126535742898</v>
       </c>
       <c r="D225" s="1" t="n">
-        <v>164.24</v>
+        <v>243.5248</v>
       </c>
       <c r="E225" s="1" t="n">
         <v>0.05497681133509232</v>
@@ -31576,7 +31576,7 @@
         <v>0.002336802538299164</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>164.237</v>
+        <v>243.525</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0.05481383444554529</v>
@@ -31593,7 +31593,7 @@
         <v>0.00234082833310125</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>164.233</v>
+        <v>243.5252</v>
       </c>
       <c r="E227" s="1" t="n">
         <v>0.05466073252972457</v>
@@ -31610,7 +31610,7 @@
         <v>0.002345041376915894</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>164.23</v>
+        <v>243.5255</v>
       </c>
       <c r="E228" s="1" t="n">
         <v>0.05451313662523762</v>
@@ -31627,7 +31627,7 @@
         <v>0.00234921743824366</v>
       </c>
       <c r="D229" s="1" t="n">
-        <v>164.227</v>
+        <v>243.5258</v>
       </c>
       <c r="E229" s="1" t="n">
         <v>0.05436601107339335</v>
@@ -31644,7 +31644,7 @@
         <v>0.002353132285585111</v>
       </c>
       <c r="D230" s="1" t="n">
-        <v>164.224</v>
+        <v>243.526</v>
       </c>
       <c r="E230" s="1" t="n">
         <v>0.05421418343801334</v>
@@ -31661,7 +31661,7 @@
         <v>0.002356629775254825</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>164.22</v>
+        <v>243.5263</v>
       </c>
       <c r="E231" s="1" t="n">
         <v>0.05405436208747426</v>
@@ -31678,7 +31678,7 @@
         <v>0.002359826114823439</v>
       </c>
       <c r="D232" s="1" t="n">
-        <v>164.217</v>
+        <v>243.5265</v>
       </c>
       <c r="E232" s="1" t="n">
         <v>0.05388885404318669</v>
@@ -31695,7 +31695,7 @@
         <v>0.002362905599675604</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>164.214</v>
+        <v>243.5267</v>
       </c>
       <c r="E233" s="1" t="n">
         <v>0.05372214930507026</v>
@@ -31712,7 +31712,7 @@
         <v>0.002366052525195971</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>164.211</v>
+        <v>243.527</v>
       </c>
       <c r="E234" s="1" t="n">
         <v>0.05355843526598324</v>
@@ -31729,7 +31729,7 @@
         <v>0.00236940104541944</v>
       </c>
       <c r="D235" s="1" t="n">
-        <v>164.208</v>
+        <v>243.5272</v>
       </c>
       <c r="E235" s="1" t="n">
         <v>0.05340069631876838</v>
@@ -31746,7 +31746,7 @@
         <v>0.002372884748981894</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>164.205</v>
+        <v>243.5275</v>
       </c>
       <c r="E236" s="1" t="n">
         <v>0.05324736443251123</v>
@@ -31763,7 +31763,7 @@
         <v>0.002376387083169464</v>
       </c>
       <c r="D237" s="1" t="n">
-        <v>164.202</v>
+        <v>243.5277</v>
       </c>
       <c r="E237" s="1" t="n">
         <v>0.05309577834186136</v>
@@ -31780,7 +31780,7 @@
         <v>0.002379791495268283</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>164.199</v>
+        <v>243.528</v>
       </c>
       <c r="E238" s="1" t="n">
         <v>0.05294332253446389</v>
@@ -31797,7 +31797,7 @@
         <v>0.002383016125132892</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>164.196</v>
+        <v>243.5282</v>
       </c>
       <c r="E239" s="1" t="n">
         <v>0.05278819477339353</v>
@@ -31814,7 +31814,7 @@
         <v>0.00238611788289149</v>
       </c>
       <c r="D240" s="1" t="n">
-        <v>164.193</v>
+        <v>243.5285</v>
       </c>
       <c r="E240" s="1" t="n">
         <v>0.05263168445690758</v>
@@ -31831,7 +31831,7 @@
         <v>0.002389188371240681</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>164.19</v>
+        <v>243.5288</v>
       </c>
       <c r="E241" s="1" t="n">
         <v>0.05247582108219135</v>
@@ -31848,7 +31848,7 @@
         <v>0.002392319192877076</v>
       </c>
       <c r="D242" s="1" t="n">
-        <v>164.187</v>
+        <v>243.529</v>
       </c>
       <c r="E242" s="1" t="n">
         <v>0.05232259984930951</v>
@@ -31865,7 +31865,7 @@
         <v>0.002395573604809415</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>164.184</v>
+        <v>243.5292</v>
       </c>
       <c r="E243" s="1" t="n">
         <v>0.0521733650420622</v>
@@ -31882,7 +31882,7 @@
         <v>0.002398901481294975</v>
       </c>
       <c r="D244" s="1" t="n">
-        <v>164.181</v>
+        <v>243.5295</v>
       </c>
       <c r="E244" s="1" t="n">
         <v>0.05202697939410761</v>
@@ -31899,7 +31899,7 @@
         <v>0.002402224350903167</v>
       </c>
       <c r="D245" s="1" t="n">
-        <v>164.178</v>
+        <v>243.5298</v>
       </c>
       <c r="E245" s="1" t="n">
         <v>0.05188171242607691</v>
@@ -31916,7 +31916,7 @@
         <v>0.002405463742203402</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>164.175</v>
+        <v>243.53</v>
       </c>
       <c r="E246" s="1" t="n">
         <v>0.05173586241471949</v>
@@ -31933,7 +31933,7 @@
         <v>0.002408559240228179</v>
       </c>
       <c r="D247" s="1" t="n">
-        <v>164.172</v>
+        <v>243.5302</v>
       </c>
       <c r="E247" s="1" t="n">
         <v>0.05158814254177434</v>
@@ -31950,7 +31950,7 @@
         <v>0.002411522655862361</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>164.169</v>
+        <v>243.5305</v>
       </c>
       <c r="E248" s="1" t="n">
         <v>0.05143882780250349</v>
@@ -31967,7 +31967,7 @@
         <v>0.002414383856453898</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>164.166</v>
+        <v>243.5308</v>
       </c>
       <c r="E249" s="1" t="n">
         <v>0.05128857225022866</v>
@@ -31984,7 +31984,7 @@
         <v>0.002417172709350743</v>
       </c>
       <c r="D250" s="1" t="n">
-        <v>164.164</v>
+        <v>243.531</v>
       </c>
       <c r="E250" s="1" t="n">
         <v>0.05113780408764111</v>
@@ -32001,7 +32001,7 @@
         <v>0.00241992900101967</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>164.161</v>
+        <v>243.5312</v>
       </c>
       <c r="E251" s="1" t="n">
         <v>0.05098779615105785</v>
@@ -32018,7 +32018,7 @@
         <v>0.002422732194402755</v>
       </c>
       <c r="D252" s="1" t="n">
-        <v>164.158</v>
+        <v>243.5315</v>
       </c>
       <c r="E252" s="1" t="n">
         <v>0.05083999347982419</v>
@@ -32035,7 +32035,7 @@
         <v>0.002425671671560896</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>164.155</v>
+        <v>243.5318</v>
       </c>
       <c r="E253" s="1" t="n">
         <v>0.05069623740051465</v>
@@ -32052,7 +32052,7 @@
         <v>0.002428836814554991</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>164.153</v>
+        <v>243.532</v>
       </c>
       <c r="E254" s="1" t="n">
         <v>0.05055812690361336</v>
@@ -32069,7 +32069,7 @@
         <v>0.002432276270978178</v>
       </c>
       <c r="D255" s="1" t="n">
-        <v>164.15</v>
+        <v>243.5323</v>
       </c>
       <c r="E255" s="1" t="n">
         <v>0.05042702618328389</v>
@@ -32086,7 +32086,7 @@
         <v>0.002435875750552536</v>
       </c>
       <c r="D256" s="1" t="n">
-        <v>164.148</v>
+        <v>243.5325</v>
       </c>
       <c r="E256" s="1" t="n">
         <v>0.05030006886962563</v>
@@ -32103,7 +32103,7 @@
         <v>0.002439480228532388</v>
       </c>
       <c r="D257" s="1" t="n">
-        <v>164.145</v>
+        <v>243.5327</v>
       </c>
       <c r="E257" s="1" t="n">
         <v>0.05017443834842027</v>
@@ -32120,7 +32120,7 @@
         <v>0.002442934680172049</v>
       </c>
       <c r="D258" s="1" t="n">
-        <v>164.143</v>
+        <v>243.533</v>
       </c>
       <c r="E258" s="1" t="n">
         <v>0.05004652270049628</v>
@@ -32137,7 +32137,7 @@
         <v>0.002446124769378371</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>164.14</v>
+        <v>243.5332</v>
       </c>
       <c r="E259" s="1" t="n">
         <v>0.04991443504061856</v>
@@ -32154,7 +32154,7 @@
         <v>0.002449098914668323</v>
       </c>
       <c r="D260" s="1" t="n">
-        <v>164.138</v>
+        <v>243.5335</v>
       </c>
       <c r="E260" s="1" t="n">
         <v>0.0497787904746884</v>
@@ -32171,7 +32171,7 @@
         <v>0.002451946223211407</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>164.135</v>
+        <v>243.5337</v>
       </c>
       <c r="E261" s="1" t="n">
         <v>0.04964185178516733</v>
@@ -32188,7 +32188,7 @@
         <v>0.002454755802177124</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>164.133</v>
+        <v>243.534</v>
       </c>
       <c r="E262" s="1" t="n">
         <v>0.04950501518215963</v>
@@ -32205,7 +32205,7 @@
         <v>0.002457612676435201</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>164.13</v>
+        <v>243.5342</v>
       </c>
       <c r="E263" s="1" t="n">
         <v>0.04937040226445663</v>
@@ -32222,7 +32222,7 @@
         <v>0.002460585541656275</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>164.128</v>
+        <v>243.5345</v>
       </c>
       <c r="E264" s="1" t="n">
         <v>0.04923894822745042</v>
@@ -32239,7 +32239,7 @@
         <v>0.002463739011211209</v>
       </c>
       <c r="D265" s="1" t="n">
-        <v>164.125</v>
+        <v>243.5348</v>
       </c>
       <c r="E265" s="1" t="n">
         <v>0.04911231711650424</v>
@@ -32256,7 +32256,7 @@
         <v>0.002467137698470864</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>164.123</v>
+        <v>243.535</v>
       </c>
       <c r="E266" s="1" t="n">
         <v>0.04899132496780554</v>
@@ -32273,7 +32273,7 @@
         <v>0.002470802580736493</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>164.12</v>
+        <v>243.5352</v>
       </c>
       <c r="E267" s="1" t="n">
         <v>0.04887673255766622</v>
@@ -32290,7 +32290,7 @@
         <v>0.002474580091030905</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>164.118</v>
+        <v>243.5355</v>
       </c>
       <c r="E268" s="1" t="n">
         <v>0.04876503102186772</v>
@@ -32307,7 +32307,7 @@
         <v>0.002478273026307293</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>164.115</v>
+        <v>243.5358</v>
       </c>
       <c r="E269" s="1" t="n">
         <v>0.0486527245827438</v>
@@ -32324,7 +32324,7 @@
         <v>0.002481684183518854</v>
       </c>
       <c r="D270" s="1" t="n">
-        <v>164.113</v>
+        <v>243.536</v>
       </c>
       <c r="E270" s="1" t="n">
         <v>0.04853555563411324</v>
@@ -32341,7 +32341,7 @@
         <v>0.002484690366743772</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>164.11</v>
+        <v>243.5362</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0.04841158537941274</v>
@@ -32358,7 +32358,7 @@
         <v>0.002487464408560187</v>
       </c>
       <c r="D272" s="1" t="n">
-        <v>164.108</v>
+        <v>243.5365</v>
       </c>
       <c r="E272" s="1" t="n">
         <v>0.04828383943556482</v>
@@ -32375,7 +32375,7 @@
         <v>0.002490253148671224</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>164.105</v>
+        <v>243.5368</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>0.04815753821008842</v>
@@ -32392,7 +32392,7 @@
         <v>0.002493303426780009</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>164.103</v>
+        <v>243.537</v>
       </c>
       <c r="E274" s="1" t="n">
         <v>0.0480370176579896</v>
@@ -32409,7 +32409,7 @@
         <v>0.00249677967486558</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>164.101</v>
+        <v>243.5373</v>
       </c>
       <c r="E275" s="1" t="n">
         <v>0.04792557063592997</v>
@@ -32426,7 +32426,7 @@
         <v>0.002500516694010608</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>164.098</v>
+        <v>243.5375</v>
       </c>
       <c r="E276" s="1" t="n">
         <v>0.04782013852042883</v>
@@ -32443,7 +32443,7 @@
         <v>0.002504266877573674</v>
       </c>
       <c r="D277" s="1" t="n">
-        <v>164.096</v>
+        <v>243.5378</v>
       </c>
       <c r="E277" s="1" t="n">
         <v>0.04771553632803509</v>
@@ -32460,7 +32460,7 @@
         <v>0.002507782618913359</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>164.094</v>
+        <v>243.538</v>
       </c>
       <c r="E278" s="1" t="n">
         <v>0.04760725386940356</v>
@@ -32477,7 +32477,7 @@
         <v>0.002510883024321127</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>164.091</v>
+        <v>243.5383</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0.04749210985543035</v>
@@ -32494,7 +32494,7 @@
         <v>0.002513654051819962</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>164.089</v>
+        <v>243.5385</v>
       </c>
       <c r="E280" s="1" t="n">
         <v>0.04737140106177624</v>
@@ -32511,7 +32511,7 @@
         <v>0.002516248372365732</v>
       </c>
       <c r="D281" s="1" t="n">
-        <v>164.087</v>
+        <v>243.5387</v>
       </c>
       <c r="E281" s="1" t="n">
         <v>0.0472482529602919</v>
@@ -32528,7 +32528,7 @@
         <v>0.002518818656914302</v>
       </c>
       <c r="D282" s="1" t="n">
-        <v>164.085</v>
+        <v>243.539</v>
       </c>
       <c r="E282" s="1" t="n">
         <v>0.04712554836144092</v>
@@ -32545,7 +32545,7 @@
         <v>0.002521486118649736</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>164.082</v>
+        <v>243.5392</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0.04700573994816104</v>
@@ -32562,7 +32562,7 @@
         <v>0.002524246139668868</v>
       </c>
       <c r="D284" s="1" t="n">
-        <v>164.08</v>
+        <v>243.5395</v>
       </c>
       <c r="E284" s="1" t="n">
         <v>0.04688831669380352</v>
@@ -32579,7 +32579,7 @@
         <v>0.002527062644296725</v>
       </c>
       <c r="D285" s="1" t="n">
-        <v>164.078</v>
+        <v>243.5397</v>
       </c>
       <c r="E285" s="1" t="n">
         <v>0.04677278149109811</v>
@@ -32596,7 +32596,7 @@
         <v>0.002529899556858338</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>164.075</v>
+        <v>243.54</v>
       </c>
       <c r="E286" s="1" t="n">
         <v>0.04665864518688558</v>
@@ -32613,7 +32613,7 @@
         <v>0.002532725244339933</v>
       </c>
       <c r="D287" s="1" t="n">
-        <v>164.073</v>
+        <v>243.5402</v>
       </c>
       <c r="E287" s="1" t="n">
         <v>0.04654492037245717</v>
@@ -32630,7 +32630,7 @@
         <v>0.00253552584437254</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>164.071</v>
+        <v>243.5405</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0.04643154358355026</v>
@@ -32647,7 +32647,7 @@
         <v>0.002538291937248384</v>
       </c>
       <c r="D289" s="1" t="n">
-        <v>164.068</v>
+        <v>243.5408</v>
       </c>
       <c r="E289" s="1" t="n">
         <v>0.04631853419056781</v>
@@ -32664,7 +32664,7 @@
         <v>0.002541014103259693</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>164.066</v>
+        <v>243.541</v>
       </c>
       <c r="E290" s="1" t="n">
         <v>0.04620532867471523</v>
@@ -32681,7 +32681,7 @@
         <v>0.002543692228776573</v>
       </c>
       <c r="D291" s="1" t="n">
-        <v>164.064</v>
+        <v>243.5412</v>
       </c>
       <c r="E291" s="1" t="n">
         <v>0.04609212039956135</v>
@@ -32698,7 +32698,7 @@
         <v>0.002546363424480635</v>
       </c>
       <c r="D292" s="1" t="n">
-        <v>164.062</v>
+        <v>243.5415</v>
       </c>
       <c r="E292" s="1" t="n">
         <v>0.04597957948003637</v>
@@ -32715,7 +32715,7 @@
         <v>0.002549074107131369</v>
       </c>
       <c r="D293" s="1" t="n">
-        <v>164.059</v>
+        <v>243.5418</v>
       </c>
       <c r="E293" s="1" t="n">
         <v>0.04586872724392396</v>
@@ -32732,7 +32732,7 @@
         <v>0.002551870693488263</v>
       </c>
       <c r="D294" s="1" t="n">
-        <v>164.057</v>
+        <v>243.542</v>
       </c>
       <c r="E294" s="1" t="n">
         <v>0.04575999386372017</v>
@@ -32749,7 +32749,7 @@
         <v>0.002554784044390916</v>
       </c>
       <c r="D295" s="1" t="n">
-        <v>164.055</v>
+        <v>243.5422</v>
       </c>
       <c r="E295" s="1" t="n">
         <v>0.04565410039900038</v>
@@ -32766,7 +32766,7 @@
         <v>0.002557782796999358</v>
       </c>
       <c r="D296" s="1" t="n">
-        <v>164.053</v>
+        <v>243.5425</v>
       </c>
       <c r="E296" s="1" t="n">
         <v>0.04555045899647557</v>
@@ -32783,7 +32783,7 @@
         <v>0.002560820032553728</v>
       </c>
       <c r="D297" s="1" t="n">
-        <v>164.051</v>
+        <v>243.5428</v>
       </c>
       <c r="E297" s="1" t="n">
         <v>0.04544821378551758</v>
@@ -32800,7 +32800,7 @@
         <v>0.002563848832294164</v>
       </c>
       <c r="D298" s="1" t="n">
-        <v>164.048</v>
+        <v>243.543</v>
       </c>
       <c r="E298" s="1" t="n">
         <v>0.04534671147791106</v>
@@ -32817,7 +32817,7 @@
         <v>0.002566835940862289</v>
       </c>
       <c r="D299" s="1" t="n">
-        <v>164.046</v>
+        <v>243.5433</v>
       </c>
       <c r="E299" s="1" t="n">
         <v>0.04524497803756976</v>
@@ -32834,7 +32834,7 @@
         <v>0.002569802756505658</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>164.044</v>
+        <v>243.5435</v>
       </c>
       <c r="E300" s="1" t="n">
         <v>0.04514358106673132</v>
@@ -32851,7 +32851,7 @@
         <v>0.002572784340873312</v>
       </c>
       <c r="D301" s="1" t="n">
-        <v>164.042</v>
+        <v>243.5438</v>
       </c>
       <c r="E301" s="1" t="n">
         <v>0.04504313097802874</v>
@@ -32868,7 +32868,7 @@
         <v>0.002575815755614292</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>164.04</v>
+        <v>243.544</v>
       </c>
       <c r="E302" s="1" t="n">
         <v>0.04494422995587797</v>
@@ -32885,7 +32885,7 @@
         <v>0.002578910488888114</v>
       </c>
       <c r="D303" s="1" t="n">
-        <v>164.038</v>
+        <v>243.5443</v>
       </c>
       <c r="E303" s="1" t="n">
         <v>0.0448470969333271</v>
@@ -32902,7 +32902,7 @@
         <v>0.002581995734896212</v>
       </c>
       <c r="D304" s="1" t="n">
-        <v>164.036</v>
+        <v>243.5445</v>
       </c>
       <c r="E304" s="1" t="n">
         <v>0.04475045228903878</v>
@@ -32919,7 +32919,7 @@
         <v>0.002584977114350495</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>164.034</v>
+        <v>243.5447</v>
       </c>
       <c r="E305" s="1" t="n">
         <v>0.04465266081949579</v>
@@ -32936,7 +32936,7 @@
         <v>0.002587760247962873</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>164.032</v>
+        <v>243.545</v>
       </c>
       <c r="E306" s="1" t="n">
         <v>0.04455210906917189</v>
@@ -32953,7 +32953,7 @@
         <v>0.002590286936673096</v>
       </c>
       <c r="D307" s="1" t="n">
-        <v>164.03</v>
+        <v>243.5452</v>
       </c>
       <c r="E307" s="1" t="n">
         <v>0.04444782580105264</v>
@@ -32970,7 +32970,7 @@
         <v>0.002592643702332273</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>164.029</v>
+        <v>243.5455</v>
       </c>
       <c r="E308" s="1" t="n">
         <v>0.04434114106403567</v>
@@ -32987,7 +32987,7 @@
         <v>0.002594953247019354</v>
       </c>
       <c r="D309" s="1" t="n">
-        <v>164.027</v>
+        <v>243.5457</v>
       </c>
       <c r="E309" s="1" t="n">
         <v>0.04423454213449209</v>
@@ -33004,7 +33004,7 @@
         <v>0.002597338272813285</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>164.025</v>
+        <v>243.546</v>
       </c>
       <c r="E310" s="1" t="n">
         <v>0.04412992763816211</v>
@@ -33021,7 +33021,7 @@
         <v>0.002599892614548459</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>164.023</v>
+        <v>243.5462</v>
       </c>
       <c r="E311" s="1" t="n">
         <v>0.04402886716991383</v>
@@ -33038,7 +33038,7 @@
         <v>0.00260259463808105</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>164.021</v>
+        <v>243.5465</v>
       </c>
       <c r="E312" s="1" t="n">
         <v>0.04393096078115136</v>
@@ -33055,7 +33055,7 @@
         <v>0.002605393842022673</v>
       </c>
       <c r="D313" s="1" t="n">
-        <v>164.019</v>
+        <v>243.5468</v>
       </c>
       <c r="E313" s="1" t="n">
         <v>0.0438353280353798</v>
@@ -33072,7 +33072,7 @@
         <v>0.002608239724984948</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>164.017</v>
+        <v>243.547</v>
       </c>
       <c r="E314" s="1" t="n">
         <v>0.04374109990182199</v>
@@ -33089,7 +33089,7 @@
         <v>0.002611090627059857</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>164.015</v>
+        <v>243.5472</v>
       </c>
       <c r="E315" s="1" t="n">
         <v>0.04364756636699312</v>
@@ -33106,7 +33106,7 @@
         <v>0.002613940254260855</v>
       </c>
       <c r="D316" s="1" t="n">
-        <v>164.013</v>
+        <v>243.5475</v>
       </c>
       <c r="E316" s="1" t="n">
         <v>0.04355461583794608</v>
@@ -33123,7 +33123,7 @@
         <v>0.002616791154081766</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>164.012</v>
+        <v>243.5478</v>
       </c>
       <c r="E317" s="1" t="n">
         <v>0.04346210201949714</v>
@@ -33140,7 +33140,7 @@
         <v>0.002619645874016409</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>164.01</v>
+        <v>243.548</v>
       </c>
       <c r="E318" s="1" t="n">
         <v>0.04337042747839819</v>
@@ -33157,7 +33157,7 @@
         <v>0.002622512905061223</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>164.008</v>
+        <v>243.5482</v>
       </c>
       <c r="E319" s="1" t="n">
         <v>0.04327954268787869</v>
@@ -33174,7 +33174,7 @@
         <v>0.002625424512223105</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>164.005</v>
+        <v>243.5485</v>
       </c>
       <c r="E320" s="1" t="n">
         <v>0.0431901527294298</v>
@@ -33191,7 +33191,7 @@
         <v>0.002628418904011567</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>164.003</v>
+        <v>243.5488</v>
       </c>
       <c r="E321" s="1" t="n">
         <v>0.04310250763246569</v>
@@ -33208,7 +33208,7 @@
         <v>0.002631534288936124</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>164.001</v>
+        <v>243.549</v>
       </c>
       <c r="E322" s="1" t="n">
         <v>0.04301739594297883</v>
@@ -33225,7 +33225,7 @@
         <v>0.002634784846871753</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>164</v>
+        <v>243.5493</v>
       </c>
       <c r="E323" s="1" t="n">
         <v>0.04293484403144383</v>
@@ -33242,7 +33242,7 @@
         <v>0.002638088643155306</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>163.998</v>
+        <v>243.5495</v>
       </c>
       <c r="E324" s="1" t="n">
         <v>0.04285385700604676</v>
@@ -33259,7 +33259,7 @@
         <v>0.002641339714489095</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>163.996</v>
+        <v>243.5498</v>
       </c>
       <c r="E325" s="1" t="n">
         <v>0.04277252484209025</v>
@@ -33276,7 +33276,7 @@
         <v>0.002644432097575436</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>163.995</v>
+        <v>243.55</v>
       </c>
       <c r="E326" s="1" t="n">
         <v>0.04268896044537206</v>
@@ -33293,7 +33293,7 @@
         <v>0.00264729707707867</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>163.993</v>
+        <v>243.5503</v>
       </c>
       <c r="E327" s="1" t="n">
         <v>0.04260243694910931</v>
@@ -33310,7 +33310,7 @@
         <v>0.002650014929511228</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>163.991</v>
+        <v>243.5505</v>
       </c>
       <c r="E328" s="1" t="n">
         <v>0.04251409129184186</v>
@@ -33327,7 +33327,7 @@
         <v>0.00265270317934757</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>163.99</v>
+        <v>243.5507</v>
       </c>
       <c r="E329" s="1" t="n">
         <v>0.04242564132254642</v>
@@ -33344,7 +33344,7 @@
         <v>0.002655479351062153</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>163.988</v>
+        <v>243.551</v>
       </c>
       <c r="E330" s="1" t="n">
         <v>0.0423393178069956</v>
@@ -33361,7 +33361,7 @@
         <v>0.002658428708915467</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>163.987</v>
+        <v>243.551</v>
       </c>
       <c r="E331" s="1" t="n">
         <v>0.04225610116866424</v>
@@ -33378,7 +33378,7 @@
         <v>0.002661507476312136</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>163.985</v>
+        <v>243.551</v>
       </c>
       <c r="E332" s="1" t="n">
         <v>0.04217562372339787</v>
@@ -33395,7 +33395,7 @@
         <v>0.002664639616442814</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>163.984</v>
+        <v>243.551</v>
       </c>
       <c r="E333" s="1" t="n">
         <v>0.04209630525983715</v>
@@ -33412,7 +33412,7 @@
         <v>0.002667749092498159</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>163.982</v>
+        <v>243.551</v>
       </c>
       <c r="E334" s="1" t="n">
         <v>0.04201729082274133</v>
@@ -33429,7 +33429,7 @@
         <v>0.00267078366668017</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>163.98</v>
+        <v>243.5512</v>
       </c>
       <c r="E335" s="1" t="n">
         <v>0.04193758140939358</v>
@@ -33446,7 +33446,7 @@
         <v>0.002673786297236219</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>163.979</v>
+        <v>243.5515</v>
       </c>
       <c r="E336" s="1" t="n">
         <v>0.04185767956343576</v>
@@ -33463,7 +33463,7 @@
         <v>0.002676823741425023</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>163.977</v>
+        <v>243.5517</v>
       </c>
       <c r="E337" s="1" t="n">
         <v>0.04177898018199667</v>
@@ -33480,7 +33480,7 @@
         <v>0.0026799627565053</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>163.975</v>
+        <v>243.552</v>
       </c>
       <c r="E338" s="1" t="n">
         <v>0.0417023362184622</v>
@@ -33497,7 +33497,7 @@
         <v>0.00268323748076434</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>163.974</v>
+        <v>243.5522</v>
       </c>
       <c r="E339" s="1" t="n">
         <v>0.04162808353460793</v>
@@ -33514,7 +33514,7 @@
         <v>0.002686551576603729</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>163.972</v>
+        <v>243.5525</v>
       </c>
       <c r="E340" s="1" t="n">
         <v>0.04155505987626922</v>
@@ -33531,7 +33531,7 @@
         <v>0.002689776087453629</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>163.97</v>
+        <v>243.5528</v>
       </c>
       <c r="E341" s="1" t="n">
         <v>0.04148109148824371</v>
@@ -33548,7 +33548,7 @@
         <v>0.0026927820567442</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>163.968</v>
+        <v>243.553</v>
       </c>
       <c r="E342" s="1" t="n">
         <v>0.04140420393524109</v>
@@ -33565,7 +33565,7 @@
         <v>0.002695485344366245</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>163.966</v>
+        <v>243.5532</v>
       </c>
       <c r="E343" s="1" t="n">
         <v>0.04132313320947383</v>
@@ -33582,7 +33582,7 @@
         <v>0.002697981076053135</v>
       </c>
       <c r="D344" s="1" t="n">
-        <v>163.964</v>
+        <v>243.5535</v>
       </c>
       <c r="E344" s="1" t="n">
         <v>0.0412393703453792</v>
@@ -33599,7 +33599,7 @@
         <v>0.002700409193998884</v>
       </c>
       <c r="D345" s="1" t="n">
-        <v>163.962</v>
+        <v>243.5538</v>
       </c>
       <c r="E345" s="1" t="n">
         <v>0.04115507184963291</v>
@@ -33616,7 +33616,7 @@
         <v>0.002702909640397504</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>163.96</v>
+        <v>243.554</v>
       </c>
       <c r="E346" s="1" t="n">
         <v>0.0410723689298793</v>
@@ -33633,7 +33633,7 @@
         <v>0.002705596627527859</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>163.958</v>
+        <v>243.554</v>
       </c>
       <c r="E347" s="1" t="n">
         <v>0.0409929780271454</v>
@@ -33650,7 +33650,7 @@
         <v>0.002708481448008219</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>163.957</v>
+        <v>243.554</v>
       </c>
       <c r="E348" s="1" t="n">
         <v>0.04091686845128338</v>
@@ -33667,7 +33667,7 @@
         <v>0.002711549664541707</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>163.955</v>
+        <v>243.554</v>
       </c>
       <c r="E349" s="1" t="n">
         <v>0.04084413751790485</v>
@@ -33684,7 +33684,7 @@
         <v>0.002714786839831445</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>163.953</v>
+        <v>243.554</v>
       </c>
       <c r="E350" s="1" t="n">
         <v>0.04077436787362581</v>
@@ -33701,7 +33701,7 @@
         <v>0.002718161811461362</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>163.952</v>
+        <v>243.5542</v>
       </c>
       <c r="E351" s="1" t="n">
         <v>0.04070689571953433</v>
@@ -33718,7 +33718,7 @@
         <v>0.002721576516538622</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>163.951</v>
+        <v>243.5545</v>
       </c>
       <c r="E352" s="1" t="n">
         <v>0.04064040733030442</v>
@@ -33735,7 +33735,7 @@
         <v>0.002724916167051194</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>163.949</v>
+        <v>243.5548</v>
       </c>
       <c r="E353" s="1" t="n">
         <v>0.04057335591310763</v>
@@ -33752,7 +33752,7 @@
         <v>0.002728065974987051</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>163.948</v>
+        <v>243.555</v>
       </c>
       <c r="E354" s="1" t="n">
         <v>0.04050370150509663</v>
@@ -33769,7 +33769,7 @@
         <v>0.002730949457716863</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>163.946</v>
+        <v>243.5553</v>
       </c>
       <c r="E355" s="1" t="n">
         <v>0.04043067409481046</v>
@@ -33786,7 +33786,7 @@
         <v>0.002733643354142108</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>163.945</v>
+        <v>243.5555</v>
       </c>
       <c r="E356" s="1" t="n">
         <v>0.04035509599984082</v>
@@ -33803,7 +33803,7 @@
         <v>0.002736262708546968</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>163.944</v>
+        <v>243.5558</v>
       </c>
       <c r="E357" s="1" t="n">
         <v>0.04027885159717454</v>
@@ -33820,7 +33820,7 @@
         <v>0.00273892256521562</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>163.943</v>
+        <v>243.556</v>
       </c>
       <c r="E358" s="1" t="n">
         <v>0.04020363524441288</v>
@@ -33837,7 +33837,7 @@
         <v>0.00274171713171767</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>163.941</v>
+        <v>243.556</v>
       </c>
       <c r="E359" s="1" t="n">
         <v>0.04013098614543645</v>
@@ -33854,7 +33854,7 @@
         <v>0.00274465726876441</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>163.94</v>
+        <v>243.556</v>
       </c>
       <c r="E360" s="1" t="n">
         <v>0.0400607042132638</v>
@@ -33871,7 +33871,7 @@
         <v>0.002747733000352561</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>163.939</v>
+        <v>243.556</v>
       </c>
       <c r="E361" s="1" t="n">
         <v>0.03999279215326177</v>
@@ -33888,7 +33888,7 @@
         <v>0.002750934350478841</v>
       </c>
       <c r="D362" s="1" t="n">
-        <v>163.938</v>
+        <v>243.556</v>
       </c>
       <c r="E362" s="1" t="n">
         <v>0.03992708522766771</v>
@@ -33905,7 +33905,7 @@
         <v>0.002754245213961733</v>
       </c>
       <c r="D363" s="1" t="n">
-        <v>163.936</v>
+        <v>243.5563</v>
       </c>
       <c r="E363" s="1" t="n">
         <v>0.03986349971573203</v>
@@ -33922,7 +33922,7 @@
         <v>0.002757624968906782</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>163.935</v>
+        <v>243.5565</v>
       </c>
       <c r="E364" s="1" t="n">
         <v>0.03980109693971774</v>
@@ -33939,7 +33939,7 @@
         <v>0.002761026864241299</v>
       </c>
       <c r="D365" s="1" t="n">
-        <v>163.934</v>
+        <v>243.5567</v>
       </c>
       <c r="E365" s="1" t="n">
         <v>0.03973936088845491</v>
@@ -33956,7 +33956,7 @@
         <v>0.002764404148892593</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>163.933</v>
+        <v>243.557</v>
       </c>
       <c r="E366" s="1" t="n">
         <v>0.03967761498971051</v>
@@ -33973,7 +33973,7 @@
         <v>0.002767715294805458</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>163.932</v>
+        <v>243.5572</v>
       </c>
       <c r="E367" s="1" t="n">
         <v>0.03961526491547717</v>
@@ -33990,7 +33990,7 @@
         <v>0.002770939665994619</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>163.931</v>
+        <v>243.5575</v>
       </c>
       <c r="E368" s="1" t="n">
         <v>0.03955202110552562</v>
@@ -34007,7 +34007,7 @@
         <v>0.002774061849492286</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>163.93</v>
+        <v>243.5577</v>
       </c>
       <c r="E369" s="1" t="n">
         <v>0.03948767153300912</v>
@@ -34024,7 +34024,7 @@
         <v>0.002777066432330666</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>163.929</v>
+        <v>243.558</v>
       </c>
       <c r="E370" s="1" t="n">
         <v>0.03942200649736012</v>
@@ -34041,7 +34041,7 @@
         <v>0.002779946545831645</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>163.928</v>
+        <v>243.558</v>
       </c>
       <c r="E371" s="1" t="n">
         <v>0.03935493955158495</v>
@@ -34058,7 +34058,7 @@
         <v>0.002782729498475804</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>163.927</v>
+        <v>243.558</v>
       </c>
       <c r="E372" s="1" t="n">
         <v>0.03928686770855263</v>
@@ -34075,7 +34075,7 @@
         <v>0.002785451143033405</v>
       </c>
       <c r="D373" s="1" t="n">
-        <v>163.926</v>
+        <v>243.558</v>
       </c>
       <c r="E373" s="1" t="n">
         <v>0.03921830396149059</v>
@@ -34092,7 +34092,7 @@
         <v>0.002788147332274702</v>
       </c>
       <c r="D374" s="1" t="n">
-        <v>163.925</v>
+        <v>243.558</v>
       </c>
       <c r="E374" s="1" t="n">
         <v>0.03914975573609351</v>
@@ -34109,7 +34109,7 @@
         <v>0.00279084606234751</v>
       </c>
       <c r="D375" s="1" t="n">
-        <v>163.924</v>
+        <v>243.5582</v>
       </c>
       <c r="E375" s="1" t="n">
         <v>0.03908161494574626</v>
@@ -34126,7 +34126,7 @@
         <v>0.002793543902909862</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>163.922</v>
+        <v>243.5585</v>
       </c>
       <c r="E376" s="1" t="n">
         <v>0.03901399469601056</v>
@@ -34143,7 +34143,7 @@
         <v>0.002796229566997343</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>163.921</v>
+        <v>243.5588</v>
       </c>
       <c r="E377" s="1" t="n">
         <v>0.03894640598434541</v>
@@ -34160,7 +34160,7 @@
         <v>0.002798891767645538</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>163.92</v>
+        <v>243.559</v>
       </c>
       <c r="E378" s="1" t="n">
         <v>0.03887885504245432</v>
@@ -34177,7 +34177,7 @@
         <v>0.002801524926377552</v>
       </c>
       <c r="D379" s="1" t="n">
-        <v>163.919</v>
+        <v>243.559</v>
       </c>
       <c r="E379" s="1" t="n">
         <v>0.0388112642803517</v>
@@ -34194,7 +34194,7 @@
         <v>0.002804146298666551</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>163.918</v>
+        <v>243.559</v>
       </c>
       <c r="E380" s="1" t="n">
         <v>0.0387438724249995</v>
@@ -34211,7 +34211,7 @@
         <v>0.002806778848473216</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>163.917</v>
+        <v>243.559</v>
       </c>
       <c r="E381" s="1" t="n">
         <v>0.03867699432305197</v>
@@ -34228,7 +34228,7 @@
         <v>0.002809445539758229</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>163.916</v>
+        <v>243.559</v>
       </c>
       <c r="E382" s="1" t="n">
         <v>0.03861094147704788</v>
@@ -34245,7 +34245,7 @@
         <v>0.002812168378511871</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>163.915</v>
+        <v>243.5592</v>
       </c>
       <c r="E383" s="1" t="n">
         <v>0.03854600895899237</v>
@@ -34262,7 +34262,7 @@
         <v>0.002814965538842815</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>163.914</v>
+        <v>243.5595</v>
       </c>
       <c r="E384" s="1" t="n">
         <v>0.03848243633915395</v>
@@ -34279,7 +34279,7 @@
         <v>0.00281785423688933</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>163.913</v>
+        <v>243.5598</v>
       </c>
       <c r="E385" s="1" t="n">
         <v>0.03842044760194174</v>
@@ -34296,7 +34296,7 @@
         <v>0.00282085168878969</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>163.912</v>
+        <v>243.56</v>
       </c>
       <c r="E386" s="1" t="n">
         <v>0.03836026437797884</v>
@@ -34313,7 +34313,7 @@
         <v>0.002823960266170831</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>163.912</v>
+        <v>243.56</v>
       </c>
       <c r="E387" s="1" t="n">
         <v>0.03830174331193087</v>
@@ -34330,7 +34330,7 @@
         <v>0.002827122962614354</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>163.911</v>
+        <v>243.56</v>
       </c>
       <c r="E388" s="1" t="n">
         <v>0.03824442182335558</v>
@@ -34347,7 +34347,7 @@
         <v>0.002830267927190527</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>163.91</v>
+        <v>243.56</v>
       </c>
       <c r="E389" s="1" t="n">
         <v>0.03818716077873646</v>
@@ -34364,7 +34364,7 @@
         <v>0.002833323308969617</v>
       </c>
       <c r="D390" s="1" t="n">
-        <v>163.909</v>
+        <v>243.56</v>
       </c>
       <c r="E390" s="1" t="n">
         <v>0.03812899278051249</v>
@@ -34381,7 +34381,7 @@
         <v>0.002836239390289215</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>163.908</v>
+        <v>243.5602</v>
       </c>
       <c r="E391" s="1" t="n">
         <v>0.0380692575482459</v>
@@ -34398,7 +34398,7 @@
         <v>0.002839054986556198</v>
       </c>
       <c r="D392" s="1" t="n">
-        <v>163.908</v>
+        <v>243.5605</v>
       </c>
       <c r="E392" s="1" t="n">
         <v>0.03800832679792949</v>
@@ -34415,7 +34415,7 @@
         <v>0.002841831046444766</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>163.907</v>
+        <v>243.5608</v>
       </c>
       <c r="E393" s="1" t="n">
         <v>0.037947342836457</v>
@@ -34432,7 +34432,7 @@
         <v>0.00284462851862912</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>163.906</v>
+        <v>243.561</v>
       </c>
       <c r="E394" s="1" t="n">
         <v>0.03788695872359545</v>
@@ -34449,7 +34449,7 @@
         <v>0.002847490565412407</v>
       </c>
       <c r="D395" s="1" t="n">
-        <v>163.905</v>
+        <v>243.561</v>
       </c>
       <c r="E395" s="1" t="n">
         <v>0.03782774323033996</v>
@@ -34466,7 +34466,7 @@
         <v>0.002850389203613561</v>
       </c>
       <c r="D396" s="1" t="n">
-        <v>163.904</v>
+        <v>243.561</v>
       </c>
       <c r="E396" s="1" t="n">
         <v>0.03776931658468268</v>
@@ -34483,7 +34483,7 @@
         <v>0.002853278663680464</v>
       </c>
       <c r="D397" s="1" t="n">
-        <v>163.904</v>
+        <v>243.561</v>
       </c>
       <c r="E397" s="1" t="n">
         <v>0.03771090897455863</v>
@@ -34500,7 +34500,7 @@
         <v>0.002856113176060995</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>163.903</v>
+        <v>243.561</v>
       </c>
       <c r="E398" s="1" t="n">
         <v>0.03765223358149444</v>
@@ -34517,7 +34517,7 @@
         <v>0.002858863213172433</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>163.902</v>
+        <v>243.5613</v>
       </c>
       <c r="E399" s="1" t="n">
         <v>0.03759274629503093</v>
@@ -34534,7 +34534,7 @@
         <v>0.002861564215309643</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>163.901</v>
+        <v>243.5615</v>
       </c>
       <c r="E400" s="1" t="n">
         <v>0.03753291812595761</v>
@@ -34551,7 +34551,7 @@
         <v>0.002864267864736888</v>
       </c>
       <c r="D401" s="1" t="n">
-        <v>163.901</v>
+        <v>243.5618</v>
       </c>
       <c r="E401" s="1" t="n">
         <v>0.03747326997602723</v>
@@ -34568,7 +34568,7 @@
         <v>0.002867025843718431</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>163.9</v>
+        <v>243.562</v>
       </c>
       <c r="E402" s="1" t="n">
         <v>0.03741478967403043</v>
@@ -34585,7 +34585,7 @@
         <v>0.002869880154792552</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>163.899</v>
+        <v>243.562</v>
       </c>
       <c r="E403" s="1" t="n">
         <v>0.03735785826282902</v>
@@ -34602,7 +34602,7 @@
         <v>0.002872834081593617</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>163.899</v>
+        <v>243.562</v>
       </c>
       <c r="E404" s="1" t="n">
         <v>0.03730234959635792</v>
@@ -34619,7 +34619,7 @@
         <v>0.002875881228030007</v>
       </c>
       <c r="D405" s="1" t="n">
-        <v>163.898</v>
+        <v>243.562</v>
       </c>
       <c r="E405" s="1" t="n">
         <v>0.03724848344254497</v>
@@ -34636,7 +34636,7 @@
         <v>0.002879015198010104</v>
       </c>
       <c r="D406" s="1" t="n">
-        <v>163.897</v>
+        <v>243.562</v>
       </c>
       <c r="E406" s="1" t="n">
         <v>0.03719600868648638</v>
@@ -34653,7 +34653,7 @@
         <v>0.00288222631180793</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>163.896</v>
+        <v>243.5623</v>
       </c>
       <c r="E407" s="1" t="n">
         <v>0.03714479018506674</v>
@@ -34670,7 +34670,7 @@
         <v>0.002885491755160053</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>163.896</v>
+        <v>243.5625</v>
       </c>
       <c r="E408" s="1" t="n">
         <v>0.03709436903702726</v>
@@ -34687,7 +34687,7 @@
         <v>0.00288878543016868</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>163.895</v>
+        <v>243.5627</v>
       </c>
       <c r="E409" s="1" t="n">
         <v>0.03704471618832048</v>
@@ -34704,7 +34704,7 @@
         <v>0.002892081238936018</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>163.894</v>
+        <v>243.563</v>
       </c>
       <c r="E410" s="1" t="n">
         <v>0.03699533679696589</v>
@@ -34721,7 +34721,7 @@
         <v>0.002895362754680313</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>163.894</v>
+        <v>243.563</v>
       </c>
       <c r="E411" s="1" t="n">
         <v>0.03694586360012115</v>
@@ -34738,7 +34738,7 @@
         <v>0.002898652235083972</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>163.893</v>
+        <v>243.563</v>
       </c>
       <c r="E412" s="1" t="n">
         <v>0.03689689091333281</v>
@@ -34755,7 +34755,7 @@
         <v>0.002901981608945441</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>163.892</v>
+        <v>243.563</v>
       </c>
       <c r="E413" s="1" t="n">
         <v>0.03684866578930559</v>
@@ -34772,7 +34772,7 @@
         <v>0.002905382805063169</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>163.892</v>
+        <v>243.563</v>
       </c>
       <c r="E414" s="1" t="n">
         <v>0.03680143215186225</v>
@@ -34789,7 +34789,7 @@
         <v>0.002908868473666604</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>163.891</v>
+        <v>243.563</v>
       </c>
       <c r="E415" s="1" t="n">
         <v>0.03675565167657615</v>
@@ -34806,7 +34806,7 @@
         <v>0.0029123741507092</v>
       </c>
       <c r="D416" s="1" t="n">
-        <v>163.89</v>
+        <v>243.563</v>
       </c>
       <c r="E416" s="1" t="n">
         <v>0.03671034709761771</v>
@@ -34823,7 +34823,7 @@
         <v>0.002915816093575416</v>
       </c>
       <c r="D417" s="1" t="n">
-        <v>163.89</v>
+        <v>243.563</v>
       </c>
       <c r="E417" s="1" t="n">
         <v>0.03666430749467369</v>
@@ -34840,7 +34840,7 @@
         <v>0.002919110559649708</v>
       </c>
       <c r="D418" s="1" t="n">
-        <v>163.889</v>
+        <v>243.563</v>
       </c>
       <c r="E418" s="1" t="n">
         <v>0.03661679571142003</v>
@@ -34857,7 +34857,7 @@
         <v>0.002922203747695932</v>
       </c>
       <c r="D419" s="1" t="n">
-        <v>163.889</v>
+        <v>243.5632</v>
       </c>
       <c r="E419" s="1" t="n">
         <v>0.03656684163370246</v>
@@ -34874,7 +34874,7 @@
         <v>0.002925161621995538</v>
       </c>
       <c r="D420" s="1" t="n">
-        <v>163.888</v>
+        <v>243.5635</v>
       </c>
       <c r="E420" s="1" t="n">
         <v>0.03651559354387375</v>
@@ -34891,7 +34891,7 @@
         <v>0.002928080088209374</v>
       </c>
       <c r="D421" s="1" t="n">
-        <v>163.887</v>
+        <v>243.5637</v>
       </c>
       <c r="E421" s="1" t="n">
         <v>0.03646410198581545</v>
@@ -34908,7 +34908,7 @@
         <v>0.002931055051998289</v>
       </c>
       <c r="D422" s="1" t="n">
-        <v>163.887</v>
+        <v>243.564</v>
       </c>
       <c r="E422" s="1" t="n">
         <v>0.03641340679316579</v>
@@ -34925,7 +34925,7 @@
         <v>0.002934151853618653</v>
       </c>
       <c r="D423" s="1" t="n">
-        <v>163.886</v>
+        <v>243.564</v>
       </c>
       <c r="E423" s="1" t="n">
         <v>0.03636461792293541</v>
@@ -34942,7 +34942,7 @@
         <v>0.002937313571708925</v>
       </c>
       <c r="D424" s="1" t="n">
-        <v>163.885</v>
+        <v>243.564</v>
       </c>
       <c r="E424" s="1" t="n">
         <v>0.03631686544161021</v>
@@ -34959,7 +34959,7 @@
         <v>0.002940452719503088</v>
       </c>
       <c r="D425" s="1" t="n">
-        <v>163.885</v>
+        <v>243.564</v>
       </c>
       <c r="E425" s="1" t="n">
         <v>0.03626891005251308</v>
@@ -34976,7 +34976,7 @@
         <v>0.002943481810235123</v>
       </c>
       <c r="D426" s="1" t="n">
-        <v>163.884</v>
+        <v>243.564</v>
       </c>
       <c r="E426" s="1" t="n">
         <v>0.03621998133224055</v>
@@ -34993,7 +34993,7 @@
         <v>0.002946349249464728</v>
       </c>
       <c r="D427" s="1" t="n">
-        <v>163.884</v>
+        <v>243.564</v>
       </c>
       <c r="E427" s="1" t="n">
         <v>0.03616914857788806</v>
@@ -35010,7 +35010,7 @@
         <v>0.002949147012054461</v>
       </c>
       <c r="D428" s="1" t="n">
-        <v>163.883</v>
+        <v>243.564</v>
       </c>
       <c r="E428" s="1" t="n">
         <v>0.03611785556215387</v>
@@ -35027,7 +35027,7 @@
         <v>0.002952002965192596</v>
       </c>
       <c r="D429" s="1" t="n">
-        <v>163.883</v>
+        <v>243.564</v>
       </c>
       <c r="E429" s="1" t="n">
         <v>0.03606736439519542</v>
@@ -35044,7 +35044,7 @@
         <v>0.002955044976067411</v>
       </c>
       <c r="D430" s="1" t="n">
-        <v>163.882</v>
+        <v>243.564</v>
       </c>
       <c r="E430" s="1" t="n">
         <v>0.0360195310025718</v>
@@ -35061,7 +35061,7 @@
         <v>0.002958353273221817</v>
       </c>
       <c r="D431" s="1" t="n">
-        <v>163.881</v>
+        <v>243.5642</v>
       </c>
       <c r="E431" s="1" t="n">
         <v>0.03597516120506233</v>
@@ -35078,7 +35078,7 @@
         <v>0.00296181753061728</v>
       </c>
       <c r="D432" s="1" t="n">
-        <v>163.881</v>
+        <v>243.5645</v>
       </c>
       <c r="E432" s="1" t="n">
         <v>0.0359327408060854</v>
@@ -35095,7 +35095,7 @@
         <v>0.002965279783569906</v>
       </c>
       <c r="D433" s="1" t="n">
-        <v>163.88</v>
+        <v>243.5648</v>
       </c>
       <c r="E433" s="1" t="n">
         <v>0.03589064602446865</v>
@@ -35112,7 +35112,7 @@
         <v>0.002968582067395803</v>
       </c>
       <c r="D434" s="1" t="n">
-        <v>163.88</v>
+        <v>243.565</v>
       </c>
       <c r="E434" s="1" t="n">
         <v>0.03584666560580482</v>
@@ -35129,7 +35129,7 @@
         <v>0.002971618387875193</v>
       </c>
       <c r="D435" s="1" t="n">
-        <v>163.879</v>
+        <v>243.565</v>
       </c>
       <c r="E435" s="1" t="n">
         <v>0.03579983691597866</v>
@@ -35146,7 +35146,7 @@
         <v>0.002974490632644774</v>
       </c>
       <c r="D436" s="1" t="n">
-        <v>163.879</v>
+        <v>243.565</v>
       </c>
       <c r="E436" s="1" t="n">
         <v>0.03575110366784212</v>
@@ -35163,7 +35163,7 @@
         <v>0.002977352659805366</v>
       </c>
       <c r="D437" s="1" t="n">
-        <v>163.878</v>
+        <v>243.565</v>
       </c>
       <c r="E437" s="1" t="n">
         <v>0.03570262443428618</v>
@@ -35180,7 +35180,7 @@
         <v>0.002980358327457785</v>
       </c>
       <c r="D438" s="1" t="n">
-        <v>163.878</v>
+        <v>243.565</v>
       </c>
       <c r="E438" s="1" t="n">
         <v>0.03565593820020543</v>
@@ -35197,7 +35197,7 @@
         <v>0.002983609550026233</v>
       </c>
       <c r="D439" s="1" t="n">
-        <v>163.877</v>
+        <v>243.565</v>
       </c>
       <c r="E439" s="1" t="n">
         <v>0.03561254857160247</v>
@@ -35214,7 +35214,7 @@
         <v>0.002987000467228455</v>
       </c>
       <c r="D440" s="1" t="n">
-        <v>163.877</v>
+        <v>243.565</v>
       </c>
       <c r="E440" s="1" t="n">
         <v>0.0355708729475139</v>
@@ -35231,7 +35231,7 @@
         <v>0.002990373275105584</v>
       </c>
       <c r="D441" s="1" t="n">
-        <v>163.876</v>
+        <v>243.565</v>
       </c>
       <c r="E441" s="1" t="n">
         <v>0.0355293234436366</v>
@@ -35248,7 +35248,7 @@
         <v>0.002993570169698749</v>
       </c>
       <c r="D442" s="1" t="n">
-        <v>163.876</v>
+        <v>243.565</v>
       </c>
       <c r="E442" s="1" t="n">
         <v>0.03548573010406043</v>
@@ -35265,7 +35265,7 @@
         <v>0.002996483480386401</v>
       </c>
       <c r="D443" s="1" t="n">
-        <v>163.875</v>
+        <v>243.565</v>
       </c>
       <c r="E443" s="1" t="n">
         <v>0.03543913165902259</v>
@@ -35282,7 +35282,7 @@
         <v>0.002999206069896262</v>
       </c>
       <c r="D444" s="1" t="n">
-        <v>163.875</v>
+        <v>243.565</v>
       </c>
       <c r="E444" s="1" t="n">
         <v>0.03539034669709464</v>
@@ -35299,7 +35299,7 @@
         <v>0.003001880934293376</v>
       </c>
       <c r="D445" s="1" t="n">
-        <v>163.874</v>
+        <v>243.565</v>
       </c>
       <c r="E445" s="1" t="n">
         <v>0.03534137099898882</v>
@@ -35316,7 +35316,7 @@
         <v>0.003004651069642785</v>
       </c>
       <c r="D446" s="1" t="n">
-        <v>163.874</v>
+        <v>243.565</v>
       </c>
       <c r="E446" s="1" t="n">
         <v>0.03529358859350266</v>
@@ -35333,7 +35333,7 @@
         <v>0.003007629345905354</v>
       </c>
       <c r="D447" s="1" t="n">
-        <v>163.873</v>
+        <v>243.5652</v>
       </c>
       <c r="E447" s="1" t="n">
         <v>0.03524861072149778</v>
@@ -35350,7 +35350,7 @@
         <v>0.003010808128625226</v>
       </c>
       <c r="D448" s="1" t="n">
-        <v>163.873</v>
+        <v>243.5655</v>
       </c>
       <c r="E448" s="1" t="n">
         <v>0.03520603292972336</v>
@@ -35367,7 +35367,7 @@
         <v>0.003014149657242367</v>
       </c>
       <c r="D449" s="1" t="n">
-        <v>163.872</v>
+        <v>243.5658</v>
       </c>
       <c r="E449" s="1" t="n">
         <v>0.03516569422913823</v>
@@ -35384,7 +35384,7 @@
         <v>0.003017616171196739</v>
       </c>
       <c r="D450" s="1" t="n">
-        <v>163.872</v>
+        <v>243.566</v>
       </c>
       <c r="E450" s="1" t="n">
         <v>0.0351268444964167</v>
@@ -35401,7 +35401,7 @@
         <v>0.003021164576478739</v>
       </c>
       <c r="D451" s="1" t="n">
-        <v>163.871</v>
+        <v>243.566</v>
       </c>
       <c r="E451" s="1" t="n">
         <v>0.03508926830849118</v>
@@ -35418,7 +35418,7 @@
         <v>0.003024730445280483</v>
       </c>
       <c r="D452" s="1" t="n">
-        <v>163.871</v>
+        <v>243.566</v>
       </c>
       <c r="E452" s="1" t="n">
         <v>0.03505191568557497</v>
@@ -35435,7 +35435,7 @@
         <v>0.003028244016344515</v>
       </c>
       <c r="D453" s="1" t="n">
-        <v>163.87</v>
+        <v>243.566</v>
       </c>
       <c r="E453" s="1" t="n">
         <v>0.03501427299738689</v>
@@ -35452,7 +35452,7 @@
         <v>0.003031635528413383</v>
       </c>
       <c r="D454" s="1" t="n">
-        <v>163.869</v>
+        <v>243.566</v>
       </c>
       <c r="E454" s="1" t="n">
         <v>0.03497539052874503</v>
@@ -35469,7 +35469,7 @@
         <v>0.003034853734642631</v>
       </c>
       <c r="D455" s="1" t="n">
-        <v>163.869</v>
+        <v>243.566</v>
       </c>
       <c r="E455" s="1" t="n">
         <v>0.03493453946649071</v>
@@ -35486,7 +35486,7 @@
         <v>0.003037921445839805</v>
       </c>
       <c r="D456" s="1" t="n">
-        <v>163.869</v>
+        <v>243.566</v>
       </c>
       <c r="E456" s="1" t="n">
         <v>0.03489214144913171</v>
@@ -35503,7 +35503,7 @@
         <v>0.003040879987225449</v>
       </c>
       <c r="D457" s="1" t="n">
-        <v>163.868</v>
+        <v>243.566</v>
       </c>
       <c r="E457" s="1" t="n">
         <v>0.03484882716322004</v>
@@ -35520,7 +35520,7 @@
         <v>0.00304377068402011</v>
       </c>
       <c r="D458" s="1" t="n">
-        <v>163.868</v>
+        <v>243.566</v>
       </c>
       <c r="E458" s="1" t="n">
         <v>0.034804782407545</v>
@@ -35537,7 +35537,7 @@
         <v>0.003046633780640474</v>
       </c>
       <c r="D459" s="1" t="n">
-        <v>163.867</v>
+        <v>243.566</v>
       </c>
       <c r="E459" s="1" t="n">
         <v>0.03476076364165121</v>
@@ -35554,7 +35554,7 @@
         <v>0.003049505198287787</v>
       </c>
       <c r="D460" s="1" t="n">
-        <v>163.867</v>
+        <v>243.566</v>
       </c>
       <c r="E460" s="1" t="n">
         <v>0.03471688754472568</v>
@@ -35571,7 +35571,7 @@
         <v>0.003052419777359436</v>
       </c>
       <c r="D461" s="1" t="n">
-        <v>163.866</v>
+        <v>243.566</v>
       </c>
       <c r="E461" s="1" t="n">
         <v>0.03467384066894467</v>
@@ -35588,7 +35588,7 @@
         <v>0.003055412358252812</v>
       </c>
       <c r="D462" s="1" t="n">
-        <v>163.866</v>
+        <v>243.566</v>
       </c>
       <c r="E462" s="1" t="n">
         <v>0.03463172109945254</v>
@@ -35605,7 +35605,7 @@
         <v>0.003058505517829356</v>
       </c>
       <c r="D463" s="1" t="n">
-        <v>163.865</v>
+        <v>243.566</v>
       </c>
       <c r="E463" s="1" t="n">
         <v>0.03459106910282245</v>
@@ -35622,7 +35622,7 @@
         <v>0.003061672778806734</v>
       </c>
       <c r="D464" s="1" t="n">
-        <v>163.865</v>
+        <v>243.566</v>
       </c>
       <c r="E464" s="1" t="n">
         <v>0.03455128561013299</v>
@@ -35639,7 +35639,7 @@
         <v>0.003064875400366671</v>
       </c>
       <c r="D465" s="1" t="n">
-        <v>163.864</v>
+        <v>243.566</v>
       </c>
       <c r="E465" s="1" t="n">
         <v>0.0345122190354735</v>
@@ -35656,7 +35656,7 @@
         <v>0.003068074641690885</v>
       </c>
       <c r="D466" s="1" t="n">
-        <v>163.864</v>
+        <v>243.566</v>
       </c>
       <c r="E466" s="1" t="n">
         <v>0.03447313941141421</v>
@@ -35673,7 +35673,7 @@
         <v>0.003071240539804948</v>
       </c>
       <c r="D467" s="1" t="n">
-        <v>163.863</v>
+        <v>243.566</v>
       </c>
       <c r="E467" s="1" t="n">
         <v>0.03443400055804478</v>
@@ -35690,7 +35690,7 @@
         <v>0.003074378243109818</v>
       </c>
       <c r="D468" s="1" t="n">
-        <v>163.863</v>
+        <v>243.566</v>
       </c>
       <c r="E468" s="1" t="n">
         <v>0.03439457110881074</v>
@@ -35707,7 +35707,7 @@
         <v>0.003077501677850308</v>
       </c>
       <c r="D469" s="1" t="n">
-        <v>163.862</v>
+        <v>243.566</v>
       </c>
       <c r="E469" s="1" t="n">
         <v>0.03435529742782134</v>
@@ -35724,7 +35724,7 @@
         <v>0.003080624770271225</v>
       </c>
       <c r="D470" s="1" t="n">
-        <v>163.862</v>
+        <v>243.566</v>
       </c>
       <c r="E470" s="1" t="n">
         <v>0.03431604494395332</v>
@@ -35741,7 +35741,7 @@
         <v>0.003083761555475374</v>
       </c>
       <c r="D471" s="1" t="n">
-        <v>163.861</v>
+        <v>243.566</v>
       </c>
       <c r="E471" s="1" t="n">
         <v>0.03427725789128176</v>
@@ -35758,7 +35758,7 @@
         <v>0.003086926503997539</v>
       </c>
       <c r="D472" s="1" t="n">
-        <v>163.861</v>
+        <v>243.566</v>
       </c>
       <c r="E472" s="1" t="n">
         <v>0.03423880573487946</v>
@@ -35775,7 +35775,7 @@
         <v>0.003090134195230498</v>
       </c>
       <c r="D473" s="1" t="n">
-        <v>163.86</v>
+        <v>243.566</v>
       </c>
       <c r="E473" s="1" t="n">
         <v>0.03420113540667794</v>
@@ -35792,7 +35792,7 @@
         <v>0.003093399208567031</v>
       </c>
       <c r="D474" s="1" t="n">
-        <v>163.86</v>
+        <v>243.566</v>
       </c>
       <c r="E474" s="1" t="n">
         <v>0.03416411551356069</v>
@@ -35809,7 +35809,7 @@
         <v>0.00309671990044548</v>
       </c>
       <c r="D475" s="1" t="n">
-        <v>163.859</v>
+        <v>243.5662</v>
       </c>
       <c r="E475" s="1" t="n">
         <v>0.03412801087711729</v>
@@ -35826,7 +35826,7 @@
         <v>0.003100029735486445</v>
       </c>
       <c r="D476" s="1" t="n">
-        <v>163.859</v>
+        <v>243.5665</v>
       </c>
       <c r="E476" s="1" t="n">
         <v>0.03409179716625124</v>
@@ -35843,7 +35843,7 @@
         <v>0.003103245955356087</v>
       </c>
       <c r="D477" s="1" t="n">
-        <v>163.858</v>
+        <v>243.5668</v>
       </c>
       <c r="E477" s="1" t="n">
         <v>0.03405485337359269</v>
@@ -35860,7 +35860,7 @@
         <v>0.003106285801720571</v>
       </c>
       <c r="D478" s="1" t="n">
-        <v>163.858</v>
+        <v>243.567</v>
       </c>
       <c r="E478" s="1" t="n">
         <v>0.03401599169412351</v>
@@ -35877,7 +35877,7 @@
         <v>0.003109101157587793</v>
       </c>
       <c r="D479" s="1" t="n">
-        <v>163.857</v>
+        <v>243.567</v>
       </c>
       <c r="E479" s="1" t="n">
         <v>0.03397498433687397</v>
@@ -35894,7 +35894,7 @@
         <v>0.00311178247133258</v>
       </c>
       <c r="D480" s="1" t="n">
-        <v>163.857</v>
+        <v>243.567</v>
       </c>
       <c r="E480" s="1" t="n">
         <v>0.03393254563841257</v>
@@ -35911,7 +35911,7 @@
         <v>0.003114454832671495</v>
       </c>
       <c r="D481" s="1" t="n">
-        <v>163.856</v>
+        <v>243.567</v>
       </c>
       <c r="E481" s="1" t="n">
         <v>0.0338903309889757</v>
@@ -35928,7 +35928,7 @@
         <v>0.0031172433313211</v>
       </c>
       <c r="D482" s="1" t="n">
-        <v>163.855</v>
+        <v>243.567</v>
       </c>
       <c r="E482" s="1" t="n">
         <v>0.03384955507078623</v>
@@ -35945,7 +35945,7 @@
         <v>0.003120240788955578</v>
       </c>
       <c r="D483" s="1" t="n">
-        <v>163.854</v>
+        <v>243.567</v>
       </c>
       <c r="E483" s="1" t="n">
         <v>0.03381121467528279</v>
@@ -35962,7 +35962,7 @@
         <v>0.003123410955079591</v>
       </c>
       <c r="D484" s="1" t="n">
-        <v>163.853</v>
+        <v>243.567</v>
       </c>
       <c r="E484" s="1" t="n">
         <v>0.03377490255176996</v>
@@ -35979,7 +35979,7 @@
         <v>0.003126685311155424</v>
       </c>
       <c r="D485" s="1" t="n">
-        <v>163.853</v>
+        <v>243.567</v>
       </c>
       <c r="E485" s="1" t="n">
         <v>0.03373972449677278</v>
@@ -35996,7 +35996,7 @@
         <v>0.00312999533864536</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>163.852</v>
+        <v>243.567</v>
       </c>
       <c r="E486" s="1" t="n">
         <v>0.03370521914008606</v>
@@ -36013,7 +36013,7 @@
         <v>0.00313328283369617</v>
       </c>
       <c r="D487" s="1" t="n">
-        <v>163.851</v>
+        <v>243.567</v>
       </c>
       <c r="E487" s="1" t="n">
         <v>0.03367061542155308</v>
@@ -36030,7 +36030,7 @@
         <v>0.003136530851192564</v>
       </c>
       <c r="D488" s="1" t="n">
-        <v>163.851</v>
+        <v>243.567</v>
       </c>
       <c r="E488" s="1" t="n">
         <v>0.03363559052614026</v>
@@ -36047,7 +36047,7 @@
         <v>0.003139732760703741</v>
       </c>
       <c r="D489" s="1" t="n">
-        <v>163.85</v>
+        <v>243.567</v>
       </c>
       <c r="E489" s="1" t="n">
         <v>0.03360035878939919</v>
@@ -36064,7 +36064,7 @@
         <v>0.0031428819317989</v>
       </c>
       <c r="D490" s="1" t="n">
-        <v>163.85</v>
+        <v>243.567</v>
       </c>
       <c r="E490" s="1" t="n">
         <v>0.03356456829423139</v>
@@ -36081,7 +36081,7 @@
         <v>0.003145973608353518</v>
       </c>
       <c r="D491" s="1" t="n">
-        <v>163.849</v>
+        <v>243.567</v>
       </c>
       <c r="E491" s="1" t="n">
         <v>0.03352845389456494</v>
@@ -36098,7 +36098,7 @@
         <v>0.003149010531468193</v>
       </c>
       <c r="D492" s="1" t="n">
-        <v>163.849</v>
+        <v>243.567</v>
       </c>
       <c r="E492" s="1" t="n">
         <v>0.03349176494903629</v>
@@ -36115,7 +36115,7 @@
         <v>0.0031519973165498</v>
       </c>
       <c r="D493" s="1" t="n">
-        <v>163.849</v>
+        <v>243.567</v>
       </c>
       <c r="E493" s="1" t="n">
         <v>0.03345469452133577</v>
@@ -36132,7 +36132,7 @@
         <v>0.003154938579005215</v>
       </c>
       <c r="D494" s="1" t="n">
-        <v>163.848</v>
+        <v>243.567</v>
       </c>
       <c r="E494" s="1" t="n">
         <v>0.03341743463187195</v>
@@ -36149,7 +36149,7 @@
         <v>0.003157853892579203</v>
       </c>
       <c r="D495" s="1" t="n">
-        <v>163.848</v>
+        <v>243.567</v>
       </c>
       <c r="E495" s="1" t="n">
         <v>0.03337991247376353</v>
@@ -36166,7 +36166,7 @@
         <v>0.003160822664368089</v>
       </c>
       <c r="D496" s="1" t="n">
-        <v>163.847</v>
+        <v>243.567</v>
       </c>
       <c r="E496" s="1" t="n">
         <v>0.03334324786769326</v>
@@ -36183,7 +36183,7 @@
         <v>0.003163939259806087</v>
       </c>
       <c r="D497" s="1" t="n">
-        <v>163.847</v>
+        <v>243.567</v>
       </c>
       <c r="E497" s="1" t="n">
         <v>0.03330814875255304</v>
@@ -36200,7 +36200,7 @@
         <v>0.003167298044327407</v>
       </c>
       <c r="D498" s="1" t="n">
-        <v>163.847</v>
+        <v>243.567</v>
       </c>
       <c r="E498" s="1" t="n">
         <v>0.03327573676316694</v>
@@ -36217,7 +36217,7 @@
         <v>0.003170949024662984</v>
       </c>
       <c r="D499" s="1" t="n">
-        <v>163.846</v>
+        <v>243.567</v>
       </c>
       <c r="E499" s="1" t="n">
         <v>0.033246659924816</v>
@@ -36234,7 +36234,7 @@
         <v>0.003174764772730618</v>
       </c>
       <c r="D500" s="1" t="n">
-        <v>163.846</v>
+        <v>243.567</v>
       </c>
       <c r="E500" s="1" t="n">
         <v>0.03321928523479678</v>
@@ -36251,7 +36251,7 @@
         <v>0.003178573501744832</v>
       </c>
       <c r="D501" s="1" t="n">
-        <v>163.846</v>
+        <v>243.567</v>
       </c>
       <c r="E501" s="1" t="n">
         <v>0.03319194785379597</v>
@@ -36268,7 +36268,7 @@
         <v>0.003182203424920144</v>
       </c>
       <c r="D502" s="1" t="n">
-        <v>163.845</v>
+        <v>243.567</v>
       </c>
       <c r="E502" s="1" t="n">
         <v>0.03316299702423371</v>
@@ -36285,7 +36285,7 @@
         <v>0.003185523789264427</v>
       </c>
       <c r="D503" s="1" t="n">
-        <v>163.845</v>
+        <v>243.567</v>
       </c>
       <c r="E503" s="1" t="n">
         <v>0.03313080387513771</v>
@@ -36302,7 +36302,7 @@
         <v>0.003188567976958948</v>
       </c>
       <c r="D504" s="1" t="n">
-        <v>163.845</v>
+        <v>243.567</v>
       </c>
       <c r="E504" s="1" t="n">
         <v>0.03309587342881808</v>
@@ -36319,7 +36319,7 @@
         <v>0.003191410403978326</v>
       </c>
       <c r="D505" s="1" t="n">
-        <v>163.845</v>
+        <v>243.567</v>
       </c>
       <c r="E505" s="1" t="n">
         <v>0.0330589929977602</v>
@@ -36336,7 +36336,7 @@
         <v>0.003194125486297179</v>
       </c>
       <c r="D506" s="1" t="n">
-        <v>163.844</v>
+        <v>243.567</v>
       </c>
       <c r="E506" s="1" t="n">
         <v>0.03302108271702439</v>
@@ -36353,7 +36353,7 @@
         <v>0.003196784224084905</v>
       </c>
       <c r="D507" s="1" t="n">
-        <v>163.844</v>
+        <v>243.567</v>
       </c>
       <c r="E507" s="1" t="n">
         <v>0.0329826037185006</v>
@@ -36370,7 +36370,7 @@
         <v>0.003199443954290036</v>
       </c>
       <c r="D508" s="1" t="n">
-        <v>163.844</v>
+        <v>243.567</v>
       </c>
       <c r="E508" s="1" t="n">
         <v>0.03294428824156202</v>
@@ -36387,7 +36387,7 @@
         <v>0.00320215859805588</v>
       </c>
       <c r="D509" s="1" t="n">
-        <v>163.843</v>
+        <v>243.567</v>
       </c>
       <c r="E509" s="1" t="n">
         <v>0.03290682806691216</v>
@@ -36404,7 +36404,7 @@
         <v>0.003204982076525748</v>
       </c>
       <c r="D510" s="1" t="n">
-        <v>163.843</v>
+        <v>243.567</v>
       </c>
       <c r="E510" s="1" t="n">
         <v>0.03287049451129534</v>
@@ -36421,7 +36421,7 @@
         <v>0.003207949176642839</v>
       </c>
       <c r="D511" s="1" t="n">
-        <v>163.843</v>
+        <v>243.567</v>
       </c>
       <c r="E511" s="1" t="n">
         <v>0.03283577492663313</v>
@@ -36438,7 +36438,7 @@
         <v>0.003211018148549895</v>
       </c>
       <c r="D512" s="1" t="n">
-        <v>163.843</v>
+        <v>243.567</v>
       </c>
       <c r="E512" s="1" t="n">
         <v>0.03280223324725524</v>
@@ -36455,7 +36455,7 @@
         <v>0.00321412810818955</v>
       </c>
       <c r="D513" s="1" t="n">
-        <v>163.842</v>
+        <v>243.567</v>
       </c>
       <c r="E513" s="1" t="n">
         <v>0.03276937982929296</v>
@@ -36472,7 +36472,7 @@
         <v>0.003217218171504436</v>
       </c>
       <c r="D514" s="1" t="n">
-        <v>163.842</v>
+        <v>243.567</v>
       </c>
       <c r="E514" s="1" t="n">
         <v>0.03273631564677065</v>
@@ -36489,7 +36489,7 @@
         <v>0.003220244319935379</v>
       </c>
       <c r="D515" s="1" t="n">
-        <v>163.842</v>
+        <v>243.567</v>
       </c>
       <c r="E515" s="1" t="n">
         <v>0.0327027323039548</v>
@@ -36506,7 +36506,7 @@
         <v>0.00322322999691599</v>
       </c>
       <c r="D516" s="1" t="n">
-        <v>163.842</v>
+        <v>243.567</v>
       </c>
       <c r="E516" s="1" t="n">
         <v>0.03266887046436228</v>
@@ -36523,7 +36523,7 @@
         <v>0.003226215511378072</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>163.841</v>
+        <v>243.567</v>
       </c>
       <c r="E517" s="1" t="n">
         <v>0.03263527700983268</v>
@@ -36540,7 +36540,7 @@
         <v>0.00322924117225343</v>
       </c>
       <c r="D518" s="1" t="n">
-        <v>163.841</v>
+        <v>243.567</v>
       </c>
       <c r="E518" s="1" t="n">
         <v>0.03260208299191231</v>
@@ -36557,7 +36557,7 @@
         <v>0.003232332431896556</v>
       </c>
       <c r="D519" s="1" t="n">
-        <v>163.841</v>
+        <v>243.567</v>
       </c>
       <c r="E519" s="1" t="n">
         <v>0.0325696793727132</v>
@@ -36574,7 +36574,7 @@
         <v>0.003235455316352684</v>
       </c>
       <c r="D520" s="1" t="n">
-        <v>163.841</v>
+        <v>243.567</v>
       </c>
       <c r="E520" s="1" t="n">
         <v>0.03253771987612034</v>
@@ -36591,7 +36591,7 @@
         <v>0.003238560995089733</v>
       </c>
       <c r="D521" s="1" t="n">
-        <v>163.84</v>
+        <v>243.567</v>
       </c>
       <c r="E521" s="1" t="n">
         <v>0.0325058487514648</v>
@@ -36608,7 +36608,7 @@
         <v>0.003241600637575623</v>
       </c>
       <c r="D522" s="1" t="n">
-        <v>163.84</v>
+        <v>243.567</v>
       </c>
       <c r="E522" s="1" t="n">
         <v>0.03247330307240877</v>
@@ -36625,7 +36625,7 @@
         <v>0.003244546244085651</v>
       </c>
       <c r="D523" s="1" t="n">
-        <v>163.84</v>
+        <v>243.567</v>
       </c>
       <c r="E523" s="1" t="n">
         <v>0.03243994309560674</v>
@@ -36642,7 +36642,7 @@
         <v>0.003247453138124612</v>
       </c>
       <c r="D524" s="1" t="n">
-        <v>163.84</v>
+        <v>243.567</v>
       </c>
       <c r="E524" s="1" t="n">
         <v>0.03240632561016549</v>
@@ -36659,7 +36659,7 @@
         <v>0.003250397474004677</v>
       </c>
       <c r="D525" s="1" t="n">
-        <v>163.839</v>
+        <v>243.567</v>
       </c>
       <c r="E525" s="1" t="n">
         <v>0.03237334697896601</v>
@@ -36676,7 +36676,7 @@
         <v>0.003253455406038018</v>
       </c>
       <c r="D526" s="1" t="n">
-        <v>163.839</v>
+        <v>243.567</v>
       </c>
       <c r="E526" s="1" t="n">
         <v>0.03234148839983535</v>
@@ -36693,7 +36693,7 @@
         <v>0.0032566770304402</v>
       </c>
       <c r="D527" s="1" t="n">
-        <v>163.839</v>
+        <v>243.567</v>
       </c>
       <c r="E527" s="1" t="n">
         <v>0.03231137620517033</v>
@@ -36710,7 +36710,7 @@
         <v>0.003260008211040364</v>
       </c>
       <c r="D528" s="1" t="n">
-        <v>163.839</v>
+        <v>243.567</v>
       </c>
       <c r="E528" s="1" t="n">
         <v>0.03228246427097808</v>
@@ -36727,7 +36727,7 @@
         <v>0.003263368753571038</v>
       </c>
       <c r="D529" s="1" t="n">
-        <v>163.838</v>
+        <v>243.567</v>
       </c>
       <c r="E529" s="1" t="n">
         <v>0.03225408899443685</v>
@@ -36744,7 +36744,7 @@
         <v>0.003266678463764757</v>
       </c>
       <c r="D530" s="1" t="n">
-        <v>163.838</v>
+        <v>243.567</v>
       </c>
       <c r="E530" s="1" t="n">
         <v>0.03222518507469931</v>
@@ -36761,7 +36761,7 @@
         <v>0.003269877461825629</v>
       </c>
       <c r="D531" s="1" t="n">
-        <v>163.838</v>
+        <v>243.5668</v>
       </c>
       <c r="E531" s="1" t="n">
         <v>0.03219530119050279</v>
@@ -36778,7 +36778,7 @@
         <v>0.003272987125844066</v>
       </c>
       <c r="D532" s="1" t="n">
-        <v>163.838</v>
+        <v>243.5665</v>
       </c>
       <c r="E532" s="1" t="n">
         <v>0.03216465302008006</v>
@@ -36795,7 +36795,7 @@
         <v>0.003276049148382058</v>
       </c>
       <c r="D533" s="1" t="n">
-        <v>163.837</v>
+        <v>243.5662</v>
       </c>
       <c r="E533" s="1" t="n">
         <v>0.0321337892492052</v>
@@ -36812,7 +36812,7 @@
         <v>0.00327910522200159</v>
       </c>
       <c r="D534" s="1" t="n">
-        <v>163.837</v>
+        <v>243.566</v>
       </c>
       <c r="E534" s="1" t="n">
         <v>0.03210284914180341</v>
@@ -36829,7 +36829,7 @@
         <v>0.003282185825208224</v>
       </c>
       <c r="D535" s="1" t="n">
-        <v>163.837</v>
+        <v>243.566</v>
       </c>
       <c r="E535" s="1" t="n">
         <v>0.032072265703985</v>
@@ -36846,7 +36846,7 @@
         <v>0.003285276580281795</v>
       </c>
       <c r="D536" s="1" t="n">
-        <v>163.837</v>
+        <v>243.566</v>
       </c>
       <c r="E536" s="1" t="n">
         <v>0.03204189668836028</v>
@@ -36863,7 +36863,7 @@
         <v>0.003288351895445709</v>
       </c>
       <c r="D537" s="1" t="n">
-        <v>163.836</v>
+        <v>243.566</v>
       </c>
       <c r="E537" s="1" t="n">
         <v>0.03201162662502011</v>
@@ -36880,7 +36880,7 @@
         <v>0.003291386178923372</v>
       </c>
       <c r="D538" s="1" t="n">
-        <v>163.836</v>
+        <v>243.566</v>
       </c>
       <c r="E538" s="1" t="n">
         <v>0.0319809371789803</v>
@@ -36897,7 +36897,7 @@
         <v>0.003294373123433378</v>
       </c>
       <c r="D539" s="1" t="n">
-        <v>163.836</v>
+        <v>243.566</v>
       </c>
       <c r="E539" s="1" t="n">
         <v>0.03194990378160622</v>
@@ -36914,7 +36914,7 @@
         <v>0.003297383559675082</v>
       </c>
       <c r="D540" s="1" t="n">
-        <v>163.836</v>
+        <v>243.566</v>
       </c>
       <c r="E540" s="1" t="n">
         <v>0.03191921401800311</v>
@@ -36931,7 +36931,7 @@
         <v>0.003300507602843026</v>
       </c>
       <c r="D541" s="1" t="n">
-        <v>163.835</v>
+        <v>243.566</v>
       </c>
       <c r="E541" s="1" t="n">
         <v>0.03188987102086537</v>
@@ -36948,7 +36948,7 @@
         <v>0.003303835368131752</v>
       </c>
       <c r="D542" s="1" t="n">
-        <v>163.835</v>
+        <v>243.566</v>
       </c>
       <c r="E542" s="1" t="n">
         <v>0.03186246824326656</v>
@@ -36965,7 +36965,7 @@
         <v>0.003307411550121405</v>
       </c>
       <c r="D543" s="1" t="n">
-        <v>163.835</v>
+        <v>243.566</v>
       </c>
       <c r="E543" s="1" t="n">
         <v>0.03183755881478069</v>
@@ -36982,7 +36982,7 @@
         <v>0.003311099160934539</v>
       </c>
       <c r="D544" s="1" t="n">
-        <v>163.835</v>
+        <v>243.566</v>
       </c>
       <c r="E544" s="1" t="n">
         <v>0.03181381262051296</v>
@@ -36999,7 +36999,7 @@
         <v>0.003314715792079305</v>
       </c>
       <c r="D545" s="1" t="n">
-        <v>163.835</v>
+        <v>243.566</v>
       </c>
       <c r="E545" s="1" t="n">
         <v>0.03178947381436899</v>
@@ -37016,7 +37016,7 @@
         <v>0.003318079035063862</v>
       </c>
       <c r="D546" s="1" t="n">
-        <v>163.834</v>
+        <v>243.566</v>
       </c>
       <c r="E546" s="1" t="n">
         <v>0.03176293338252775</v>
@@ -37033,7 +37033,7 @@
         <v>0.003321074949665413</v>
       </c>
       <c r="D547" s="1" t="n">
-        <v>163.834</v>
+        <v>243.566</v>
       </c>
       <c r="E547" s="1" t="n">
         <v>0.03173284780352627</v>
@@ -37050,7 +37050,7 @@
         <v>0.00332386346873737</v>
       </c>
       <c r="D548" s="1" t="n">
-        <v>163.834</v>
+        <v>243.566</v>
       </c>
       <c r="E548" s="1" t="n">
         <v>0.03170089523479826</v>
@@ -37067,7 +37067,7 @@
         <v>0.003326672993402191</v>
       </c>
       <c r="D549" s="1" t="n">
-        <v>163.834</v>
+        <v>243.566</v>
       </c>
       <c r="E549" s="1" t="n">
         <v>0.03166926032412462</v>
@@ -37084,7 +37084,7 @@
         <v>0.003329731924782338</v>
       </c>
       <c r="D550" s="1" t="n">
-        <v>163.834</v>
+        <v>243.566</v>
       </c>
       <c r="E550" s="1" t="n">
         <v>0.0316401116556997</v>
@@ -37101,7 +37101,7 @@
         <v>0.003333194424467846</v>
       </c>
       <c r="D551" s="1" t="n">
-        <v>163.833</v>
+        <v>243.566</v>
       </c>
       <c r="E551" s="1" t="n">
         <v>0.03161503094900514</v>
@@ -37118,7 +37118,7 @@
         <v>0.003336917695919064</v>
       </c>
       <c r="D552" s="1" t="n">
-        <v>163.833</v>
+        <v>243.566</v>
       </c>
       <c r="E552" s="1" t="n">
         <v>0.03159237815697535</v>
@@ -37135,7 +37135,7 @@
         <v>0.003340684703063917</v>
       </c>
       <c r="D553" s="1" t="n">
-        <v>163.833</v>
+        <v>243.566</v>
       </c>
       <c r="E553" s="1" t="n">
         <v>0.03157022150264815</v>
@@ -37152,7 +37152,7 @@
         <v>0.003344278409830328</v>
       </c>
       <c r="D554" s="1" t="n">
-        <v>163.832</v>
+        <v>243.566</v>
       </c>
       <c r="E554" s="1" t="n">
         <v>0.03154664388887744</v>
@@ -37169,7 +37169,7 @@
         <v>0.003347544140623844</v>
       </c>
       <c r="D555" s="1" t="n">
-        <v>163.832</v>
+        <v>243.566</v>
       </c>
       <c r="E555" s="1" t="n">
         <v>0.03151993146844212</v>
@@ -37186,7 +37186,7 @@
         <v>0.003350576661760504</v>
       </c>
       <c r="D556" s="1" t="n">
-        <v>163.831</v>
+        <v>243.566</v>
       </c>
       <c r="E556" s="1" t="n">
         <v>0.03149125699537735</v>
@@ -37203,7 +37203,7 @@
         <v>0.003353533100033963</v>
       </c>
       <c r="D557" s="1" t="n">
-        <v>163.831</v>
+        <v>243.566</v>
       </c>
       <c r="E557" s="1" t="n">
         <v>0.03146184049494797</v>
@@ -37220,7 +37220,7 @@
         <v>0.003356570582237882</v>
       </c>
       <c r="D558" s="1" t="n">
-        <v>163.83</v>
+        <v>243.566</v>
       </c>
       <c r="E558" s="1" t="n">
         <v>0.0314334219683667</v>
@@ -37237,7 +37237,7 @@
         <v>0.003359802464261758</v>
       </c>
       <c r="D559" s="1" t="n">
-        <v>163.829</v>
+        <v>243.566</v>
       </c>
       <c r="E559" s="1" t="n">
         <v>0.03140692368166999</v>
@@ -37254,7 +37254,7 @@
         <v>0.003363167018378446</v>
       </c>
       <c r="D560" s="1" t="n">
-        <v>163.829</v>
+        <v>243.566</v>
       </c>
       <c r="E560" s="1" t="n">
         <v>0.03138162705372188</v>
@@ -37271,7 +37271,7 @@
         <v>0.003366558745956641</v>
       </c>
       <c r="D561" s="1" t="n">
-        <v>163.829</v>
+        <v>243.566</v>
       </c>
       <c r="E561" s="1" t="n">
         <v>0.03135667468282518</v>
@@ -37288,7 +37288,7 @@
         <v>0.003369872148365033</v>
       </c>
       <c r="D562" s="1" t="n">
-        <v>163.828</v>
+        <v>243.566</v>
       </c>
       <c r="E562" s="1" t="n">
         <v>0.03133121585781993</v>
@@ -37305,7 +37305,7 @@
         <v>0.003373036292194859</v>
       </c>
       <c r="D563" s="1" t="n">
-        <v>163.828</v>
+        <v>243.5658</v>
       </c>
       <c r="E563" s="1" t="n">
         <v>0.03130433157041842</v>
@@ -37322,7 +37322,7 @@
         <v>0.0033761185049275</v>
       </c>
       <c r="D564" s="1" t="n">
-        <v>163.828</v>
+        <v>243.5655</v>
       </c>
       <c r="E564" s="1" t="n">
         <v>0.03127678462252537</v>
@@ -37339,7 +37339,7 @@
         <v>0.003379220679266879</v>
       </c>
       <c r="D565" s="1" t="n">
-        <v>163.827</v>
+        <v>243.5652</v>
       </c>
       <c r="E565" s="1" t="n">
         <v>0.03124965249588798</v>
@@ -37356,7 +37356,7 @@
         <v>0.00338244470791692</v>
       </c>
       <c r="D566" s="1" t="n">
-        <v>163.827</v>
+        <v>243.565</v>
       </c>
       <c r="E566" s="1" t="n">
         <v>0.03122361080482643</v>
@@ -37373,7 +37373,7 @@
         <v>0.003385852318604769</v>
       </c>
       <c r="D567" s="1" t="n">
-        <v>163.827</v>
+        <v>243.565</v>
       </c>
       <c r="E567" s="1" t="n">
         <v>0.03119935359333735</v>
@@ -37390,7 +37390,7 @@
         <v>0.003389344579150461</v>
       </c>
       <c r="D568" s="1" t="n">
-        <v>163.827</v>
+        <v>243.565</v>
       </c>
       <c r="E568" s="1" t="n">
         <v>0.03117596133506514</v>
@@ -37407,7 +37407,7 @@
         <v>0.003392782392397253</v>
       </c>
       <c r="D569" s="1" t="n">
-        <v>163.826</v>
+        <v>243.565</v>
       </c>
       <c r="E569" s="1" t="n">
         <v>0.03115228350392542</v>
@@ -37424,7 +37424,7 @@
         <v>0.003396026661188406</v>
       </c>
       <c r="D570" s="1" t="n">
-        <v>163.826</v>
+        <v>243.565</v>
       </c>
       <c r="E570" s="1" t="n">
         <v>0.03112678478428052</v>
@@ -37441,7 +37441,7 @@
         <v>0.003398986926103126</v>
       </c>
       <c r="D571" s="1" t="n">
-        <v>163.826</v>
+        <v>243.565</v>
       </c>
       <c r="E571" s="1" t="n">
         <v>0.03109877785326449</v>
@@ -37458,7 +37458,7 @@
         <v>0.00340176727866442</v>
       </c>
       <c r="D572" s="1" t="n">
-        <v>163.825</v>
+        <v>243.565</v>
       </c>
       <c r="E572" s="1" t="n">
         <v>0.03106935760902262</v>
@@ -37475,7 +37475,7 @@
         <v>0.003404520448131242</v>
       </c>
       <c r="D573" s="1" t="n">
-        <v>163.825</v>
+        <v>243.565</v>
       </c>
       <c r="E573" s="1" t="n">
         <v>0.03103966273537433</v>
@@ -37492,7 +37492,7 @@
         <v>0.003407399163762548</v>
       </c>
       <c r="D574" s="1" t="n">
-        <v>163.825</v>
+        <v>243.565</v>
       </c>
       <c r="E574" s="1" t="n">
         <v>0.03101121503429373</v>
@@ -37509,7 +37509,7 @@
         <v>0.00341051304749818</v>
       </c>
       <c r="D575" s="1" t="n">
-        <v>163.825</v>
+        <v>243.565</v>
       </c>
       <c r="E575" s="1" t="n">
         <v>0.03098500386134256</v>
@@ -37526,7 +37526,7 @@
         <v>0.003413799292001526</v>
       </c>
       <c r="D576" s="1" t="n">
-        <v>163.824</v>
+        <v>243.565</v>
       </c>
       <c r="E576" s="1" t="n">
         <v>0.03096057828362666</v>
@@ -37543,7 +37543,7 @@
         <v>0.00341715198261686</v>
       </c>
       <c r="D577" s="1" t="n">
-        <v>163.824</v>
+        <v>243.565</v>
       </c>
       <c r="E577" s="1" t="n">
         <v>0.03093670972308062</v>
@@ -37560,7 +37560,7 @@
         <v>0.00342046520468846</v>
       </c>
       <c r="D578" s="1" t="n">
-        <v>163.824</v>
+        <v>243.565</v>
       </c>
       <c r="E578" s="1" t="n">
         <v>0.03091256792076477</v>
@@ -37577,7 +37577,7 @@
         <v>0.003423653091857699</v>
       </c>
       <c r="D579" s="1" t="n">
-        <v>163.823</v>
+        <v>243.565</v>
       </c>
       <c r="E579" s="1" t="n">
         <v>0.03088750978514269</v>
@@ -37594,7 +37594,7 @@
         <v>0.003426709970954357</v>
       </c>
       <c r="D580" s="1" t="n">
-        <v>163.823</v>
+        <v>243.565</v>
       </c>
       <c r="E580" s="1" t="n">
         <v>0.0308612292947832</v>
@@ -37611,7 +37611,7 @@
         <v>0.003429650217105316</v>
       </c>
       <c r="D581" s="1" t="n">
-        <v>163.823</v>
+        <v>243.565</v>
       </c>
       <c r="E581" s="1" t="n">
         <v>0.03083399163580246</v>
@@ -37628,7 +37628,7 @@
         <v>0.003432488205437455</v>
       </c>
       <c r="D582" s="1" t="n">
-        <v>163.822</v>
+        <v>243.565</v>
       </c>
       <c r="E582" s="1" t="n">
         <v>0.03080606060849126</v>
@@ -37645,7 +37645,7 @@
         <v>0.003435260106508675</v>
       </c>
       <c r="D583" s="1" t="n">
-        <v>163.822</v>
+        <v>243.5648</v>
       </c>
       <c r="E583" s="1" t="n">
         <v>0.03077750483173348</v>
@@ -37662,7 +37662,7 @@
         <v>0.003438089272600953</v>
       </c>
       <c r="D584" s="1" t="n">
-        <v>163.821</v>
+        <v>243.5645</v>
       </c>
       <c r="E584" s="1" t="n">
         <v>0.03074968959443403</v>
@@ -37679,7 +37679,7 @@
         <v>0.003441120851427287</v>
       </c>
       <c r="D585" s="1" t="n">
-        <v>163.821</v>
+        <v>243.5642</v>
       </c>
       <c r="E585" s="1" t="n">
         <v>0.03072364842219987</v>
@@ -37696,7 +37696,7 @@
         <v>0.003444499990700675</v>
       </c>
       <c r="D586" s="1" t="n">
-        <v>163.821</v>
+        <v>243.564</v>
       </c>
       <c r="E586" s="1" t="n">
         <v>0.03070079484998892</v>
@@ -37713,7 +37713,7 @@
         <v>0.00344830684142655</v>
       </c>
       <c r="D587" s="1" t="n">
-        <v>163.82</v>
+        <v>243.564</v>
       </c>
       <c r="E587" s="1" t="n">
         <v>0.03068195485331526</v>
@@ -37730,7 +37730,7 @@
         <v>0.003452361567780092</v>
       </c>
       <c r="D588" s="1" t="n">
-        <v>163.82</v>
+        <v>243.564</v>
       </c>
       <c r="E588" s="1" t="n">
         <v>0.03066525241452246</v>
@@ -37747,7 +37747,7 @@
         <v>0.003456419337228916</v>
       </c>
       <c r="D589" s="1" t="n">
-        <v>163.82</v>
+        <v>243.564</v>
       </c>
       <c r="E589" s="1" t="n">
         <v>0.03064863425759837</v>
@@ -37764,7 +37764,7 @@
         <v>0.003460235317240637</v>
       </c>
       <c r="D590" s="1" t="n">
-        <v>163.819</v>
+        <v>243.564</v>
       </c>
       <c r="E590" s="1" t="n">
         <v>0.03063006175804949</v>
@@ -37781,7 +37781,7 @@
         <v>0.003463635160121401</v>
       </c>
       <c r="D591" s="1" t="n">
-        <v>163.819</v>
+        <v>243.564</v>
       </c>
       <c r="E591" s="1" t="n">
         <v>0.030607746699764</v>
@@ -37798,7 +37798,7 @@
         <v>0.003466726457531482</v>
       </c>
       <c r="D592" s="1" t="n">
-        <v>163.819</v>
+        <v>243.564</v>
       </c>
       <c r="E592" s="1" t="n">
         <v>0.0305827858740151</v>
@@ -37815,7 +37815,7 @@
         <v>0.003469687285969676</v>
       </c>
       <c r="D593" s="1" t="n">
-        <v>163.819</v>
+        <v>243.564</v>
       </c>
       <c r="E593" s="1" t="n">
         <v>0.0305567610825698</v>
@@ -37832,7 +37832,7 @@
         <v>0.003472695721934791</v>
       </c>
       <c r="D594" s="1" t="n">
-        <v>163.818</v>
+        <v>243.564</v>
       </c>
       <c r="E594" s="1" t="n">
         <v>0.03053137201240926</v>
@@ -37849,7 +37849,7 @@
         <v>0.00347587867817815</v>
       </c>
       <c r="D595" s="1" t="n">
-        <v>163.818</v>
+        <v>243.564</v>
       </c>
       <c r="E595" s="1" t="n">
         <v>0.03050747258560272</v>
@@ -37866,7 +37866,7 @@
         <v>0.003479158412461188</v>
       </c>
       <c r="D596" s="1" t="n">
-        <v>163.818</v>
+        <v>243.564</v>
       </c>
       <c r="E596" s="1" t="n">
         <v>0.03048450214621648</v>
@@ -37883,7 +37883,7 @@
         <v>0.003482406018797867</v>
       </c>
       <c r="D597" s="1" t="n">
-        <v>163.818</v>
+        <v>243.564</v>
       </c>
       <c r="E597" s="1" t="n">
         <v>0.03046132841115696</v>
@@ -37900,7 +37900,7 @@
         <v>0.003485492591202144</v>
       </c>
       <c r="D598" s="1" t="n">
-        <v>163.817</v>
+        <v>243.564</v>
       </c>
       <c r="E598" s="1" t="n">
         <v>0.03043695499637085</v>
@@ -37917,7 +37917,7 @@
         <v>0.003488331917533506</v>
       </c>
       <c r="D599" s="1" t="n">
-        <v>163.817</v>
+        <v>243.5637</v>
       </c>
       <c r="E599" s="1" t="n">
         <v>0.03041038043884439</v>
@@ -37934,7 +37934,7 @@
         <v>0.003491008561033535</v>
       </c>
       <c r="D600" s="1" t="n">
-        <v>163.817</v>
+        <v>243.5635</v>
       </c>
       <c r="E600" s="1" t="n">
         <v>0.03038247951844966</v>
@@ -37951,7 +37951,7 @@
         <v>0.003493649778789342</v>
       </c>
       <c r="D601" s="1" t="n">
-        <v>163.816</v>
+        <v>243.5632</v>
       </c>
       <c r="E601" s="1" t="n">
         <v>0.03035449248978299</v>
@@ -37968,7 +37968,7 @@
         <v>0.003496382827888034</v>
       </c>
       <c r="D602" s="1" t="n">
-        <v>163.816</v>
+        <v>243.563</v>
       </c>
       <c r="E602" s="1" t="n">
         <v>0.03032726832260561</v>
@@ -37985,7 +37985,7 @@
         <v>0.003499307531055794</v>
       </c>
       <c r="D603" s="1" t="n">
-        <v>163.816</v>
+        <v>243.563</v>
       </c>
       <c r="E603" s="1" t="n">
         <v>0.03030179496196215</v>
@@ -38002,7 +38002,7 @@
         <v>0.003502413973575099</v>
       </c>
       <c r="D604" s="1" t="n">
-        <v>163.815</v>
+        <v>243.563</v>
       </c>
       <c r="E604" s="1" t="n">
         <v>0.03027810549314507</v>
@@ -38019,7 +38019,7 @@
         <v>0.003505664806367504</v>
       </c>
       <c r="D605" s="1" t="n">
-        <v>163.815</v>
+        <v>243.563</v>
       </c>
       <c r="E605" s="1" t="n">
         <v>0.03025561402595645</v>
@@ -38036,7 +38036,7 @@
         <v>0.003509022680354561</v>
       </c>
       <c r="D606" s="1" t="n">
-        <v>163.815</v>
+        <v>243.563</v>
       </c>
       <c r="E606" s="1" t="n">
         <v>0.03023411980886202</v>
@@ -38053,7 +38053,7 @@
         <v>0.003512451223835116</v>
       </c>
       <c r="D607" s="1" t="n">
-        <v>163.814</v>
+        <v>243.563</v>
       </c>
       <c r="E607" s="1" t="n">
         <v>0.03021343231108096</v>
@@ -38070,7 +38070,7 @@
         <v>0.003515917974617204</v>
       </c>
       <c r="D608" s="1" t="n">
-        <v>163.814</v>
+        <v>243.563</v>
       </c>
       <c r="E608" s="1" t="n">
         <v>0.03019301467575908</v>
@@ -38087,7 +38087,7 @@
         <v>0.00351939144788615</v>
       </c>
       <c r="D609" s="1" t="n">
-        <v>163.814</v>
+        <v>243.563</v>
       </c>
       <c r="E609" s="1" t="n">
         <v>0.03017272239437153</v>
@@ -38104,7 +38104,7 @@
         <v>0.003522840158827285</v>
       </c>
       <c r="D610" s="1" t="n">
-        <v>163.813</v>
+        <v>243.563</v>
       </c>
       <c r="E610" s="1" t="n">
         <v>0.03015241241479917</v>
@@ -38121,7 +38121,7 @@
         <v>0.003526239149007052</v>
       </c>
       <c r="D611" s="1" t="n">
-        <v>163.813</v>
+        <v>243.5627</v>
       </c>
       <c r="E611" s="1" t="n">
         <v>0.03013161799559376</v>
@@ -38138,7 +38138,7 @@
         <v>0.003529589565516365</v>
       </c>
       <c r="D612" s="1" t="n">
-        <v>163.813</v>
+        <v>243.5625</v>
       </c>
       <c r="E612" s="1" t="n">
         <v>0.03011047782905513</v>
@@ -38155,7 +38155,7 @@
         <v>0.003532899081827256</v>
       </c>
       <c r="D613" s="1" t="n">
-        <v>163.813</v>
+        <v>243.5623</v>
       </c>
       <c r="E613" s="1" t="n">
         <v>0.03008905897754973</v>
@@ -38172,7 +38172,7 @@
         <v>0.003536175371411757</v>
       </c>
       <c r="D614" s="1" t="n">
-        <v>163.813</v>
+        <v>243.562</v>
       </c>
       <c r="E614" s="1" t="n">
         <v>0.03006742806224422</v>
@@ -38189,7 +38189,7 @@
         <v>0.003539424259683123</v>
       </c>
       <c r="D615" s="1" t="n">
-        <v>163.813</v>
+        <v>243.562</v>
       </c>
       <c r="E615" s="1" t="n">
         <v>0.0300456355788372</v>
@@ -38206,7 +38206,7 @@
         <v>0.003542644179819511</v>
       </c>
       <c r="D616" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E616" s="1" t="n">
         <v>0.03002379555348183</v>
@@ -38223,7 +38223,7 @@
         <v>0.003545831716940305</v>
       </c>
       <c r="D617" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E617" s="1" t="n">
         <v>0.0300016268333155</v>
@@ -38240,7 +38240,7 @@
         <v>0.003548983456164884</v>
       </c>
       <c r="D618" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E618" s="1" t="n">
         <v>0.02997922816538489</v>
@@ -38257,7 +38257,7 @@
         <v>0.003552097374192507</v>
       </c>
       <c r="D619" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E619" s="1" t="n">
         <v>0.02995658361155618</v>
@@ -38274,7 +38274,7 @@
         <v>0.003555177014041948</v>
       </c>
       <c r="D620" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E620" s="1" t="n">
         <v>0.02993372420458104</v>
@@ -38291,7 +38291,7 @@
         <v>0.003558227310311859</v>
       </c>
       <c r="D621" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E621" s="1" t="n">
         <v>0.02991069247308399</v>
@@ -38308,7 +38308,7 @@
         <v>0.00356125319760089</v>
       </c>
       <c r="D622" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E622" s="1" t="n">
         <v>0.0298875306695296</v>
@@ -38325,7 +38325,7 @@
         <v>0.00356426149998984</v>
       </c>
       <c r="D623" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E623" s="1" t="n">
         <v>0.02986429660408655</v>
@@ -38342,7 +38342,7 @@
         <v>0.003567266599488105</v>
       </c>
       <c r="D624" s="1" t="n">
-        <v>163.812</v>
+        <v>243.562</v>
       </c>
       <c r="E624" s="1" t="n">
         <v>0.02984111093678197</v>
@@ -38359,7 +38359,7 @@
         <v>0.003570284767587227</v>
       </c>
       <c r="D625" s="1" t="n">
-        <v>163.811</v>
+        <v>243.562</v>
       </c>
       <c r="E625" s="1" t="n">
         <v>0.02981823497303774</v>
@@ -38376,7 +38376,7 @@
         <v>0.003573332275778752</v>
       </c>
       <c r="D626" s="1" t="n">
-        <v>163.811</v>
+        <v>243.562</v>
       </c>
       <c r="E626" s="1" t="n">
         <v>0.02979555211357533</v>
@@ -38393,7 +38393,7 @@
         <v>0.00357642328048239</v>
       </c>
       <c r="D627" s="1" t="n">
-        <v>163.811</v>
+        <v>243.5618</v>
       </c>
       <c r="E627" s="1" t="n">
         <v>0.02977330441016298</v>
@@ -38410,7 +38410,7 @@
         <v>0.003579563477830536</v>
       </c>
       <c r="D628" s="1" t="n">
-        <v>163.811</v>
+        <v>243.5615</v>
       </c>
       <c r="E628" s="1" t="n">
         <v>0.02975153710737417</v>
@@ -38427,7 +38427,7 @@
         <v>0.00358275644888375</v>
       </c>
       <c r="D629" s="1" t="n">
-        <v>163.811</v>
+        <v>243.5613</v>
       </c>
       <c r="E629" s="1" t="n">
         <v>0.02973027760808813</v>
@@ -38444,7 +38444,7 @@
         <v>0.003586005774702598</v>
       </c>
       <c r="D630" s="1" t="n">
-        <v>163.811</v>
+        <v>243.561</v>
       </c>
       <c r="E630" s="1" t="n">
         <v>0.02970955313952463</v>
@@ -38461,7 +38461,7 @@
         <v>0.003589310742150968</v>
       </c>
       <c r="D631" s="1" t="n">
-        <v>163.811</v>
+        <v>243.561</v>
       </c>
       <c r="E631" s="1" t="n">
         <v>0.02968935523475708</v>
@@ -38478,7 +38478,7 @@
         <v>0.00359265346130607</v>
       </c>
       <c r="D632" s="1" t="n">
-        <v>163.811</v>
+        <v>243.561</v>
       </c>
       <c r="E632" s="1" t="n">
         <v>0.02966953362835626</v>
@@ -38495,7 +38495,7 @@
         <v>0.00359601174804844</v>
       </c>
       <c r="D633" s="1" t="n">
-        <v>163.811</v>
+        <v>243.561</v>
       </c>
       <c r="E633" s="1" t="n">
         <v>0.02964990360693306</v>
@@ -38512,7 +38512,7 @@
         <v>0.003599363418258617</v>
       </c>
       <c r="D634" s="1" t="n">
-        <v>163.81</v>
+        <v>243.561</v>
       </c>
       <c r="E634" s="1" t="n">
         <v>0.02963040648732329</v>
@@ -38529,7 +38529,7 @@
         <v>0.00360269243652826</v>
       </c>
       <c r="D635" s="1" t="n">
-        <v>163.81</v>
+        <v>243.561</v>
       </c>
       <c r="E635" s="1" t="n">
         <v>0.02961066064547442</v>
@@ -38546,7 +38546,7 @@
         <v>0.003606007362293521</v>
       </c>
       <c r="D636" s="1" t="n">
-        <v>163.81</v>
+        <v>243.561</v>
       </c>
       <c r="E636" s="1" t="n">
         <v>0.02959086184588191</v>
@@ -38563,7 +38563,7 @@
         <v>0.003609322903701675</v>
       </c>
       <c r="D637" s="1" t="n">
-        <v>163.809</v>
+        <v>243.561</v>
       </c>
       <c r="E637" s="1" t="n">
         <v>0.02957125544895248</v>
@@ -38580,7 +38580,7 @@
         <v>0.003612653768899996</v>
       </c>
       <c r="D638" s="1" t="n">
-        <v>163.809</v>
+        <v>243.561</v>
       </c>
       <c r="E638" s="1" t="n">
         <v>0.02955171215350788</v>
@@ -38597,7 +38597,7 @@
         <v>0.003616007683777291</v>
       </c>
       <c r="D639" s="1" t="n">
-        <v>163.808</v>
+        <v>243.5608</v>
       </c>
       <c r="E639" s="1" t="n">
         <v>0.0295325432984351</v>
@@ -38614,7 +38614,7 @@
         <v>0.003619364445188515</v>
       </c>
       <c r="D640" s="1" t="n">
-        <v>163.808</v>
+        <v>243.5605</v>
       </c>
       <c r="E640" s="1" t="n">
         <v>0.0295133339935224</v>
@@ -38631,7 +38631,7 @@
         <v>0.003622696867730154</v>
       </c>
       <c r="D641" s="1" t="n">
-        <v>163.807</v>
+        <v>243.5602</v>
       </c>
       <c r="E641" s="1" t="n">
         <v>0.02949411131776148</v>
@@ -38648,7 +38648,7 @@
         <v>0.003625977765998694</v>
       </c>
       <c r="D642" s="1" t="n">
-        <v>163.807</v>
+        <v>243.56</v>
       </c>
       <c r="E642" s="1" t="n">
         <v>0.02947440629501574</v>
@@ -38665,7 +38665,7 @@
         <v>0.003629190344185621</v>
       </c>
       <c r="D643" s="1" t="n">
-        <v>163.806</v>
+        <v>243.56</v>
       </c>
       <c r="E643" s="1" t="n">
         <v>0.02945433277421799</v>
@@ -38682,7 +38682,7 @@
         <v>0.003632359364862405</v>
       </c>
       <c r="D644" s="1" t="n">
-        <v>163.806</v>
+        <v>243.56</v>
       </c>
       <c r="E644" s="1" t="n">
         <v>0.029433845413624</v>
@@ -38699,7 +38699,7 @@
         <v>0.003635519980195511</v>
       </c>
       <c r="D645" s="1" t="n">
-        <v>163.806</v>
+        <v>243.56</v>
       </c>
       <c r="E645" s="1" t="n">
         <v>0.02941335417237571</v>
@@ -38716,7 +38716,7 @@
         <v>0.003638707342351408</v>
       </c>
       <c r="D646" s="1" t="n">
-        <v>163.806</v>
+        <v>243.56</v>
       </c>
       <c r="E646" s="1" t="n">
         <v>0.02939314302462918</v>
@@ -38733,7 +38733,7 @@
         <v>0.003641948664153753</v>
       </c>
       <c r="D647" s="1" t="n">
-        <v>163.805</v>
+        <v>243.56</v>
       </c>
       <c r="E647" s="1" t="n">
         <v>0.02937355391325631</v>
@@ -38750,7 +38750,7 @@
         <v>0.003645239401054959</v>
       </c>
       <c r="D648" s="1" t="n">
-        <v>163.805</v>
+        <v>243.56</v>
       </c>
       <c r="E648" s="1" t="n">
         <v>0.02935430028469507</v>
@@ -38767,7 +38767,7 @@
         <v>0.003648567069164632</v>
       </c>
       <c r="D649" s="1" t="n">
-        <v>163.805</v>
+        <v>243.56</v>
       </c>
       <c r="E649" s="1" t="n">
         <v>0.02933540347927475</v>
@@ -38784,7 +38784,7 @@
         <v>0.003651919184592374</v>
       </c>
       <c r="D650" s="1" t="n">
-        <v>163.805</v>
+        <v>243.56</v>
       </c>
       <c r="E650" s="1" t="n">
         <v>0.02931676161699426</v>
@@ -38801,7 +38801,7 @@
         <v>0.003655278695413185</v>
       </c>
       <c r="D651" s="1" t="n">
-        <v>163.804</v>
+        <v>243.5598</v>
       </c>
       <c r="E651" s="1" t="n">
         <v>0.02929836029308094</v>
@@ -38818,7 +38818,7 @@
         <v>0.003658610277563641</v>
       </c>
       <c r="D652" s="1" t="n">
-        <v>163.804</v>
+        <v>243.5595</v>
       </c>
       <c r="E652" s="1" t="n">
         <v>0.02927966927422223</v>
@@ -38835,7 +38835,7 @@
         <v>0.003661874038945717</v>
       </c>
       <c r="D653" s="1" t="n">
-        <v>163.804</v>
+        <v>243.5592</v>
       </c>
       <c r="E653" s="1" t="n">
         <v>0.02926049410564283</v>
@@ -38852,7 +38852,7 @@
         <v>0.003665030087461379</v>
       </c>
       <c r="D654" s="1" t="n">
-        <v>163.804</v>
+        <v>243.559</v>
       </c>
       <c r="E654" s="1" t="n">
         <v>0.02924051875972748</v>
@@ -38869,7 +38869,7 @@
         <v>0.003668053702250028</v>
       </c>
       <c r="D655" s="1" t="n">
-        <v>163.804</v>
+        <v>243.559</v>
       </c>
       <c r="E655" s="1" t="n">
         <v>0.02921955001003462</v>
@@ -38886,7 +38886,7 @@
         <v>0.003670980847400753</v>
       </c>
       <c r="D656" s="1" t="n">
-        <v>163.803</v>
+        <v>243.559</v>
       </c>
       <c r="E656" s="1" t="n">
         <v>0.02919800152437161</v>
@@ -38903,7 +38903,7 @@
         <v>0.00367386265824007</v>
       </c>
       <c r="D657" s="1" t="n">
-        <v>163.803</v>
+        <v>243.559</v>
       </c>
       <c r="E657" s="1" t="n">
         <v>0.02917603646840524</v>
@@ -38920,7 +38920,7 @@
         <v>0.003676750270094494</v>
       </c>
       <c r="D658" s="1" t="n">
-        <v>163.803</v>
+        <v>243.559</v>
       </c>
       <c r="E658" s="1" t="n">
         <v>0.02915418478810357</v>
@@ -38937,7 +38937,7 @@
         <v>0.003679683212834614</v>
       </c>
       <c r="D659" s="1" t="n">
-        <v>163.803</v>
+        <v>243.559</v>
       </c>
       <c r="E659" s="1" t="n">
         <v>0.02913275892817815</v>
@@ -38954,7 +38954,7 @@
         <v>0.003682654594507305</v>
       </c>
       <c r="D660" s="1" t="n">
-        <v>163.802</v>
+        <v>243.559</v>
       </c>
       <c r="E660" s="1" t="n">
         <v>0.02911182512653455</v>
@@ -38971,7 +38971,7 @@
         <v>0.00368564591770352</v>
       </c>
       <c r="D661" s="1" t="n">
-        <v>163.802</v>
+        <v>243.559</v>
       </c>
       <c r="E661" s="1" t="n">
         <v>0.02909099025777364</v>
@@ -38988,7 +38988,7 @@
         <v>0.003688638685014209</v>
       </c>
       <c r="D662" s="1" t="n">
-        <v>163.802</v>
+        <v>243.559</v>
       </c>
       <c r="E662" s="1" t="n">
         <v>0.0290702302910472</v>
@@ -39005,7 +39005,7 @@
         <v>0.003691618136628069</v>
       </c>
       <c r="D663" s="1" t="n">
-        <v>163.801</v>
+        <v>243.5588</v>
       </c>
       <c r="E663" s="1" t="n">
         <v>0.0290495511498367</v>
@@ -39022,7 +39022,7 @@
         <v>0.003694584463124793</v>
       </c>
       <c r="D664" s="1" t="n">
-        <v>163.801</v>
+        <v>243.5585</v>
       </c>
       <c r="E664" s="1" t="n">
         <v>0.02902870961171944</v>
@@ -39039,7 +39039,7 @@
         <v>0.003697541592681825</v>
       </c>
       <c r="D665" s="1" t="n">
-        <v>163.8</v>
+        <v>243.5582</v>
       </c>
       <c r="E665" s="1" t="n">
         <v>0.02900798141016084</v>
@@ -39056,7 +39056,7 @@
         <v>0.003700493453476603</v>
       </c>
       <c r="D666" s="1" t="n">
-        <v>163.8</v>
+        <v>243.558</v>
       </c>
       <c r="E666" s="1" t="n">
         <v>0.02898715279610252</v>
@@ -39073,7 +39073,7 @@
         <v>0.003703451844237278</v>
       </c>
       <c r="D667" s="1" t="n">
-        <v>163.799</v>
+        <v>243.558</v>
       </c>
       <c r="E667" s="1" t="n">
         <v>0.02896656033961734</v>
@@ -39090,7 +39090,7 @@
         <v>0.003706460045894823</v>
       </c>
       <c r="D668" s="1" t="n">
-        <v>163.799</v>
+        <v>243.558</v>
       </c>
       <c r="E668" s="1" t="n">
         <v>0.02894629732319361</v>
@@ -39107,7 +39107,7 @@
         <v>0.003709569209930919</v>
       </c>
       <c r="D669" s="1" t="n">
-        <v>163.799</v>
+        <v>243.558</v>
       </c>
       <c r="E669" s="1" t="n">
         <v>0.02892688272743742</v>
@@ -39124,7 +39124,7 @@
         <v>0.003712830487827249</v>
       </c>
       <c r="D670" s="1" t="n">
-        <v>163.798</v>
+        <v>243.558</v>
       </c>
       <c r="E670" s="1" t="n">
         <v>0.02890883281237169</v>
@@ -39141,7 +39141,7 @@
         <v>0.003716273830622135</v>
       </c>
       <c r="D671" s="1" t="n">
-        <v>163.798</v>
+        <v>243.5577</v>
       </c>
       <c r="E671" s="1" t="n">
         <v>0.02889213111502984</v>
@@ -39158,7 +39158,7 @@
         <v>0.003719844387580464</v>
       </c>
       <c r="D672" s="1" t="n">
-        <v>163.798</v>
+        <v>243.5575</v>
       </c>
       <c r="E672" s="1" t="n">
         <v>0.02887646711306443</v>
@@ -39175,7 +39175,7 @@
         <v>0.003723466107523772</v>
       </c>
       <c r="D673" s="1" t="n">
-        <v>163.797</v>
+        <v>243.5572</v>
       </c>
       <c r="E673" s="1" t="n">
         <v>0.02886136827286849</v>
@@ -39192,7 +39192,7 @@
         <v>0.003727062939273587</v>
       </c>
       <c r="D674" s="1" t="n">
-        <v>163.797</v>
+        <v>243.557</v>
       </c>
       <c r="E674" s="1" t="n">
         <v>0.02884600069427026</v>
@@ -39209,7 +39209,7 @@
         <v>0.003730558831651444</v>
       </c>
       <c r="D675" s="1" t="n">
-        <v>163.797</v>
+        <v>243.557</v>
       </c>
       <c r="E675" s="1" t="n">
         <v>0.02882989899434722</v>
@@ -39226,7 +39226,7 @@
         <v>0.003733877733478871</v>
       </c>
       <c r="D676" s="1" t="n">
-        <v>163.797</v>
+        <v>243.557</v>
       </c>
       <c r="E676" s="1" t="n">
         <v>0.02881247961104503</v>
@@ -39243,7 +39243,7 @@
         <v>0.003736943593577402</v>
       </c>
       <c r="D677" s="1" t="n">
-        <v>163.796</v>
+        <v>243.557</v>
       </c>
       <c r="E677" s="1" t="n">
         <v>0.02879328379454835</v>
@@ -39260,7 +39260,7 @@
         <v>0.003739680360768567</v>
       </c>
       <c r="D678" s="1" t="n">
-        <v>163.796</v>
+        <v>243.557</v>
       </c>
       <c r="E678" s="1" t="n">
         <v>0.02877149215565401</v>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27470,7 +27470,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>243.571</v>
+        <v>219.9</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
@@ -27550,7 +27550,7 @@
         <v>2.661398770219695e-05</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>243.5695</v>
+        <v>219.8985</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>0.1112857237805481</v>
@@ -27630,7 +27630,7 @@
         <v>5.261538975502517e-05</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>243.568</v>
+        <v>219.897</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.1154668076100317</v>
@@ -27710,7 +27710,7 @@
         <v>7.810692926740683e-05</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>243.5665</v>
+        <v>219.8955</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.1176226100741688</v>
@@ -27790,7 +27790,7 @@
         <v>0.0001031913293482641</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0.1190558697427829</v>
@@ -27855,7 +27855,7 @@
         <v>0.0001279713131065191</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>243.5648</v>
+        <v>219.8938</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0.1200895057210479</v>
@@ -27900,7 +27900,7 @@
         <v>0.0001525496036510941</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>243.5645</v>
+        <v>219.8935</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0.1208797211170362</v>
@@ -27934,7 +27934,7 @@
         <v>0.0001770289240909113</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>243.5642</v>
+        <v>219.8932</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.1215268809056527</v>
@@ -27964,7 +27964,7 @@
         <v>0.0002015119975348927</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.1221030145613062</v>
@@ -27989,7 +27989,7 @@
         <v>0.0002260726832141147</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>243.5637</v>
+        <v>219.8927</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.1226465337943992</v>
@@ -28006,7 +28006,7 @@
         <v>0.0002506693848482696</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>243.5635</v>
+        <v>219.8925</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0.1231313538342954</v>
@@ -28023,7 +28023,7 @@
         <v>0.0002752316422792043</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>243.5632</v>
+        <v>219.8922</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>0.1235321314044198</v>
@@ -28040,7 +28040,7 @@
         <v>0.0002996889953487651</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.1238339079555154</v>
@@ -28057,7 +28057,7 @@
         <v>0.0003239640399071632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.1240254217468656</v>
@@ -28074,7 +28074,7 @@
         <v>0.0003479515958380678</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>0.1240894832507529</v>
@@ -28091,7 +28091,7 @@
         <v>0.0003715395390335124</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>0.1240118522378651</v>
@@ -28108,7 +28108,7 @@
         <v>0.0003946157453855307</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>0.1237820992815037</v>
@@ -28125,7 +28125,7 @@
         <v>0.0004170775537410905</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0.1233955996827052</v>
@@ -28142,7 +28142,7 @@
         <v>0.0004388601547668969</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0.1228584881388688</v>
@@ -28159,7 +28159,7 @@
         <v>0.0004599082020845885</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>0.1221787452775384</v>
@@ -28176,7 +28176,7 @@
         <v>0.0004801663493158043</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0.1213637245757375</v>
@@ -28193,7 +28193,7 @@
         <v>0.0004996144084749656</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>243.5623</v>
+        <v>219.8913</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.1204272510841864</v>
@@ -28210,7 +28210,7 @@
         <v>0.0005183728251476213</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>243.5615</v>
+        <v>219.8905</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>0.1194131562024102</v>
@@ -28227,7 +28227,7 @@
         <v>0.0005365972033121028</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>243.5607</v>
+        <v>219.8897</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0.1183655353721301</v>
@@ -28244,7 +28244,7 @@
         <v>0.0005544431469467415</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>0.1173216363539563</v>
@@ -28261,7 +28261,7 @@
         <v>0.0005720440726142114</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>243.5592</v>
+        <v>219.8882</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>0.1163081869633094</v>
@@ -28278,7 +28278,7 @@
         <v>0.0005894446472145586</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>243.5585</v>
+        <v>219.8875</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>0.1153302643339966</v>
@@ -28295,7 +28295,7 @@
         <v>0.0006066673502321717</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>243.5577</v>
+        <v>219.8867</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>0.114388645785176</v>
@@ -28312,7 +28312,7 @@
         <v>0.0006237346611514396</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>0.1134837162942553</v>
@@ -28329,7 +28329,7 @@
         <v>0.0006406799617838726</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>0.1126178495617659</v>
@@ -28346,7 +28346,7 @@
         <v>0.0006575802432494677</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>243.555</v>
+        <v>219.884</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>0.1117997089875733</v>
@@ -28363,7 +28363,7 @@
         <v>0.0006745233989953432</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>0.1110400528034714</v>
@@ -28380,7 +28380,7 @@
         <v>0.0006915973224686174</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>243.553</v>
+        <v>219.882</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>0.1103466271593397</v>
@@ -28397,7 +28397,7 @@
         <v>0.0007088418133964745</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>243.5523</v>
+        <v>219.8813</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>0.1097205986317153</v>
@@ -28414,7 +28414,7 @@
         <v>0.0007261042966263634</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>243.5515</v>
+        <v>219.8805</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>0.1091328583492951</v>
@@ -28431,7 +28431,7 @@
         <v>0.0007431841032857985</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>243.5507</v>
+        <v>219.8797</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>0.1085510121743906</v>
@@ -28448,7 +28448,7 @@
         <v>0.0007598805645022946</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>243.55</v>
+        <v>219.879</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>0.1079458151702543</v>
@@ -28465,7 +28465,7 @@
         <v>0.0007760517094351554</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>243.5493</v>
+        <v>219.8783</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>0.1073001618543659</v>
@@ -28482,7 +28482,7 @@
         <v>0.0007917903593708433</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>243.5485</v>
+        <v>219.8775</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>0.1066290900331442</v>
@@ -28499,7 +28499,7 @@
         <v>0.0008072480336276096</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>243.5478</v>
+        <v>219.8768</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>0.1059546719306844</v>
@@ -28516,7 +28516,7 @@
         <v>0.0008225762515237059</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>243.547</v>
+        <v>219.876</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>0.1052963957719576</v>
@@ -28533,7 +28533,7 @@
         <v>0.0008379002154167179</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>243.5462</v>
+        <v>219.8752</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>0.1046694585321525</v>
@@ -28550,7 +28550,7 @@
         <v>0.0008532398598215696</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>243.5455</v>
+        <v>219.8745</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>0.1040735468549181</v>
@@ -28567,7 +28567,7 @@
         <v>0.0008685888022925192</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>243.5448</v>
+        <v>219.8738</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>0.1035060759143579</v>
@@ -28584,7 +28584,7 @@
         <v>0.0008839406603838247</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>243.544</v>
+        <v>219.873</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>0.1029638654141289</v>
@@ -28601,7 +28601,7 @@
         <v>0.0008992686264573183</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>243.5433</v>
+        <v>219.8723</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>0.1024429444577545</v>
@@ -28618,7 +28618,7 @@
         <v>0.0009144641921051261</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>243.5425</v>
+        <v>219.8715</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>0.1019289328018456</v>
@@ -28635,7 +28635,7 @@
         <v>0.0009293984237269484</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>243.5418</v>
+        <v>219.8708</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>0.1014080761625971</v>
@@ -28652,7 +28652,7 @@
         <v>0.0009439423877224854</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>243.541</v>
+        <v>219.87</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>0.1008669688875111</v>
@@ -28669,7 +28669,7 @@
         <v>0.0009580248387294006</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>243.5403</v>
+        <v>219.8693</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>0.1002989122045029</v>
@@ -28686,7 +28686,7 @@
         <v>0.0009718052843372098</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>243.5395</v>
+        <v>219.8685</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>0.09972222949425953</v>
@@ -28703,7 +28703,7 @@
         <v>0.0009855009203733921</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>243.5387</v>
+        <v>219.8677</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>0.09915923256847266</v>
@@ -28720,7 +28720,7 @@
         <v>0.0009993289426654271</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>243.538</v>
+        <v>219.867</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>0.098630942852046</v>
@@ -28737,7 +28737,7 @@
         <v>0.001013457143978018</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>243.5375</v>
+        <v>219.8665</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>0.0981508134539094</v>
@@ -28754,7 +28754,7 @@
         <v>0.001027855704824765</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>243.537</v>
+        <v>219.866</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>0.09771411145470539</v>
@@ -28771,7 +28771,7 @@
         <v>0.001042445402656492</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>243.5365</v>
+        <v>219.8655</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>0.0973106579992216</v>
@@ -28788,7 +28788,7 @@
         <v>0.001057147014924023</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>243.536</v>
+        <v>219.865</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>0.09693178568761178</v>
@@ -28805,7 +28805,7 @@
         <v>0.001071878193075125</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>243.5352</v>
+        <v>219.8642</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>0.09656876836882189</v>
@@ -28822,7 +28822,7 @@
         <v>0.001086544084545324</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>243.5345</v>
+        <v>219.8635</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>0.09621196842422147</v>
@@ -28839,7 +28839,7 @@
         <v>0.00110104671076709</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>243.5337</v>
+        <v>219.8627</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>0.0958529072251585</v>
@@ -28856,7 +28856,7 @@
         <v>0.001115288093172891</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>243.533</v>
+        <v>219.862</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>0.09548368957349142</v>
@@ -28873,7 +28873,7 @@
         <v>0.001129204542136493</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>243.5325</v>
+        <v>219.8615</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>0.09509904665700883</v>
@@ -28890,7 +28890,7 @@
         <v>0.001142869523796845</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>243.532</v>
+        <v>219.861</v>
       </c>
       <c r="E68" s="1" t="n">
         <v>0.09470579067421878</v>
@@ -28907,7 +28907,7 @@
         <v>0.00115639079323419</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>243.5315</v>
+        <v>219.8605</v>
       </c>
       <c r="E69" s="1" t="n">
         <v>0.09431310051574124</v>
@@ -28924,7 +28924,7 @@
         <v>0.001169876105528773</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>243.531</v>
+        <v>219.86</v>
       </c>
       <c r="E70" s="1" t="n">
         <v>0.09392997805670734</v>
@@ -28941,7 +28941,7 @@
         <v>0.001183398583241379</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>243.5305</v>
+        <v>219.8595</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>0.09356137035534468</v>
@@ -28958,7 +28958,7 @@
         <v>0.001196892818854963</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>243.53</v>
+        <v>219.859</v>
       </c>
       <c r="E72" s="1" t="n">
         <v>0.09320151171390739</v>
@@ -28975,7 +28975,7 @@
         <v>0.001210258772333016</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>243.5295</v>
+        <v>219.8585</v>
       </c>
       <c r="E73" s="1" t="n">
         <v>0.09284271134072715</v>
@@ -28992,7 +28992,7 @@
         <v>0.001223396403639034</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>243.529</v>
+        <v>219.858</v>
       </c>
       <c r="E74" s="1" t="n">
         <v>0.09247697085479535</v>
@@ -29009,7 +29009,7 @@
         <v>0.001236233964005328</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>243.5283</v>
+        <v>219.8573</v>
       </c>
       <c r="E75" s="1" t="n">
         <v>0.09209961654602945</v>
@@ -29026,7 +29026,7 @@
         <v>0.001248812869739474</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>243.5275</v>
+        <v>219.8565</v>
       </c>
       <c r="E76" s="1" t="n">
         <v>0.09171379883304261</v>
@@ -29043,7 +29043,7 @@
         <v>0.001261202828417863</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>243.5267</v>
+        <v>219.8557</v>
       </c>
       <c r="E77" s="1" t="n">
         <v>0.09132490757534896</v>
@@ -29060,7 +29060,7 @@
         <v>0.001273473547616889</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>243.526</v>
+        <v>219.855</v>
       </c>
       <c r="E78" s="1" t="n">
         <v>0.09093803483082658</v>
@@ -29077,7 +29077,7 @@
         <v>0.001285695902402913</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>243.5258</v>
+        <v>219.8548</v>
       </c>
       <c r="E79" s="1" t="n">
         <v>0.09055845680085915</v>
@@ -29094,7 +29094,7 @@
         <v>0.001297945437802176</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>243.5255</v>
+        <v>219.8545</v>
       </c>
       <c r="E80" s="1" t="n">
         <v>0.09019112662327873</v>
@@ -29111,7 +29111,7 @@
         <v>0.001310298866330885</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>243.5252</v>
+        <v>219.8542</v>
       </c>
       <c r="E81" s="1" t="n">
         <v>0.08984043797640451</v>
@@ -29128,7 +29128,7 @@
         <v>0.001322832900505251</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>243.525</v>
+        <v>219.854</v>
       </c>
       <c r="E82" s="1" t="n">
         <v>0.08951091532630005</v>
@@ -29145,7 +29145,7 @@
         <v>0.001335586209595795</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>243.5245</v>
+        <v>219.8535</v>
       </c>
       <c r="E83" s="1" t="n">
         <v>0.08920468188120592</v>
@@ -29162,7 +29162,7 @@
         <v>0.001348445289890304</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>243.524</v>
+        <v>219.853</v>
       </c>
       <c r="E84" s="1" t="n">
         <v>0.08891335992498277</v>
@@ -29179,7 +29179,7 @@
         <v>0.001361258594430875</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>243.5235</v>
+        <v>219.8525</v>
       </c>
       <c r="E85" s="1" t="n">
         <v>0.08862614604751046</v>
@@ -29196,7 +29196,7 @@
         <v>0.00137387457625961</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>243.523</v>
+        <v>219.852</v>
       </c>
       <c r="E86" s="1" t="n">
         <v>0.08833387229966326</v>
@@ -29213,7 +29213,7 @@
         <v>0.001386167395906253</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>243.5225</v>
+        <v>219.8515</v>
       </c>
       <c r="E87" s="1" t="n">
         <v>0.08802800479848273</v>
@@ -29230,7 +29230,7 @@
         <v>0.001398114043851136</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>243.522</v>
+        <v>219.851</v>
       </c>
       <c r="E88" s="1" t="n">
         <v>0.08770758483141153</v>
@@ -29247,7 +29247,7 @@
         <v>0.001409717218062237</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>243.5215</v>
+        <v>219.8505</v>
       </c>
       <c r="E89" s="1" t="n">
         <v>0.08737402622344086</v>
@@ -29264,7 +29264,7 @@
         <v>0.001420979616507535</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>243.521</v>
+        <v>219.85</v>
       </c>
       <c r="E90" s="1" t="n">
         <v>0.08702723974231855</v>
@@ -29281,7 +29281,7 @@
         <v>0.001431931678207736</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>243.5207</v>
+        <v>219.8497</v>
       </c>
       <c r="E91" s="1" t="n">
         <v>0.08666988679736835</v>
@@ -29298,7 +29298,7 @@
         <v>0.001442714806394464</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>243.5205</v>
+        <v>219.8495</v>
       </c>
       <c r="E92" s="1" t="n">
         <v>0.08631079314327535</v>
@@ -29315,7 +29315,7 @@
         <v>0.00145349814535207</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>243.5203</v>
+        <v>219.8493</v>
       </c>
       <c r="E93" s="1" t="n">
         <v>0.08595966027640642</v>
@@ -29332,7 +29332,7 @@
         <v>0.001464450839364906</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>243.52</v>
+        <v>219.849</v>
       </c>
       <c r="E94" s="1" t="n">
         <v>0.08562645772838749</v>
@@ -29349,7 +29349,7 @@
         <v>0.001475680364579871</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>243.5195</v>
+        <v>219.8485</v>
       </c>
       <c r="E95" s="1" t="n">
         <v>0.08531643816295487</v>
@@ -29366,7 +29366,7 @@
         <v>0.00148704752459405</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>243.519</v>
+        <v>219.848</v>
       </c>
       <c r="E96" s="1" t="n">
         <v>0.0850215769850417</v>
@@ -29383,7 +29383,7 @@
         <v>0.001498351454867077</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>243.5185</v>
+        <v>219.8475</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>0.08472931410638661</v>
@@ -29400,7 +29400,7 @@
         <v>0.001509391290858582</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>243.518</v>
+        <v>219.847</v>
       </c>
       <c r="E98" s="1" t="n">
         <v>0.08442867512139254</v>
@@ -29417,7 +29417,7 @@
         <v>0.001520018269174404</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>243.5178</v>
+        <v>219.8468</v>
       </c>
       <c r="E99" s="1" t="n">
         <v>0.08411169679232629</v>
@@ -29434,7 +29434,7 @@
         <v>0.001530292031005206</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>243.5175</v>
+        <v>219.8465</v>
       </c>
       <c r="E100" s="1" t="n">
         <v>0.08378216361978076</v>
@@ -29451,7 +29451,7 @@
         <v>0.001540324318687857</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>243.5172</v>
+        <v>219.8462</v>
       </c>
       <c r="E101" s="1" t="n">
         <v>0.0834465237514761</v>
@@ -29468,7 +29468,7 @@
         <v>0.001550226874559223</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>243.517</v>
+        <v>219.846</v>
       </c>
       <c r="E102" s="1" t="n">
         <v>0.0831109574662191</v>
@@ -29485,7 +29485,7 @@
         <v>0.001560110856307789</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>243.5168</v>
+        <v>219.8458</v>
       </c>
       <c r="E103" s="1" t="n">
         <v>0.08278135995956597</v>
@@ -29502,7 +29502,7 @@
         <v>0.001570085083028485</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>243.5165</v>
+        <v>219.8455</v>
       </c>
       <c r="E104" s="1" t="n">
         <v>0.08246291781169843</v>
@@ -29519,7 +29519,7 @@
         <v>0.001580257789167853</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>243.5162</v>
+        <v>219.8452</v>
       </c>
       <c r="E105" s="1" t="n">
         <v>0.08216160353758246</v>
@@ -29536,7 +29536,7 @@
         <v>0.001590737209172439</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>243.516</v>
+        <v>219.845</v>
       </c>
       <c r="E106" s="1" t="n">
         <v>0.08188179523644272</v>
@@ -29553,7 +29553,7 @@
         <v>0.001601567094611052</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>243.5157</v>
+        <v>219.8447</v>
       </c>
       <c r="E107" s="1" t="n">
         <v>0.0816254210145958</v>
@@ -29570,7 +29570,7 @@
         <v>0.001612533265541569</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>243.5155</v>
+        <v>219.8445</v>
       </c>
       <c r="E108" s="1" t="n">
         <v>0.08138132546288539</v>
@@ -29587,7 +29587,7 @@
         <v>0.00162335705914413</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>243.5152</v>
+        <v>219.8442</v>
       </c>
       <c r="E109" s="1" t="n">
         <v>0.08113455019743158</v>
@@ -29604,7 +29604,7 @@
         <v>0.001633759812598878</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>243.515</v>
+        <v>219.844</v>
       </c>
       <c r="E110" s="1" t="n">
         <v>0.08087137124245822</v>
@@ -29621,7 +29621,7 @@
         <v>0.001643545611554173</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>243.5147</v>
+        <v>219.8437</v>
       </c>
       <c r="E111" s="1" t="n">
         <v>0.08058331988090196</v>
@@ -29638,7 +29638,7 @@
         <v>0.001652849535531249</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>243.5145</v>
+        <v>219.8435</v>
       </c>
       <c r="E112" s="1" t="n">
         <v>0.08027732729997705</v>
@@ -29655,7 +29655,7 @@
         <v>0.001661889412519558</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>243.5143</v>
+        <v>219.8433</v>
       </c>
       <c r="E113" s="1" t="n">
         <v>0.07996437561390424</v>
@@ -29672,7 +29672,7 @@
         <v>0.001670883070508552</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>0.07965504141184</v>
@@ -29689,7 +29689,7 @@
         <v>0.001680002981852637</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>243.5138</v>
+        <v>219.8428</v>
       </c>
       <c r="E115" s="1" t="n">
         <v>0.07935737192106723</v>
@@ -29706,7 +29706,7 @@
         <v>0.001689240196366028</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>243.5135</v>
+        <v>219.8425</v>
       </c>
       <c r="E116" s="1" t="n">
         <v>0.07907063059222802</v>
@@ -29723,7 +29723,7 @@
         <v>0.001698540408227893</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>243.5132</v>
+        <v>219.8422</v>
       </c>
       <c r="E117" s="1" t="n">
         <v>0.07879200340939584</v>
@@ -29740,7 +29740,7 @@
         <v>0.0017078493116174</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E118" s="1" t="n">
         <v>0.07851877656387476</v>
@@ -29757,7 +29757,7 @@
         <v>0.001717111562107486</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>243.5128</v>
+        <v>219.8418</v>
       </c>
       <c r="E119" s="1" t="n">
         <v>0.07824795627706468</v>
@@ -29774,7 +29774,7 @@
         <v>0.001726267660846155</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>243.5125</v>
+        <v>219.8415</v>
       </c>
       <c r="E120" s="1" t="n">
         <v>0.0779774407055526</v>
@@ -29791,7 +29791,7 @@
         <v>0.001735257070375183</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>243.5122</v>
+        <v>219.8412</v>
       </c>
       <c r="E121" s="1" t="n">
         <v>0.07770386354634869</v>
@@ -29808,7 +29808,7 @@
         <v>0.001744019253236343</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E122" s="1" t="n">
         <v>0.07742526079464357</v>
@@ -29825,7 +29825,7 @@
         <v>0.001752515844284814</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E123" s="1" t="n">
         <v>0.07713942903919103</v>
@@ -29842,7 +29842,7 @@
         <v>0.001760797167629392</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E124" s="1" t="n">
         <v>0.07684906541954119</v>
@@ -29859,7 +29859,7 @@
         <v>0.001768935719692276</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E125" s="1" t="n">
         <v>0.07655742104023924</v>
@@ -29876,7 +29876,7 @@
         <v>0.001777003996895664</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E126" s="1" t="n">
         <v>0.07626763894907877</v>
@@ -29893,7 +29893,7 @@
         <v>0.00178506885825409</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>243.5118</v>
+        <v>219.8408</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>0.07598251864268254</v>
@@ -29910,7 +29910,7 @@
         <v>0.001793174613151416</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>243.5115</v>
+        <v>219.8405</v>
       </c>
       <c r="E128" s="1" t="n">
         <v>0.07570381612035583</v>
@@ -29927,7 +29927,7 @@
         <v>0.001801359933563841</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>243.5112</v>
+        <v>219.8402</v>
       </c>
       <c r="E129" s="1" t="n">
         <v>0.07543299439295768</v>
@@ -29944,7 +29944,7 @@
         <v>0.001809663491467559</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E130" s="1" t="n">
         <v>0.07517146943931527</v>
@@ -29961,7 +29961,7 @@
         <v>0.001818106811959512</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E131" s="1" t="n">
         <v>0.07491959096390317</v>
@@ -29978,7 +29978,7 @@
         <v>0.001826642832619614</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E132" s="1" t="n">
         <v>0.07467582834172752</v>
@@ -29995,7 +29995,7 @@
         <v>0.001835207344148521</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E133" s="1" t="n">
         <v>0.07443707764424058</v>
@@ -30012,7 +30012,7 @@
         <v>0.001843736137246892</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E134" s="1" t="n">
         <v>0.07420032586385963</v>
@@ -30029,7 +30029,7 @@
         <v>0.001852171233657576</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E135" s="1" t="n">
         <v>0.07396382794560923</v>
@@ -30046,7 +30046,7 @@
         <v>0.001860479579292194</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E136" s="1" t="n">
         <v>0.07372565302328093</v>
@@ -30063,7 +30063,7 @@
         <v>0.001868634351104557</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E137" s="1" t="n">
         <v>0.07348539732740578</v>
@@ -30080,7 +30080,7 @@
         <v>0.00187660872604848</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E138" s="1" t="n">
         <v>0.073241449781997</v>
@@ -30097,7 +30097,7 @@
         <v>0.001884384226049059</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E139" s="1" t="n">
         <v>0.07299378654942464</v>
@@ -30114,7 +30114,7 @@
         <v>0.001891975752916537</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E140" s="1" t="n">
         <v>0.07274245606748407</v>
@@ -30131,7 +30131,7 @@
         <v>0.001899406553432437</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E141" s="1" t="n">
         <v>0.07248903169380341</v>
@@ -30148,7 +30148,7 @@
         <v>0.001906699874378286</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E142" s="1" t="n">
         <v>0.0722338367551119</v>
@@ -30165,7 +30165,7 @@
         <v>0.001913874049517385</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E143" s="1" t="n">
         <v>0.07197789797869525</v>
@@ -30182,7 +30182,7 @@
         <v>0.001920927760540145</v>
       </c>
       <c r="D144" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E144" s="1" t="n">
         <v>0.07172148323675412</v>
@@ -30199,7 +30199,7 @@
         <v>0.00192785477611875</v>
       </c>
       <c r="D145" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E145" s="1" t="n">
         <v>0.07146377455220949</v>
@@ -30216,7 +30216,7 @@
         <v>0.001934648864925388</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E146" s="1" t="n">
         <v>0.07120516486028444</v>
@@ -30233,7 +30233,7 @@
         <v>0.001941318081847259</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E147" s="1" t="n">
         <v>0.07094537457178263</v>
@@ -30250,7 +30250,7 @@
         <v>0.001947927626631631</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E148" s="1" t="n">
         <v>0.07068738501140739</v>
@@ -30267,7 +30267,7 @@
         <v>0.001954556985240787</v>
       </c>
       <c r="D149" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E149" s="1" t="n">
         <v>0.0704334339643997</v>
@@ -30284,7 +30284,7 @@
         <v>0.001961285643637013</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E150" s="1" t="n">
         <v>0.07018657358347999</v>
@@ -30301,7 +30301,7 @@
         <v>0.001968161884976572</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E151" s="1" t="n">
         <v>0.06994866717354301</v>
@@ -30318,7 +30318,7 @@
         <v>0.001975109181191667</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E152" s="1" t="n">
         <v>0.06971624730426294</v>
@@ -30335,7 +30335,7 @@
         <v>0.001982019801408476</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E153" s="1" t="n">
         <v>0.06948600598764205</v>
@@ -30352,7 +30352,7 @@
         <v>0.001988786014753182</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E154" s="1" t="n">
         <v>0.0692535687888145</v>
@@ -30369,7 +30369,7 @@
         <v>0.001995328602121302</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E155" s="1" t="n">
         <v>0.0690165264330737</v>
@@ -30386,7 +30386,7 @@
         <v>0.002001682391485688</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E156" s="1" t="n">
         <v>0.06877616720064846</v>
@@ -30403,7 +30403,7 @@
         <v>0.002007910722588528</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E157" s="1" t="n">
         <v>0.06853471851876157</v>
@@ -30420,7 +30420,7 @@
         <v>0.002014076935172008</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>243.511</v>
+        <v>219.84</v>
       </c>
       <c r="E158" s="1" t="n">
         <v>0.06829434937854423</v>
@@ -30437,7 +30437,7 @@
         <v>0.002020226539476091</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>243.5112</v>
+        <v>219.8402</v>
       </c>
       <c r="E159" s="1" t="n">
         <v>0.06805657161169748</v>
@@ -30454,7 +30454,7 @@
         <v>0.002026333727731821</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>243.5115</v>
+        <v>219.8405</v>
       </c>
       <c r="E160" s="1" t="n">
         <v>0.06782047092812034</v>
@@ -30471,7 +30471,7 @@
         <v>0.002032354862668019</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>243.5118</v>
+        <v>219.8408</v>
       </c>
       <c r="E161" s="1" t="n">
         <v>0.06758456365234446</v>
@@ -30488,7 +30488,7 @@
         <v>0.002038246307013504</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E162" s="1" t="n">
         <v>0.06734740403070419</v>
@@ -30505,7 +30505,7 @@
         <v>0.002043984623523161</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E163" s="1" t="n">
         <v>0.06710824623229301</v>
@@ -30522,7 +30522,7 @@
         <v>0.00204962717505614</v>
       </c>
       <c r="D164" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E164" s="1" t="n">
         <v>0.06686899934368876</v>
@@ -30539,7 +30539,7 @@
         <v>0.002055251524497656</v>
       </c>
       <c r="D165" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E165" s="1" t="n">
         <v>0.06663217947431646</v>
@@ -30556,7 +30556,7 @@
         <v>0.002060935234732921</v>
       </c>
       <c r="D166" s="1" t="n">
-        <v>243.512</v>
+        <v>219.841</v>
       </c>
       <c r="E166" s="1" t="n">
         <v>0.06639996105175112</v>
@@ -30573,7 +30573,7 @@
         <v>0.002066736533294453</v>
       </c>
       <c r="D167" s="1" t="n">
-        <v>243.5122</v>
+        <v>219.8412</v>
       </c>
       <c r="E167" s="1" t="n">
         <v>0.0661746765660404</v>
@@ -30590,7 +30590,7 @@
         <v>0.002072636306303973</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>243.5125</v>
+        <v>219.8415</v>
       </c>
       <c r="E168" s="1" t="n">
         <v>0.06595531483318721</v>
@@ -30607,7 +30607,7 @@
         <v>0.002078596104530505</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>243.5128</v>
+        <v>219.8418</v>
       </c>
       <c r="E169" s="1" t="n">
         <v>0.06574055099377865</v>
@@ -30624,7 +30624,7 @@
         <v>0.00208457747874307</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E170" s="1" t="n">
         <v>0.06552909240048935</v>
@@ -30641,7 +30641,7 @@
         <v>0.002090553558184468</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E171" s="1" t="n">
         <v>0.06532003941520105</v>
@@ -30658,7 +30658,7 @@
         <v>0.002096543785992593</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E172" s="1" t="n">
         <v>0.06511395241349904</v>
@@ -30675,7 +30675,7 @@
         <v>0.002102579183779113</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E173" s="1" t="n">
         <v>0.06491146308099088</v>
@@ -30692,7 +30692,7 @@
         <v>0.002108690773155699</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>243.513</v>
+        <v>219.842</v>
       </c>
       <c r="E174" s="1" t="n">
         <v>0.06471400079436644</v>
@@ -30709,7 +30709,7 @@
         <v>0.002114886102030925</v>
       </c>
       <c r="D175" s="1" t="n">
-        <v>243.5132</v>
+        <v>219.8422</v>
       </c>
       <c r="E175" s="1" t="n">
         <v>0.06452143797568857</v>
@@ -30726,7 +30726,7 @@
         <v>0.002121078823500985</v>
       </c>
       <c r="D176" s="1" t="n">
-        <v>243.5135</v>
+        <v>219.8425</v>
       </c>
       <c r="E176" s="1" t="n">
         <v>0.06433106947369424</v>
@@ -30743,7 +30743,7 @@
         <v>0.002127159116958984</v>
       </c>
       <c r="D177" s="1" t="n">
-        <v>243.5138</v>
+        <v>219.8428</v>
       </c>
       <c r="E177" s="1" t="n">
         <v>0.06413954540166739</v>
@@ -30760,7 +30760,7 @@
         <v>0.00213301716179802</v>
       </c>
       <c r="D178" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E178" s="1" t="n">
         <v>0.06394332476785552</v>
@@ -30777,7 +30777,7 @@
         <v>0.002138565696239664</v>
       </c>
       <c r="D179" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E179" s="1" t="n">
         <v>0.06374042138330177</v>
@@ -30794,7 +30794,7 @@
         <v>0.002143807693819359</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E180" s="1" t="n">
         <v>0.06353077310637087</v>
@@ -30811,7 +30811,7 @@
         <v>0.002148768686901016</v>
       </c>
       <c r="D181" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E181" s="1" t="n">
         <v>0.06331498121943306</v>
@@ -30828,7 +30828,7 @@
         <v>0.002153474207848548</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>243.514</v>
+        <v>219.843</v>
       </c>
       <c r="E182" s="1" t="n">
         <v>0.06309442659848397</v>
@@ -30845,7 +30845,7 @@
         <v>0.002157972926543238</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>243.5143</v>
+        <v>219.8433</v>
       </c>
       <c r="E183" s="1" t="n">
         <v>0.06287008071645467</v>
@@ -30862,7 +30862,7 @@
         <v>0.002162406062935862</v>
       </c>
       <c r="D184" s="1" t="n">
-        <v>243.5145</v>
+        <v>219.8435</v>
       </c>
       <c r="E184" s="1" t="n">
         <v>0.06264662334061398</v>
@@ -30879,7 +30879,7 @@
         <v>0.002166937974494568</v>
       </c>
       <c r="D185" s="1" t="n">
-        <v>243.5147</v>
+        <v>219.8437</v>
       </c>
       <c r="E185" s="1" t="n">
         <v>0.06242825138601774</v>
@@ -30896,7 +30896,7 @@
         <v>0.002171733018687505</v>
       </c>
       <c r="D186" s="1" t="n">
-        <v>243.515</v>
+        <v>219.844</v>
       </c>
       <c r="E186" s="1" t="n">
         <v>0.06221984890078584</v>
@@ -30913,7 +30913,7 @@
         <v>0.002176901077804824</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>243.5152</v>
+        <v>219.8442</v>
       </c>
       <c r="E187" s="1" t="n">
         <v>0.0620246425073574</v>
@@ -30930,7 +30930,7 @@
         <v>0.002182334133424685</v>
       </c>
       <c r="D188" s="1" t="n">
-        <v>243.5155</v>
+        <v>219.8445</v>
       </c>
       <c r="E188" s="1" t="n">
         <v>0.06183883651045132</v>
@@ -30947,7 +30947,7 @@
         <v>0.002187869691947251</v>
       </c>
       <c r="D189" s="1" t="n">
-        <v>243.5157</v>
+        <v>219.8447</v>
       </c>
       <c r="E189" s="1" t="n">
         <v>0.06165795507290891</v>
@@ -30964,7 +30964,7 @@
         <v>0.002193345259772684</v>
       </c>
       <c r="D190" s="1" t="n">
-        <v>243.516</v>
+        <v>219.845</v>
       </c>
       <c r="E190" s="1" t="n">
         <v>0.06147736350846496</v>
@@ -30981,7 +30981,7 @@
         <v>0.002198630832435984</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>243.5162</v>
+        <v>219.8452</v>
       </c>
       <c r="E191" s="1" t="n">
         <v>0.06129369042552286</v>
@@ -30998,7 +30998,7 @@
         <v>0.002203726362011487</v>
       </c>
       <c r="D192" s="1" t="n">
-        <v>243.5165</v>
+        <v>219.8455</v>
       </c>
       <c r="E192" s="1" t="n">
         <v>0.06110647198914575</v>
@@ -31015,7 +31015,7 @@
         <v>0.002208664289708364</v>
       </c>
       <c r="D193" s="1" t="n">
-        <v>243.5168</v>
+        <v>219.8458</v>
       </c>
       <c r="E193" s="1" t="n">
         <v>0.06091691385045522</v>
@@ -31032,7 +31032,7 @@
         <v>0.002213477056735786</v>
       </c>
       <c r="D194" s="1" t="n">
-        <v>243.517</v>
+        <v>219.846</v>
       </c>
       <c r="E194" s="1" t="n">
         <v>0.0607259431401001</v>
@@ -31049,7 +31049,7 @@
         <v>0.002218185060532989</v>
       </c>
       <c r="D195" s="1" t="n">
-        <v>243.5172</v>
+        <v>219.8462</v>
       </c>
       <c r="E195" s="1" t="n">
         <v>0.06053439323680806</v>
@@ -31066,7 +31066,7 @@
         <v>0.002222760523459464</v>
       </c>
       <c r="D196" s="1" t="n">
-        <v>243.5175</v>
+        <v>219.8465</v>
       </c>
       <c r="E196" s="1" t="n">
         <v>0.06034101331060278</v>
@@ -31083,7 +31083,7 @@
         <v>0.002227163624104767</v>
       </c>
       <c r="D197" s="1" t="n">
-        <v>243.5178</v>
+        <v>219.8468</v>
       </c>
       <c r="E197" s="1" t="n">
         <v>0.06014500781608029</v>
@@ -31100,7 +31100,7 @@
         <v>0.002231354541058451</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>243.518</v>
+        <v>219.847</v>
       </c>
       <c r="E198" s="1" t="n">
         <v>0.05994534774201475</v>
@@ -31117,7 +31117,7 @@
         <v>0.002235325085873816</v>
       </c>
       <c r="D199" s="1" t="n">
-        <v>243.5182</v>
+        <v>219.8472</v>
       </c>
       <c r="E199" s="1" t="n">
         <v>0.05974187076292248</v>
@@ -31134,7 +31134,7 @@
         <v>0.002239193601959133</v>
       </c>
       <c r="D200" s="1" t="n">
-        <v>243.5185</v>
+        <v>219.8475</v>
       </c>
       <c r="E200" s="1" t="n">
         <v>0.05953778223335349</v>
@@ -31151,7 +31151,7 @@
         <v>0.00224311006568642</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>243.5188</v>
+        <v>219.8478</v>
       </c>
       <c r="E201" s="1" t="n">
         <v>0.05933730823316435</v>
@@ -31168,7 +31168,7 @@
         <v>0.002247224453427692</v>
       </c>
       <c r="D202" s="1" t="n">
-        <v>243.519</v>
+        <v>219.848</v>
       </c>
       <c r="E202" s="1" t="n">
         <v>0.05914384470982588</v>
@@ -31185,7 +31185,7 @@
         <v>0.002251631134770238</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>243.5192</v>
+        <v>219.8482</v>
       </c>
       <c r="E203" s="1" t="n">
         <v>0.05896000278338819</v>
@@ -31202,7 +31202,7 @@
         <v>0.002256202052162433</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>243.5195</v>
+        <v>219.8485</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0.05878230068974353</v>
@@ -31219,7 +31219,7 @@
         <v>0.002260753541267923</v>
       </c>
       <c r="D205" s="1" t="n">
-        <v>243.5198</v>
+        <v>219.8488</v>
       </c>
       <c r="E205" s="1" t="n">
         <v>0.05860588492288851</v>
@@ -31236,7 +31236,7 @@
         <v>0.002265101937750358</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>243.52</v>
+        <v>219.849</v>
       </c>
       <c r="E206" s="1" t="n">
         <v>0.05842624439730312</v>
@@ -31253,7 +31253,7 @@
         <v>0.002269117332231759</v>
       </c>
       <c r="D207" s="1" t="n">
-        <v>243.5203</v>
+        <v>219.8493</v>
       </c>
       <c r="E207" s="1" t="n">
         <v>0.05823960426362389</v>
@@ -31270,7 +31270,7 @@
         <v>0.002272884835167656</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>243.5205</v>
+        <v>219.8495</v>
       </c>
       <c r="E208" s="1" t="n">
         <v>0.05804848449286561</v>
@@ -31287,7 +31287,7 @@
         <v>0.002276543311971955</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>243.5207</v>
+        <v>219.8497</v>
       </c>
       <c r="E209" s="1" t="n">
         <v>0.05785648011938557</v>
@@ -31304,7 +31304,7 @@
         <v>0.00228023162805856</v>
       </c>
       <c r="D210" s="1" t="n">
-        <v>243.521</v>
+        <v>219.85</v>
       </c>
       <c r="E210" s="1" t="n">
         <v>0.05766735841838327</v>
@@ -31321,7 +31321,7 @@
         <v>0.002284048575570907</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>243.5212</v>
+        <v>219.8502</v>
       </c>
       <c r="E211" s="1" t="n">
         <v>0.05748308133949132</v>
@@ -31338,7 +31338,7 @@
         <v>0.002287932653570548</v>
       </c>
       <c r="D212" s="1" t="n">
-        <v>243.5215</v>
+        <v>219.8505</v>
       </c>
       <c r="E212" s="1" t="n">
         <v>0.05730227791930999</v>
@@ -31355,7 +31355,7 @@
         <v>0.002291782287848565</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>243.5217</v>
+        <v>219.8507</v>
       </c>
       <c r="E213" s="1" t="n">
         <v>0.05712236617602257</v>
@@ -31372,7 +31372,7 @@
         <v>0.002295495904196042</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>243.522</v>
+        <v>219.851</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0.05694081361178396</v>
@@ -31389,7 +31389,7 @@
         <v>0.002299004864902178</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>243.5222</v>
+        <v>219.8512</v>
       </c>
       <c r="E215" s="1" t="n">
         <v>0.05675594913816879</v>
@@ -31406,7 +31406,7 @@
         <v>0.002302372278248647</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>243.5225</v>
+        <v>219.8515</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0.05656937038733476</v>
@@ -31423,7 +31423,7 @@
         <v>0.002305694189015241</v>
       </c>
       <c r="D217" s="1" t="n">
-        <v>243.5228</v>
+        <v>219.8518</v>
       </c>
       <c r="E217" s="1" t="n">
         <v>0.05638321311314566</v>
@@ -31440,7 +31440,7 @@
         <v>0.002309066641981755</v>
       </c>
       <c r="D218" s="1" t="n">
-        <v>243.523</v>
+        <v>219.852</v>
       </c>
       <c r="E218" s="1" t="n">
         <v>0.05620028059415675</v>
@@ -31457,7 +31457,7 @@
         <v>0.00231255639534559</v>
       </c>
       <c r="D219" s="1" t="n">
-        <v>243.5232</v>
+        <v>219.8522</v>
       </c>
       <c r="E219" s="1" t="n">
         <v>0.05602191014562068</v>
@@ -31474,7 +31474,7 @@
         <v>0.002316113060974595</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>243.5235</v>
+        <v>219.8525</v>
       </c>
       <c r="E220" s="1" t="n">
         <v>0.05584682298218582</v>
@@ -31491,7 +31491,7 @@
         <v>0.002319656964154227</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>243.5238</v>
+        <v>219.8528</v>
       </c>
       <c r="E221" s="1" t="n">
         <v>0.05567282698254609</v>
@@ -31508,7 +31508,7 @@
         <v>0.002323108430169946</v>
       </c>
       <c r="D222" s="1" t="n">
-        <v>243.524</v>
+        <v>219.853</v>
       </c>
       <c r="E222" s="1" t="n">
         <v>0.05549846934028149</v>
@@ -31525,7 +31525,7 @@
         <v>0.002326425379775902</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>243.5242</v>
+        <v>219.8532</v>
       </c>
       <c r="E223" s="1" t="n">
         <v>0.0553225226661764</v>
@@ -31542,7 +31542,7 @@
         <v>0.002329716115601015</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>243.5245</v>
+        <v>219.8535</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>0.05514734038644178</v>
@@ -31559,7 +31559,7 @@
         <v>0.002333126535742898</v>
       </c>
       <c r="D225" s="1" t="n">
-        <v>243.5248</v>
+        <v>219.8538</v>
       </c>
       <c r="E225" s="1" t="n">
         <v>0.05497681133509232</v>
@@ -31576,7 +31576,7 @@
         <v>0.002336802538299164</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>243.525</v>
+        <v>219.854</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0.05481383444554529</v>
@@ -31593,7 +31593,7 @@
         <v>0.00234082833310125</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>243.5252</v>
+        <v>219.8542</v>
       </c>
       <c r="E227" s="1" t="n">
         <v>0.05466073252972457</v>
@@ -31610,7 +31610,7 @@
         <v>0.002345041376915894</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>243.5255</v>
+        <v>219.8545</v>
       </c>
       <c r="E228" s="1" t="n">
         <v>0.05451313662523762</v>
@@ -31627,7 +31627,7 @@
         <v>0.00234921743824366</v>
       </c>
       <c r="D229" s="1" t="n">
-        <v>243.5258</v>
+        <v>219.8548</v>
       </c>
       <c r="E229" s="1" t="n">
         <v>0.05436601107339335</v>
@@ -31644,7 +31644,7 @@
         <v>0.002353132285585111</v>
       </c>
       <c r="D230" s="1" t="n">
-        <v>243.526</v>
+        <v>219.855</v>
       </c>
       <c r="E230" s="1" t="n">
         <v>0.05421418343801334</v>
@@ -31661,7 +31661,7 @@
         <v>0.002356629775254825</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>243.5263</v>
+        <v>219.8553</v>
       </c>
       <c r="E231" s="1" t="n">
         <v>0.05405436208747426</v>
@@ -31678,7 +31678,7 @@
         <v>0.002359826114823439</v>
       </c>
       <c r="D232" s="1" t="n">
-        <v>243.5265</v>
+        <v>219.8555</v>
       </c>
       <c r="E232" s="1" t="n">
         <v>0.05388885404318669</v>
@@ -31695,7 +31695,7 @@
         <v>0.002362905599675604</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>243.5267</v>
+        <v>219.8557</v>
       </c>
       <c r="E233" s="1" t="n">
         <v>0.05372214930507026</v>
@@ -31712,7 +31712,7 @@
         <v>0.002366052525195971</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>243.527</v>
+        <v>219.856</v>
       </c>
       <c r="E234" s="1" t="n">
         <v>0.05355843526598324</v>
@@ -31729,7 +31729,7 @@
         <v>0.00236940104541944</v>
       </c>
       <c r="D235" s="1" t="n">
-        <v>243.5272</v>
+        <v>219.8562</v>
       </c>
       <c r="E235" s="1" t="n">
         <v>0.05340069631876838</v>
@@ -31746,7 +31746,7 @@
         <v>0.002372884748981894</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>243.5275</v>
+        <v>219.8565</v>
       </c>
       <c r="E236" s="1" t="n">
         <v>0.05324736443251123</v>
@@ -31763,7 +31763,7 @@
         <v>0.002376387083169464</v>
       </c>
       <c r="D237" s="1" t="n">
-        <v>243.5277</v>
+        <v>219.8567</v>
       </c>
       <c r="E237" s="1" t="n">
         <v>0.05309577834186136</v>
@@ -31780,7 +31780,7 @@
         <v>0.002379791495268283</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>243.528</v>
+        <v>219.857</v>
       </c>
       <c r="E238" s="1" t="n">
         <v>0.05294332253446389</v>
@@ -31797,7 +31797,7 @@
         <v>0.002383016125132892</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>243.5282</v>
+        <v>219.8572</v>
       </c>
       <c r="E239" s="1" t="n">
         <v>0.05278819477339353</v>
@@ -31814,7 +31814,7 @@
         <v>0.00238611788289149</v>
       </c>
       <c r="D240" s="1" t="n">
-        <v>243.5285</v>
+        <v>219.8575</v>
       </c>
       <c r="E240" s="1" t="n">
         <v>0.05263168445690758</v>
@@ -31831,7 +31831,7 @@
         <v>0.002389188371240681</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>243.5288</v>
+        <v>219.8578</v>
       </c>
       <c r="E241" s="1" t="n">
         <v>0.05247582108219135</v>
@@ -31848,7 +31848,7 @@
         <v>0.002392319192877076</v>
       </c>
       <c r="D242" s="1" t="n">
-        <v>243.529</v>
+        <v>219.858</v>
       </c>
       <c r="E242" s="1" t="n">
         <v>0.05232259984930951</v>
@@ -31865,7 +31865,7 @@
         <v>0.002395573604809415</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>243.5292</v>
+        <v>219.8582</v>
       </c>
       <c r="E243" s="1" t="n">
         <v>0.0521733650420622</v>
@@ -31882,7 +31882,7 @@
         <v>0.002398901481294975</v>
       </c>
       <c r="D244" s="1" t="n">
-        <v>243.5295</v>
+        <v>219.8585</v>
       </c>
       <c r="E244" s="1" t="n">
         <v>0.05202697939410761</v>
@@ -31899,7 +31899,7 @@
         <v>0.002402224350903167</v>
       </c>
       <c r="D245" s="1" t="n">
-        <v>243.5298</v>
+        <v>219.8588</v>
       </c>
       <c r="E245" s="1" t="n">
         <v>0.05188171242607691</v>
@@ -31916,7 +31916,7 @@
         <v>0.002405463742203402</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>243.53</v>
+        <v>219.859</v>
       </c>
       <c r="E246" s="1" t="n">
         <v>0.05173586241471949</v>
@@ -31933,7 +31933,7 @@
         <v>0.002408559240228179</v>
       </c>
       <c r="D247" s="1" t="n">
-        <v>243.5302</v>
+        <v>219.8592</v>
       </c>
       <c r="E247" s="1" t="n">
         <v>0.05158814254177434</v>
@@ -31950,7 +31950,7 @@
         <v>0.002411522655862361</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>243.5305</v>
+        <v>219.8595</v>
       </c>
       <c r="E248" s="1" t="n">
         <v>0.05143882780250349</v>
@@ -31967,7 +31967,7 @@
         <v>0.002414383856453898</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>243.5308</v>
+        <v>219.8598</v>
       </c>
       <c r="E249" s="1" t="n">
         <v>0.05128857225022866</v>
@@ -31984,7 +31984,7 @@
         <v>0.002417172709350743</v>
       </c>
       <c r="D250" s="1" t="n">
-        <v>243.531</v>
+        <v>219.86</v>
       </c>
       <c r="E250" s="1" t="n">
         <v>0.05113780408764111</v>
@@ -32001,7 +32001,7 @@
         <v>0.00241992900101967</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>243.5312</v>
+        <v>219.8602</v>
       </c>
       <c r="E251" s="1" t="n">
         <v>0.05098779615105785</v>
@@ -32018,7 +32018,7 @@
         <v>0.002422732194402755</v>
       </c>
       <c r="D252" s="1" t="n">
-        <v>243.5315</v>
+        <v>219.8605</v>
       </c>
       <c r="E252" s="1" t="n">
         <v>0.05083999347982419</v>
@@ -32035,7 +32035,7 @@
         <v>0.002425671671560896</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>243.5318</v>
+        <v>219.8608</v>
       </c>
       <c r="E253" s="1" t="n">
         <v>0.05069623740051465</v>
@@ -32052,7 +32052,7 @@
         <v>0.002428836814554991</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>243.532</v>
+        <v>219.861</v>
       </c>
       <c r="E254" s="1" t="n">
         <v>0.05055812690361336</v>
@@ -32069,7 +32069,7 @@
         <v>0.002432276270978178</v>
       </c>
       <c r="D255" s="1" t="n">
-        <v>243.5323</v>
+        <v>219.8613</v>
       </c>
       <c r="E255" s="1" t="n">
         <v>0.05042702618328389</v>
@@ -32086,7 +32086,7 @@
         <v>0.002435875750552536</v>
       </c>
       <c r="D256" s="1" t="n">
-        <v>243.5325</v>
+        <v>219.8615</v>
       </c>
       <c r="E256" s="1" t="n">
         <v>0.05030006886962563</v>
@@ -32103,7 +32103,7 @@
         <v>0.002439480228532388</v>
       </c>
       <c r="D257" s="1" t="n">
-        <v>243.5327</v>
+        <v>219.8617</v>
       </c>
       <c r="E257" s="1" t="n">
         <v>0.05017443834842027</v>
@@ -32120,7 +32120,7 @@
         <v>0.002442934680172049</v>
       </c>
       <c r="D258" s="1" t="n">
-        <v>243.533</v>
+        <v>219.862</v>
       </c>
       <c r="E258" s="1" t="n">
         <v>0.05004652270049628</v>
@@ -32137,7 +32137,7 @@
         <v>0.002446124769378371</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>243.5332</v>
+        <v>219.8622</v>
       </c>
       <c r="E259" s="1" t="n">
         <v>0.04991443504061856</v>
@@ -32154,7 +32154,7 @@
         <v>0.002449098914668323</v>
       </c>
       <c r="D260" s="1" t="n">
-        <v>243.5335</v>
+        <v>219.8625</v>
       </c>
       <c r="E260" s="1" t="n">
         <v>0.0497787904746884</v>
@@ -32171,7 +32171,7 @@
         <v>0.002451946223211407</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>243.5337</v>
+        <v>219.8627</v>
       </c>
       <c r="E261" s="1" t="n">
         <v>0.04964185178516733</v>
@@ -32188,7 +32188,7 @@
         <v>0.002454755802177124</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>243.534</v>
+        <v>219.863</v>
       </c>
       <c r="E262" s="1" t="n">
         <v>0.04950501518215963</v>
@@ -32205,7 +32205,7 @@
         <v>0.002457612676435201</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>243.5342</v>
+        <v>219.8632</v>
       </c>
       <c r="E263" s="1" t="n">
         <v>0.04937040226445663</v>
@@ -32222,7 +32222,7 @@
         <v>0.002460585541656275</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>243.5345</v>
+        <v>219.8635</v>
       </c>
       <c r="E264" s="1" t="n">
         <v>0.04923894822745042</v>
@@ -32239,7 +32239,7 @@
         <v>0.002463739011211209</v>
       </c>
       <c r="D265" s="1" t="n">
-        <v>243.5348</v>
+        <v>219.8638</v>
       </c>
       <c r="E265" s="1" t="n">
         <v>0.04911231711650424</v>
@@ -32256,7 +32256,7 @@
         <v>0.002467137698470864</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>243.535</v>
+        <v>219.864</v>
       </c>
       <c r="E266" s="1" t="n">
         <v>0.04899132496780554</v>
@@ -32273,7 +32273,7 @@
         <v>0.002470802580736493</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>243.5352</v>
+        <v>219.8642</v>
       </c>
       <c r="E267" s="1" t="n">
         <v>0.04887673255766622</v>
@@ -32290,7 +32290,7 @@
         <v>0.002474580091030905</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>243.5355</v>
+        <v>219.8645</v>
       </c>
       <c r="E268" s="1" t="n">
         <v>0.04876503102186772</v>
@@ -32307,7 +32307,7 @@
         <v>0.002478273026307293</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>243.5358</v>
+        <v>219.8648</v>
       </c>
       <c r="E269" s="1" t="n">
         <v>0.0486527245827438</v>
@@ -32324,7 +32324,7 @@
         <v>0.002481684183518854</v>
       </c>
       <c r="D270" s="1" t="n">
-        <v>243.536</v>
+        <v>219.865</v>
       </c>
       <c r="E270" s="1" t="n">
         <v>0.04853555563411324</v>
@@ -32341,7 +32341,7 @@
         <v>0.002484690366743772</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>243.5362</v>
+        <v>219.8652</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0.04841158537941274</v>
@@ -32358,7 +32358,7 @@
         <v>0.002487464408560187</v>
       </c>
       <c r="D272" s="1" t="n">
-        <v>243.5365</v>
+        <v>219.8655</v>
       </c>
       <c r="E272" s="1" t="n">
         <v>0.04828383943556482</v>
@@ -32375,7 +32375,7 @@
         <v>0.002490253148671224</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>243.5368</v>
+        <v>219.8658</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>0.04815753821008842</v>
@@ -32392,7 +32392,7 @@
         <v>0.002493303426780009</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>243.537</v>
+        <v>219.866</v>
       </c>
       <c r="E274" s="1" t="n">
         <v>0.0480370176579896</v>
@@ -32409,7 +32409,7 @@
         <v>0.00249677967486558</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>243.5373</v>
+        <v>219.8663</v>
       </c>
       <c r="E275" s="1" t="n">
         <v>0.04792557063592997</v>
@@ -32426,7 +32426,7 @@
         <v>0.002500516694010608</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>243.5375</v>
+        <v>219.8665</v>
       </c>
       <c r="E276" s="1" t="n">
         <v>0.04782013852042883</v>
@@ -32443,7 +32443,7 @@
         <v>0.002504266877573674</v>
       </c>
       <c r="D277" s="1" t="n">
-        <v>243.5378</v>
+        <v>219.8668</v>
       </c>
       <c r="E277" s="1" t="n">
         <v>0.04771553632803509</v>
@@ -32460,7 +32460,7 @@
         <v>0.002507782618913359</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>243.538</v>
+        <v>219.867</v>
       </c>
       <c r="E278" s="1" t="n">
         <v>0.04760725386940356</v>
@@ -32477,7 +32477,7 @@
         <v>0.002510883024321127</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>243.5383</v>
+        <v>219.8673</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0.04749210985543035</v>
@@ -32494,7 +32494,7 @@
         <v>0.002513654051819962</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>243.5385</v>
+        <v>219.8675</v>
       </c>
       <c r="E280" s="1" t="n">
         <v>0.04737140106177624</v>
@@ -32511,7 +32511,7 @@
         <v>0.002516248372365732</v>
       </c>
       <c r="D281" s="1" t="n">
-        <v>243.5387</v>
+        <v>219.8677</v>
       </c>
       <c r="E281" s="1" t="n">
         <v>0.0472482529602919</v>
@@ -32528,7 +32528,7 @@
         <v>0.002518818656914302</v>
       </c>
       <c r="D282" s="1" t="n">
-        <v>243.539</v>
+        <v>219.868</v>
       </c>
       <c r="E282" s="1" t="n">
         <v>0.04712554836144092</v>
@@ -32545,7 +32545,7 @@
         <v>0.002521486118649736</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>243.5392</v>
+        <v>219.8682</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0.04700573994816104</v>
@@ -32562,7 +32562,7 @@
         <v>0.002524246139668868</v>
       </c>
       <c r="D284" s="1" t="n">
-        <v>243.5395</v>
+        <v>219.8685</v>
       </c>
       <c r="E284" s="1" t="n">
         <v>0.04688831669380352</v>
@@ -32579,7 +32579,7 @@
         <v>0.002527062644296725</v>
       </c>
       <c r="D285" s="1" t="n">
-        <v>243.5397</v>
+        <v>219.8687</v>
       </c>
       <c r="E285" s="1" t="n">
         <v>0.04677278149109811</v>
@@ -32596,7 +32596,7 @@
         <v>0.002529899556858338</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>243.54</v>
+        <v>219.869</v>
       </c>
       <c r="E286" s="1" t="n">
         <v>0.04665864518688558</v>
@@ -32613,7 +32613,7 @@
         <v>0.002532725244339933</v>
       </c>
       <c r="D287" s="1" t="n">
-        <v>243.5402</v>
+        <v>219.8692</v>
       </c>
       <c r="E287" s="1" t="n">
         <v>0.04654492037245717</v>
@@ -32630,7 +32630,7 @@
         <v>0.00253552584437254</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>243.5405</v>
+        <v>219.8695</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0.04643154358355026</v>
@@ -32647,7 +32647,7 @@
         <v>0.002538291937248384</v>
       </c>
       <c r="D289" s="1" t="n">
-        <v>243.5408</v>
+        <v>219.8698</v>
       </c>
       <c r="E289" s="1" t="n">
         <v>0.04631853419056781</v>
@@ -32664,7 +32664,7 @@
         <v>0.002541014103259693</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>243.541</v>
+        <v>219.87</v>
       </c>
       <c r="E290" s="1" t="n">
         <v>0.04620532867471523</v>
@@ -32681,7 +32681,7 @@
         <v>0.002543692228776573</v>
       </c>
       <c r="D291" s="1" t="n">
-        <v>243.5412</v>
+        <v>219.8702</v>
       </c>
       <c r="E291" s="1" t="n">
         <v>0.04609212039956135</v>
@@ -32698,7 +32698,7 @@
         <v>0.002546363424480635</v>
       </c>
       <c r="D292" s="1" t="n">
-        <v>243.5415</v>
+        <v>219.8705</v>
       </c>
       <c r="E292" s="1" t="n">
         <v>0.04597957948003637</v>
@@ -32715,7 +32715,7 @@
         <v>0.002549074107131369</v>
       </c>
       <c r="D293" s="1" t="n">
-        <v>243.5418</v>
+        <v>219.8708</v>
       </c>
       <c r="E293" s="1" t="n">
         <v>0.04586872724392396</v>
@@ -32732,7 +32732,7 @@
         <v>0.002551870693488263</v>
       </c>
       <c r="D294" s="1" t="n">
-        <v>243.542</v>
+        <v>219.871</v>
       </c>
       <c r="E294" s="1" t="n">
         <v>0.04575999386372017</v>
@@ -32749,7 +32749,7 @@
         <v>0.002554784044390916</v>
       </c>
       <c r="D295" s="1" t="n">
-        <v>243.5422</v>
+        <v>219.8712</v>
       </c>
       <c r="E295" s="1" t="n">
         <v>0.04565410039900038</v>
@@ -32766,7 +32766,7 @@
         <v>0.002557782796999358</v>
       </c>
       <c r="D296" s="1" t="n">
-        <v>243.5425</v>
+        <v>219.8715</v>
       </c>
       <c r="E296" s="1" t="n">
         <v>0.04555045899647557</v>
@@ -32783,7 +32783,7 @@
         <v>0.002560820032553728</v>
       </c>
       <c r="D297" s="1" t="n">
-        <v>243.5428</v>
+        <v>219.8718</v>
       </c>
       <c r="E297" s="1" t="n">
         <v>0.04544821378551758</v>
@@ -32800,7 +32800,7 @@
         <v>0.002563848832294164</v>
       </c>
       <c r="D298" s="1" t="n">
-        <v>243.543</v>
+        <v>219.872</v>
       </c>
       <c r="E298" s="1" t="n">
         <v>0.04534671147791106</v>
@@ -32817,7 +32817,7 @@
         <v>0.002566835940862289</v>
       </c>
       <c r="D299" s="1" t="n">
-        <v>243.5433</v>
+        <v>219.8723</v>
       </c>
       <c r="E299" s="1" t="n">
         <v>0.04524497803756976</v>
@@ -32834,7 +32834,7 @@
         <v>0.002569802756505658</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>243.5435</v>
+        <v>219.8725</v>
       </c>
       <c r="E300" s="1" t="n">
         <v>0.04514358106673132</v>
@@ -32851,7 +32851,7 @@
         <v>0.002572784340873312</v>
       </c>
       <c r="D301" s="1" t="n">
-        <v>243.5438</v>
+        <v>219.8728</v>
       </c>
       <c r="E301" s="1" t="n">
         <v>0.04504313097802874</v>
@@ -32868,7 +32868,7 @@
         <v>0.002575815755614292</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>243.544</v>
+        <v>219.873</v>
       </c>
       <c r="E302" s="1" t="n">
         <v>0.04494422995587797</v>
@@ -32885,7 +32885,7 @@
         <v>0.002578910488888114</v>
       </c>
       <c r="D303" s="1" t="n">
-        <v>243.5443</v>
+        <v>219.8733</v>
       </c>
       <c r="E303" s="1" t="n">
         <v>0.0448470969333271</v>
@@ -32902,7 +32902,7 @@
         <v>0.002581995734896212</v>
       </c>
       <c r="D304" s="1" t="n">
-        <v>243.5445</v>
+        <v>219.8735</v>
       </c>
       <c r="E304" s="1" t="n">
         <v>0.04475045228903878</v>
@@ -32919,7 +32919,7 @@
         <v>0.002584977114350495</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>243.5447</v>
+        <v>219.8737</v>
       </c>
       <c r="E305" s="1" t="n">
         <v>0.04465266081949579</v>
@@ -32936,7 +32936,7 @@
         <v>0.002587760247962873</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>243.545</v>
+        <v>219.874</v>
       </c>
       <c r="E306" s="1" t="n">
         <v>0.04455210906917189</v>
@@ -32953,7 +32953,7 @@
         <v>0.002590286936673096</v>
       </c>
       <c r="D307" s="1" t="n">
-        <v>243.5452</v>
+        <v>219.8742</v>
       </c>
       <c r="E307" s="1" t="n">
         <v>0.04444782580105264</v>
@@ -32970,7 +32970,7 @@
         <v>0.002592643702332273</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>243.5455</v>
+        <v>219.8745</v>
       </c>
       <c r="E308" s="1" t="n">
         <v>0.04434114106403567</v>
@@ -32987,7 +32987,7 @@
         <v>0.002594953247019354</v>
       </c>
       <c r="D309" s="1" t="n">
-        <v>243.5457</v>
+        <v>219.8747</v>
       </c>
       <c r="E309" s="1" t="n">
         <v>0.04423454213449209</v>
@@ -33004,7 +33004,7 @@
         <v>0.002597338272813285</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>243.546</v>
+        <v>219.875</v>
       </c>
       <c r="E310" s="1" t="n">
         <v>0.04412992763816211</v>
@@ -33021,7 +33021,7 @@
         <v>0.002599892614548459</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>243.5462</v>
+        <v>219.8752</v>
       </c>
       <c r="E311" s="1" t="n">
         <v>0.04402886716991383</v>
@@ -33038,7 +33038,7 @@
         <v>0.00260259463808105</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>243.5465</v>
+        <v>219.8755</v>
       </c>
       <c r="E312" s="1" t="n">
         <v>0.04393096078115136</v>
@@ -33055,7 +33055,7 @@
         <v>0.002605393842022673</v>
       </c>
       <c r="D313" s="1" t="n">
-        <v>243.5468</v>
+        <v>219.8758</v>
       </c>
       <c r="E313" s="1" t="n">
         <v>0.0438353280353798</v>
@@ -33072,7 +33072,7 @@
         <v>0.002608239724984948</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>243.547</v>
+        <v>219.876</v>
       </c>
       <c r="E314" s="1" t="n">
         <v>0.04374109990182199</v>
@@ -33089,7 +33089,7 @@
         <v>0.002611090627059857</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>243.5472</v>
+        <v>219.8762</v>
       </c>
       <c r="E315" s="1" t="n">
         <v>0.04364756636699312</v>
@@ -33106,7 +33106,7 @@
         <v>0.002613940254260855</v>
       </c>
       <c r="D316" s="1" t="n">
-        <v>243.5475</v>
+        <v>219.8765</v>
       </c>
       <c r="E316" s="1" t="n">
         <v>0.04355461583794608</v>
@@ -33123,7 +33123,7 @@
         <v>0.002616791154081766</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>243.5478</v>
+        <v>219.8768</v>
       </c>
       <c r="E317" s="1" t="n">
         <v>0.04346210201949714</v>
@@ -33140,7 +33140,7 @@
         <v>0.002619645874016409</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>243.548</v>
+        <v>219.877</v>
       </c>
       <c r="E318" s="1" t="n">
         <v>0.04337042747839819</v>
@@ -33157,7 +33157,7 @@
         <v>0.002622512905061223</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>243.5482</v>
+        <v>219.8772</v>
       </c>
       <c r="E319" s="1" t="n">
         <v>0.04327954268787869</v>
@@ -33174,7 +33174,7 @@
         <v>0.002625424512223105</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>243.5485</v>
+        <v>219.8775</v>
       </c>
       <c r="E320" s="1" t="n">
         <v>0.0431901527294298</v>
@@ -33191,7 +33191,7 @@
         <v>0.002628418904011567</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>243.5488</v>
+        <v>219.8778</v>
       </c>
       <c r="E321" s="1" t="n">
         <v>0.04310250763246569</v>
@@ -33208,7 +33208,7 @@
         <v>0.002631534288936124</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>243.549</v>
+        <v>219.878</v>
       </c>
       <c r="E322" s="1" t="n">
         <v>0.04301739594297883</v>
@@ -33225,7 +33225,7 @@
         <v>0.002634784846871753</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>243.5493</v>
+        <v>219.8783</v>
       </c>
       <c r="E323" s="1" t="n">
         <v>0.04293484403144383</v>
@@ -33242,7 +33242,7 @@
         <v>0.002638088643155306</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>243.5495</v>
+        <v>219.8785</v>
       </c>
       <c r="E324" s="1" t="n">
         <v>0.04285385700604676</v>
@@ -33259,7 +33259,7 @@
         <v>0.002641339714489095</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>243.5498</v>
+        <v>219.8788</v>
       </c>
       <c r="E325" s="1" t="n">
         <v>0.04277252484209025</v>
@@ -33276,7 +33276,7 @@
         <v>0.002644432097575436</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>243.55</v>
+        <v>219.879</v>
       </c>
       <c r="E326" s="1" t="n">
         <v>0.04268896044537206</v>
@@ -33293,7 +33293,7 @@
         <v>0.00264729707707867</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>243.5503</v>
+        <v>219.8793</v>
       </c>
       <c r="E327" s="1" t="n">
         <v>0.04260243694910931</v>
@@ -33310,7 +33310,7 @@
         <v>0.002650014929511228</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>243.5505</v>
+        <v>219.8795</v>
       </c>
       <c r="E328" s="1" t="n">
         <v>0.04251409129184186</v>
@@ -33327,7 +33327,7 @@
         <v>0.00265270317934757</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>243.5507</v>
+        <v>219.8797</v>
       </c>
       <c r="E329" s="1" t="n">
         <v>0.04242564132254642</v>
@@ -33344,7 +33344,7 @@
         <v>0.002655479351062153</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>243.551</v>
+        <v>219.88</v>
       </c>
       <c r="E330" s="1" t="n">
         <v>0.0423393178069956</v>
@@ -33361,7 +33361,7 @@
         <v>0.002658428708915467</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>243.551</v>
+        <v>219.88</v>
       </c>
       <c r="E331" s="1" t="n">
         <v>0.04225610116866424</v>
@@ -33378,7 +33378,7 @@
         <v>0.002661507476312136</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>243.551</v>
+        <v>219.88</v>
       </c>
       <c r="E332" s="1" t="n">
         <v>0.04217562372339787</v>
@@ -33395,7 +33395,7 @@
         <v>0.002664639616442814</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>243.551</v>
+        <v>219.88</v>
       </c>
       <c r="E333" s="1" t="n">
         <v>0.04209630525983715</v>
@@ -33412,7 +33412,7 @@
         <v>0.002667749092498159</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>243.551</v>
+        <v>219.88</v>
       </c>
       <c r="E334" s="1" t="n">
         <v>0.04201729082274133</v>
@@ -33429,7 +33429,7 @@
         <v>0.00267078366668017</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>243.5512</v>
+        <v>219.8802</v>
       </c>
       <c r="E335" s="1" t="n">
         <v>0.04193758140939358</v>
@@ -33446,7 +33446,7 @@
         <v>0.002673786297236219</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>243.5515</v>
+        <v>219.8805</v>
       </c>
       <c r="E336" s="1" t="n">
         <v>0.04185767956343576</v>
@@ -33463,7 +33463,7 @@
         <v>0.002676823741425023</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>243.5517</v>
+        <v>219.8807</v>
       </c>
       <c r="E337" s="1" t="n">
         <v>0.04177898018199667</v>
@@ -33480,7 +33480,7 @@
         <v>0.0026799627565053</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>243.552</v>
+        <v>219.881</v>
       </c>
       <c r="E338" s="1" t="n">
         <v>0.0417023362184622</v>
@@ -33497,7 +33497,7 @@
         <v>0.00268323748076434</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>243.5522</v>
+        <v>219.8812</v>
       </c>
       <c r="E339" s="1" t="n">
         <v>0.04162808353460793</v>
@@ -33514,7 +33514,7 @@
         <v>0.002686551576603729</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>243.5525</v>
+        <v>219.8815</v>
       </c>
       <c r="E340" s="1" t="n">
         <v>0.04155505987626922</v>
@@ -33531,7 +33531,7 @@
         <v>0.002689776087453629</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>243.5528</v>
+        <v>219.8818</v>
       </c>
       <c r="E341" s="1" t="n">
         <v>0.04148109148824371</v>
@@ -33548,7 +33548,7 @@
         <v>0.0026927820567442</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>243.553</v>
+        <v>219.882</v>
       </c>
       <c r="E342" s="1" t="n">
         <v>0.04140420393524109</v>
@@ -33565,7 +33565,7 @@
         <v>0.002695485344366245</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>243.5532</v>
+        <v>219.8822</v>
       </c>
       <c r="E343" s="1" t="n">
         <v>0.04132313320947383</v>
@@ -33582,7 +33582,7 @@
         <v>0.002697981076053135</v>
       </c>
       <c r="D344" s="1" t="n">
-        <v>243.5535</v>
+        <v>219.8825</v>
       </c>
       <c r="E344" s="1" t="n">
         <v>0.0412393703453792</v>
@@ -33599,7 +33599,7 @@
         <v>0.002700409193998884</v>
       </c>
       <c r="D345" s="1" t="n">
-        <v>243.5538</v>
+        <v>219.8828</v>
       </c>
       <c r="E345" s="1" t="n">
         <v>0.04115507184963291</v>
@@ -33616,7 +33616,7 @@
         <v>0.002702909640397504</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E346" s="1" t="n">
         <v>0.0410723689298793</v>
@@ -33633,7 +33633,7 @@
         <v>0.002705596627527859</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E347" s="1" t="n">
         <v>0.0409929780271454</v>
@@ -33650,7 +33650,7 @@
         <v>0.002708481448008219</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E348" s="1" t="n">
         <v>0.04091686845128338</v>
@@ -33667,7 +33667,7 @@
         <v>0.002711549664541707</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E349" s="1" t="n">
         <v>0.04084413751790485</v>
@@ -33684,7 +33684,7 @@
         <v>0.002714786839831445</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>243.554</v>
+        <v>219.883</v>
       </c>
       <c r="E350" s="1" t="n">
         <v>0.04077436787362581</v>
@@ -33701,7 +33701,7 @@
         <v>0.002718161811461362</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>243.5542</v>
+        <v>219.8832</v>
       </c>
       <c r="E351" s="1" t="n">
         <v>0.04070689571953433</v>
@@ -33718,7 +33718,7 @@
         <v>0.002721576516538622</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>243.5545</v>
+        <v>219.8835</v>
       </c>
       <c r="E352" s="1" t="n">
         <v>0.04064040733030442</v>
@@ -33735,7 +33735,7 @@
         <v>0.002724916167051194</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>243.5548</v>
+        <v>219.8838</v>
       </c>
       <c r="E353" s="1" t="n">
         <v>0.04057335591310763</v>
@@ -33752,7 +33752,7 @@
         <v>0.002728065974987051</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>243.555</v>
+        <v>219.884</v>
       </c>
       <c r="E354" s="1" t="n">
         <v>0.04050370150509663</v>
@@ -33769,7 +33769,7 @@
         <v>0.002730949457716863</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>243.5553</v>
+        <v>219.8843</v>
       </c>
       <c r="E355" s="1" t="n">
         <v>0.04043067409481046</v>
@@ -33786,7 +33786,7 @@
         <v>0.002733643354142108</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>243.5555</v>
+        <v>219.8845</v>
       </c>
       <c r="E356" s="1" t="n">
         <v>0.04035509599984082</v>
@@ -33803,7 +33803,7 @@
         <v>0.002736262708546968</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>243.5558</v>
+        <v>219.8848</v>
       </c>
       <c r="E357" s="1" t="n">
         <v>0.04027885159717454</v>
@@ -33820,7 +33820,7 @@
         <v>0.00273892256521562</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E358" s="1" t="n">
         <v>0.04020363524441288</v>
@@ -33837,7 +33837,7 @@
         <v>0.00274171713171767</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E359" s="1" t="n">
         <v>0.04013098614543645</v>
@@ -33854,7 +33854,7 @@
         <v>0.00274465726876441</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E360" s="1" t="n">
         <v>0.0400607042132638</v>
@@ -33871,7 +33871,7 @@
         <v>0.002747733000352561</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E361" s="1" t="n">
         <v>0.03999279215326177</v>
@@ -33888,7 +33888,7 @@
         <v>0.002750934350478841</v>
       </c>
       <c r="D362" s="1" t="n">
-        <v>243.556</v>
+        <v>219.885</v>
       </c>
       <c r="E362" s="1" t="n">
         <v>0.03992708522766771</v>
@@ -33905,7 +33905,7 @@
         <v>0.002754245213961733</v>
       </c>
       <c r="D363" s="1" t="n">
-        <v>243.5563</v>
+        <v>219.8853</v>
       </c>
       <c r="E363" s="1" t="n">
         <v>0.03986349971573203</v>
@@ -33922,7 +33922,7 @@
         <v>0.002757624968906782</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>243.5565</v>
+        <v>219.8855</v>
       </c>
       <c r="E364" s="1" t="n">
         <v>0.03980109693971774</v>
@@ -33939,7 +33939,7 @@
         <v>0.002761026864241299</v>
       </c>
       <c r="D365" s="1" t="n">
-        <v>243.5567</v>
+        <v>219.8857</v>
       </c>
       <c r="E365" s="1" t="n">
         <v>0.03973936088845491</v>
@@ -33956,7 +33956,7 @@
         <v>0.002764404148892593</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E366" s="1" t="n">
         <v>0.03967761498971051</v>
@@ -33973,7 +33973,7 @@
         <v>0.002767715294805458</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>243.5572</v>
+        <v>219.8862</v>
       </c>
       <c r="E367" s="1" t="n">
         <v>0.03961526491547717</v>
@@ -33990,7 +33990,7 @@
         <v>0.002770939665994619</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>243.5575</v>
+        <v>219.8865</v>
       </c>
       <c r="E368" s="1" t="n">
         <v>0.03955202110552562</v>
@@ -34007,7 +34007,7 @@
         <v>0.002774061849492286</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>243.5577</v>
+        <v>219.8867</v>
       </c>
       <c r="E369" s="1" t="n">
         <v>0.03948767153300912</v>
@@ -34024,7 +34024,7 @@
         <v>0.002777066432330666</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E370" s="1" t="n">
         <v>0.03942200649736012</v>
@@ -34041,7 +34041,7 @@
         <v>0.002779946545831645</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E371" s="1" t="n">
         <v>0.03935493955158495</v>
@@ -34058,7 +34058,7 @@
         <v>0.002782729498475804</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E372" s="1" t="n">
         <v>0.03928686770855263</v>
@@ -34075,7 +34075,7 @@
         <v>0.002785451143033405</v>
       </c>
       <c r="D373" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E373" s="1" t="n">
         <v>0.03921830396149059</v>
@@ -34092,7 +34092,7 @@
         <v>0.002788147332274702</v>
       </c>
       <c r="D374" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E374" s="1" t="n">
         <v>0.03914975573609351</v>
@@ -34109,7 +34109,7 @@
         <v>0.00279084606234751</v>
       </c>
       <c r="D375" s="1" t="n">
-        <v>243.5582</v>
+        <v>219.8872</v>
       </c>
       <c r="E375" s="1" t="n">
         <v>0.03908161494574626</v>
@@ -34126,7 +34126,7 @@
         <v>0.002793543902909862</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>243.5585</v>
+        <v>219.8875</v>
       </c>
       <c r="E376" s="1" t="n">
         <v>0.03901399469601056</v>
@@ -34143,7 +34143,7 @@
         <v>0.002796229566997343</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>243.5588</v>
+        <v>219.8878</v>
       </c>
       <c r="E377" s="1" t="n">
         <v>0.03894640598434541</v>
@@ -34160,7 +34160,7 @@
         <v>0.002798891767645538</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E378" s="1" t="n">
         <v>0.03887885504245432</v>
@@ -34177,7 +34177,7 @@
         <v>0.002801524926377552</v>
       </c>
       <c r="D379" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E379" s="1" t="n">
         <v>0.0388112642803517</v>
@@ -34194,7 +34194,7 @@
         <v>0.002804146298666551</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E380" s="1" t="n">
         <v>0.0387438724249995</v>
@@ -34211,7 +34211,7 @@
         <v>0.002806778848473216</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E381" s="1" t="n">
         <v>0.03867699432305197</v>
@@ -34228,7 +34228,7 @@
         <v>0.002809445539758229</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E382" s="1" t="n">
         <v>0.03861094147704788</v>
@@ -34245,7 +34245,7 @@
         <v>0.002812168378511871</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>243.5592</v>
+        <v>219.8882</v>
       </c>
       <c r="E383" s="1" t="n">
         <v>0.03854600895899237</v>
@@ -34262,7 +34262,7 @@
         <v>0.002814965538842815</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>243.5595</v>
+        <v>219.8885</v>
       </c>
       <c r="E384" s="1" t="n">
         <v>0.03848243633915395</v>
@@ -34279,7 +34279,7 @@
         <v>0.00281785423688933</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>243.5598</v>
+        <v>219.8888</v>
       </c>
       <c r="E385" s="1" t="n">
         <v>0.03842044760194174</v>
@@ -34296,7 +34296,7 @@
         <v>0.00282085168878969</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E386" s="1" t="n">
         <v>0.03836026437797884</v>
@@ -34313,7 +34313,7 @@
         <v>0.002823960266170831</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E387" s="1" t="n">
         <v>0.03830174331193087</v>
@@ -34330,7 +34330,7 @@
         <v>0.002827122962614354</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E388" s="1" t="n">
         <v>0.03824442182335558</v>
@@ -34347,7 +34347,7 @@
         <v>0.002830267927190527</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E389" s="1" t="n">
         <v>0.03818716077873646</v>
@@ -34364,7 +34364,7 @@
         <v>0.002833323308969617</v>
       </c>
       <c r="D390" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E390" s="1" t="n">
         <v>0.03812899278051249</v>
@@ -34381,7 +34381,7 @@
         <v>0.002836239390289215</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>243.5602</v>
+        <v>219.8892</v>
       </c>
       <c r="E391" s="1" t="n">
         <v>0.0380692575482459</v>
@@ -34398,7 +34398,7 @@
         <v>0.002839054986556198</v>
       </c>
       <c r="D392" s="1" t="n">
-        <v>243.5605</v>
+        <v>219.8895</v>
       </c>
       <c r="E392" s="1" t="n">
         <v>0.03800832679792949</v>
@@ -34415,7 +34415,7 @@
         <v>0.002841831046444766</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>243.5608</v>
+        <v>219.8898</v>
       </c>
       <c r="E393" s="1" t="n">
         <v>0.037947342836457</v>
@@ -34432,7 +34432,7 @@
         <v>0.00284462851862912</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E394" s="1" t="n">
         <v>0.03788695872359545</v>
@@ -34449,7 +34449,7 @@
         <v>0.002847490565412407</v>
       </c>
       <c r="D395" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E395" s="1" t="n">
         <v>0.03782774323033996</v>
@@ -34466,7 +34466,7 @@
         <v>0.002850389203613561</v>
       </c>
       <c r="D396" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E396" s="1" t="n">
         <v>0.03776931658468268</v>
@@ -34483,7 +34483,7 @@
         <v>0.002853278663680464</v>
       </c>
       <c r="D397" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E397" s="1" t="n">
         <v>0.03771090897455863</v>
@@ -34500,7 +34500,7 @@
         <v>0.002856113176060995</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E398" s="1" t="n">
         <v>0.03765223358149444</v>
@@ -34517,7 +34517,7 @@
         <v>0.002858863213172433</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>243.5613</v>
+        <v>219.8903</v>
       </c>
       <c r="E399" s="1" t="n">
         <v>0.03759274629503093</v>
@@ -34534,7 +34534,7 @@
         <v>0.002861564215309643</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>243.5615</v>
+        <v>219.8905</v>
       </c>
       <c r="E400" s="1" t="n">
         <v>0.03753291812595761</v>
@@ -34551,7 +34551,7 @@
         <v>0.002864267864736888</v>
       </c>
       <c r="D401" s="1" t="n">
-        <v>243.5618</v>
+        <v>219.8908</v>
       </c>
       <c r="E401" s="1" t="n">
         <v>0.03747326997602723</v>
@@ -34568,7 +34568,7 @@
         <v>0.002867025843718431</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E402" s="1" t="n">
         <v>0.03741478967403043</v>
@@ -34585,7 +34585,7 @@
         <v>0.002869880154792552</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E403" s="1" t="n">
         <v>0.03735785826282902</v>
@@ -34602,7 +34602,7 @@
         <v>0.002872834081593617</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E404" s="1" t="n">
         <v>0.03730234959635792</v>
@@ -34619,7 +34619,7 @@
         <v>0.002875881228030007</v>
       </c>
       <c r="D405" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E405" s="1" t="n">
         <v>0.03724848344254497</v>
@@ -34636,7 +34636,7 @@
         <v>0.002879015198010104</v>
       </c>
       <c r="D406" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E406" s="1" t="n">
         <v>0.03719600868648638</v>
@@ -34653,7 +34653,7 @@
         <v>0.00288222631180793</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>243.5623</v>
+        <v>219.8913</v>
       </c>
       <c r="E407" s="1" t="n">
         <v>0.03714479018506674</v>
@@ -34670,7 +34670,7 @@
         <v>0.002885491755160053</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>243.5625</v>
+        <v>219.8915</v>
       </c>
       <c r="E408" s="1" t="n">
         <v>0.03709436903702726</v>
@@ -34687,7 +34687,7 @@
         <v>0.00288878543016868</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>243.5627</v>
+        <v>219.8917</v>
       </c>
       <c r="E409" s="1" t="n">
         <v>0.03704471618832048</v>
@@ -34704,7 +34704,7 @@
         <v>0.002892081238936018</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E410" s="1" t="n">
         <v>0.03699533679696589</v>
@@ -34721,7 +34721,7 @@
         <v>0.002895362754680313</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E411" s="1" t="n">
         <v>0.03694586360012115</v>
@@ -34738,7 +34738,7 @@
         <v>0.002898652235083972</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E412" s="1" t="n">
         <v>0.03689689091333281</v>
@@ -34755,7 +34755,7 @@
         <v>0.002901981608945441</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E413" s="1" t="n">
         <v>0.03684866578930559</v>
@@ -34772,7 +34772,7 @@
         <v>0.002905382805063169</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E414" s="1" t="n">
         <v>0.03680143215186225</v>
@@ -34789,7 +34789,7 @@
         <v>0.002908868473666604</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E415" s="1" t="n">
         <v>0.03675565167657615</v>
@@ -34806,7 +34806,7 @@
         <v>0.0029123741507092</v>
       </c>
       <c r="D416" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E416" s="1" t="n">
         <v>0.03671034709761771</v>
@@ -34823,7 +34823,7 @@
         <v>0.002915816093575416</v>
       </c>
       <c r="D417" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E417" s="1" t="n">
         <v>0.03666430749467369</v>
@@ -34840,7 +34840,7 @@
         <v>0.002919110559649708</v>
       </c>
       <c r="D418" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E418" s="1" t="n">
         <v>0.03661679571142003</v>
@@ -34857,7 +34857,7 @@
         <v>0.002922203747695932</v>
       </c>
       <c r="D419" s="1" t="n">
-        <v>243.5632</v>
+        <v>219.8922</v>
       </c>
       <c r="E419" s="1" t="n">
         <v>0.03656684163370246</v>
@@ -34874,7 +34874,7 @@
         <v>0.002925161621995538</v>
       </c>
       <c r="D420" s="1" t="n">
-        <v>243.5635</v>
+        <v>219.8925</v>
       </c>
       <c r="E420" s="1" t="n">
         <v>0.03651559354387375</v>
@@ -34891,7 +34891,7 @@
         <v>0.002928080088209374</v>
       </c>
       <c r="D421" s="1" t="n">
-        <v>243.5637</v>
+        <v>219.8927</v>
       </c>
       <c r="E421" s="1" t="n">
         <v>0.03646410198581545</v>
@@ -34908,7 +34908,7 @@
         <v>0.002931055051998289</v>
       </c>
       <c r="D422" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E422" s="1" t="n">
         <v>0.03641340679316579</v>
@@ -34925,7 +34925,7 @@
         <v>0.002934151853618653</v>
       </c>
       <c r="D423" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E423" s="1" t="n">
         <v>0.03636461792293541</v>
@@ -34942,7 +34942,7 @@
         <v>0.002937313571708925</v>
       </c>
       <c r="D424" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E424" s="1" t="n">
         <v>0.03631686544161021</v>
@@ -34959,7 +34959,7 @@
         <v>0.002940452719503088</v>
       </c>
       <c r="D425" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E425" s="1" t="n">
         <v>0.03626891005251308</v>
@@ -34976,7 +34976,7 @@
         <v>0.002943481810235123</v>
       </c>
       <c r="D426" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E426" s="1" t="n">
         <v>0.03621998133224055</v>
@@ -34993,7 +34993,7 @@
         <v>0.002946349249464728</v>
       </c>
       <c r="D427" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E427" s="1" t="n">
         <v>0.03616914857788806</v>
@@ -35010,7 +35010,7 @@
         <v>0.002949147012054461</v>
       </c>
       <c r="D428" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E428" s="1" t="n">
         <v>0.03611785556215387</v>
@@ -35027,7 +35027,7 @@
         <v>0.002952002965192596</v>
       </c>
       <c r="D429" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E429" s="1" t="n">
         <v>0.03606736439519542</v>
@@ -35044,7 +35044,7 @@
         <v>0.002955044976067411</v>
       </c>
       <c r="D430" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E430" s="1" t="n">
         <v>0.0360195310025718</v>
@@ -35061,7 +35061,7 @@
         <v>0.002958353273221817</v>
       </c>
       <c r="D431" s="1" t="n">
-        <v>243.5642</v>
+        <v>219.8932</v>
       </c>
       <c r="E431" s="1" t="n">
         <v>0.03597516120506233</v>
@@ -35078,7 +35078,7 @@
         <v>0.00296181753061728</v>
       </c>
       <c r="D432" s="1" t="n">
-        <v>243.5645</v>
+        <v>219.8935</v>
       </c>
       <c r="E432" s="1" t="n">
         <v>0.0359327408060854</v>
@@ -35095,7 +35095,7 @@
         <v>0.002965279783569906</v>
       </c>
       <c r="D433" s="1" t="n">
-        <v>243.5648</v>
+        <v>219.8938</v>
       </c>
       <c r="E433" s="1" t="n">
         <v>0.03589064602446865</v>
@@ -35112,7 +35112,7 @@
         <v>0.002968582067395803</v>
       </c>
       <c r="D434" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E434" s="1" t="n">
         <v>0.03584666560580482</v>
@@ -35129,7 +35129,7 @@
         <v>0.002971618387875193</v>
       </c>
       <c r="D435" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E435" s="1" t="n">
         <v>0.03579983691597866</v>
@@ -35146,7 +35146,7 @@
         <v>0.002974490632644774</v>
       </c>
       <c r="D436" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E436" s="1" t="n">
         <v>0.03575110366784212</v>
@@ -35163,7 +35163,7 @@
         <v>0.002977352659805366</v>
       </c>
       <c r="D437" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E437" s="1" t="n">
         <v>0.03570262443428618</v>
@@ -35180,7 +35180,7 @@
         <v>0.002980358327457785</v>
       </c>
       <c r="D438" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E438" s="1" t="n">
         <v>0.03565593820020543</v>
@@ -35197,7 +35197,7 @@
         <v>0.002983609550026233</v>
       </c>
       <c r="D439" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E439" s="1" t="n">
         <v>0.03561254857160247</v>
@@ -35214,7 +35214,7 @@
         <v>0.002987000467228455</v>
       </c>
       <c r="D440" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E440" s="1" t="n">
         <v>0.0355708729475139</v>
@@ -35231,7 +35231,7 @@
         <v>0.002990373275105584</v>
       </c>
       <c r="D441" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E441" s="1" t="n">
         <v>0.0355293234436366</v>
@@ -35248,7 +35248,7 @@
         <v>0.002993570169698749</v>
       </c>
       <c r="D442" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E442" s="1" t="n">
         <v>0.03548573010406043</v>
@@ -35265,7 +35265,7 @@
         <v>0.002996483480386401</v>
       </c>
       <c r="D443" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E443" s="1" t="n">
         <v>0.03543913165902259</v>
@@ -35282,7 +35282,7 @@
         <v>0.002999206069896262</v>
       </c>
       <c r="D444" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E444" s="1" t="n">
         <v>0.03539034669709464</v>
@@ -35299,7 +35299,7 @@
         <v>0.003001880934293376</v>
       </c>
       <c r="D445" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E445" s="1" t="n">
         <v>0.03534137099898882</v>
@@ -35316,7 +35316,7 @@
         <v>0.003004651069642785</v>
       </c>
       <c r="D446" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E446" s="1" t="n">
         <v>0.03529358859350266</v>
@@ -35333,7 +35333,7 @@
         <v>0.003007629345905354</v>
       </c>
       <c r="D447" s="1" t="n">
-        <v>243.5652</v>
+        <v>219.8942</v>
       </c>
       <c r="E447" s="1" t="n">
         <v>0.03524861072149778</v>
@@ -35350,7 +35350,7 @@
         <v>0.003010808128625226</v>
       </c>
       <c r="D448" s="1" t="n">
-        <v>243.5655</v>
+        <v>219.8945</v>
       </c>
       <c r="E448" s="1" t="n">
         <v>0.03520603292972336</v>
@@ -35367,7 +35367,7 @@
         <v>0.003014149657242367</v>
       </c>
       <c r="D449" s="1" t="n">
-        <v>243.5658</v>
+        <v>219.8948</v>
       </c>
       <c r="E449" s="1" t="n">
         <v>0.03516569422913823</v>
@@ -35384,7 +35384,7 @@
         <v>0.003017616171196739</v>
       </c>
       <c r="D450" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E450" s="1" t="n">
         <v>0.0351268444964167</v>
@@ -35401,7 +35401,7 @@
         <v>0.003021164576478739</v>
       </c>
       <c r="D451" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E451" s="1" t="n">
         <v>0.03508926830849118</v>
@@ -35418,7 +35418,7 @@
         <v>0.003024730445280483</v>
       </c>
       <c r="D452" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E452" s="1" t="n">
         <v>0.03505191568557497</v>
@@ -35435,7 +35435,7 @@
         <v>0.003028244016344515</v>
       </c>
       <c r="D453" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E453" s="1" t="n">
         <v>0.03501427299738689</v>
@@ -35452,7 +35452,7 @@
         <v>0.003031635528413383</v>
       </c>
       <c r="D454" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E454" s="1" t="n">
         <v>0.03497539052874503</v>
@@ -35469,7 +35469,7 @@
         <v>0.003034853734642631</v>
       </c>
       <c r="D455" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E455" s="1" t="n">
         <v>0.03493453946649071</v>
@@ -35486,7 +35486,7 @@
         <v>0.003037921445839805</v>
       </c>
       <c r="D456" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E456" s="1" t="n">
         <v>0.03489214144913171</v>
@@ -35503,7 +35503,7 @@
         <v>0.003040879987225449</v>
       </c>
       <c r="D457" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E457" s="1" t="n">
         <v>0.03484882716322004</v>
@@ -35520,7 +35520,7 @@
         <v>0.00304377068402011</v>
       </c>
       <c r="D458" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E458" s="1" t="n">
         <v>0.034804782407545</v>
@@ -35537,7 +35537,7 @@
         <v>0.003046633780640474</v>
       </c>
       <c r="D459" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E459" s="1" t="n">
         <v>0.03476076364165121</v>
@@ -35554,7 +35554,7 @@
         <v>0.003049505198287787</v>
       </c>
       <c r="D460" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E460" s="1" t="n">
         <v>0.03471688754472568</v>
@@ -35571,7 +35571,7 @@
         <v>0.003052419777359436</v>
       </c>
       <c r="D461" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E461" s="1" t="n">
         <v>0.03467384066894467</v>
@@ -35588,7 +35588,7 @@
         <v>0.003055412358252812</v>
       </c>
       <c r="D462" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E462" s="1" t="n">
         <v>0.03463172109945254</v>
@@ -35605,7 +35605,7 @@
         <v>0.003058505517829356</v>
       </c>
       <c r="D463" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E463" s="1" t="n">
         <v>0.03459106910282245</v>
@@ -35622,7 +35622,7 @@
         <v>0.003061672778806734</v>
       </c>
       <c r="D464" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E464" s="1" t="n">
         <v>0.03455128561013299</v>
@@ -35639,7 +35639,7 @@
         <v>0.003064875400366671</v>
       </c>
       <c r="D465" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E465" s="1" t="n">
         <v>0.0345122190354735</v>
@@ -35656,7 +35656,7 @@
         <v>0.003068074641690885</v>
       </c>
       <c r="D466" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E466" s="1" t="n">
         <v>0.03447313941141421</v>
@@ -35673,7 +35673,7 @@
         <v>0.003071240539804948</v>
       </c>
       <c r="D467" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E467" s="1" t="n">
         <v>0.03443400055804478</v>
@@ -35690,7 +35690,7 @@
         <v>0.003074378243109818</v>
       </c>
       <c r="D468" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E468" s="1" t="n">
         <v>0.03439457110881074</v>
@@ -35707,7 +35707,7 @@
         <v>0.003077501677850308</v>
       </c>
       <c r="D469" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E469" s="1" t="n">
         <v>0.03435529742782134</v>
@@ -35724,7 +35724,7 @@
         <v>0.003080624770271225</v>
       </c>
       <c r="D470" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E470" s="1" t="n">
         <v>0.03431604494395332</v>
@@ -35741,7 +35741,7 @@
         <v>0.003083761555475374</v>
       </c>
       <c r="D471" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E471" s="1" t="n">
         <v>0.03427725789128176</v>
@@ -35758,7 +35758,7 @@
         <v>0.003086926503997539</v>
       </c>
       <c r="D472" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E472" s="1" t="n">
         <v>0.03423880573487946</v>
@@ -35775,7 +35775,7 @@
         <v>0.003090134195230498</v>
       </c>
       <c r="D473" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E473" s="1" t="n">
         <v>0.03420113540667794</v>
@@ -35792,7 +35792,7 @@
         <v>0.003093399208567031</v>
       </c>
       <c r="D474" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E474" s="1" t="n">
         <v>0.03416411551356069</v>
@@ -35809,7 +35809,7 @@
         <v>0.00309671990044548</v>
       </c>
       <c r="D475" s="1" t="n">
-        <v>243.5662</v>
+        <v>219.8952</v>
       </c>
       <c r="E475" s="1" t="n">
         <v>0.03412801087711729</v>
@@ -35826,7 +35826,7 @@
         <v>0.003100029735486445</v>
       </c>
       <c r="D476" s="1" t="n">
-        <v>243.5665</v>
+        <v>219.8955</v>
       </c>
       <c r="E476" s="1" t="n">
         <v>0.03409179716625124</v>
@@ -35843,7 +35843,7 @@
         <v>0.003103245955356087</v>
       </c>
       <c r="D477" s="1" t="n">
-        <v>243.5668</v>
+        <v>219.8958</v>
       </c>
       <c r="E477" s="1" t="n">
         <v>0.03405485337359269</v>
@@ -35860,7 +35860,7 @@
         <v>0.003106285801720571</v>
       </c>
       <c r="D478" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E478" s="1" t="n">
         <v>0.03401599169412351</v>
@@ -35877,7 +35877,7 @@
         <v>0.003109101157587793</v>
       </c>
       <c r="D479" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E479" s="1" t="n">
         <v>0.03397498433687397</v>
@@ -35894,7 +35894,7 @@
         <v>0.00311178247133258</v>
       </c>
       <c r="D480" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E480" s="1" t="n">
         <v>0.03393254563841257</v>
@@ -35911,7 +35911,7 @@
         <v>0.003114454832671495</v>
       </c>
       <c r="D481" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E481" s="1" t="n">
         <v>0.0338903309889757</v>
@@ -35928,7 +35928,7 @@
         <v>0.0031172433313211</v>
       </c>
       <c r="D482" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E482" s="1" t="n">
         <v>0.03384955507078623</v>
@@ -35945,7 +35945,7 @@
         <v>0.003120240788955578</v>
       </c>
       <c r="D483" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E483" s="1" t="n">
         <v>0.03381121467528279</v>
@@ -35962,7 +35962,7 @@
         <v>0.003123410955079591</v>
       </c>
       <c r="D484" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E484" s="1" t="n">
         <v>0.03377490255176996</v>
@@ -35979,7 +35979,7 @@
         <v>0.003126685311155424</v>
       </c>
       <c r="D485" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E485" s="1" t="n">
         <v>0.03373972449677278</v>
@@ -35996,7 +35996,7 @@
         <v>0.00312999533864536</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E486" s="1" t="n">
         <v>0.03370521914008606</v>
@@ -36013,7 +36013,7 @@
         <v>0.00313328283369617</v>
       </c>
       <c r="D487" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E487" s="1" t="n">
         <v>0.03367061542155308</v>
@@ -36030,7 +36030,7 @@
         <v>0.003136530851192564</v>
       </c>
       <c r="D488" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E488" s="1" t="n">
         <v>0.03363559052614026</v>
@@ -36047,7 +36047,7 @@
         <v>0.003139732760703741</v>
       </c>
       <c r="D489" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E489" s="1" t="n">
         <v>0.03360035878939919</v>
@@ -36064,7 +36064,7 @@
         <v>0.0031428819317989</v>
       </c>
       <c r="D490" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E490" s="1" t="n">
         <v>0.03356456829423139</v>
@@ -36081,7 +36081,7 @@
         <v>0.003145973608353518</v>
       </c>
       <c r="D491" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E491" s="1" t="n">
         <v>0.03352845389456494</v>
@@ -36098,7 +36098,7 @@
         <v>0.003149010531468193</v>
       </c>
       <c r="D492" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E492" s="1" t="n">
         <v>0.03349176494903629</v>
@@ -36115,7 +36115,7 @@
         <v>0.0031519973165498</v>
       </c>
       <c r="D493" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E493" s="1" t="n">
         <v>0.03345469452133577</v>
@@ -36132,7 +36132,7 @@
         <v>0.003154938579005215</v>
       </c>
       <c r="D494" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E494" s="1" t="n">
         <v>0.03341743463187195</v>
@@ -36149,7 +36149,7 @@
         <v>0.003157853892579203</v>
       </c>
       <c r="D495" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E495" s="1" t="n">
         <v>0.03337991247376353</v>
@@ -36166,7 +36166,7 @@
         <v>0.003160822664368089</v>
       </c>
       <c r="D496" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E496" s="1" t="n">
         <v>0.03334324786769326</v>
@@ -36183,7 +36183,7 @@
         <v>0.003163939259806087</v>
       </c>
       <c r="D497" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E497" s="1" t="n">
         <v>0.03330814875255304</v>
@@ -36200,7 +36200,7 @@
         <v>0.003167298044327407</v>
       </c>
       <c r="D498" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E498" s="1" t="n">
         <v>0.03327573676316694</v>
@@ -36217,7 +36217,7 @@
         <v>0.003170949024662984</v>
       </c>
       <c r="D499" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E499" s="1" t="n">
         <v>0.033246659924816</v>
@@ -36234,7 +36234,7 @@
         <v>0.003174764772730618</v>
       </c>
       <c r="D500" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E500" s="1" t="n">
         <v>0.03321928523479678</v>
@@ -36251,7 +36251,7 @@
         <v>0.003178573501744832</v>
       </c>
       <c r="D501" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E501" s="1" t="n">
         <v>0.03319194785379597</v>
@@ -36268,7 +36268,7 @@
         <v>0.003182203424920144</v>
       </c>
       <c r="D502" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E502" s="1" t="n">
         <v>0.03316299702423371</v>
@@ -36285,7 +36285,7 @@
         <v>0.003185523789264427</v>
       </c>
       <c r="D503" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E503" s="1" t="n">
         <v>0.03313080387513771</v>
@@ -36302,7 +36302,7 @@
         <v>0.003188567976958948</v>
       </c>
       <c r="D504" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E504" s="1" t="n">
         <v>0.03309587342881808</v>
@@ -36319,7 +36319,7 @@
         <v>0.003191410403978326</v>
       </c>
       <c r="D505" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E505" s="1" t="n">
         <v>0.0330589929977602</v>
@@ -36336,7 +36336,7 @@
         <v>0.003194125486297179</v>
       </c>
       <c r="D506" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E506" s="1" t="n">
         <v>0.03302108271702439</v>
@@ -36353,7 +36353,7 @@
         <v>0.003196784224084905</v>
       </c>
       <c r="D507" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E507" s="1" t="n">
         <v>0.0329826037185006</v>
@@ -36370,7 +36370,7 @@
         <v>0.003199443954290036</v>
       </c>
       <c r="D508" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E508" s="1" t="n">
         <v>0.03294428824156202</v>
@@ -36387,7 +36387,7 @@
         <v>0.00320215859805588</v>
       </c>
       <c r="D509" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E509" s="1" t="n">
         <v>0.03290682806691216</v>
@@ -36404,7 +36404,7 @@
         <v>0.003204982076525748</v>
       </c>
       <c r="D510" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E510" s="1" t="n">
         <v>0.03287049451129534</v>
@@ -36421,7 +36421,7 @@
         <v>0.003207949176642839</v>
       </c>
       <c r="D511" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E511" s="1" t="n">
         <v>0.03283577492663313</v>
@@ -36438,7 +36438,7 @@
         <v>0.003211018148549895</v>
       </c>
       <c r="D512" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E512" s="1" t="n">
         <v>0.03280223324725524</v>
@@ -36455,7 +36455,7 @@
         <v>0.00321412810818955</v>
       </c>
       <c r="D513" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E513" s="1" t="n">
         <v>0.03276937982929296</v>
@@ -36472,7 +36472,7 @@
         <v>0.003217218171504436</v>
       </c>
       <c r="D514" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E514" s="1" t="n">
         <v>0.03273631564677065</v>
@@ -36489,7 +36489,7 @@
         <v>0.003220244319935379</v>
       </c>
       <c r="D515" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E515" s="1" t="n">
         <v>0.0327027323039548</v>
@@ -36506,7 +36506,7 @@
         <v>0.00322322999691599</v>
       </c>
       <c r="D516" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E516" s="1" t="n">
         <v>0.03266887046436228</v>
@@ -36523,7 +36523,7 @@
         <v>0.003226215511378072</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E517" s="1" t="n">
         <v>0.03263527700983268</v>
@@ -36540,7 +36540,7 @@
         <v>0.00322924117225343</v>
       </c>
       <c r="D518" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E518" s="1" t="n">
         <v>0.03260208299191231</v>
@@ -36557,7 +36557,7 @@
         <v>0.003232332431896556</v>
       </c>
       <c r="D519" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E519" s="1" t="n">
         <v>0.0325696793727132</v>
@@ -36574,7 +36574,7 @@
         <v>0.003235455316352684</v>
       </c>
       <c r="D520" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E520" s="1" t="n">
         <v>0.03253771987612034</v>
@@ -36591,7 +36591,7 @@
         <v>0.003238560995089733</v>
       </c>
       <c r="D521" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E521" s="1" t="n">
         <v>0.0325058487514648</v>
@@ -36608,7 +36608,7 @@
         <v>0.003241600637575623</v>
       </c>
       <c r="D522" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E522" s="1" t="n">
         <v>0.03247330307240877</v>
@@ -36625,7 +36625,7 @@
         <v>0.003244546244085651</v>
       </c>
       <c r="D523" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E523" s="1" t="n">
         <v>0.03243994309560674</v>
@@ -36642,7 +36642,7 @@
         <v>0.003247453138124612</v>
       </c>
       <c r="D524" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E524" s="1" t="n">
         <v>0.03240632561016549</v>
@@ -36659,7 +36659,7 @@
         <v>0.003250397474004677</v>
       </c>
       <c r="D525" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E525" s="1" t="n">
         <v>0.03237334697896601</v>
@@ -36676,7 +36676,7 @@
         <v>0.003253455406038018</v>
       </c>
       <c r="D526" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E526" s="1" t="n">
         <v>0.03234148839983535</v>
@@ -36693,7 +36693,7 @@
         <v>0.0032566770304402</v>
       </c>
       <c r="D527" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E527" s="1" t="n">
         <v>0.03231137620517033</v>
@@ -36710,7 +36710,7 @@
         <v>0.003260008211040364</v>
       </c>
       <c r="D528" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E528" s="1" t="n">
         <v>0.03228246427097808</v>
@@ -36727,7 +36727,7 @@
         <v>0.003263368753571038</v>
       </c>
       <c r="D529" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E529" s="1" t="n">
         <v>0.03225408899443685</v>
@@ -36744,7 +36744,7 @@
         <v>0.003266678463764757</v>
       </c>
       <c r="D530" s="1" t="n">
-        <v>243.567</v>
+        <v>219.896</v>
       </c>
       <c r="E530" s="1" t="n">
         <v>0.03222518507469931</v>
@@ -36761,7 +36761,7 @@
         <v>0.003269877461825629</v>
       </c>
       <c r="D531" s="1" t="n">
-        <v>243.5668</v>
+        <v>219.8958</v>
       </c>
       <c r="E531" s="1" t="n">
         <v>0.03219530119050279</v>
@@ -36778,7 +36778,7 @@
         <v>0.003272987125844066</v>
       </c>
       <c r="D532" s="1" t="n">
-        <v>243.5665</v>
+        <v>219.8955</v>
       </c>
       <c r="E532" s="1" t="n">
         <v>0.03216465302008006</v>
@@ -36795,7 +36795,7 @@
         <v>0.003276049148382058</v>
       </c>
       <c r="D533" s="1" t="n">
-        <v>243.5662</v>
+        <v>219.8952</v>
       </c>
       <c r="E533" s="1" t="n">
         <v>0.0321337892492052</v>
@@ -36812,7 +36812,7 @@
         <v>0.00327910522200159</v>
       </c>
       <c r="D534" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E534" s="1" t="n">
         <v>0.03210284914180341</v>
@@ -36829,7 +36829,7 @@
         <v>0.003282185825208224</v>
       </c>
       <c r="D535" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E535" s="1" t="n">
         <v>0.032072265703985</v>
@@ -36846,7 +36846,7 @@
         <v>0.003285276580281795</v>
       </c>
       <c r="D536" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E536" s="1" t="n">
         <v>0.03204189668836028</v>
@@ -36863,7 +36863,7 @@
         <v>0.003288351895445709</v>
       </c>
       <c r="D537" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E537" s="1" t="n">
         <v>0.03201162662502011</v>
@@ -36880,7 +36880,7 @@
         <v>0.003291386178923372</v>
       </c>
       <c r="D538" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E538" s="1" t="n">
         <v>0.0319809371789803</v>
@@ -36897,7 +36897,7 @@
         <v>0.003294373123433378</v>
       </c>
       <c r="D539" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E539" s="1" t="n">
         <v>0.03194990378160622</v>
@@ -36914,7 +36914,7 @@
         <v>0.003297383559675082</v>
       </c>
       <c r="D540" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E540" s="1" t="n">
         <v>0.03191921401800311</v>
@@ -36931,7 +36931,7 @@
         <v>0.003300507602843026</v>
       </c>
       <c r="D541" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E541" s="1" t="n">
         <v>0.03188987102086537</v>
@@ -36948,7 +36948,7 @@
         <v>0.003303835368131752</v>
       </c>
       <c r="D542" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E542" s="1" t="n">
         <v>0.03186246824326656</v>
@@ -36965,7 +36965,7 @@
         <v>0.003307411550121405</v>
       </c>
       <c r="D543" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E543" s="1" t="n">
         <v>0.03183755881478069</v>
@@ -36982,7 +36982,7 @@
         <v>0.003311099160934539</v>
       </c>
       <c r="D544" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E544" s="1" t="n">
         <v>0.03181381262051296</v>
@@ -36999,7 +36999,7 @@
         <v>0.003314715792079305</v>
       </c>
       <c r="D545" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E545" s="1" t="n">
         <v>0.03178947381436899</v>
@@ -37016,7 +37016,7 @@
         <v>0.003318079035063862</v>
       </c>
       <c r="D546" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E546" s="1" t="n">
         <v>0.03176293338252775</v>
@@ -37033,7 +37033,7 @@
         <v>0.003321074949665413</v>
       </c>
       <c r="D547" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E547" s="1" t="n">
         <v>0.03173284780352627</v>
@@ -37050,7 +37050,7 @@
         <v>0.00332386346873737</v>
       </c>
       <c r="D548" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E548" s="1" t="n">
         <v>0.03170089523479826</v>
@@ -37067,7 +37067,7 @@
         <v>0.003326672993402191</v>
       </c>
       <c r="D549" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E549" s="1" t="n">
         <v>0.03166926032412462</v>
@@ -37084,7 +37084,7 @@
         <v>0.003329731924782338</v>
       </c>
       <c r="D550" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E550" s="1" t="n">
         <v>0.0316401116556997</v>
@@ -37101,7 +37101,7 @@
         <v>0.003333194424467846</v>
       </c>
       <c r="D551" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E551" s="1" t="n">
         <v>0.03161503094900514</v>
@@ -37118,7 +37118,7 @@
         <v>0.003336917695919064</v>
       </c>
       <c r="D552" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E552" s="1" t="n">
         <v>0.03159237815697535</v>
@@ -37135,7 +37135,7 @@
         <v>0.003340684703063917</v>
       </c>
       <c r="D553" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E553" s="1" t="n">
         <v>0.03157022150264815</v>
@@ -37152,7 +37152,7 @@
         <v>0.003344278409830328</v>
       </c>
       <c r="D554" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E554" s="1" t="n">
         <v>0.03154664388887744</v>
@@ -37169,7 +37169,7 @@
         <v>0.003347544140623844</v>
       </c>
       <c r="D555" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E555" s="1" t="n">
         <v>0.03151993146844212</v>
@@ -37186,7 +37186,7 @@
         <v>0.003350576661760504</v>
       </c>
       <c r="D556" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E556" s="1" t="n">
         <v>0.03149125699537735</v>
@@ -37203,7 +37203,7 @@
         <v>0.003353533100033963</v>
       </c>
       <c r="D557" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E557" s="1" t="n">
         <v>0.03146184049494797</v>
@@ -37220,7 +37220,7 @@
         <v>0.003356570582237882</v>
       </c>
       <c r="D558" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E558" s="1" t="n">
         <v>0.0314334219683667</v>
@@ -37237,7 +37237,7 @@
         <v>0.003359802464261758</v>
       </c>
       <c r="D559" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E559" s="1" t="n">
         <v>0.03140692368166999</v>
@@ -37254,7 +37254,7 @@
         <v>0.003363167018378446</v>
       </c>
       <c r="D560" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E560" s="1" t="n">
         <v>0.03138162705372188</v>
@@ -37271,7 +37271,7 @@
         <v>0.003366558745956641</v>
       </c>
       <c r="D561" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E561" s="1" t="n">
         <v>0.03135667468282518</v>
@@ -37288,7 +37288,7 @@
         <v>0.003369872148365033</v>
       </c>
       <c r="D562" s="1" t="n">
-        <v>243.566</v>
+        <v>219.895</v>
       </c>
       <c r="E562" s="1" t="n">
         <v>0.03133121585781993</v>
@@ -37305,7 +37305,7 @@
         <v>0.003373036292194859</v>
       </c>
       <c r="D563" s="1" t="n">
-        <v>243.5658</v>
+        <v>219.8948</v>
       </c>
       <c r="E563" s="1" t="n">
         <v>0.03130433157041842</v>
@@ -37322,7 +37322,7 @@
         <v>0.0033761185049275</v>
       </c>
       <c r="D564" s="1" t="n">
-        <v>243.5655</v>
+        <v>219.8945</v>
       </c>
       <c r="E564" s="1" t="n">
         <v>0.03127678462252537</v>
@@ -37339,7 +37339,7 @@
         <v>0.003379220679266879</v>
       </c>
       <c r="D565" s="1" t="n">
-        <v>243.5652</v>
+        <v>219.8942</v>
       </c>
       <c r="E565" s="1" t="n">
         <v>0.03124965249588798</v>
@@ -37356,7 +37356,7 @@
         <v>0.00338244470791692</v>
       </c>
       <c r="D566" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E566" s="1" t="n">
         <v>0.03122361080482643</v>
@@ -37373,7 +37373,7 @@
         <v>0.003385852318604769</v>
       </c>
       <c r="D567" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E567" s="1" t="n">
         <v>0.03119935359333735</v>
@@ -37390,7 +37390,7 @@
         <v>0.003389344579150461</v>
       </c>
       <c r="D568" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E568" s="1" t="n">
         <v>0.03117596133506514</v>
@@ -37407,7 +37407,7 @@
         <v>0.003392782392397253</v>
       </c>
       <c r="D569" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E569" s="1" t="n">
         <v>0.03115228350392542</v>
@@ -37424,7 +37424,7 @@
         <v>0.003396026661188406</v>
       </c>
       <c r="D570" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E570" s="1" t="n">
         <v>0.03112678478428052</v>
@@ -37441,7 +37441,7 @@
         <v>0.003398986926103126</v>
       </c>
       <c r="D571" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E571" s="1" t="n">
         <v>0.03109877785326449</v>
@@ -37458,7 +37458,7 @@
         <v>0.00340176727866442</v>
       </c>
       <c r="D572" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E572" s="1" t="n">
         <v>0.03106935760902262</v>
@@ -37475,7 +37475,7 @@
         <v>0.003404520448131242</v>
       </c>
       <c r="D573" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E573" s="1" t="n">
         <v>0.03103966273537433</v>
@@ -37492,7 +37492,7 @@
         <v>0.003407399163762548</v>
       </c>
       <c r="D574" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E574" s="1" t="n">
         <v>0.03101121503429373</v>
@@ -37509,7 +37509,7 @@
         <v>0.00341051304749818</v>
       </c>
       <c r="D575" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E575" s="1" t="n">
         <v>0.03098500386134256</v>
@@ -37526,7 +37526,7 @@
         <v>0.003413799292001526</v>
       </c>
       <c r="D576" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E576" s="1" t="n">
         <v>0.03096057828362666</v>
@@ -37543,7 +37543,7 @@
         <v>0.00341715198261686</v>
       </c>
       <c r="D577" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E577" s="1" t="n">
         <v>0.03093670972308062</v>
@@ -37560,7 +37560,7 @@
         <v>0.00342046520468846</v>
       </c>
       <c r="D578" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E578" s="1" t="n">
         <v>0.03091256792076477</v>
@@ -37577,7 +37577,7 @@
         <v>0.003423653091857699</v>
       </c>
       <c r="D579" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E579" s="1" t="n">
         <v>0.03088750978514269</v>
@@ -37594,7 +37594,7 @@
         <v>0.003426709970954357</v>
       </c>
       <c r="D580" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E580" s="1" t="n">
         <v>0.0308612292947832</v>
@@ -37611,7 +37611,7 @@
         <v>0.003429650217105316</v>
       </c>
       <c r="D581" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E581" s="1" t="n">
         <v>0.03083399163580246</v>
@@ -37628,7 +37628,7 @@
         <v>0.003432488205437455</v>
       </c>
       <c r="D582" s="1" t="n">
-        <v>243.565</v>
+        <v>219.894</v>
       </c>
       <c r="E582" s="1" t="n">
         <v>0.03080606060849126</v>
@@ -37645,7 +37645,7 @@
         <v>0.003435260106508675</v>
       </c>
       <c r="D583" s="1" t="n">
-        <v>243.5648</v>
+        <v>219.8938</v>
       </c>
       <c r="E583" s="1" t="n">
         <v>0.03077750483173348</v>
@@ -37662,7 +37662,7 @@
         <v>0.003438089272600953</v>
       </c>
       <c r="D584" s="1" t="n">
-        <v>243.5645</v>
+        <v>219.8935</v>
       </c>
       <c r="E584" s="1" t="n">
         <v>0.03074968959443403</v>
@@ -37679,7 +37679,7 @@
         <v>0.003441120851427287</v>
       </c>
       <c r="D585" s="1" t="n">
-        <v>243.5642</v>
+        <v>219.8932</v>
       </c>
       <c r="E585" s="1" t="n">
         <v>0.03072364842219987</v>
@@ -37696,7 +37696,7 @@
         <v>0.003444499990700675</v>
       </c>
       <c r="D586" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E586" s="1" t="n">
         <v>0.03070079484998892</v>
@@ -37713,7 +37713,7 @@
         <v>0.00344830684142655</v>
       </c>
       <c r="D587" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E587" s="1" t="n">
         <v>0.03068195485331526</v>
@@ -37730,7 +37730,7 @@
         <v>0.003452361567780092</v>
       </c>
       <c r="D588" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E588" s="1" t="n">
         <v>0.03066525241452246</v>
@@ -37747,7 +37747,7 @@
         <v>0.003456419337228916</v>
       </c>
       <c r="D589" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E589" s="1" t="n">
         <v>0.03064863425759837</v>
@@ -37764,7 +37764,7 @@
         <v>0.003460235317240637</v>
       </c>
       <c r="D590" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E590" s="1" t="n">
         <v>0.03063006175804949</v>
@@ -37781,7 +37781,7 @@
         <v>0.003463635160121401</v>
       </c>
       <c r="D591" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E591" s="1" t="n">
         <v>0.030607746699764</v>
@@ -37798,7 +37798,7 @@
         <v>0.003466726457531482</v>
       </c>
       <c r="D592" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E592" s="1" t="n">
         <v>0.0305827858740151</v>
@@ -37815,7 +37815,7 @@
         <v>0.003469687285969676</v>
       </c>
       <c r="D593" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E593" s="1" t="n">
         <v>0.0305567610825698</v>
@@ -37832,7 +37832,7 @@
         <v>0.003472695721934791</v>
       </c>
       <c r="D594" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E594" s="1" t="n">
         <v>0.03053137201240926</v>
@@ -37849,7 +37849,7 @@
         <v>0.00347587867817815</v>
       </c>
       <c r="D595" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E595" s="1" t="n">
         <v>0.03050747258560272</v>
@@ -37866,7 +37866,7 @@
         <v>0.003479158412461188</v>
       </c>
       <c r="D596" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E596" s="1" t="n">
         <v>0.03048450214621648</v>
@@ -37883,7 +37883,7 @@
         <v>0.003482406018797867</v>
       </c>
       <c r="D597" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E597" s="1" t="n">
         <v>0.03046132841115696</v>
@@ -37900,7 +37900,7 @@
         <v>0.003485492591202144</v>
       </c>
       <c r="D598" s="1" t="n">
-        <v>243.564</v>
+        <v>219.893</v>
       </c>
       <c r="E598" s="1" t="n">
         <v>0.03043695499637085</v>
@@ -37917,7 +37917,7 @@
         <v>0.003488331917533506</v>
       </c>
       <c r="D599" s="1" t="n">
-        <v>243.5637</v>
+        <v>219.8927</v>
       </c>
       <c r="E599" s="1" t="n">
         <v>0.03041038043884439</v>
@@ -37934,7 +37934,7 @@
         <v>0.003491008561033535</v>
       </c>
       <c r="D600" s="1" t="n">
-        <v>243.5635</v>
+        <v>219.8925</v>
       </c>
       <c r="E600" s="1" t="n">
         <v>0.03038247951844966</v>
@@ -37951,7 +37951,7 @@
         <v>0.003493649778789342</v>
       </c>
       <c r="D601" s="1" t="n">
-        <v>243.5632</v>
+        <v>219.8922</v>
       </c>
       <c r="E601" s="1" t="n">
         <v>0.03035449248978299</v>
@@ -37968,7 +37968,7 @@
         <v>0.003496382827888034</v>
       </c>
       <c r="D602" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E602" s="1" t="n">
         <v>0.03032726832260561</v>
@@ -37985,7 +37985,7 @@
         <v>0.003499307531055794</v>
       </c>
       <c r="D603" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E603" s="1" t="n">
         <v>0.03030179496196215</v>
@@ -38002,7 +38002,7 @@
         <v>0.003502413973575099</v>
       </c>
       <c r="D604" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E604" s="1" t="n">
         <v>0.03027810549314507</v>
@@ -38019,7 +38019,7 @@
         <v>0.003505664806367504</v>
       </c>
       <c r="D605" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E605" s="1" t="n">
         <v>0.03025561402595645</v>
@@ -38036,7 +38036,7 @@
         <v>0.003509022680354561</v>
       </c>
       <c r="D606" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E606" s="1" t="n">
         <v>0.03023411980886202</v>
@@ -38053,7 +38053,7 @@
         <v>0.003512451223835116</v>
       </c>
       <c r="D607" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E607" s="1" t="n">
         <v>0.03021343231108096</v>
@@ -38070,7 +38070,7 @@
         <v>0.003515917974617204</v>
       </c>
       <c r="D608" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E608" s="1" t="n">
         <v>0.03019301467575908</v>
@@ -38087,7 +38087,7 @@
         <v>0.00351939144788615</v>
       </c>
       <c r="D609" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E609" s="1" t="n">
         <v>0.03017272239437153</v>
@@ -38104,7 +38104,7 @@
         <v>0.003522840158827285</v>
       </c>
       <c r="D610" s="1" t="n">
-        <v>243.563</v>
+        <v>219.892</v>
       </c>
       <c r="E610" s="1" t="n">
         <v>0.03015241241479917</v>
@@ -38121,7 +38121,7 @@
         <v>0.003526239149007052</v>
       </c>
       <c r="D611" s="1" t="n">
-        <v>243.5627</v>
+        <v>219.8917</v>
       </c>
       <c r="E611" s="1" t="n">
         <v>0.03013161799559376</v>
@@ -38138,7 +38138,7 @@
         <v>0.003529589565516365</v>
       </c>
       <c r="D612" s="1" t="n">
-        <v>243.5625</v>
+        <v>219.8915</v>
       </c>
       <c r="E612" s="1" t="n">
         <v>0.03011047782905513</v>
@@ -38155,7 +38155,7 @@
         <v>0.003532899081827256</v>
       </c>
       <c r="D613" s="1" t="n">
-        <v>243.5623</v>
+        <v>219.8913</v>
       </c>
       <c r="E613" s="1" t="n">
         <v>0.03008905897754973</v>
@@ -38172,7 +38172,7 @@
         <v>0.003536175371411757</v>
       </c>
       <c r="D614" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E614" s="1" t="n">
         <v>0.03006742806224422</v>
@@ -38189,7 +38189,7 @@
         <v>0.003539424259683123</v>
       </c>
       <c r="D615" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E615" s="1" t="n">
         <v>0.0300456355788372</v>
@@ -38206,7 +38206,7 @@
         <v>0.003542644179819511</v>
       </c>
       <c r="D616" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E616" s="1" t="n">
         <v>0.03002379555348183</v>
@@ -38223,7 +38223,7 @@
         <v>0.003545831716940305</v>
       </c>
       <c r="D617" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E617" s="1" t="n">
         <v>0.0300016268333155</v>
@@ -38240,7 +38240,7 @@
         <v>0.003548983456164884</v>
       </c>
       <c r="D618" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E618" s="1" t="n">
         <v>0.02997922816538489</v>
@@ -38257,7 +38257,7 @@
         <v>0.003552097374192507</v>
       </c>
       <c r="D619" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E619" s="1" t="n">
         <v>0.02995658361155618</v>
@@ -38274,7 +38274,7 @@
         <v>0.003555177014041948</v>
       </c>
       <c r="D620" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E620" s="1" t="n">
         <v>0.02993372420458104</v>
@@ -38291,7 +38291,7 @@
         <v>0.003558227310311859</v>
       </c>
       <c r="D621" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E621" s="1" t="n">
         <v>0.02991069247308399</v>
@@ -38308,7 +38308,7 @@
         <v>0.00356125319760089</v>
       </c>
       <c r="D622" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E622" s="1" t="n">
         <v>0.0298875306695296</v>
@@ -38325,7 +38325,7 @@
         <v>0.00356426149998984</v>
       </c>
       <c r="D623" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E623" s="1" t="n">
         <v>0.02986429660408655</v>
@@ -38342,7 +38342,7 @@
         <v>0.003567266599488105</v>
       </c>
       <c r="D624" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E624" s="1" t="n">
         <v>0.02984111093678197</v>
@@ -38359,7 +38359,7 @@
         <v>0.003570284767587227</v>
       </c>
       <c r="D625" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E625" s="1" t="n">
         <v>0.02981823497303774</v>
@@ -38376,7 +38376,7 @@
         <v>0.003573332275778752</v>
       </c>
       <c r="D626" s="1" t="n">
-        <v>243.562</v>
+        <v>219.891</v>
       </c>
       <c r="E626" s="1" t="n">
         <v>0.02979555211357533</v>
@@ -38393,7 +38393,7 @@
         <v>0.00357642328048239</v>
       </c>
       <c r="D627" s="1" t="n">
-        <v>243.5618</v>
+        <v>219.8908</v>
       </c>
       <c r="E627" s="1" t="n">
         <v>0.02977330441016298</v>
@@ -38410,7 +38410,7 @@
         <v>0.003579563477830536</v>
       </c>
       <c r="D628" s="1" t="n">
-        <v>243.5615</v>
+        <v>219.8905</v>
       </c>
       <c r="E628" s="1" t="n">
         <v>0.02975153710737417</v>
@@ -38427,7 +38427,7 @@
         <v>0.00358275644888375</v>
       </c>
       <c r="D629" s="1" t="n">
-        <v>243.5613</v>
+        <v>219.8903</v>
       </c>
       <c r="E629" s="1" t="n">
         <v>0.02973027760808813</v>
@@ -38444,7 +38444,7 @@
         <v>0.003586005774702598</v>
       </c>
       <c r="D630" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E630" s="1" t="n">
         <v>0.02970955313952463</v>
@@ -38461,7 +38461,7 @@
         <v>0.003589310742150968</v>
       </c>
       <c r="D631" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E631" s="1" t="n">
         <v>0.02968935523475708</v>
@@ -38478,7 +38478,7 @@
         <v>0.00359265346130607</v>
       </c>
       <c r="D632" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E632" s="1" t="n">
         <v>0.02966953362835626</v>
@@ -38495,7 +38495,7 @@
         <v>0.00359601174804844</v>
       </c>
       <c r="D633" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E633" s="1" t="n">
         <v>0.02964990360693306</v>
@@ -38512,7 +38512,7 @@
         <v>0.003599363418258617</v>
       </c>
       <c r="D634" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E634" s="1" t="n">
         <v>0.02963040648732329</v>
@@ -38529,7 +38529,7 @@
         <v>0.00360269243652826</v>
       </c>
       <c r="D635" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E635" s="1" t="n">
         <v>0.02961066064547442</v>
@@ -38546,7 +38546,7 @@
         <v>0.003606007362293521</v>
       </c>
       <c r="D636" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E636" s="1" t="n">
         <v>0.02959086184588191</v>
@@ -38563,7 +38563,7 @@
         <v>0.003609322903701675</v>
       </c>
       <c r="D637" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E637" s="1" t="n">
         <v>0.02957125544895248</v>
@@ -38580,7 +38580,7 @@
         <v>0.003612653768899996</v>
       </c>
       <c r="D638" s="1" t="n">
-        <v>243.561</v>
+        <v>219.89</v>
       </c>
       <c r="E638" s="1" t="n">
         <v>0.02955171215350788</v>
@@ -38597,7 +38597,7 @@
         <v>0.003616007683777291</v>
       </c>
       <c r="D639" s="1" t="n">
-        <v>243.5608</v>
+        <v>219.8898</v>
       </c>
       <c r="E639" s="1" t="n">
         <v>0.0295325432984351</v>
@@ -38614,7 +38614,7 @@
         <v>0.003619364445188515</v>
       </c>
       <c r="D640" s="1" t="n">
-        <v>243.5605</v>
+        <v>219.8895</v>
       </c>
       <c r="E640" s="1" t="n">
         <v>0.0295133339935224</v>
@@ -38631,7 +38631,7 @@
         <v>0.003622696867730154</v>
       </c>
       <c r="D641" s="1" t="n">
-        <v>243.5602</v>
+        <v>219.8892</v>
       </c>
       <c r="E641" s="1" t="n">
         <v>0.02949411131776148</v>
@@ -38648,7 +38648,7 @@
         <v>0.003625977765998694</v>
       </c>
       <c r="D642" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E642" s="1" t="n">
         <v>0.02947440629501574</v>
@@ -38665,7 +38665,7 @@
         <v>0.003629190344185621</v>
       </c>
       <c r="D643" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E643" s="1" t="n">
         <v>0.02945433277421799</v>
@@ -38682,7 +38682,7 @@
         <v>0.003632359364862405</v>
       </c>
       <c r="D644" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E644" s="1" t="n">
         <v>0.029433845413624</v>
@@ -38699,7 +38699,7 @@
         <v>0.003635519980195511</v>
       </c>
       <c r="D645" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E645" s="1" t="n">
         <v>0.02941335417237571</v>
@@ -38716,7 +38716,7 @@
         <v>0.003638707342351408</v>
       </c>
       <c r="D646" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E646" s="1" t="n">
         <v>0.02939314302462918</v>
@@ -38733,7 +38733,7 @@
         <v>0.003641948664153753</v>
       </c>
       <c r="D647" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E647" s="1" t="n">
         <v>0.02937355391325631</v>
@@ -38750,7 +38750,7 @@
         <v>0.003645239401054959</v>
       </c>
       <c r="D648" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E648" s="1" t="n">
         <v>0.02935430028469507</v>
@@ -38767,7 +38767,7 @@
         <v>0.003648567069164632</v>
       </c>
       <c r="D649" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E649" s="1" t="n">
         <v>0.02933540347927475</v>
@@ -38784,7 +38784,7 @@
         <v>0.003651919184592374</v>
       </c>
       <c r="D650" s="1" t="n">
-        <v>243.56</v>
+        <v>219.889</v>
       </c>
       <c r="E650" s="1" t="n">
         <v>0.02931676161699426</v>
@@ -38801,7 +38801,7 @@
         <v>0.003655278695413185</v>
       </c>
       <c r="D651" s="1" t="n">
-        <v>243.5598</v>
+        <v>219.8888</v>
       </c>
       <c r="E651" s="1" t="n">
         <v>0.02929836029308094</v>
@@ -38818,7 +38818,7 @@
         <v>0.003658610277563641</v>
       </c>
       <c r="D652" s="1" t="n">
-        <v>243.5595</v>
+        <v>219.8885</v>
       </c>
       <c r="E652" s="1" t="n">
         <v>0.02927966927422223</v>
@@ -38835,7 +38835,7 @@
         <v>0.003661874038945717</v>
       </c>
       <c r="D653" s="1" t="n">
-        <v>243.5592</v>
+        <v>219.8882</v>
       </c>
       <c r="E653" s="1" t="n">
         <v>0.02926049410564283</v>
@@ -38852,7 +38852,7 @@
         <v>0.003665030087461379</v>
       </c>
       <c r="D654" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E654" s="1" t="n">
         <v>0.02924051875972748</v>
@@ -38869,7 +38869,7 @@
         <v>0.003668053702250028</v>
       </c>
       <c r="D655" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E655" s="1" t="n">
         <v>0.02921955001003462</v>
@@ -38886,7 +38886,7 @@
         <v>0.003670980847400753</v>
       </c>
       <c r="D656" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E656" s="1" t="n">
         <v>0.02919800152437161</v>
@@ -38903,7 +38903,7 @@
         <v>0.00367386265824007</v>
       </c>
       <c r="D657" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E657" s="1" t="n">
         <v>0.02917603646840524</v>
@@ -38920,7 +38920,7 @@
         <v>0.003676750270094494</v>
       </c>
       <c r="D658" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E658" s="1" t="n">
         <v>0.02915418478810357</v>
@@ -38937,7 +38937,7 @@
         <v>0.003679683212834614</v>
       </c>
       <c r="D659" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E659" s="1" t="n">
         <v>0.02913275892817815</v>
@@ -38954,7 +38954,7 @@
         <v>0.003682654594507305</v>
       </c>
       <c r="D660" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E660" s="1" t="n">
         <v>0.02911182512653455</v>
@@ -38971,7 +38971,7 @@
         <v>0.00368564591770352</v>
       </c>
       <c r="D661" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E661" s="1" t="n">
         <v>0.02909099025777364</v>
@@ -38988,7 +38988,7 @@
         <v>0.003688638685014209</v>
       </c>
       <c r="D662" s="1" t="n">
-        <v>243.559</v>
+        <v>219.888</v>
       </c>
       <c r="E662" s="1" t="n">
         <v>0.0290702302910472</v>
@@ -39005,7 +39005,7 @@
         <v>0.003691618136628069</v>
       </c>
       <c r="D663" s="1" t="n">
-        <v>243.5588</v>
+        <v>219.8878</v>
       </c>
       <c r="E663" s="1" t="n">
         <v>0.0290495511498367</v>
@@ -39022,7 +39022,7 @@
         <v>0.003694584463124793</v>
       </c>
       <c r="D664" s="1" t="n">
-        <v>243.5585</v>
+        <v>219.8875</v>
       </c>
       <c r="E664" s="1" t="n">
         <v>0.02902870961171944</v>
@@ -39039,7 +39039,7 @@
         <v>0.003697541592681825</v>
       </c>
       <c r="D665" s="1" t="n">
-        <v>243.5582</v>
+        <v>219.8872</v>
       </c>
       <c r="E665" s="1" t="n">
         <v>0.02900798141016084</v>
@@ -39056,7 +39056,7 @@
         <v>0.003700493453476603</v>
       </c>
       <c r="D666" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E666" s="1" t="n">
         <v>0.02898715279610252</v>
@@ -39073,7 +39073,7 @@
         <v>0.003703451844237278</v>
       </c>
       <c r="D667" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E667" s="1" t="n">
         <v>0.02896656033961734</v>
@@ -39090,7 +39090,7 @@
         <v>0.003706460045894823</v>
       </c>
       <c r="D668" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E668" s="1" t="n">
         <v>0.02894629732319361</v>
@@ -39107,7 +39107,7 @@
         <v>0.003709569209930919</v>
       </c>
       <c r="D669" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E669" s="1" t="n">
         <v>0.02892688272743742</v>
@@ -39124,7 +39124,7 @@
         <v>0.003712830487827249</v>
       </c>
       <c r="D670" s="1" t="n">
-        <v>243.558</v>
+        <v>219.887</v>
       </c>
       <c r="E670" s="1" t="n">
         <v>0.02890883281237169</v>
@@ -39141,7 +39141,7 @@
         <v>0.003716273830622135</v>
       </c>
       <c r="D671" s="1" t="n">
-        <v>243.5577</v>
+        <v>219.8867</v>
       </c>
       <c r="E671" s="1" t="n">
         <v>0.02889213111502984</v>
@@ -39158,7 +39158,7 @@
         <v>0.003719844387580464</v>
       </c>
       <c r="D672" s="1" t="n">
-        <v>243.5575</v>
+        <v>219.8865</v>
       </c>
       <c r="E672" s="1" t="n">
         <v>0.02887646711306443</v>
@@ -39175,7 +39175,7 @@
         <v>0.003723466107523772</v>
       </c>
       <c r="D673" s="1" t="n">
-        <v>243.5572</v>
+        <v>219.8862</v>
       </c>
       <c r="E673" s="1" t="n">
         <v>0.02886136827286849</v>
@@ -39192,7 +39192,7 @@
         <v>0.003727062939273587</v>
       </c>
       <c r="D674" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E674" s="1" t="n">
         <v>0.02884600069427026</v>
@@ -39209,7 +39209,7 @@
         <v>0.003730558831651444</v>
       </c>
       <c r="D675" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E675" s="1" t="n">
         <v>0.02882989899434722</v>
@@ -39226,7 +39226,7 @@
         <v>0.003733877733478871</v>
       </c>
       <c r="D676" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E676" s="1" t="n">
         <v>0.02881247961104503</v>
@@ -39243,7 +39243,7 @@
         <v>0.003736943593577402</v>
       </c>
       <c r="D677" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E677" s="1" t="n">
         <v>0.02879328379454835</v>
@@ -39260,7 +39260,7 @@
         <v>0.003739680360768567</v>
       </c>
       <c r="D678" s="1" t="n">
-        <v>243.557</v>
+        <v>219.886</v>
       </c>
       <c r="E678" s="1" t="n">
         <v>0.02877149215565401</v>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27251,7 +27251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE678"/>
+  <dimension ref="A1:AE679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="22" max="22"/>
@@ -27290,6 +27290,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -27406,7 +27407,7 @@
         <v>0.04943550000000001</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>72.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
@@ -27506,7 +27507,7 @@
         <v>0.113546</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>18.78</v>
+        <v>8.35</v>
       </c>
       <c r="V6" t="n">
         <v>24</v>
@@ -27586,7 +27587,7 @@
         <v>0.188016</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>4.53</v>
+        <v>-10.17</v>
       </c>
       <c r="V7" t="n">
         <v>72</v>
@@ -27666,7 +27667,7 @@
         <v>0.240095</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>3.18</v>
+        <v>-5.59</v>
       </c>
       <c r="V8" t="n">
         <v>168</v>
@@ -27746,7 +27747,7 @@
         <v>0.333439</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>3.15</v>
+        <v>7.25</v>
       </c>
       <c r="V9" t="n">
         <v>336</v>
@@ -27920,7 +27921,7 @@
         </is>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.01853</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="13">
@@ -27950,7 +27951,7 @@
         </is>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>10.02</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="14">
@@ -27975,7 +27976,7 @@
         </is>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.9637</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="15">
@@ -27994,6 +27995,11 @@
       <c r="E15" s="1" t="n">
         <v>0.1226465337943992</v>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Error (%) = (Sim - Exp)/Exp x 100 (signed). Relative RMSE = RMSE / mean(Exp) x 100. n = 5 time points.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -39266,6 +39272,7 @@
         <v>0.02877149215565401</v>
       </c>
     </row>
+    <row r="679"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27374,11 +27374,7 @@
           <t>Mass Loss (%)</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>CR (mm/yr)</t>
-        </is>
-      </c>
+      <c r="I5" s="1" t="n"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
           <t>Time (h)</t>
@@ -27482,9 +27478,7 @@
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" s="1" t="n"/>
       <c r="K6" s="1" t="n">
         <v>0</v>
       </c>
@@ -27562,9 +27556,7 @@
       <c r="H7" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>0.1067952306653765</v>
-      </c>
+      <c r="I7" s="1" t="n"/>
       <c r="K7" s="1" t="n">
         <v>24</v>
       </c>
@@ -27642,9 +27634,7 @@
       <c r="H8" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>0.08409364711831444</v>
-      </c>
+      <c r="I8" s="1" t="n"/>
       <c r="K8" s="1" t="n">
         <v>48</v>
       </c>
@@ -27722,9 +27712,7 @@
       <c r="H9" s="1" t="n">
         <v>0.209</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>0.07193659722129592</v>
-      </c>
+      <c r="I9" s="1" t="n"/>
       <c r="K9" s="1" t="n">
         <v>120</v>
       </c>
@@ -27802,9 +27790,7 @@
       <c r="H10" s="1" t="n">
         <v>0.254</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>0.04380212733658804</v>
-      </c>
+      <c r="I10" s="1" t="n"/>
       <c r="K10" s="1" t="n">
         <v>168</v>
       </c>
@@ -27867,9 +27853,7 @@
       <c r="H11" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0.02674901834980745</v>
-      </c>
+      <c r="I11" s="1" t="n"/>
       <c r="K11" s="1" t="n">
         <v>240</v>
       </c>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -27385,11 +27385,7 @@
           <t>Mass Loss (%)</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>CR (mm/yr)</t>
-        </is>
-      </c>
+      <c r="M5" s="1" t="n"/>
       <c r="P5" s="1" t="n">
         <v>24</v>
       </c>
@@ -27485,9 +27481,7 @@
       <c r="L6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M6" s="1" t="n"/>
       <c r="P6" s="1" t="n">
         <v>72</v>
       </c>
@@ -27563,9 +27557,7 @@
       <c r="L7" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>0.1186613674059739</v>
-      </c>
+      <c r="M7" s="1" t="n"/>
       <c r="P7" s="1" t="n">
         <v>168</v>
       </c>
@@ -27641,9 +27633,7 @@
       <c r="L8" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>0.1078609506302521</v>
-      </c>
+      <c r="M8" s="1" t="n"/>
       <c r="P8" s="1" t="n">
         <v>336</v>
       </c>
@@ -27719,9 +27709,7 @@
       <c r="L9" s="1" t="n">
         <v>0.13</v>
       </c>
-      <c r="M9" s="1" t="n">
-        <v>0.06257682180156594</v>
-      </c>
+      <c r="M9" s="1" t="n"/>
       <c r="P9" s="1" t="n">
         <v>672</v>
       </c>
@@ -27797,9 +27785,7 @@
       <c r="L10" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>0.06883884901559419</v>
-      </c>
+      <c r="M10" s="1" t="n"/>
       <c r="V10" t="n">
         <v>672</v>
       </c>
@@ -27860,9 +27846,7 @@
       <c r="L11" s="1" t="n">
         <v>0.27</v>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>0.06512907265689372</v>
-      </c>
+      <c r="M11" s="1" t="n"/>
       <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
@@ -27896,9 +27880,7 @@
       <c r="L12" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>0.05518378247129202</v>
-      </c>
+      <c r="M12" s="1" t="n"/>
       <c r="P12" s="1" t="inlineStr">
         <is>
           <t>RMSE (absolute)</t>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -39550,7 +39550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D725"/>
+  <dimension ref="A1:D729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39615,7 +39615,7 @@
         <v>12.2546</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.014076</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="7">
@@ -39629,7 +39629,7 @@
         <v>12.2508</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.122745</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="8">
@@ -39643,7 +39643,7 @@
         <v>12.2474</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.156301</v>
+        <v>0.0414</v>
       </c>
     </row>
     <row r="9">
@@ -39657,7 +39657,7 @@
         <v>12.2441</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.171456</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="10">
@@ -39671,7 +39671,7 @@
         <v>12.2411</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.179216</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -39685,7 +39685,7 @@
         <v>12.2381</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.183577</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="12">
@@ -39699,7 +39699,7 @@
         <v>12.2352</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.185982</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="13">
@@ -39713,7 +39713,7 @@
         <v>12.2324</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.187354</v>
+        <v>0.0906</v>
       </c>
     </row>
     <row r="14">
@@ -39727,7 +39727,7 @@
         <v>12.2297</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.188082</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="15">
@@ -39741,7 +39741,7 @@
         <v>12.2271</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.188414</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="16">
@@ -39755,7 +39755,7 @@
         <v>12.2245</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.188485</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="17">
@@ -39769,7 +39769,7 @@
         <v>12.222</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.188136</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="18">
@@ -39783,7 +39783,7 @@
         <v>12.2195</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.187623</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="19">
@@ -39797,7 +39797,7 @@
         <v>12.2171</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.187017</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="20">
@@ -39811,7 +39811,7 @@
         <v>12.2147</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.186305</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -39825,7 +39825,7 @@
         <v>12.2124</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.185531</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="22">
@@ -39839,7 +39839,7 @@
         <v>12.2101</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.184745</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="23">
@@ -39853,7 +39853,7 @@
         <v>12.2078</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.183916</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="24">
@@ -39867,7 +39867,7 @@
         <v>12.2056</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.183055</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="25">
@@ -39881,7 +39881,7 @@
         <v>12.2034</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.182146</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="26">
@@ -39895,7 +39895,7 @@
         <v>12.2012</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.181171</v>
+        <v>0.1366</v>
       </c>
     </row>
     <row r="27">
@@ -39909,7 +39909,7 @@
         <v>12.1991</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.180228</v>
+        <v>0.1382</v>
       </c>
     </row>
     <row r="28">
@@ -39923,7 +39923,7 @@
         <v>12.1971</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.179259</v>
+        <v>0.1398</v>
       </c>
     </row>
     <row r="29">
@@ -39937,7 +39937,7 @@
         <v>12.195</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.178319</v>
+        <v>0.1414</v>
       </c>
     </row>
     <row r="30">
@@ -39951,7 +39951,7 @@
         <v>12.193</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.177367</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="31">
@@ -39965,7 +39965,7 @@
         <v>12.1911</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.176368</v>
+        <v>0.1446</v>
       </c>
     </row>
     <row r="32">
@@ -39979,7 +39979,7 @@
         <v>12.1891</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.175401</v>
+        <v>0.1462</v>
       </c>
     </row>
     <row r="33">
@@ -39993,7 +39993,7 @@
         <v>12.1872</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.174477</v>
+        <v>0.1478</v>
       </c>
     </row>
     <row r="34">
@@ -40007,7 +40007,7 @@
         <v>12.1854</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.173574</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="35">
@@ -40021,7 +40021,7 @@
         <v>12.1835</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.172623</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="36">
@@ -40035,7 +40035,7 @@
         <v>12.1818</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.171704</v>
+        <v>0.1514</v>
       </c>
     </row>
     <row r="37">
@@ -40049,7 +40049,7 @@
         <v>12.18</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.170759</v>
+        <v>0.1518</v>
       </c>
     </row>
     <row r="38">
@@ -40063,7 +40063,7 @@
         <v>12.1783</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.169804</v>
+        <v>0.1522</v>
       </c>
     </row>
     <row r="39">
@@ -40077,7 +40077,7 @@
         <v>12.1766</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.16887</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="40">
@@ -40091,7 +40091,7 @@
         <v>12.1749</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.167945</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="41">
@@ -40105,7 +40105,7 @@
         <v>12.1733</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.167005</v>
+        <v>0.1534</v>
       </c>
     </row>
     <row r="42">
@@ -40119,7 +40119,7 @@
         <v>12.1717</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.166086</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="43">
@@ -40133,7 +40133,7 @@
         <v>12.1702</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.165164</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="44">
@@ -40147,7 +40147,7 @@
         <v>12.1687</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.164255</v>
+        <v>0.1546</v>
       </c>
     </row>
     <row r="45">
@@ -40161,7 +40161,7 @@
         <v>12.1672</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.16332</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="46">
@@ -40175,7 +40175,7 @@
         <v>12.1657</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.162425</v>
+        <v>0.1546</v>
       </c>
     </row>
     <row r="47">
@@ -40189,7 +40189,7 @@
         <v>12.1643</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.161514</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="48">
@@ -40203,7 +40203,7 @@
         <v>12.1629</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.160612</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="49">
@@ -40217,7 +40217,7 @@
         <v>12.1615</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.159721</v>
+        <v>0.1534</v>
       </c>
     </row>
     <row r="50">
@@ -40231,7 +40231,7 @@
         <v>12.1602</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.158829</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="51">
@@ -40245,7 +40245,7 @@
         <v>12.1589</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.157963</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="52">
@@ -40259,7 +40259,7 @@
         <v>12.1576</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.157066</v>
+        <v>0.1522</v>
       </c>
     </row>
     <row r="53">
@@ -40273,7 +40273,7 @@
         <v>12.1564</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.156192</v>
+        <v>0.1518</v>
       </c>
     </row>
     <row r="54">
@@ -40287,7 +40287,7 @@
         <v>12.1552</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.155318</v>
+        <v>0.1514</v>
       </c>
     </row>
     <row r="55">
@@ -40301,7 +40301,7 @@
         <v>12.154</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.154436</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="56">
@@ -40315,7 +40315,7 @@
         <v>12.1528</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.153578</v>
+        <v>0.1506</v>
       </c>
     </row>
     <row r="57">
@@ -40329,7 +40329,7 @@
         <v>12.1517</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.152712</v>
+        <v>0.1502</v>
       </c>
     </row>
     <row r="58">
@@ -40343,7 +40343,7 @@
         <v>12.1505</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>0.151854</v>
+        <v>0.1498</v>
       </c>
     </row>
     <row r="59">
@@ -40357,7 +40357,7 @@
         <v>12.1495</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0.150995</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="60">
@@ -40371,7 +40371,7 @@
         <v>12.1484</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>0.150135</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="61">
@@ -40385,7 +40385,7 @@
         <v>12.1473</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>0.149292</v>
+        <v>0.1486</v>
       </c>
     </row>
     <row r="62">
@@ -40399,7 +40399,7 @@
         <v>12.1463</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.148451</v>
+        <v>0.1482</v>
       </c>
     </row>
     <row r="63">
@@ -40413,7 +40413,7 @@
         <v>12.1453</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.14762</v>
+        <v>0.1478</v>
       </c>
     </row>
     <row r="64">
@@ -40427,7 +40427,7 @@
         <v>12.1443</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.146806</v>
+        <v>0.1474</v>
       </c>
     </row>
     <row r="65">
@@ -40441,7 +40441,7 @@
         <v>12.1433</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>0.145992</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="66">
@@ -40455,7 +40455,7 @@
         <v>12.1423</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>0.145171</v>
+        <v>0.1464</v>
       </c>
     </row>
     <row r="67">
@@ -40469,7 +40469,7 @@
         <v>12.1414</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.144359</v>
+        <v>0.1459</v>
       </c>
     </row>
     <row r="68">
@@ -40483,7 +40483,7 @@
         <v>12.1405</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>0.143558</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="69">
@@ -40497,7 +40497,7 @@
         <v>12.1395</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>0.142787</v>
+        <v>0.1447</v>
       </c>
     </row>
     <row r="70">
@@ -40511,7 +40511,7 @@
         <v>12.1386</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>0.142002</v>
+        <v>0.1441</v>
       </c>
     </row>
     <row r="71">
@@ -40525,7 +40525,7 @@
         <v>12.1377</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>0.141224</v>
+        <v>0.1436</v>
       </c>
     </row>
     <row r="72">
@@ -40539,7 +40539,7 @@
         <v>12.1369</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>0.14047</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="73">
@@ -40553,7 +40553,7 @@
         <v>12.136</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>0.139711</v>
+        <v>0.1424</v>
       </c>
     </row>
     <row r="74">
@@ -40567,7 +40567,7 @@
         <v>12.1351</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.138967</v>
+        <v>0.1418</v>
       </c>
     </row>
     <row r="75">
@@ -40581,7 +40581,7 @@
         <v>12.1343</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>0.138221</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="76">
@@ -40595,7 +40595,7 @@
         <v>12.1335</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.137488</v>
+        <v>0.1407</v>
       </c>
     </row>
     <row r="77">
@@ -40609,7 +40609,7 @@
         <v>12.1326</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>0.13675</v>
+        <v>0.1401</v>
       </c>
     </row>
     <row r="78">
@@ -40623,7 +40623,7 @@
         <v>12.1318</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>0.136027</v>
+        <v>0.1395</v>
       </c>
     </row>
     <row r="79">
@@ -40637,7 +40637,7 @@
         <v>12.131</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>0.13531</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="80">
@@ -40651,7 +40651,7 @@
         <v>12.1302</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>0.134597</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="81">
@@ -40665,7 +40665,7 @@
         <v>12.1294</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>0.133889</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="82">
@@ -40679,7 +40679,7 @@
         <v>12.1286</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>0.133197</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="83">
@@ -40693,7 +40693,7 @@
         <v>12.1279</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>0.132526</v>
+        <v>0.1367</v>
       </c>
     </row>
     <row r="84">
@@ -40707,7 +40707,7 @@
         <v>12.1271</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>0.13185</v>
+        <v>0.1361</v>
       </c>
     </row>
     <row r="85">
@@ -40721,7 +40721,7 @@
         <v>12.1263</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>0.13118</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="86">
@@ -40735,7 +40735,7 @@
         <v>12.1256</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>0.130516</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="87">
@@ -40749,7 +40749,7 @@
         <v>12.1248</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>0.129864</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="88">
@@ -40763,7 +40763,7 @@
         <v>12.124</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.129225</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="89">
@@ -40777,7 +40777,7 @@
         <v>12.1233</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>0.128594</v>
+        <v>0.1332</v>
       </c>
     </row>
     <row r="90">
@@ -40791,7 +40791,7 @@
         <v>12.1225</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0.127959</v>
+        <v>0.1326</v>
       </c>
     </row>
     <row r="91">
@@ -40805,7 +40805,7 @@
         <v>12.1218</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0.127337</v>
+        <v>0.1321</v>
       </c>
     </row>
     <row r="92">
@@ -40819,7 +40819,7 @@
         <v>12.1211</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0.12673</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="93">
@@ -40833,7 +40833,7 @@
         <v>12.1203</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>0.12613</v>
+        <v>0.1309</v>
       </c>
     </row>
     <row r="94">
@@ -40847,7 +40847,7 @@
         <v>12.1196</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>0.125525</v>
+        <v>0.1303</v>
       </c>
     </row>
     <row r="95">
@@ -40861,7 +40861,7 @@
         <v>12.1189</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>0.124927</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="96">
@@ -40875,7 +40875,7 @@
         <v>12.1181</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>0.124347</v>
+        <v>0.1292</v>
       </c>
     </row>
     <row r="97">
@@ -40889,7 +40889,7 @@
         <v>12.1174</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>0.123781</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="98">
@@ -40903,7 +40903,7 @@
         <v>12.1167</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>0.123208</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="99">
@@ -40917,7 +40917,7 @@
         <v>12.1159</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>0.122648</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="100">
@@ -40931,7 +40931,7 @@
         <v>12.1152</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>0.1221</v>
+        <v>0.1269</v>
       </c>
     </row>
     <row r="101">
@@ -40945,7 +40945,7 @@
         <v>12.1145</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>0.121556</v>
+        <v>0.1263</v>
       </c>
     </row>
     <row r="102">
@@ -40959,7 +40959,7 @@
         <v>12.1138</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>0.121019</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="103">
@@ -40973,7 +40973,7 @@
         <v>12.113</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>0.120483</v>
+        <v>0.1252</v>
       </c>
     </row>
     <row r="104">
@@ -40987,7 +40987,7 @@
         <v>12.1123</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>0.119957</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="105">
@@ -41001,7 +41001,7 @@
         <v>12.1116</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>0.119436</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="106">
@@ -49300,6 +49300,10 @@
       <c r="C725" s="1" t="n"/>
       <c r="D725" s="1" t="n"/>
     </row>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -39550,7 +39550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D729"/>
+  <dimension ref="A1:D677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49012,298 +49012,6 @@
         <v>0.059566</v>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" s="1" t="n"/>
-      <c r="B678" s="1" t="n"/>
-      <c r="C678" s="1" t="n"/>
-      <c r="D678" s="1" t="n"/>
-    </row>
-    <row r="679">
-      <c r="A679" s="1" t="n"/>
-      <c r="B679" s="1" t="n"/>
-      <c r="C679" s="1" t="n"/>
-      <c r="D679" s="1" t="n"/>
-    </row>
-    <row r="680">
-      <c r="A680" s="1" t="n"/>
-      <c r="B680" s="1" t="n"/>
-      <c r="C680" s="1" t="n"/>
-      <c r="D680" s="1" t="n"/>
-    </row>
-    <row r="681">
-      <c r="A681" s="1" t="n"/>
-      <c r="B681" s="1" t="n"/>
-      <c r="C681" s="1" t="n"/>
-      <c r="D681" s="1" t="n"/>
-    </row>
-    <row r="682">
-      <c r="A682" s="1" t="n"/>
-      <c r="B682" s="1" t="n"/>
-      <c r="C682" s="1" t="n"/>
-      <c r="D682" s="1" t="n"/>
-    </row>
-    <row r="683">
-      <c r="A683" s="1" t="n"/>
-      <c r="B683" s="1" t="n"/>
-      <c r="C683" s="1" t="n"/>
-      <c r="D683" s="1" t="n"/>
-    </row>
-    <row r="684">
-      <c r="A684" s="1" t="n"/>
-      <c r="B684" s="1" t="n"/>
-      <c r="C684" s="1" t="n"/>
-      <c r="D684" s="1" t="n"/>
-    </row>
-    <row r="685">
-      <c r="A685" s="1" t="n"/>
-      <c r="B685" s="1" t="n"/>
-      <c r="C685" s="1" t="n"/>
-      <c r="D685" s="1" t="n"/>
-    </row>
-    <row r="686">
-      <c r="A686" s="1" t="n"/>
-      <c r="B686" s="1" t="n"/>
-      <c r="C686" s="1" t="n"/>
-      <c r="D686" s="1" t="n"/>
-    </row>
-    <row r="687">
-      <c r="A687" s="1" t="n"/>
-      <c r="B687" s="1" t="n"/>
-      <c r="C687" s="1" t="n"/>
-      <c r="D687" s="1" t="n"/>
-    </row>
-    <row r="688">
-      <c r="A688" s="1" t="n"/>
-      <c r="B688" s="1" t="n"/>
-      <c r="C688" s="1" t="n"/>
-      <c r="D688" s="1" t="n"/>
-    </row>
-    <row r="689">
-      <c r="A689" s="1" t="n"/>
-      <c r="B689" s="1" t="n"/>
-      <c r="C689" s="1" t="n"/>
-      <c r="D689" s="1" t="n"/>
-    </row>
-    <row r="690">
-      <c r="A690" s="1" t="n"/>
-      <c r="B690" s="1" t="n"/>
-      <c r="C690" s="1" t="n"/>
-      <c r="D690" s="1" t="n"/>
-    </row>
-    <row r="691">
-      <c r="A691" s="1" t="n"/>
-      <c r="B691" s="1" t="n"/>
-      <c r="C691" s="1" t="n"/>
-      <c r="D691" s="1" t="n"/>
-    </row>
-    <row r="692">
-      <c r="A692" s="1" t="n"/>
-      <c r="B692" s="1" t="n"/>
-      <c r="C692" s="1" t="n"/>
-      <c r="D692" s="1" t="n"/>
-    </row>
-    <row r="693">
-      <c r="A693" s="1" t="n"/>
-      <c r="B693" s="1" t="n"/>
-      <c r="C693" s="1" t="n"/>
-      <c r="D693" s="1" t="n"/>
-    </row>
-    <row r="694">
-      <c r="A694" s="1" t="n"/>
-      <c r="B694" s="1" t="n"/>
-      <c r="C694" s="1" t="n"/>
-      <c r="D694" s="1" t="n"/>
-    </row>
-    <row r="695">
-      <c r="A695" s="1" t="n"/>
-      <c r="B695" s="1" t="n"/>
-      <c r="C695" s="1" t="n"/>
-      <c r="D695" s="1" t="n"/>
-    </row>
-    <row r="696">
-      <c r="A696" s="1" t="n"/>
-      <c r="B696" s="1" t="n"/>
-      <c r="C696" s="1" t="n"/>
-      <c r="D696" s="1" t="n"/>
-    </row>
-    <row r="697">
-      <c r="A697" s="1" t="n"/>
-      <c r="B697" s="1" t="n"/>
-      <c r="C697" s="1" t="n"/>
-      <c r="D697" s="1" t="n"/>
-    </row>
-    <row r="698">
-      <c r="A698" s="1" t="n"/>
-      <c r="B698" s="1" t="n"/>
-      <c r="C698" s="1" t="n"/>
-      <c r="D698" s="1" t="n"/>
-    </row>
-    <row r="699">
-      <c r="A699" s="1" t="n"/>
-      <c r="B699" s="1" t="n"/>
-      <c r="C699" s="1" t="n"/>
-      <c r="D699" s="1" t="n"/>
-    </row>
-    <row r="700">
-      <c r="A700" s="1" t="n"/>
-      <c r="B700" s="1" t="n"/>
-      <c r="C700" s="1" t="n"/>
-      <c r="D700" s="1" t="n"/>
-    </row>
-    <row r="701">
-      <c r="A701" s="1" t="n"/>
-      <c r="B701" s="1" t="n"/>
-      <c r="C701" s="1" t="n"/>
-      <c r="D701" s="1" t="n"/>
-    </row>
-    <row r="702">
-      <c r="A702" s="1" t="n"/>
-      <c r="B702" s="1" t="n"/>
-      <c r="C702" s="1" t="n"/>
-      <c r="D702" s="1" t="n"/>
-    </row>
-    <row r="703">
-      <c r="A703" s="1" t="n"/>
-      <c r="B703" s="1" t="n"/>
-      <c r="C703" s="1" t="n"/>
-      <c r="D703" s="1" t="n"/>
-    </row>
-    <row r="704">
-      <c r="A704" s="1" t="n"/>
-      <c r="B704" s="1" t="n"/>
-      <c r="C704" s="1" t="n"/>
-      <c r="D704" s="1" t="n"/>
-    </row>
-    <row r="705">
-      <c r="A705" s="1" t="n"/>
-      <c r="B705" s="1" t="n"/>
-      <c r="C705" s="1" t="n"/>
-      <c r="D705" s="1" t="n"/>
-    </row>
-    <row r="706">
-      <c r="A706" s="1" t="n"/>
-      <c r="B706" s="1" t="n"/>
-      <c r="C706" s="1" t="n"/>
-      <c r="D706" s="1" t="n"/>
-    </row>
-    <row r="707">
-      <c r="A707" s="1" t="n"/>
-      <c r="B707" s="1" t="n"/>
-      <c r="C707" s="1" t="n"/>
-      <c r="D707" s="1" t="n"/>
-    </row>
-    <row r="708">
-      <c r="A708" s="1" t="n"/>
-      <c r="B708" s="1" t="n"/>
-      <c r="C708" s="1" t="n"/>
-      <c r="D708" s="1" t="n"/>
-    </row>
-    <row r="709">
-      <c r="A709" s="1" t="n"/>
-      <c r="B709" s="1" t="n"/>
-      <c r="C709" s="1" t="n"/>
-      <c r="D709" s="1" t="n"/>
-    </row>
-    <row r="710">
-      <c r="A710" s="1" t="n"/>
-      <c r="B710" s="1" t="n"/>
-      <c r="C710" s="1" t="n"/>
-      <c r="D710" s="1" t="n"/>
-    </row>
-    <row r="711">
-      <c r="A711" s="1" t="n"/>
-      <c r="B711" s="1" t="n"/>
-      <c r="C711" s="1" t="n"/>
-      <c r="D711" s="1" t="n"/>
-    </row>
-    <row r="712">
-      <c r="A712" s="1" t="n"/>
-      <c r="B712" s="1" t="n"/>
-      <c r="C712" s="1" t="n"/>
-      <c r="D712" s="1" t="n"/>
-    </row>
-    <row r="713">
-      <c r="A713" s="1" t="n"/>
-      <c r="B713" s="1" t="n"/>
-      <c r="C713" s="1" t="n"/>
-      <c r="D713" s="1" t="n"/>
-    </row>
-    <row r="714">
-      <c r="A714" s="1" t="n"/>
-      <c r="B714" s="1" t="n"/>
-      <c r="C714" s="1" t="n"/>
-      <c r="D714" s="1" t="n"/>
-    </row>
-    <row r="715">
-      <c r="A715" s="1" t="n"/>
-      <c r="B715" s="1" t="n"/>
-      <c r="C715" s="1" t="n"/>
-      <c r="D715" s="1" t="n"/>
-    </row>
-    <row r="716">
-      <c r="A716" s="1" t="n"/>
-      <c r="B716" s="1" t="n"/>
-      <c r="C716" s="1" t="n"/>
-      <c r="D716" s="1" t="n"/>
-    </row>
-    <row r="717">
-      <c r="A717" s="1" t="n"/>
-      <c r="B717" s="1" t="n"/>
-      <c r="C717" s="1" t="n"/>
-      <c r="D717" s="1" t="n"/>
-    </row>
-    <row r="718">
-      <c r="A718" s="1" t="n"/>
-      <c r="B718" s="1" t="n"/>
-      <c r="C718" s="1" t="n"/>
-      <c r="D718" s="1" t="n"/>
-    </row>
-    <row r="719">
-      <c r="A719" s="1" t="n"/>
-      <c r="B719" s="1" t="n"/>
-      <c r="C719" s="1" t="n"/>
-      <c r="D719" s="1" t="n"/>
-    </row>
-    <row r="720">
-      <c r="A720" s="1" t="n"/>
-      <c r="B720" s="1" t="n"/>
-      <c r="C720" s="1" t="n"/>
-      <c r="D720" s="1" t="n"/>
-    </row>
-    <row r="721">
-      <c r="A721" s="1" t="n"/>
-      <c r="B721" s="1" t="n"/>
-      <c r="C721" s="1" t="n"/>
-      <c r="D721" s="1" t="n"/>
-    </row>
-    <row r="722">
-      <c r="A722" s="1" t="n"/>
-      <c r="B722" s="1" t="n"/>
-      <c r="C722" s="1" t="n"/>
-      <c r="D722" s="1" t="n"/>
-    </row>
-    <row r="723">
-      <c r="A723" s="1" t="n"/>
-      <c r="B723" s="1" t="n"/>
-      <c r="C723" s="1" t="n"/>
-      <c r="D723" s="1" t="n"/>
-    </row>
-    <row r="724">
-      <c r="A724" s="1" t="n"/>
-      <c r="B724" s="1" t="n"/>
-      <c r="C724" s="1" t="n"/>
-      <c r="D724" s="1" t="n"/>
-    </row>
-    <row r="725">
-      <c r="A725" s="1" t="n"/>
-      <c r="B725" s="1" t="n"/>
-      <c r="C725" s="1" t="n"/>
-      <c r="D725" s="1" t="n"/>
-    </row>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -7717,6 +7717,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -13151,6 +13158,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -20679,6 +20693,13 @@
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Bayesian optimization history of the 3D reaction-diffusion model (32 evaluations; global search -&gt; Phase 2 EI -&gt; dip verification -&gt; Phase 3 local refinement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
         </is>
       </c>
     </row>
@@ -27290,7 +27311,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -37544,7 +37571,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -18179,7 +18179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18192,10 +18192,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study (Supplementary Figure 5a). Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified.</t>
+          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study (Supplementary Figure 5a). Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -18238,6 +18239,21 @@
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Thin strut t=0.0825mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mid strut t=0.165mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Thick strut t=0.2475mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -18252,6 +18268,15 @@
       <c r="D7" s="1" t="n">
         <v>0.080549</v>
       </c>
+      <c r="F7" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.156707</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.11544</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -18266,6 +18291,15 @@
       <c r="D8" s="1" t="n">
         <v>0.115457</v>
       </c>
+      <c r="F8" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.226212</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.165469</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -18280,6 +18314,15 @@
       <c r="D9" s="1" t="n">
         <v>0.148604</v>
       </c>
+      <c r="F9" t="n">
+        <v>0.444558</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.288974</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.212974</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -18294,6 +18337,15 @@
       <c r="D10" s="1" t="n">
         <v>0.175336</v>
       </c>
+      <c r="F10" t="n">
+        <v>0.478412</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.358074</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.251286</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -18308,6 +18360,15 @@
       <c r="D11" s="1" t="n">
         <v>0.190526</v>
       </c>
+      <c r="F11" t="n">
+        <v>0.537705</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.394545</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.273055</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -18322,6 +18383,15 @@
       <c r="D12" s="1" t="n">
         <v>0.211982</v>
       </c>
+      <c r="F12" t="n">
+        <v>0.583607</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.455424</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.303805</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -18336,6 +18406,15 @@
       <c r="D13" s="1" t="n">
         <v>0.230155</v>
       </c>
+      <c r="F13" t="n">
+        <v>0.6235810000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.501674</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.32985</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -18350,6 +18429,15 @@
       <c r="D14" s="1" t="n">
         <v>0.262609</v>
       </c>
+      <c r="F14" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.591842</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.376362</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -18364,6 +18452,15 @@
       <c r="D15" s="1" t="n">
         <v>0.288579</v>
       </c>
+      <c r="F15" t="n">
+        <v>0.832283</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.679275</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.413582</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -18378,6 +18475,15 @@
       <c r="D16" s="1" t="n">
         <v>0.308554</v>
       </c>
+      <c r="F16" t="n">
+        <v>0.987999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.760812</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.442209</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -18392,6 +18498,15 @@
       <c r="D17" s="1" t="n">
         <v>0.34109</v>
       </c>
+      <c r="F17" t="n">
+        <v>1.117237</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.824048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.488839</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -18406,6 +18521,15 @@
       <c r="D18" s="1" t="n">
         <v>0.368947</v>
       </c>
+      <c r="F18" t="n">
+        <v>1.250565</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.905471</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.528762</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -18420,6 +18544,15 @@
       <c r="D19" s="1" t="n">
         <v>0.382127</v>
       </c>
+      <c r="F19" t="n">
+        <v>1.309973</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.951856</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.547651</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -18434,6 +18567,15 @@
       <c r="D20" s="1" t="n">
         <v>0.42003</v>
       </c>
+      <c r="F20" t="n">
+        <v>1.449346</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.040782</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.601973</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -18448,6 +18590,15 @@
       <c r="D21" s="1" t="n">
         <v>0.456405</v>
       </c>
+      <c r="F21" t="n">
+        <v>1.601649</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.131677</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.654104</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -18462,6 +18613,15 @@
       <c r="D22" s="1" t="n">
         <v>0.491695</v>
       </c>
+      <c r="F22" t="n">
+        <v>1.701928</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.175681</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.704681</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -18476,6 +18636,15 @@
       <c r="D23" s="1" t="n">
         <v>0.518161</v>
       </c>
+      <c r="F23" t="n">
+        <v>1.82217</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.245708</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.742611</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -18490,6 +18659,15 @@
       <c r="D24" s="1" t="n">
         <v>0.550017</v>
       </c>
+      <c r="F24" t="n">
+        <v>1.960227</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.305031</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.788266</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -18504,6 +18682,15 @@
       <c r="D25" s="1" t="n">
         <v>0.572665</v>
       </c>
+      <c r="F25" t="n">
+        <v>2.093268</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.37146</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.820724</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -18518,6 +18705,15 @@
       <c r="D26" s="1" t="n">
         <v>0.60609</v>
       </c>
+      <c r="F26" t="n">
+        <v>2.202719</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.437895</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.868628</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -18532,6 +18728,15 @@
       <c r="D27" s="1" t="n">
         <v>0.623081</v>
       </c>
+      <c r="F27" t="n">
+        <v>2.308573</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.503291</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.892979</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -18546,6 +18751,15 @@
       <c r="D28" s="1" t="n">
         <v>0.652014</v>
       </c>
+      <c r="F28" t="n">
+        <v>2.430306</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.566809</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9344440000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -18560,6 +18774,15 @@
       <c r="D29" s="1" t="n">
         <v>0.680528</v>
       </c>
+      <c r="F29" t="n">
+        <v>2.541878</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.625196</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.97531</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -18574,6 +18797,15 @@
       <c r="D30" s="1" t="n">
         <v>0.713676</v>
       </c>
+      <c r="F30" t="n">
+        <v>2.651243</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.688671</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.022816</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -18588,6 +18820,15 @@
       <c r="D31" s="1" t="n">
         <v>0.7526350000000001</v>
       </c>
+      <c r="F31" t="n">
+        <v>2.774753</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.728857</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.078651</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -18602,6 +18843,15 @@
       <c r="D32" s="1" t="n">
         <v>0.784246</v>
       </c>
+      <c r="F32" t="n">
+        <v>2.869714</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.77843</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.123955</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -18616,6 +18866,15 @@
       <c r="D33" s="1" t="n">
         <v>0.800565</v>
       </c>
+      <c r="F33" t="n">
+        <v>2.937661</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.837247</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.147343</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -18630,6 +18889,15 @@
       <c r="D34" s="1" t="n">
         <v>0.81098</v>
       </c>
+      <c r="F34" t="n">
+        <v>3.048874</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.885817</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.162269</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -18644,6 +18912,15 @@
       <c r="D35" s="1" t="n">
         <v>0.825368</v>
       </c>
+      <c r="F35" t="n">
+        <v>3.155144</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.933771</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.182889</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -18658,6 +18935,15 @@
       <c r="D36" s="1" t="n">
         <v>0.847023</v>
       </c>
+      <c r="F36" t="n">
+        <v>3.217415</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.988231</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.213925</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -18672,6 +18958,15 @@
       <c r="D37" s="1" t="n">
         <v>0.870138</v>
       </c>
+      <c r="F37" t="n">
+        <v>3.306171</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.036658</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.247052</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -18686,6 +18981,15 @@
       <c r="D38" s="1" t="n">
         <v>0.906923</v>
       </c>
+      <c r="F38" t="n">
+        <v>3.382229</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.112057</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.299771</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -18700,6 +19004,15 @@
       <c r="D39" s="1" t="n">
         <v>0.926669</v>
       </c>
+      <c r="F39" t="n">
+        <v>3.448756</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.164496</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.328071</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -18714,6 +19027,15 @@
       <c r="D40" s="1" t="n">
         <v>0.956117</v>
       </c>
+      <c r="F40" t="n">
+        <v>3.54217</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.21599</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.370274</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -18728,6 +19050,15 @@
       <c r="D41" s="1" t="n">
         <v>0.971294</v>
       </c>
+      <c r="F41" t="n">
+        <v>3.608311</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.234191</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.392026</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -18742,6 +19073,15 @@
       <c r="D42" s="1" t="n">
         <v>0.9946430000000001</v>
       </c>
+      <c r="F42" t="n">
+        <v>3.682807</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.283492</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.425489</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -18756,6 +19096,15 @@
       <c r="D43" s="1" t="n">
         <v>1.01903</v>
       </c>
+      <c r="F43" t="n">
+        <v>3.74052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.346136</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.460439</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -18770,6 +19119,15 @@
       <c r="D44" s="1" t="n">
         <v>1.03921</v>
       </c>
+      <c r="F44" t="n">
+        <v>3.790996</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.403792</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.48936</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -18784,6 +19142,15 @@
       <c r="D45" s="1" t="n">
         <v>1.07658</v>
       </c>
+      <c r="F45" t="n">
+        <v>3.921888</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.439435</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.542918</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -18798,6 +19165,15 @@
       <c r="D46" s="1" t="n">
         <v>1.10228</v>
       </c>
+      <c r="F46" t="n">
+        <v>4.027655</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.516482</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.57975</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -18812,6 +19188,15 @@
       <c r="D47" s="1" t="n">
         <v>1.11116</v>
       </c>
+      <c r="F47" t="n">
+        <v>4.096261</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.560093</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.592477</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -18826,6 +19211,15 @@
       <c r="D48" s="1" t="n">
         <v>1.12241</v>
       </c>
+      <c r="F48" t="n">
+        <v>4.203935</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.588241</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.6086</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -18840,6 +19234,15 @@
       <c r="D49" s="1" t="n">
         <v>1.14546</v>
       </c>
+      <c r="F49" t="n">
+        <v>4.269215</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.611358</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.641634</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -18854,6 +19257,15 @@
       <c r="D50" s="1" t="n">
         <v>1.16656</v>
       </c>
+      <c r="F50" t="n">
+        <v>4.360838</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.633901</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.671874</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -18868,6 +19280,15 @@
       <c r="D51" s="1" t="n">
         <v>1.17928</v>
       </c>
+      <c r="F51" t="n">
+        <v>4.449379</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.682213</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.690104</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -18882,6 +19303,15 @@
       <c r="D52" s="1" t="n">
         <v>1.18637</v>
       </c>
+      <c r="F52" t="n">
+        <v>4.529593</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.730769</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.700265</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -18896,6 +19326,15 @@
       <c r="D53" s="1" t="n">
         <v>1.1889</v>
       </c>
+      <c r="F53" t="n">
+        <v>4.592079</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.775842</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.703891</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -18910,6 +19349,15 @@
       <c r="D54" s="1" t="n">
         <v>1.20113</v>
       </c>
+      <c r="F54" t="n">
+        <v>4.662476</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.798328</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.721419</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -18924,6 +19372,15 @@
       <c r="D55" s="1" t="n">
         <v>1.21171</v>
       </c>
+      <c r="F55" t="n">
+        <v>4.724403</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.841581</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.736582</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -18938,6 +19395,15 @@
       <c r="D56" s="1" t="n">
         <v>1.24036</v>
       </c>
+      <c r="F56" t="n">
+        <v>4.809161</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.91152</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.777642</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -18952,6 +19418,15 @@
       <c r="D57" s="1" t="n">
         <v>1.25048</v>
       </c>
+      <c r="F57" t="n">
+        <v>4.892843</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.928245</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.792145</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -18966,6 +19441,15 @@
       <c r="D58" s="1" t="n">
         <v>1.26765</v>
       </c>
+      <c r="F58" t="n">
+        <v>4.98501</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.984525</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.816753</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -18980,6 +19464,15 @@
       <c r="D59" s="1" t="n">
         <v>1.26886</v>
       </c>
+      <c r="F59" t="n">
+        <v>5.055952</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.024152</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.818487</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -18994,6 +19487,15 @@
       <c r="D60" s="1" t="n">
         <v>1.28162</v>
       </c>
+      <c r="F60" t="n">
+        <v>5.120459</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.052687</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.836774</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -19008,6 +19510,15 @@
       <c r="D61" s="1" t="n">
         <v>1.29374</v>
       </c>
+      <c r="F61" t="n">
+        <v>5.187588</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.082969</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.854144</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -19022,6 +19533,15 @@
       <c r="D62" s="1" t="n">
         <v>1.31956</v>
       </c>
+      <c r="F62" t="n">
+        <v>5.271285</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3.116577</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.891149</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -19036,6 +19556,15 @@
       <c r="D63" s="1" t="n">
         <v>1.33983</v>
       </c>
+      <c r="F63" t="n">
+        <v>5.353061</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.143621</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.920199</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -19050,6 +19579,15 @@
       <c r="D64" s="1" t="n">
         <v>1.35912</v>
       </c>
+      <c r="F64" t="n">
+        <v>5.414874</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.187204</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.947845</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -19064,6 +19602,15 @@
       <c r="D65" s="1" t="n">
         <v>1.36612</v>
       </c>
+      <c r="F65" t="n">
+        <v>5.47726</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.226888</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.957877</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -19078,6 +19625,15 @@
       <c r="D66" s="1" t="n">
         <v>1.37803</v>
       </c>
+      <c r="F66" t="n">
+        <v>5.525443</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.268421</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.974946</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -19092,6 +19648,15 @@
       <c r="D67" s="1" t="n">
         <v>1.38899</v>
       </c>
+      <c r="F67" t="n">
+        <v>5.577739</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.313738</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.990653</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -19106,6 +19671,15 @@
       <c r="D68" s="1" t="n">
         <v>1.39966</v>
       </c>
+      <c r="F68" t="n">
+        <v>5.647047</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.329531</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.005945</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -19120,6 +19694,15 @@
       <c r="D69" s="1" t="n">
         <v>1.41277</v>
       </c>
+      <c r="F69" t="n">
+        <v>5.701235</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.350112</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.024734</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -19134,6 +19717,15 @@
       <c r="D70" s="1" t="n">
         <v>1.44189</v>
       </c>
+      <c r="F70" t="n">
+        <v>5.747942</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.38038</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.066468</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -19148,6 +19740,15 @@
       <c r="D71" s="1" t="n">
         <v>1.47372</v>
       </c>
+      <c r="F71" t="n">
+        <v>5.802244</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3.389294</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.112085</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -19162,6 +19763,15 @@
       <c r="D72" s="1" t="n">
         <v>1.48617</v>
       </c>
+      <c r="F72" t="n">
+        <v>5.875966</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.426686</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.129928</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -19176,6 +19786,15 @@
       <c r="D73" s="1" t="n">
         <v>1.50328</v>
       </c>
+      <c r="F73" t="n">
+        <v>5.95181</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3.44685</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.15445</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -19190,6 +19809,15 @@
       <c r="D74" s="1" t="n">
         <v>1.53038</v>
       </c>
+      <c r="F74" t="n">
+        <v>6.016861</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3.473765</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.193289</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -19204,6 +19832,15 @@
       <c r="D75" s="1" t="n">
         <v>1.54369</v>
       </c>
+      <c r="F75" t="n">
+        <v>6.057878</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.487036</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.212364</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -19218,6 +19855,15 @@
       <c r="D76" s="1" t="n">
         <v>1.55269</v>
       </c>
+      <c r="F76" t="n">
+        <v>6.107509</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.519297</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.225263</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -19232,6 +19878,15 @@
       <c r="D77" s="1" t="n">
         <v>1.56403</v>
       </c>
+      <c r="F77" t="n">
+        <v>6.164721</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.54154</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.241515</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -19246,6 +19901,15 @@
       <c r="D78" s="1" t="n">
         <v>1.57682</v>
       </c>
+      <c r="F78" t="n">
+        <v>6.209307</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3.566978</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.259845</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -19260,6 +19924,15 @@
       <c r="D79" s="1" t="n">
         <v>1.58776</v>
       </c>
+      <c r="F79" t="n">
+        <v>6.266433</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3.604126</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.275524</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -19274,6 +19947,15 @@
       <c r="D80" s="1" t="n">
         <v>1.60776</v>
       </c>
+      <c r="F80" t="n">
+        <v>6.315762</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3.635942</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.304187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -19288,6 +19970,15 @@
       <c r="D81" s="1" t="n">
         <v>1.62079</v>
       </c>
+      <c r="F81" t="n">
+        <v>6.392823</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.651048</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.322861</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -19302,6 +19993,15 @@
       <c r="D82" s="1" t="n">
         <v>1.63519</v>
       </c>
+      <c r="F82" t="n">
+        <v>6.453876</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.668862</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.343499</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -19316,6 +20016,15 @@
       <c r="D83" s="1" t="n">
         <v>1.64838</v>
       </c>
+      <c r="F83" t="n">
+        <v>6.505556</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3.710797</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.362402</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -19330,6 +20039,15 @@
       <c r="D84" s="1" t="n">
         <v>1.65518</v>
       </c>
+      <c r="F84" t="n">
+        <v>6.555846</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3.723537</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.372148</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -19344,6 +20062,15 @@
       <c r="D85" s="1" t="n">
         <v>1.66138</v>
       </c>
+      <c r="F85" t="n">
+        <v>6.618346</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.739632</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.381033</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -19358,6 +20085,15 @@
       <c r="D86" s="1" t="n">
         <v>1.68286</v>
       </c>
+      <c r="F86" t="n">
+        <v>6.661155</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3.763867</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.411818</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -19372,6 +20108,15 @@
       <c r="D87" s="1" t="n">
         <v>1.69482</v>
       </c>
+      <c r="F87" t="n">
+        <v>6.687081</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3.782397</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.428958</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -19386,6 +20131,15 @@
       <c r="D88" s="1" t="n">
         <v>1.7099</v>
       </c>
+      <c r="F88" t="n">
+        <v>6.736368</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3.807206</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.450571</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -19400,6 +20154,15 @@
       <c r="D89" s="1" t="n">
         <v>1.71279</v>
       </c>
+      <c r="F89" t="n">
+        <v>6.779821</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3.826123</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.454712</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -19414,6 +20177,15 @@
       <c r="D90" s="1" t="n">
         <v>1.72079</v>
       </c>
+      <c r="F90" t="n">
+        <v>6.796159</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3.841372</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.466178</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -19428,6 +20200,15 @@
       <c r="D91" s="1" t="n">
         <v>1.73029</v>
       </c>
+      <c r="F91" t="n">
+        <v>6.838509</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.865292</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.479793</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -19442,6 +20223,15 @@
       <c r="D92" s="1" t="n">
         <v>1.73832</v>
       </c>
+      <c r="F92" t="n">
+        <v>6.869953</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3.903013</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.491301</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -19456,6 +20246,15 @@
       <c r="D93" s="1" t="n">
         <v>1.75096</v>
       </c>
+      <c r="F93" t="n">
+        <v>6.91623</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3.919924</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.509416</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -19470,6 +20269,15 @@
       <c r="D94" s="1" t="n">
         <v>1.76108</v>
       </c>
+      <c r="F94" t="n">
+        <v>6.953464</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.945391</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.52392</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -19484,6 +20292,15 @@
       <c r="D95" s="1" t="n">
         <v>1.77134</v>
       </c>
+      <c r="F95" t="n">
+        <v>7.017627</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.002016</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.538624</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -19498,6 +20315,15 @@
       <c r="D96" s="1" t="n">
         <v>1.78018</v>
       </c>
+      <c r="F96" t="n">
+        <v>7.082062</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4.029318</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.551294</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -19512,6 +20338,15 @@
       <c r="D97" s="1" t="n">
         <v>1.78755</v>
       </c>
+      <c r="F97" t="n">
+        <v>7.125444</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4.054642</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.561856</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -19526,6 +20361,15 @@
       <c r="D98" s="1" t="n">
         <v>1.79737</v>
       </c>
+      <c r="F98" t="n">
+        <v>7.163193</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4.098224</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.57593</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -19540,6 +20384,15 @@
       <c r="D99" s="1" t="n">
         <v>1.80363</v>
       </c>
+      <c r="F99" t="n">
+        <v>7.216736</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4.114763</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.584901</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -19554,6 +20407,15 @@
       <c r="D100" s="1" t="n">
         <v>1.80754</v>
       </c>
+      <c r="F100" t="n">
+        <v>7.281229</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4.134928</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.590505</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -19568,6 +20430,15 @@
       <c r="D101" s="1" t="n">
         <v>1.81685</v>
       </c>
+      <c r="F101" t="n">
+        <v>7.325098</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4.14688</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.603848</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -19582,6 +20453,15 @@
       <c r="D102" s="1" t="n">
         <v>1.82533</v>
       </c>
+      <c r="F102" t="n">
+        <v>7.340934</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4.170614</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.616001</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -19596,6 +20476,15 @@
       <c r="D103" s="1" t="n">
         <v>1.83871</v>
       </c>
+      <c r="F103" t="n">
+        <v>7.376706</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.180818</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.635177</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -19610,6 +20499,15 @@
       <c r="D104" s="1" t="n">
         <v>1.84555</v>
       </c>
+      <c r="F104" t="n">
+        <v>7.413567</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4.195723</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.64498</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -19624,6 +20522,15 @@
       <c r="D105" s="1" t="n">
         <v>1.85358</v>
       </c>
+      <c r="F105" t="n">
+        <v>7.459801</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4.229875</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2.656488</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -19638,6 +20545,15 @@
       <c r="D106" s="1" t="n">
         <v>1.86463</v>
       </c>
+      <c r="F106" t="n">
+        <v>7.493925</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4.253995</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2.672324</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -19652,6 +20568,15 @@
       <c r="D107" s="1" t="n">
         <v>1.87113</v>
       </c>
+      <c r="F107" t="n">
+        <v>7.52544</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4.263167</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.68164</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -19666,6 +20591,15 @@
       <c r="D108" s="1" t="n">
         <v>1.88195</v>
       </c>
+      <c r="F108" t="n">
+        <v>7.554677</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4.273343</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.697147</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -19680,6 +20614,15 @@
       <c r="D109" s="1" t="n">
         <v>1.89103</v>
       </c>
+      <c r="F109" t="n">
+        <v>7.603404</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4.289122</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.71016</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -19694,6 +20637,15 @@
       <c r="D110" s="1" t="n">
         <v>1.90702</v>
       </c>
+      <c r="F110" t="n">
+        <v>7.643361</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4.306779</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.733076</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -19708,6 +20660,15 @@
       <c r="D111" s="1" t="n">
         <v>1.91116</v>
       </c>
+      <c r="F111" t="n">
+        <v>7.692633</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4.315808</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.73901</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -19722,6 +20683,15 @@
       <c r="D112" s="1" t="n">
         <v>1.92445</v>
       </c>
+      <c r="F112" t="n">
+        <v>7.765768</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4.351393</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2.758056</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -19736,6 +20706,15 @@
       <c r="D113" s="1" t="n">
         <v>1.92549</v>
       </c>
+      <c r="F113" t="n">
+        <v>7.817419</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.364879</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2.759547</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -19750,6 +20729,15 @@
       <c r="D114" s="1" t="n">
         <v>1.92831</v>
       </c>
+      <c r="F114" t="n">
+        <v>7.883459</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4.379684</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.763588</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -19764,6 +20752,15 @@
       <c r="D115" s="1" t="n">
         <v>1.94251</v>
       </c>
+      <c r="F115" t="n">
+        <v>7.919618</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4.384456</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.783939</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -19778,6 +20775,15 @@
       <c r="D116" s="1" t="n">
         <v>1.94991</v>
       </c>
+      <c r="F116" t="n">
+        <v>7.958342</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4.395477</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2.794545</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -19792,6 +20798,15 @@
       <c r="D117" s="1" t="n">
         <v>1.97145</v>
       </c>
+      <c r="F117" t="n">
+        <v>8.035662</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4.422077</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.825415</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -19806,6 +20821,15 @@
       <c r="D118" s="1" t="n">
         <v>1.98139</v>
       </c>
+      <c r="F118" t="n">
+        <v>8.108093999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4.454452</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.839661</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -19820,6 +20844,15 @@
       <c r="D119" s="1" t="n">
         <v>1.99337</v>
       </c>
+      <c r="F119" t="n">
+        <v>8.137473999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4.489708</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2.85683</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -19834,6 +20867,15 @@
       <c r="D120" s="1" t="n">
         <v>1.99918</v>
       </c>
+      <c r="F120" t="n">
+        <v>8.164747</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4.508081</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.865157</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -19848,6 +20890,15 @@
       <c r="D121" s="1" t="n">
         <v>2.0158</v>
       </c>
+      <c r="F121" t="n">
+        <v>8.218949</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4.518916</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2.888976</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -19862,6 +20913,15 @@
       <c r="D122" s="1" t="n">
         <v>2.02218</v>
       </c>
+      <c r="F122" t="n">
+        <v>8.251353</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4.553111</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.89812</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -19876,6 +20936,15 @@
       <c r="D123" s="1" t="n">
         <v>2.02788</v>
       </c>
+      <c r="F123" t="n">
+        <v>8.303062000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4.601022</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.906289</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -19890,6 +20959,15 @@
       <c r="D124" s="1" t="n">
         <v>2.0376</v>
       </c>
+      <c r="F124" t="n">
+        <v>8.351861</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4.623336</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.920219</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -19904,6 +20982,15 @@
       <c r="D125" s="1" t="n">
         <v>2.04163</v>
       </c>
+      <c r="F125" t="n">
+        <v>8.394899000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.673669</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.925995</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -19918,6 +21005,15 @@
       <c r="D126" s="1" t="n">
         <v>2.05258</v>
       </c>
+      <c r="F126" t="n">
+        <v>8.440001000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4.696571</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.941688</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -19932,6 +21028,15 @@
       <c r="D127" s="1" t="n">
         <v>2.0558</v>
       </c>
+      <c r="F127" t="n">
+        <v>8.476475000000001</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.71536</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.946303</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -19946,6 +21051,15 @@
       <c r="D128" s="1" t="n">
         <v>2.06382</v>
       </c>
+      <c r="F128" t="n">
+        <v>8.526593</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.737631</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2.957797</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -19960,6 +21074,15 @@
       <c r="D129" s="1" t="n">
         <v>2.07587</v>
       </c>
+      <c r="F129" t="n">
+        <v>8.571365</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4.765736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.975066</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -19974,6 +21097,15 @@
       <c r="D130" s="1" t="n">
         <v>2.07942</v>
       </c>
+      <c r="F130" t="n">
+        <v>8.614331</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4.783091</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.980154</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -19988,6 +21120,15 @@
       <c r="D131" s="1" t="n">
         <v>2.0857</v>
       </c>
+      <c r="F131" t="n">
+        <v>8.653543000000001</v>
+      </c>
+      <c r="G131" t="n">
+        <v>4.792923</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.989154</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -20002,6 +21143,15 @@
       <c r="D132" s="1" t="n">
         <v>2.09229</v>
       </c>
+      <c r="F132" t="n">
+        <v>8.707114000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4.800433</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.998599</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -20016,6 +21166,15 @@
       <c r="D133" s="1" t="n">
         <v>2.09723</v>
       </c>
+      <c r="F133" t="n">
+        <v>8.769256</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4.8125</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3.005679</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -20030,6 +21189,15 @@
       <c r="D134" s="1" t="n">
         <v>2.10204</v>
       </c>
+      <c r="F134" t="n">
+        <v>8.818299</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.830071</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3.012572</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -20044,6 +21212,15 @@
       <c r="D135" s="1" t="n">
         <v>2.10633</v>
       </c>
+      <c r="F135" t="n">
+        <v>8.862928</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4.854907</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3.018721</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -20058,6 +21235,15 @@
       <c r="D136" s="1" t="n">
         <v>2.12309</v>
       </c>
+      <c r="F136" t="n">
+        <v>8.893181999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4.878053</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3.04274</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -20072,6 +21258,15 @@
       <c r="D137" s="1" t="n">
         <v>2.13156</v>
       </c>
+      <c r="F137" t="n">
+        <v>8.93665</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4.91007</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3.054879</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -20086,6 +21281,15 @@
       <c r="D138" s="1" t="n">
         <v>2.13618</v>
       </c>
+      <c r="F138" t="n">
+        <v>8.987169</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4.928515</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3.061501</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -20100,6 +21304,15 @@
       <c r="D139" s="1" t="n">
         <v>2.14776</v>
       </c>
+      <c r="F139" t="n">
+        <v>9.005743000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4.961778</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3.078097</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -20114,6 +21327,15 @@
       <c r="D140" s="1" t="n">
         <v>2.15405</v>
       </c>
+      <c r="F140" t="n">
+        <v>9.068946</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4.987547</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3.087111</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -20128,6 +21350,15 @@
       <c r="D141" s="1" t="n">
         <v>2.16547</v>
       </c>
+      <c r="F141" t="n">
+        <v>9.090759</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5.00731</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3.103478</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -20142,6 +21373,15 @@
       <c r="D142" s="1" t="n">
         <v>2.18451</v>
       </c>
+      <c r="F142" t="n">
+        <v>9.128365000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5.022831</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3.130766</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -20156,6 +21396,15 @@
       <c r="D143" s="1" t="n">
         <v>2.19587</v>
       </c>
+      <c r="F143" t="n">
+        <v>9.146953</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5.053788</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3.147046</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -20170,6 +21419,15 @@
       <c r="D144" s="1" t="n">
         <v>2.19672</v>
       </c>
+      <c r="F144" t="n">
+        <v>9.196540000000001</v>
+      </c>
+      <c r="G144" t="n">
+        <v>5.071373</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3.148265</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -20184,6 +21442,15 @@
       <c r="D145" s="1" t="n">
         <v>2.19802</v>
       </c>
+      <c r="F145" t="n">
+        <v>9.250026</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5.079069</v>
+      </c>
+      <c r="H145" t="n">
+        <v>3.150128</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -20198,6 +21465,15 @@
       <c r="D146" s="1" t="n">
         <v>2.20926</v>
       </c>
+      <c r="F146" t="n">
+        <v>9.313172</v>
+      </c>
+      <c r="G146" t="n">
+        <v>5.10564</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3.166236</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -20212,6 +21488,15 @@
       <c r="D147" s="1" t="n">
         <v>2.21202</v>
       </c>
+      <c r="F147" t="n">
+        <v>9.332362</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5.111143</v>
+      </c>
+      <c r="H147" t="n">
+        <v>3.170192</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -20226,6 +21511,15 @@
       <c r="D148" s="1" t="n">
         <v>2.21616</v>
       </c>
+      <c r="F148" t="n">
+        <v>9.353816</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5.148893</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3.176125</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -20240,6 +21534,15 @@
       <c r="D149" s="1" t="n">
         <v>2.21984</v>
       </c>
+      <c r="F149" t="n">
+        <v>9.390276</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5.164844</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3.181399</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -20254,6 +21557,15 @@
       <c r="D150" s="1" t="n">
         <v>2.22157</v>
       </c>
+      <c r="F150" t="n">
+        <v>9.439734</v>
+      </c>
+      <c r="G150" t="n">
+        <v>5.191974</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3.183879</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -20268,6 +21580,15 @@
       <c r="D151" s="1" t="n">
         <v>2.2274</v>
       </c>
+      <c r="F151" t="n">
+        <v>9.498752</v>
+      </c>
+      <c r="G151" t="n">
+        <v>5.20589</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3.192234</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -20282,6 +21603,15 @@
       <c r="D152" s="1" t="n">
         <v>2.23246</v>
       </c>
+      <c r="F152" t="n">
+        <v>9.541646999999999</v>
+      </c>
+      <c r="G152" t="n">
+        <v>5.224936</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3.199486</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -20296,6 +21626,15 @@
       <c r="D153" s="1" t="n">
         <v>2.23821</v>
       </c>
+      <c r="F153" t="n">
+        <v>9.565939</v>
+      </c>
+      <c r="G153" t="n">
+        <v>5.240257</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3.207727</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -20310,6 +21649,15 @@
       <c r="D154" s="1" t="n">
         <v>2.24165</v>
       </c>
+      <c r="F154" t="n">
+        <v>9.640306000000001</v>
+      </c>
+      <c r="G154" t="n">
+        <v>5.261224</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3.212657</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -20324,6 +21672,15 @@
       <c r="D155" s="1" t="n">
         <v>2.26331</v>
       </c>
+      <c r="F155" t="n">
+        <v>9.683529999999999</v>
+      </c>
+      <c r="G155" t="n">
+        <v>5.284398</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3.243699</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -20338,6 +21695,15 @@
       <c r="D156" s="1" t="n">
         <v>2.26769</v>
       </c>
+      <c r="F156" t="n">
+        <v>9.737503</v>
+      </c>
+      <c r="G156" t="n">
+        <v>5.29466</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3.249976</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -20352,6 +21718,15 @@
       <c r="D157" s="1" t="n">
         <v>2.26999</v>
       </c>
+      <c r="F157" t="n">
+        <v>9.768933000000001</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5.306068</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3.253273</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -20366,6 +21741,15 @@
       <c r="D158" s="1" t="n">
         <v>2.27729</v>
       </c>
+      <c r="F158" t="n">
+        <v>9.806037</v>
+      </c>
+      <c r="G158" t="n">
+        <v>5.321116</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.263735</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -20380,6 +21764,15 @@
       <c r="D159" s="1" t="n">
         <v>2.28083</v>
       </c>
+      <c r="F159" t="n">
+        <v>9.829312</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5.33893</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3.268808</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -20394,6 +21787,15 @@
       <c r="D160" s="1" t="n">
         <v>2.28603</v>
       </c>
+      <c r="F160" t="n">
+        <v>9.887413</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5.356816</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.276261</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -20408,6 +21810,15 @@
       <c r="D161" s="1" t="n">
         <v>2.29873</v>
       </c>
+      <c r="F161" t="n">
+        <v>9.911818999999999</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5.386684</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3.294462</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -20422,6 +21833,15 @@
       <c r="D162" s="1" t="n">
         <v>2.30178</v>
       </c>
+      <c r="F162" t="n">
+        <v>9.942002</v>
+      </c>
+      <c r="G162" t="n">
+        <v>5.386684</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.298833</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -20436,6 +21856,15 @@
       <c r="D163" s="1" t="n">
         <v>2.3095</v>
       </c>
+      <c r="F163" t="n">
+        <v>9.971582</v>
+      </c>
+      <c r="G163" t="n">
+        <v>5.412667</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3.309897</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -20450,6 +21879,15 @@
       <c r="D164" s="1" t="n">
         <v>2.3119</v>
       </c>
+      <c r="F164" t="n">
+        <v>10.016512</v>
+      </c>
+      <c r="G164" t="n">
+        <v>5.433448</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.313337</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -20464,6 +21902,15 @@
       <c r="D165" s="1" t="n">
         <v>2.31952</v>
       </c>
+      <c r="F165" t="n">
+        <v>10.055064</v>
+      </c>
+      <c r="G165" t="n">
+        <v>5.447321</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3.324257</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -20478,6 +21925,15 @@
       <c r="D166" s="1" t="n">
         <v>2.32311</v>
       </c>
+      <c r="F166" t="n">
+        <v>10.084874</v>
+      </c>
+      <c r="G166" t="n">
+        <v>5.466697</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3.329402</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -20492,6 +21948,15 @@
       <c r="D167" s="1" t="n">
         <v>2.32311</v>
       </c>
+      <c r="F167" t="n">
+        <v>10.129288</v>
+      </c>
+      <c r="G167" t="n">
+        <v>5.469392</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3.329402</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -20506,6 +21971,15 @@
       <c r="D168" s="1" t="n">
         <v>2.33373</v>
       </c>
+      <c r="F168" t="n">
+        <v>10.162967</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5.480241</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3.344623</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -20520,6 +21994,15 @@
       <c r="D169" s="1" t="n">
         <v>2.33651</v>
       </c>
+      <c r="F169" t="n">
+        <v>10.185525</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5.488868</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3.348607</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -20534,6 +22017,15 @@
       <c r="D170" s="1" t="n">
         <v>2.35189</v>
       </c>
+      <c r="F170" t="n">
+        <v>10.230512</v>
+      </c>
+      <c r="G170" t="n">
+        <v>5.495475</v>
+      </c>
+      <c r="H170" t="n">
+        <v>3.370649</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -20548,6 +22040,15 @@
       <c r="D171" s="1" t="n">
         <v>2.36081</v>
       </c>
+      <c r="F171" t="n">
+        <v>10.262429</v>
+      </c>
+      <c r="G171" t="n">
+        <v>5.521401</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3.383433</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -20562,6 +22063,15 @@
       <c r="D172" s="1" t="n">
         <v>2.3658</v>
       </c>
+      <c r="F172" t="n">
+        <v>10.316531</v>
+      </c>
+      <c r="G172" t="n">
+        <v>5.533182</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3.390584</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -20576,6 +22086,15 @@
       <c r="D173" s="1" t="n">
         <v>2.36887</v>
       </c>
+      <c r="F173" t="n">
+        <v>10.349723</v>
+      </c>
+      <c r="G173" t="n">
+        <v>5.550767</v>
+      </c>
+      <c r="H173" t="n">
+        <v>3.394984</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -20590,7 +22109,17 @@
       <c r="D174" s="1" t="n">
         <v>2.38034</v>
       </c>
-    </row>
+      <c r="F174" t="n">
+        <v>10.377584</v>
+      </c>
+      <c r="G174" t="n">
+        <v>5.5656</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3.411422</v>
+      </c>
+    </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -20619,6 +22148,11 @@
           <t>Final (672h) mass loss (%)</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Final (672h) mass loss, scaled x1.4332 (%)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -20635,6 +22169,9 @@
       <c r="D178" s="1" t="n">
         <v>7.24102</v>
       </c>
+      <c r="E178" t="n">
+        <v>10.37758</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -20651,6 +22188,9 @@
       <c r="D179" s="1" t="n">
         <v>3.88343</v>
       </c>
+      <c r="E179" t="n">
+        <v>5.5656</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -20666,6 +22206,9 @@
       </c>
       <c r="D180" s="1" t="n">
         <v>2.38034</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3.41142</v>
       </c>
     </row>
   </sheetData>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -18196,7 +18196,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -18225,6 +18224,21 @@
           <t>Thick strut t=0.2475mm (%)</t>
         </is>
       </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Thin strut t=0.0825mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Mid strut t=0.165mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Thick strut t=0.2475mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -18239,20 +18253,14 @@
       <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Thin strut t=0.0825mm, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Mid strut t=0.165mm, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Thick strut t=0.2475mm, scaled x1.4332 (%)</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22119,7 +22127,6 @@
         <v>3.411422</v>
       </c>
     </row>
-    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -18,12 +18,14 @@
     <sheet name="Figure 8b" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Figure 8c" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Figure 8d" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Supplementary Figure 1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Supplementary Figure 3" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Supplementary Figure 4" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Supplementary Figure 5" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Supplementary Figure 7" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Supplementary Figure 9" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Extra - O2 surface config" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Extra - O2 supply sweep" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Supplementary Figure 1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Supplementary Figure 3" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Supplementary Figure 4" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Supplementary Figure 5" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Supplementary Figure 9" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7152,6 +7154,396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Figure 8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mean local penetration depth (um, error bars = +/-1 SD) for the curved-wire (30, 90, 150 deg arcs) and two-wire spacing (straight, close gap CC = 0.30 mm, far gap CC = 1.60 mm) configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Mean depth (um)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SD (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arc 30°</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2.4434</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arc 90°</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.7046</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2231</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arc 150°</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5793</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.9315</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Straight wire</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.4384</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6573</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Close gap (CC=0.30 mm)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0518</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0146</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Far gap (CC=1.60 mm)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2.277</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6948</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Figure 8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Directional recession ratios: outer/inner surface for the arcs, outward-facing/gap-facing surface for the straight, close-gap and far-gap wires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ratio type</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ratio (x)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Numerator depth (um)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Denominator depth (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arc 30°</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>outer/inner</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.5847</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.1699</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.3693</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arc 90°</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>outer/inner</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.5967</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.6195</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.0088</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arc curvature</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arc 150°</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>outer/inner</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.1767</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.7236</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2826</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Straight wire</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>outward/facing</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.7289</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.3613</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Close gap (CC=0.30 mm)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>outward/facing</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.4955</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.4047</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5349</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Two-wire spacing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Far gap (CC=1.60 mm)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>outward/facing</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.4522</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.1674</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8839</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -7694,7 +8086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10629,7 +11021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10819,7 +11211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12112,7 +12504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12920,7 +13312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13135,7 +13527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18166,4056 +18558,6 @@
       </c>
       <c r="E227" s="1" t="n">
         <v>0.330478</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H180"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Supplementary Figure 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study (Supplementary Figure 5a). Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>(a) Mass loss vs. time, raw simulation output</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Time (hours)</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Thin strut t=0.0825mm (%)</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Mid strut (baseline) t=0.165mm (%)</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Thick strut t=0.2475mm (%)</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Thin strut t=0.0825mm, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>Mid strut t=0.165mm, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>Thick strut t=0.2475mm, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>0.189357</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.109343</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.080549</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.27138</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.156707</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.11544</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>0.253362</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0.157841</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0.115457</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.36311</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.226212</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.165469</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.310193</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0.201633</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0.148604</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.444558</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.288974</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.212974</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.333815</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>0.249848</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0.175336</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.478412</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.358074</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.251286</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.375187</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>0.275296</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0.190526</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.537705</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.394545</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.273055</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>0.407215</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>0.317775</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>0.211982</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.583607</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.455424</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.303805</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>0.435107</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0.350046</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0.230155</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6235810000000001</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.501674</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.32985</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>0.518921</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>0.412961</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0.262609</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.7437</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.591842</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.376362</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>0.58073</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0.473968</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0.288579</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.832283</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.679275</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.413582</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>0.6893820000000001</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>0.530861</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0.308554</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.987999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.760812</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.442209</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>0.779559</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>0.5749840000000001</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0.34109</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.117237</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.824048</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.488839</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>0.8725889999999999</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0.631798</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0.368947</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.250565</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.905471</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.528762</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>0.914041</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>0.6641629999999999</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>0.382127</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.309973</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.951856</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.547651</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>1.01129</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>0.726212</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>0.42003</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.449346</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.040782</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.601973</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>1.11756</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0.7896339999999999</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0.456405</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.601649</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.131677</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.654104</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>1.18753</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>0.820338</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>0.491695</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.701928</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.175681</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.704681</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>1.27143</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>0.8692</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>0.518161</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.82217</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.245708</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.742611</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>1.36776</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>0.910593</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>0.550017</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.960227</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.305031</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.788266</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>1.46059</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>0.956944</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>0.572665</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.093268</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.37146</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.820724</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>1.53696</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>0.60609</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2.202719</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.437895</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.868628</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>1.61082</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>1.04893</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>0.623081</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.308573</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.503291</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.892979</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>1.69576</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>1.09325</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>0.652014</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.430306</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.566809</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.9344440000000001</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>1.77361</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>1.13399</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>0.680528</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.541878</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.625196</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.97531</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>1.84992</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>1.17828</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>0.713676</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.651243</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.688671</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.022816</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>1.9361</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>1.20632</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>0.7526350000000001</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.774753</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.728857</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.078651</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>2.00236</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>1.24091</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0.784246</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2.869714</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.77843</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.123955</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>2.04977</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>1.28195</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>0.800565</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2.937661</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.837247</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.147343</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>2.12737</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>1.31584</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>0.81098</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.048874</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.885817</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.162269</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>2.20152</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>1.3493</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>0.825368</v>
-      </c>
-      <c r="F35" t="n">
-        <v>3.155144</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.933771</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.182889</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>2.24497</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>0.847023</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3.217415</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.988231</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.213925</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>2.3069</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>1.42109</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>0.870138</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3.306171</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.036658</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.247052</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>2.35997</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>1.4737</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>0.906923</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3.382229</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.112057</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.299771</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>2.40639</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1.51029</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>0.926669</v>
-      </c>
-      <c r="F39" t="n">
-        <v>3.448756</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2.164496</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.328071</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>2.47157</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>1.54622</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>0.956117</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3.54217</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.21599</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.370274</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>2.51772</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>1.55892</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>0.971294</v>
-      </c>
-      <c r="F41" t="n">
-        <v>3.608311</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.234191</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.392026</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>2.5697</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>1.59332</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>0.9946430000000001</v>
-      </c>
-      <c r="F42" t="n">
-        <v>3.682807</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.283492</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1.425489</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>2.60997</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>1.63703</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>1.01903</v>
-      </c>
-      <c r="F43" t="n">
-        <v>3.74052</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.346136</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.460439</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>2.64519</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>1.67726</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>1.03921</v>
-      </c>
-      <c r="F44" t="n">
-        <v>3.790996</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2.403792</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.48936</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>2.73652</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>1.70213</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>1.07658</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3.921888</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.439435</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.542918</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>2.81032</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>1.75589</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>1.10228</v>
-      </c>
-      <c r="F46" t="n">
-        <v>4.027655</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2.516482</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.57975</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>164</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>2.85819</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>1.78632</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>1.11116</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4.096261</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2.560093</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1.592477</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>168</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>2.93332</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>1.80596</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>1.12241</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4.203935</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.588241</v>
-      </c>
-      <c r="H48" t="n">
-        <v>1.6086</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>2.97887</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>1.82209</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>1.14546</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4.269215</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.611358</v>
-      </c>
-      <c r="H49" t="n">
-        <v>1.641634</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>176</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>3.0428</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>1.83782</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>1.16656</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4.360838</v>
-      </c>
-      <c r="G50" t="n">
-        <v>2.633901</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1.671874</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>3.10458</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>1.87153</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>1.17928</v>
-      </c>
-      <c r="F51" t="n">
-        <v>4.449379</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.682213</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1.690104</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>184</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>3.16055</v>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>1.90541</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>1.18637</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4.529593</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.730769</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.700265</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>188</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>3.20415</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>1.93686</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>1.1889</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4.592079</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.775842</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1.703891</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>3.25327</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>1.95255</v>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>1.20113</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4.662476</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2.798328</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.721419</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>3.29648</v>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>1.98273</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>1.21171</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4.724403</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2.841581</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.736582</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>3.35562</v>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>2.03153</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>1.24036</v>
-      </c>
-      <c r="F56" t="n">
-        <v>4.809161</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2.91152</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.777642</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>204</v>
-      </c>
-      <c r="B57" s="1" t="n">
-        <v>3.41401</v>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>2.0432</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>1.25048</v>
-      </c>
-      <c r="F57" t="n">
-        <v>4.892843</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2.928245</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.792145</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>208</v>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>3.47832</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>2.08247</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>1.26765</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.98501</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2.984525</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1.816753</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="B59" s="1" t="n">
-        <v>3.52782</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>2.11012</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>1.26886</v>
-      </c>
-      <c r="F59" t="n">
-        <v>5.055952</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3.024152</v>
-      </c>
-      <c r="H59" t="n">
-        <v>1.818487</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>216</v>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>3.57283</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>2.13003</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>1.28162</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5.120459</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.052687</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1.836774</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>3.61967</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>2.15116</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>1.29374</v>
-      </c>
-      <c r="F61" t="n">
-        <v>5.187588</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3.082969</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1.854144</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>224</v>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>3.67807</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>2.17461</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>1.31956</v>
-      </c>
-      <c r="F62" t="n">
-        <v>5.271285</v>
-      </c>
-      <c r="G62" t="n">
-        <v>3.116577</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.891149</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>3.73513</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>2.19348</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>1.33983</v>
-      </c>
-      <c r="F63" t="n">
-        <v>5.353061</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3.143621</v>
-      </c>
-      <c r="H63" t="n">
-        <v>1.920199</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>3.77826</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>2.22389</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>1.35912</v>
-      </c>
-      <c r="F64" t="n">
-        <v>5.414874</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3.187204</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1.947845</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>3.82179</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>2.25158</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>1.36612</v>
-      </c>
-      <c r="F65" t="n">
-        <v>5.47726</v>
-      </c>
-      <c r="G65" t="n">
-        <v>3.226888</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1.957877</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="B66" s="1" t="n">
-        <v>3.85541</v>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>2.28056</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>1.37803</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5.525443</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3.268421</v>
-      </c>
-      <c r="H66" t="n">
-        <v>1.974946</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="B67" s="1" t="n">
-        <v>3.8919</v>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>2.31218</v>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>1.38899</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5.577739</v>
-      </c>
-      <c r="G67" t="n">
-        <v>3.313738</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1.990653</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="B68" s="1" t="n">
-        <v>3.94026</v>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>2.3232</v>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>1.39966</v>
-      </c>
-      <c r="F68" t="n">
-        <v>5.647047</v>
-      </c>
-      <c r="G68" t="n">
-        <v>3.329531</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2.005945</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>3.97807</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>2.33756</v>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>1.41277</v>
-      </c>
-      <c r="F69" t="n">
-        <v>5.701235</v>
-      </c>
-      <c r="G69" t="n">
-        <v>3.350112</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2.024734</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="B70" s="1" t="n">
-        <v>4.01066</v>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>2.35868</v>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>1.44189</v>
-      </c>
-      <c r="F70" t="n">
-        <v>5.747942</v>
-      </c>
-      <c r="G70" t="n">
-        <v>3.38038</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2.066468</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>260</v>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>4.04855</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>2.3649</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>1.47372</v>
-      </c>
-      <c r="F71" t="n">
-        <v>5.802244</v>
-      </c>
-      <c r="G71" t="n">
-        <v>3.389294</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2.112085</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>264</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>4.09999</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>2.39099</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>1.48617</v>
-      </c>
-      <c r="F72" t="n">
-        <v>5.875966</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3.426686</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2.129928</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>268</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>4.15291</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>2.40506</v>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>1.50328</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5.95181</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3.44685</v>
-      </c>
-      <c r="H73" t="n">
-        <v>2.15445</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>272</v>
-      </c>
-      <c r="B74" s="1" t="n">
-        <v>4.1983</v>
-      </c>
-      <c r="C74" s="1" t="n">
-        <v>2.42384</v>
-      </c>
-      <c r="D74" s="1" t="n">
-        <v>1.53038</v>
-      </c>
-      <c r="F74" t="n">
-        <v>6.016861</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3.473765</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2.193289</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="B75" s="1" t="n">
-        <v>4.22692</v>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>2.4331</v>
-      </c>
-      <c r="D75" s="1" t="n">
-        <v>1.54369</v>
-      </c>
-      <c r="F75" t="n">
-        <v>6.057878</v>
-      </c>
-      <c r="G75" t="n">
-        <v>3.487036</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2.212364</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>280</v>
-      </c>
-      <c r="B76" s="1" t="n">
-        <v>4.26155</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>2.45561</v>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>1.55269</v>
-      </c>
-      <c r="F76" t="n">
-        <v>6.107509</v>
-      </c>
-      <c r="G76" t="n">
-        <v>3.519297</v>
-      </c>
-      <c r="H76" t="n">
-        <v>2.225263</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>284</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>4.30147</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>2.47113</v>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>1.56403</v>
-      </c>
-      <c r="F77" t="n">
-        <v>6.164721</v>
-      </c>
-      <c r="G77" t="n">
-        <v>3.54154</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2.241515</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>288</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <v>4.33258</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>2.48888</v>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>1.57682</v>
-      </c>
-      <c r="F78" t="n">
-        <v>6.209307</v>
-      </c>
-      <c r="G78" t="n">
-        <v>3.566978</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2.259845</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>292</v>
-      </c>
-      <c r="B79" s="1" t="n">
-        <v>4.37244</v>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>2.5148</v>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>1.58776</v>
-      </c>
-      <c r="F79" t="n">
-        <v>6.266433</v>
-      </c>
-      <c r="G79" t="n">
-        <v>3.604126</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2.275524</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>296</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <v>4.40686</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>1.60776</v>
-      </c>
-      <c r="F80" t="n">
-        <v>6.315762</v>
-      </c>
-      <c r="G80" t="n">
-        <v>3.635942</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2.304187</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>4.46063</v>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>2.54754</v>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>1.62079</v>
-      </c>
-      <c r="F81" t="n">
-        <v>6.392823</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3.651048</v>
-      </c>
-      <c r="H81" t="n">
-        <v>2.322861</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="B82" s="1" t="n">
-        <v>4.50323</v>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>2.55997</v>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>1.63519</v>
-      </c>
-      <c r="F82" t="n">
-        <v>6.453876</v>
-      </c>
-      <c r="G82" t="n">
-        <v>3.668862</v>
-      </c>
-      <c r="H82" t="n">
-        <v>2.343499</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>308</v>
-      </c>
-      <c r="B83" s="1" t="n">
-        <v>4.53929</v>
-      </c>
-      <c r="C83" s="1" t="n">
-        <v>2.58923</v>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>1.64838</v>
-      </c>
-      <c r="F83" t="n">
-        <v>6.505556</v>
-      </c>
-      <c r="G83" t="n">
-        <v>3.710797</v>
-      </c>
-      <c r="H83" t="n">
-        <v>2.362402</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>312</v>
-      </c>
-      <c r="B84" s="1" t="n">
-        <v>4.57438</v>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>2.59812</v>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>1.65518</v>
-      </c>
-      <c r="F84" t="n">
-        <v>6.555846</v>
-      </c>
-      <c r="G84" t="n">
-        <v>3.723537</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2.372148</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>316</v>
-      </c>
-      <c r="B85" s="1" t="n">
-        <v>4.61799</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>2.60935</v>
-      </c>
-      <c r="D85" s="1" t="n">
-        <v>1.66138</v>
-      </c>
-      <c r="F85" t="n">
-        <v>6.618346</v>
-      </c>
-      <c r="G85" t="n">
-        <v>3.739632</v>
-      </c>
-      <c r="H85" t="n">
-        <v>2.381033</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>320</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>4.64786</v>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>2.62626</v>
-      </c>
-      <c r="D86" s="1" t="n">
-        <v>1.68286</v>
-      </c>
-      <c r="F86" t="n">
-        <v>6.661155</v>
-      </c>
-      <c r="G86" t="n">
-        <v>3.763867</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2.411818</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>324</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>4.66595</v>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>2.63919</v>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>1.69482</v>
-      </c>
-      <c r="F87" t="n">
-        <v>6.687081</v>
-      </c>
-      <c r="G87" t="n">
-        <v>3.782397</v>
-      </c>
-      <c r="H87" t="n">
-        <v>2.428958</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>328</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>4.70034</v>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>2.6565</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>1.7099</v>
-      </c>
-      <c r="F88" t="n">
-        <v>6.736368</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3.807206</v>
-      </c>
-      <c r="H88" t="n">
-        <v>2.450571</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>332</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>4.73066</v>
-      </c>
-      <c r="C89" s="1" t="n">
-        <v>2.6697</v>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>1.71279</v>
-      </c>
-      <c r="F89" t="n">
-        <v>6.779821</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3.826123</v>
-      </c>
-      <c r="H89" t="n">
-        <v>2.454712</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>336</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>4.74206</v>
-      </c>
-      <c r="C90" s="1" t="n">
-        <v>2.68034</v>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>1.72079</v>
-      </c>
-      <c r="F90" t="n">
-        <v>6.796159</v>
-      </c>
-      <c r="G90" t="n">
-        <v>3.841372</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2.466178</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>340</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>4.77161</v>
-      </c>
-      <c r="C91" s="1" t="n">
-        <v>2.69703</v>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>1.73029</v>
-      </c>
-      <c r="F91" t="n">
-        <v>6.838509</v>
-      </c>
-      <c r="G91" t="n">
-        <v>3.865292</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2.479793</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>344</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>4.79355</v>
-      </c>
-      <c r="C92" s="1" t="n">
-        <v>2.72335</v>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>1.73832</v>
-      </c>
-      <c r="F92" t="n">
-        <v>6.869953</v>
-      </c>
-      <c r="G92" t="n">
-        <v>3.903013</v>
-      </c>
-      <c r="H92" t="n">
-        <v>2.491301</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>348</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>4.82584</v>
-      </c>
-      <c r="C93" s="1" t="n">
-        <v>2.73515</v>
-      </c>
-      <c r="D93" s="1" t="n">
-        <v>1.75096</v>
-      </c>
-      <c r="F93" t="n">
-        <v>6.91623</v>
-      </c>
-      <c r="G93" t="n">
-        <v>3.919924</v>
-      </c>
-      <c r="H93" t="n">
-        <v>2.509416</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>352</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>4.85182</v>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>2.75292</v>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>1.76108</v>
-      </c>
-      <c r="F94" t="n">
-        <v>6.953464</v>
-      </c>
-      <c r="G94" t="n">
-        <v>3.945391</v>
-      </c>
-      <c r="H94" t="n">
-        <v>2.52392</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>356</v>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>4.89659</v>
-      </c>
-      <c r="C95" s="1" t="n">
-        <v>2.79243</v>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>1.77134</v>
-      </c>
-      <c r="F95" t="n">
-        <v>7.017627</v>
-      </c>
-      <c r="G95" t="n">
-        <v>4.002016</v>
-      </c>
-      <c r="H95" t="n">
-        <v>2.538624</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>4.94155</v>
-      </c>
-      <c r="C96" s="1" t="n">
-        <v>2.81148</v>
-      </c>
-      <c r="D96" s="1" t="n">
-        <v>1.78018</v>
-      </c>
-      <c r="F96" t="n">
-        <v>7.082062</v>
-      </c>
-      <c r="G96" t="n">
-        <v>4.029318</v>
-      </c>
-      <c r="H96" t="n">
-        <v>2.551294</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>364</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>4.97182</v>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>2.82915</v>
-      </c>
-      <c r="D97" s="1" t="n">
-        <v>1.78755</v>
-      </c>
-      <c r="F97" t="n">
-        <v>7.125444</v>
-      </c>
-      <c r="G97" t="n">
-        <v>4.054642</v>
-      </c>
-      <c r="H97" t="n">
-        <v>2.561856</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>368</v>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>4.99816</v>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>2.85956</v>
-      </c>
-      <c r="D98" s="1" t="n">
-        <v>1.79737</v>
-      </c>
-      <c r="F98" t="n">
-        <v>7.163193</v>
-      </c>
-      <c r="G98" t="n">
-        <v>4.098224</v>
-      </c>
-      <c r="H98" t="n">
-        <v>2.57593</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>372</v>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>5.03552</v>
-      </c>
-      <c r="C99" s="1" t="n">
-        <v>2.8711</v>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>1.80363</v>
-      </c>
-      <c r="F99" t="n">
-        <v>7.216736</v>
-      </c>
-      <c r="G99" t="n">
-        <v>4.114763</v>
-      </c>
-      <c r="H99" t="n">
-        <v>2.584901</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>376</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>5.08052</v>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>2.88517</v>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>1.80754</v>
-      </c>
-      <c r="F100" t="n">
-        <v>7.281229</v>
-      </c>
-      <c r="G100" t="n">
-        <v>4.134928</v>
-      </c>
-      <c r="H100" t="n">
-        <v>2.590505</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>380</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>5.11113</v>
-      </c>
-      <c r="C101" s="1" t="n">
-        <v>2.89351</v>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>1.81685</v>
-      </c>
-      <c r="F101" t="n">
-        <v>7.325098</v>
-      </c>
-      <c r="G101" t="n">
-        <v>4.14688</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2.603848</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>384</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>5.12218</v>
-      </c>
-      <c r="C102" s="1" t="n">
-        <v>2.91007</v>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>1.82533</v>
-      </c>
-      <c r="F102" t="n">
-        <v>7.340934</v>
-      </c>
-      <c r="G102" t="n">
-        <v>4.170614</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2.616001</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>388</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>5.14714</v>
-      </c>
-      <c r="C103" s="1" t="n">
-        <v>2.91719</v>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>1.83871</v>
-      </c>
-      <c r="F103" t="n">
-        <v>7.376706</v>
-      </c>
-      <c r="G103" t="n">
-        <v>4.180818</v>
-      </c>
-      <c r="H103" t="n">
-        <v>2.635177</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>392</v>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>5.17286</v>
-      </c>
-      <c r="C104" s="1" t="n">
-        <v>2.92759</v>
-      </c>
-      <c r="D104" s="1" t="n">
-        <v>1.84555</v>
-      </c>
-      <c r="F104" t="n">
-        <v>7.413567</v>
-      </c>
-      <c r="G104" t="n">
-        <v>4.195723</v>
-      </c>
-      <c r="H104" t="n">
-        <v>2.64498</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>396</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>5.20512</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>2.95142</v>
-      </c>
-      <c r="D105" s="1" t="n">
-        <v>1.85358</v>
-      </c>
-      <c r="F105" t="n">
-        <v>7.459801</v>
-      </c>
-      <c r="G105" t="n">
-        <v>4.229875</v>
-      </c>
-      <c r="H105" t="n">
-        <v>2.656488</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>5.22893</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>2.96825</v>
-      </c>
-      <c r="D106" s="1" t="n">
-        <v>1.86463</v>
-      </c>
-      <c r="F106" t="n">
-        <v>7.493925</v>
-      </c>
-      <c r="G106" t="n">
-        <v>4.253995</v>
-      </c>
-      <c r="H106" t="n">
-        <v>2.672324</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>404</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>5.25092</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>2.97465</v>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>1.87113</v>
-      </c>
-      <c r="F107" t="n">
-        <v>7.52544</v>
-      </c>
-      <c r="G107" t="n">
-        <v>4.263167</v>
-      </c>
-      <c r="H107" t="n">
-        <v>2.68164</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>408</v>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>5.27132</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>2.98175</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>1.88195</v>
-      </c>
-      <c r="F108" t="n">
-        <v>7.554677</v>
-      </c>
-      <c r="G108" t="n">
-        <v>4.273343</v>
-      </c>
-      <c r="H108" t="n">
-        <v>2.697147</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>412</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>5.30532</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>2.99276</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>1.89103</v>
-      </c>
-      <c r="F109" t="n">
-        <v>7.603404</v>
-      </c>
-      <c r="G109" t="n">
-        <v>4.289122</v>
-      </c>
-      <c r="H109" t="n">
-        <v>2.71016</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>416</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>5.3332</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>3.00508</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>1.90702</v>
-      </c>
-      <c r="F110" t="n">
-        <v>7.643361</v>
-      </c>
-      <c r="G110" t="n">
-        <v>4.306779</v>
-      </c>
-      <c r="H110" t="n">
-        <v>2.733076</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>420</v>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>5.36758</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>3.01138</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>1.91116</v>
-      </c>
-      <c r="F111" t="n">
-        <v>7.692633</v>
-      </c>
-      <c r="G111" t="n">
-        <v>4.315808</v>
-      </c>
-      <c r="H111" t="n">
-        <v>2.73901</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>424</v>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>5.41861</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>3.03621</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>1.92445</v>
-      </c>
-      <c r="F112" t="n">
-        <v>7.765768</v>
-      </c>
-      <c r="G112" t="n">
-        <v>4.351393</v>
-      </c>
-      <c r="H112" t="n">
-        <v>2.758056</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>428</v>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>5.45465</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>3.04562</v>
-      </c>
-      <c r="D113" s="1" t="n">
-        <v>1.92549</v>
-      </c>
-      <c r="F113" t="n">
-        <v>7.817419</v>
-      </c>
-      <c r="G113" t="n">
-        <v>4.364879</v>
-      </c>
-      <c r="H113" t="n">
-        <v>2.759547</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>432</v>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>5.50073</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>3.05595</v>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>1.92831</v>
-      </c>
-      <c r="F114" t="n">
-        <v>7.883459</v>
-      </c>
-      <c r="G114" t="n">
-        <v>4.379684</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2.763588</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>436</v>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>5.52596</v>
-      </c>
-      <c r="C115" s="1" t="n">
-        <v>3.05928</v>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>1.94251</v>
-      </c>
-      <c r="F115" t="n">
-        <v>7.919618</v>
-      </c>
-      <c r="G115" t="n">
-        <v>4.384456</v>
-      </c>
-      <c r="H115" t="n">
-        <v>2.783939</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>440</v>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>5.55298</v>
-      </c>
-      <c r="C116" s="1" t="n">
-        <v>3.06697</v>
-      </c>
-      <c r="D116" s="1" t="n">
-        <v>1.94991</v>
-      </c>
-      <c r="F116" t="n">
-        <v>7.958342</v>
-      </c>
-      <c r="G116" t="n">
-        <v>4.395477</v>
-      </c>
-      <c r="H116" t="n">
-        <v>2.794545</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>444</v>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>5.60693</v>
-      </c>
-      <c r="C117" s="1" t="n">
-        <v>3.08553</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>1.97145</v>
-      </c>
-      <c r="F117" t="n">
-        <v>8.035662</v>
-      </c>
-      <c r="G117" t="n">
-        <v>4.422077</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2.825415</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>448</v>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>5.65747</v>
-      </c>
-      <c r="C118" s="1" t="n">
-        <v>3.10812</v>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>1.98139</v>
-      </c>
-      <c r="F118" t="n">
-        <v>8.108093999999999</v>
-      </c>
-      <c r="G118" t="n">
-        <v>4.454452</v>
-      </c>
-      <c r="H118" t="n">
-        <v>2.839661</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>452</v>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>5.67797</v>
-      </c>
-      <c r="C119" s="1" t="n">
-        <v>3.13272</v>
-      </c>
-      <c r="D119" s="1" t="n">
-        <v>1.99337</v>
-      </c>
-      <c r="F119" t="n">
-        <v>8.137473999999999</v>
-      </c>
-      <c r="G119" t="n">
-        <v>4.489708</v>
-      </c>
-      <c r="H119" t="n">
-        <v>2.85683</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>456</v>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>5.697</v>
-      </c>
-      <c r="C120" s="1" t="n">
-        <v>3.14554</v>
-      </c>
-      <c r="D120" s="1" t="n">
-        <v>1.99918</v>
-      </c>
-      <c r="F120" t="n">
-        <v>8.164747</v>
-      </c>
-      <c r="G120" t="n">
-        <v>4.508081</v>
-      </c>
-      <c r="H120" t="n">
-        <v>2.865157</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>460</v>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>5.73482</v>
-      </c>
-      <c r="C121" s="1" t="n">
-        <v>3.1531</v>
-      </c>
-      <c r="D121" s="1" t="n">
-        <v>2.0158</v>
-      </c>
-      <c r="F121" t="n">
-        <v>8.218949</v>
-      </c>
-      <c r="G121" t="n">
-        <v>4.518916</v>
-      </c>
-      <c r="H121" t="n">
-        <v>2.888976</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>464</v>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>5.75743</v>
-      </c>
-      <c r="C122" s="1" t="n">
-        <v>3.17696</v>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>2.02218</v>
-      </c>
-      <c r="F122" t="n">
-        <v>8.251353</v>
-      </c>
-      <c r="G122" t="n">
-        <v>4.553111</v>
-      </c>
-      <c r="H122" t="n">
-        <v>2.89812</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>468</v>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>5.79351</v>
-      </c>
-      <c r="C123" s="1" t="n">
-        <v>3.21039</v>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>2.02788</v>
-      </c>
-      <c r="F123" t="n">
-        <v>8.303062000000001</v>
-      </c>
-      <c r="G123" t="n">
-        <v>4.601022</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2.906289</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>472</v>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>5.82756</v>
-      </c>
-      <c r="C124" s="1" t="n">
-        <v>3.22596</v>
-      </c>
-      <c r="D124" s="1" t="n">
-        <v>2.0376</v>
-      </c>
-      <c r="F124" t="n">
-        <v>8.351861</v>
-      </c>
-      <c r="G124" t="n">
-        <v>4.623336</v>
-      </c>
-      <c r="H124" t="n">
-        <v>2.920219</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>476</v>
-      </c>
-      <c r="B125" s="1" t="n">
-        <v>5.85759</v>
-      </c>
-      <c r="C125" s="1" t="n">
-        <v>3.26108</v>
-      </c>
-      <c r="D125" s="1" t="n">
-        <v>2.04163</v>
-      </c>
-      <c r="F125" t="n">
-        <v>8.394899000000001</v>
-      </c>
-      <c r="G125" t="n">
-        <v>4.673669</v>
-      </c>
-      <c r="H125" t="n">
-        <v>2.925995</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>480</v>
-      </c>
-      <c r="B126" s="1" t="n">
-        <v>5.88906</v>
-      </c>
-      <c r="C126" s="1" t="n">
-        <v>3.27706</v>
-      </c>
-      <c r="D126" s="1" t="n">
-        <v>2.05258</v>
-      </c>
-      <c r="F126" t="n">
-        <v>8.440001000000001</v>
-      </c>
-      <c r="G126" t="n">
-        <v>4.696571</v>
-      </c>
-      <c r="H126" t="n">
-        <v>2.941688</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>484</v>
-      </c>
-      <c r="B127" s="1" t="n">
-        <v>5.91451</v>
-      </c>
-      <c r="C127" s="1" t="n">
-        <v>3.29017</v>
-      </c>
-      <c r="D127" s="1" t="n">
-        <v>2.0558</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8.476475000000001</v>
-      </c>
-      <c r="G127" t="n">
-        <v>4.71536</v>
-      </c>
-      <c r="H127" t="n">
-        <v>2.946303</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>488</v>
-      </c>
-      <c r="B128" s="1" t="n">
-        <v>5.94948</v>
-      </c>
-      <c r="C128" s="1" t="n">
-        <v>3.30571</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>2.06382</v>
-      </c>
-      <c r="F128" t="n">
-        <v>8.526593</v>
-      </c>
-      <c r="G128" t="n">
-        <v>4.737631</v>
-      </c>
-      <c r="H128" t="n">
-        <v>2.957797</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>492</v>
-      </c>
-      <c r="B129" s="1" t="n">
-        <v>5.98072</v>
-      </c>
-      <c r="C129" s="1" t="n">
-        <v>3.32532</v>
-      </c>
-      <c r="D129" s="1" t="n">
-        <v>2.07587</v>
-      </c>
-      <c r="F129" t="n">
-        <v>8.571365</v>
-      </c>
-      <c r="G129" t="n">
-        <v>4.765736</v>
-      </c>
-      <c r="H129" t="n">
-        <v>2.975066</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>496</v>
-      </c>
-      <c r="B130" s="1" t="n">
-        <v>6.0107</v>
-      </c>
-      <c r="C130" s="1" t="n">
-        <v>3.33743</v>
-      </c>
-      <c r="D130" s="1" t="n">
-        <v>2.07942</v>
-      </c>
-      <c r="F130" t="n">
-        <v>8.614331</v>
-      </c>
-      <c r="G130" t="n">
-        <v>4.783091</v>
-      </c>
-      <c r="H130" t="n">
-        <v>2.980154</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>6.03806</v>
-      </c>
-      <c r="C131" s="1" t="n">
-        <v>3.34429</v>
-      </c>
-      <c r="D131" s="1" t="n">
-        <v>2.0857</v>
-      </c>
-      <c r="F131" t="n">
-        <v>8.653543000000001</v>
-      </c>
-      <c r="G131" t="n">
-        <v>4.792923</v>
-      </c>
-      <c r="H131" t="n">
-        <v>2.989154</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>504</v>
-      </c>
-      <c r="B132" s="1" t="n">
-        <v>6.07544</v>
-      </c>
-      <c r="C132" s="1" t="n">
-        <v>3.34953</v>
-      </c>
-      <c r="D132" s="1" t="n">
-        <v>2.09229</v>
-      </c>
-      <c r="F132" t="n">
-        <v>8.707114000000001</v>
-      </c>
-      <c r="G132" t="n">
-        <v>4.800433</v>
-      </c>
-      <c r="H132" t="n">
-        <v>2.998599</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>508</v>
-      </c>
-      <c r="B133" s="1" t="n">
-        <v>6.1188</v>
-      </c>
-      <c r="C133" s="1" t="n">
-        <v>3.35795</v>
-      </c>
-      <c r="D133" s="1" t="n">
-        <v>2.09723</v>
-      </c>
-      <c r="F133" t="n">
-        <v>8.769256</v>
-      </c>
-      <c r="G133" t="n">
-        <v>4.8125</v>
-      </c>
-      <c r="H133" t="n">
-        <v>3.005679</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>512</v>
-      </c>
-      <c r="B134" s="1" t="n">
-        <v>6.15302</v>
-      </c>
-      <c r="C134" s="1" t="n">
-        <v>3.37021</v>
-      </c>
-      <c r="D134" s="1" t="n">
-        <v>2.10204</v>
-      </c>
-      <c r="F134" t="n">
-        <v>8.818299</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4.830071</v>
-      </c>
-      <c r="H134" t="n">
-        <v>3.012572</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>516</v>
-      </c>
-      <c r="B135" s="1" t="n">
-        <v>6.18416</v>
-      </c>
-      <c r="C135" s="1" t="n">
-        <v>3.38754</v>
-      </c>
-      <c r="D135" s="1" t="n">
-        <v>2.10633</v>
-      </c>
-      <c r="F135" t="n">
-        <v>8.862928</v>
-      </c>
-      <c r="G135" t="n">
-        <v>4.854907</v>
-      </c>
-      <c r="H135" t="n">
-        <v>3.018721</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="B136" s="1" t="n">
-        <v>6.20527</v>
-      </c>
-      <c r="C136" s="1" t="n">
-        <v>3.40369</v>
-      </c>
-      <c r="D136" s="1" t="n">
-        <v>2.12309</v>
-      </c>
-      <c r="F136" t="n">
-        <v>8.893181999999999</v>
-      </c>
-      <c r="G136" t="n">
-        <v>4.878053</v>
-      </c>
-      <c r="H136" t="n">
-        <v>3.04274</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>524</v>
-      </c>
-      <c r="B137" s="1" t="n">
-        <v>6.2356</v>
-      </c>
-      <c r="C137" s="1" t="n">
-        <v>3.42603</v>
-      </c>
-      <c r="D137" s="1" t="n">
-        <v>2.13156</v>
-      </c>
-      <c r="F137" t="n">
-        <v>8.93665</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4.91007</v>
-      </c>
-      <c r="H137" t="n">
-        <v>3.054879</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>528</v>
-      </c>
-      <c r="B138" s="1" t="n">
-        <v>6.27085</v>
-      </c>
-      <c r="C138" s="1" t="n">
-        <v>3.4389</v>
-      </c>
-      <c r="D138" s="1" t="n">
-        <v>2.13618</v>
-      </c>
-      <c r="F138" t="n">
-        <v>8.987169</v>
-      </c>
-      <c r="G138" t="n">
-        <v>4.928515</v>
-      </c>
-      <c r="H138" t="n">
-        <v>3.061501</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>532</v>
-      </c>
-      <c r="B139" s="1" t="n">
-        <v>6.28381</v>
-      </c>
-      <c r="C139" s="1" t="n">
-        <v>3.46211</v>
-      </c>
-      <c r="D139" s="1" t="n">
-        <v>2.14776</v>
-      </c>
-      <c r="F139" t="n">
-        <v>9.005743000000001</v>
-      </c>
-      <c r="G139" t="n">
-        <v>4.961778</v>
-      </c>
-      <c r="H139" t="n">
-        <v>3.078097</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>536</v>
-      </c>
-      <c r="B140" s="1" t="n">
-        <v>6.32791</v>
-      </c>
-      <c r="C140" s="1" t="n">
-        <v>3.48009</v>
-      </c>
-      <c r="D140" s="1" t="n">
-        <v>2.15405</v>
-      </c>
-      <c r="F140" t="n">
-        <v>9.068946</v>
-      </c>
-      <c r="G140" t="n">
-        <v>4.987547</v>
-      </c>
-      <c r="H140" t="n">
-        <v>3.087111</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>540</v>
-      </c>
-      <c r="B141" s="1" t="n">
-        <v>6.34313</v>
-      </c>
-      <c r="C141" s="1" t="n">
-        <v>3.49388</v>
-      </c>
-      <c r="D141" s="1" t="n">
-        <v>2.16547</v>
-      </c>
-      <c r="F141" t="n">
-        <v>9.090759</v>
-      </c>
-      <c r="G141" t="n">
-        <v>5.00731</v>
-      </c>
-      <c r="H141" t="n">
-        <v>3.103478</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>544</v>
-      </c>
-      <c r="B142" s="1" t="n">
-        <v>6.36937</v>
-      </c>
-      <c r="C142" s="1" t="n">
-        <v>3.50471</v>
-      </c>
-      <c r="D142" s="1" t="n">
-        <v>2.18451</v>
-      </c>
-      <c r="F142" t="n">
-        <v>9.128365000000001</v>
-      </c>
-      <c r="G142" t="n">
-        <v>5.022831</v>
-      </c>
-      <c r="H142" t="n">
-        <v>3.130766</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>548</v>
-      </c>
-      <c r="B143" s="1" t="n">
-        <v>6.38234</v>
-      </c>
-      <c r="C143" s="1" t="n">
-        <v>3.52631</v>
-      </c>
-      <c r="D143" s="1" t="n">
-        <v>2.19587</v>
-      </c>
-      <c r="F143" t="n">
-        <v>9.146953</v>
-      </c>
-      <c r="G143" t="n">
-        <v>5.053788</v>
-      </c>
-      <c r="H143" t="n">
-        <v>3.147046</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>552</v>
-      </c>
-      <c r="B144" s="1" t="n">
-        <v>6.41694</v>
-      </c>
-      <c r="C144" s="1" t="n">
-        <v>3.53858</v>
-      </c>
-      <c r="D144" s="1" t="n">
-        <v>2.19672</v>
-      </c>
-      <c r="F144" t="n">
-        <v>9.196540000000001</v>
-      </c>
-      <c r="G144" t="n">
-        <v>5.071373</v>
-      </c>
-      <c r="H144" t="n">
-        <v>3.148265</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>556</v>
-      </c>
-      <c r="B145" s="1" t="n">
-        <v>6.45426</v>
-      </c>
-      <c r="C145" s="1" t="n">
-        <v>3.54395</v>
-      </c>
-      <c r="D145" s="1" t="n">
-        <v>2.19802</v>
-      </c>
-      <c r="F145" t="n">
-        <v>9.250026</v>
-      </c>
-      <c r="G145" t="n">
-        <v>5.079069</v>
-      </c>
-      <c r="H145" t="n">
-        <v>3.150128</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>560</v>
-      </c>
-      <c r="B146" s="1" t="n">
-        <v>6.49832</v>
-      </c>
-      <c r="C146" s="1" t="n">
-        <v>3.56249</v>
-      </c>
-      <c r="D146" s="1" t="n">
-        <v>2.20926</v>
-      </c>
-      <c r="F146" t="n">
-        <v>9.313172</v>
-      </c>
-      <c r="G146" t="n">
-        <v>5.10564</v>
-      </c>
-      <c r="H146" t="n">
-        <v>3.166236</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>564</v>
-      </c>
-      <c r="B147" s="1" t="n">
-        <v>6.51171</v>
-      </c>
-      <c r="C147" s="1" t="n">
-        <v>3.56633</v>
-      </c>
-      <c r="D147" s="1" t="n">
-        <v>2.21202</v>
-      </c>
-      <c r="F147" t="n">
-        <v>9.332362</v>
-      </c>
-      <c r="G147" t="n">
-        <v>5.111143</v>
-      </c>
-      <c r="H147" t="n">
-        <v>3.170192</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>568</v>
-      </c>
-      <c r="B148" s="1" t="n">
-        <v>6.52668</v>
-      </c>
-      <c r="C148" s="1" t="n">
-        <v>3.59267</v>
-      </c>
-      <c r="D148" s="1" t="n">
-        <v>2.21616</v>
-      </c>
-      <c r="F148" t="n">
-        <v>9.353816</v>
-      </c>
-      <c r="G148" t="n">
-        <v>5.148893</v>
-      </c>
-      <c r="H148" t="n">
-        <v>3.176125</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>572</v>
-      </c>
-      <c r="B149" s="1" t="n">
-        <v>6.55212</v>
-      </c>
-      <c r="C149" s="1" t="n">
-        <v>3.6038</v>
-      </c>
-      <c r="D149" s="1" t="n">
-        <v>2.21984</v>
-      </c>
-      <c r="F149" t="n">
-        <v>9.390276</v>
-      </c>
-      <c r="G149" t="n">
-        <v>5.164844</v>
-      </c>
-      <c r="H149" t="n">
-        <v>3.181399</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>576</v>
-      </c>
-      <c r="B150" s="1" t="n">
-        <v>6.58663</v>
-      </c>
-      <c r="C150" s="1" t="n">
-        <v>3.62273</v>
-      </c>
-      <c r="D150" s="1" t="n">
-        <v>2.22157</v>
-      </c>
-      <c r="F150" t="n">
-        <v>9.439734</v>
-      </c>
-      <c r="G150" t="n">
-        <v>5.191974</v>
-      </c>
-      <c r="H150" t="n">
-        <v>3.183879</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>580</v>
-      </c>
-      <c r="B151" s="1" t="n">
-        <v>6.62781</v>
-      </c>
-      <c r="C151" s="1" t="n">
-        <v>3.63244</v>
-      </c>
-      <c r="D151" s="1" t="n">
-        <v>2.2274</v>
-      </c>
-      <c r="F151" t="n">
-        <v>9.498752</v>
-      </c>
-      <c r="G151" t="n">
-        <v>5.20589</v>
-      </c>
-      <c r="H151" t="n">
-        <v>3.192234</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>584</v>
-      </c>
-      <c r="B152" s="1" t="n">
-        <v>6.65774</v>
-      </c>
-      <c r="C152" s="1" t="n">
-        <v>3.64573</v>
-      </c>
-      <c r="D152" s="1" t="n">
-        <v>2.23246</v>
-      </c>
-      <c r="F152" t="n">
-        <v>9.541646999999999</v>
-      </c>
-      <c r="G152" t="n">
-        <v>5.224936</v>
-      </c>
-      <c r="H152" t="n">
-        <v>3.199486</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>588</v>
-      </c>
-      <c r="B153" s="1" t="n">
-        <v>6.67469</v>
-      </c>
-      <c r="C153" s="1" t="n">
-        <v>3.65642</v>
-      </c>
-      <c r="D153" s="1" t="n">
-        <v>2.23821</v>
-      </c>
-      <c r="F153" t="n">
-        <v>9.565939</v>
-      </c>
-      <c r="G153" t="n">
-        <v>5.240257</v>
-      </c>
-      <c r="H153" t="n">
-        <v>3.207727</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>592</v>
-      </c>
-      <c r="B154" s="1" t="n">
-        <v>6.72658</v>
-      </c>
-      <c r="C154" s="1" t="n">
-        <v>3.67105</v>
-      </c>
-      <c r="D154" s="1" t="n">
-        <v>2.24165</v>
-      </c>
-      <c r="F154" t="n">
-        <v>9.640306000000001</v>
-      </c>
-      <c r="G154" t="n">
-        <v>5.261224</v>
-      </c>
-      <c r="H154" t="n">
-        <v>3.212657</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>596</v>
-      </c>
-      <c r="B155" s="1" t="n">
-        <v>6.75674</v>
-      </c>
-      <c r="C155" s="1" t="n">
-        <v>3.68722</v>
-      </c>
-      <c r="D155" s="1" t="n">
-        <v>2.26331</v>
-      </c>
-      <c r="F155" t="n">
-        <v>9.683529999999999</v>
-      </c>
-      <c r="G155" t="n">
-        <v>5.284398</v>
-      </c>
-      <c r="H155" t="n">
-        <v>3.243699</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>600</v>
-      </c>
-      <c r="B156" s="1" t="n">
-        <v>6.7944</v>
-      </c>
-      <c r="C156" s="1" t="n">
-        <v>3.69438</v>
-      </c>
-      <c r="D156" s="1" t="n">
-        <v>2.26769</v>
-      </c>
-      <c r="F156" t="n">
-        <v>9.737503</v>
-      </c>
-      <c r="G156" t="n">
-        <v>5.29466</v>
-      </c>
-      <c r="H156" t="n">
-        <v>3.249976</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>604</v>
-      </c>
-      <c r="B157" s="1" t="n">
-        <v>6.81633</v>
-      </c>
-      <c r="C157" s="1" t="n">
-        <v>3.70234</v>
-      </c>
-      <c r="D157" s="1" t="n">
-        <v>2.26999</v>
-      </c>
-      <c r="F157" t="n">
-        <v>9.768933000000001</v>
-      </c>
-      <c r="G157" t="n">
-        <v>5.306068</v>
-      </c>
-      <c r="H157" t="n">
-        <v>3.253273</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>608</v>
-      </c>
-      <c r="B158" s="1" t="n">
-        <v>6.84222</v>
-      </c>
-      <c r="C158" s="1" t="n">
-        <v>3.71284</v>
-      </c>
-      <c r="D158" s="1" t="n">
-        <v>2.27729</v>
-      </c>
-      <c r="F158" t="n">
-        <v>9.806037</v>
-      </c>
-      <c r="G158" t="n">
-        <v>5.321116</v>
-      </c>
-      <c r="H158" t="n">
-        <v>3.263735</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>612</v>
-      </c>
-      <c r="B159" s="1" t="n">
-        <v>6.85846</v>
-      </c>
-      <c r="C159" s="1" t="n">
-        <v>3.72527</v>
-      </c>
-      <c r="D159" s="1" t="n">
-        <v>2.28083</v>
-      </c>
-      <c r="F159" t="n">
-        <v>9.829312</v>
-      </c>
-      <c r="G159" t="n">
-        <v>5.33893</v>
-      </c>
-      <c r="H159" t="n">
-        <v>3.268808</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>616</v>
-      </c>
-      <c r="B160" s="1" t="n">
-        <v>6.899</v>
-      </c>
-      <c r="C160" s="1" t="n">
-        <v>3.73775</v>
-      </c>
-      <c r="D160" s="1" t="n">
-        <v>2.28603</v>
-      </c>
-      <c r="F160" t="n">
-        <v>9.887413</v>
-      </c>
-      <c r="G160" t="n">
-        <v>5.356816</v>
-      </c>
-      <c r="H160" t="n">
-        <v>3.276261</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>620</v>
-      </c>
-      <c r="B161" s="1" t="n">
-        <v>6.91603</v>
-      </c>
-      <c r="C161" s="1" t="n">
-        <v>3.75859</v>
-      </c>
-      <c r="D161" s="1" t="n">
-        <v>2.29873</v>
-      </c>
-      <c r="F161" t="n">
-        <v>9.911818999999999</v>
-      </c>
-      <c r="G161" t="n">
-        <v>5.386684</v>
-      </c>
-      <c r="H161" t="n">
-        <v>3.294462</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>624</v>
-      </c>
-      <c r="B162" s="1" t="n">
-        <v>6.93709</v>
-      </c>
-      <c r="C162" s="1" t="n">
-        <v>3.75859</v>
-      </c>
-      <c r="D162" s="1" t="n">
-        <v>2.30178</v>
-      </c>
-      <c r="F162" t="n">
-        <v>9.942002</v>
-      </c>
-      <c r="G162" t="n">
-        <v>5.386684</v>
-      </c>
-      <c r="H162" t="n">
-        <v>3.298833</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>628</v>
-      </c>
-      <c r="B163" s="1" t="n">
-        <v>6.95773</v>
-      </c>
-      <c r="C163" s="1" t="n">
-        <v>3.77672</v>
-      </c>
-      <c r="D163" s="1" t="n">
-        <v>2.3095</v>
-      </c>
-      <c r="F163" t="n">
-        <v>9.971582</v>
-      </c>
-      <c r="G163" t="n">
-        <v>5.412667</v>
-      </c>
-      <c r="H163" t="n">
-        <v>3.309897</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>632</v>
-      </c>
-      <c r="B164" s="1" t="n">
-        <v>6.98908</v>
-      </c>
-      <c r="C164" s="1" t="n">
-        <v>3.79122</v>
-      </c>
-      <c r="D164" s="1" t="n">
-        <v>2.3119</v>
-      </c>
-      <c r="F164" t="n">
-        <v>10.016512</v>
-      </c>
-      <c r="G164" t="n">
-        <v>5.433448</v>
-      </c>
-      <c r="H164" t="n">
-        <v>3.313337</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>636</v>
-      </c>
-      <c r="B165" s="1" t="n">
-        <v>7.01598</v>
-      </c>
-      <c r="C165" s="1" t="n">
-        <v>3.8009</v>
-      </c>
-      <c r="D165" s="1" t="n">
-        <v>2.31952</v>
-      </c>
-      <c r="F165" t="n">
-        <v>10.055064</v>
-      </c>
-      <c r="G165" t="n">
-        <v>5.447321</v>
-      </c>
-      <c r="H165" t="n">
-        <v>3.324257</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>640</v>
-      </c>
-      <c r="B166" s="1" t="n">
-        <v>7.03678</v>
-      </c>
-      <c r="C166" s="1" t="n">
-        <v>3.81442</v>
-      </c>
-      <c r="D166" s="1" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="F166" t="n">
-        <v>10.084874</v>
-      </c>
-      <c r="G166" t="n">
-        <v>5.466697</v>
-      </c>
-      <c r="H166" t="n">
-        <v>3.329402</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>644</v>
-      </c>
-      <c r="B167" s="1" t="n">
-        <v>7.06777</v>
-      </c>
-      <c r="C167" s="1" t="n">
-        <v>3.8163</v>
-      </c>
-      <c r="D167" s="1" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="F167" t="n">
-        <v>10.129288</v>
-      </c>
-      <c r="G167" t="n">
-        <v>5.469392</v>
-      </c>
-      <c r="H167" t="n">
-        <v>3.329402</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>648</v>
-      </c>
-      <c r="B168" s="1" t="n">
-        <v>7.09127</v>
-      </c>
-      <c r="C168" s="1" t="n">
-        <v>3.82387</v>
-      </c>
-      <c r="D168" s="1" t="n">
-        <v>2.33373</v>
-      </c>
-      <c r="F168" t="n">
-        <v>10.162967</v>
-      </c>
-      <c r="G168" t="n">
-        <v>5.480241</v>
-      </c>
-      <c r="H168" t="n">
-        <v>3.344623</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>652</v>
-      </c>
-      <c r="B169" s="1" t="n">
-        <v>7.10701</v>
-      </c>
-      <c r="C169" s="1" t="n">
-        <v>3.82989</v>
-      </c>
-      <c r="D169" s="1" t="n">
-        <v>2.33651</v>
-      </c>
-      <c r="F169" t="n">
-        <v>10.185525</v>
-      </c>
-      <c r="G169" t="n">
-        <v>5.488868</v>
-      </c>
-      <c r="H169" t="n">
-        <v>3.348607</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>656</v>
-      </c>
-      <c r="B170" s="1" t="n">
-        <v>7.1384</v>
-      </c>
-      <c r="C170" s="1" t="n">
-        <v>3.8345</v>
-      </c>
-      <c r="D170" s="1" t="n">
-        <v>2.35189</v>
-      </c>
-      <c r="F170" t="n">
-        <v>10.230512</v>
-      </c>
-      <c r="G170" t="n">
-        <v>5.495475</v>
-      </c>
-      <c r="H170" t="n">
-        <v>3.370649</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>660</v>
-      </c>
-      <c r="B171" s="1" t="n">
-        <v>7.16067</v>
-      </c>
-      <c r="C171" s="1" t="n">
-        <v>3.85259</v>
-      </c>
-      <c r="D171" s="1" t="n">
-        <v>2.36081</v>
-      </c>
-      <c r="F171" t="n">
-        <v>10.262429</v>
-      </c>
-      <c r="G171" t="n">
-        <v>5.521401</v>
-      </c>
-      <c r="H171" t="n">
-        <v>3.383433</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>664</v>
-      </c>
-      <c r="B172" s="1" t="n">
-        <v>7.19842</v>
-      </c>
-      <c r="C172" s="1" t="n">
-        <v>3.86081</v>
-      </c>
-      <c r="D172" s="1" t="n">
-        <v>2.3658</v>
-      </c>
-      <c r="F172" t="n">
-        <v>10.316531</v>
-      </c>
-      <c r="G172" t="n">
-        <v>5.533182</v>
-      </c>
-      <c r="H172" t="n">
-        <v>3.390584</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>668</v>
-      </c>
-      <c r="B173" s="1" t="n">
-        <v>7.22158</v>
-      </c>
-      <c r="C173" s="1" t="n">
-        <v>3.87308</v>
-      </c>
-      <c r="D173" s="1" t="n">
-        <v>2.36887</v>
-      </c>
-      <c r="F173" t="n">
-        <v>10.349723</v>
-      </c>
-      <c r="G173" t="n">
-        <v>5.550767</v>
-      </c>
-      <c r="H173" t="n">
-        <v>3.394984</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>672</v>
-      </c>
-      <c r="B174" s="1" t="n">
-        <v>7.24102</v>
-      </c>
-      <c r="C174" s="1" t="n">
-        <v>3.88343</v>
-      </c>
-      <c r="D174" s="1" t="n">
-        <v>2.38034</v>
-      </c>
-      <c r="F174" t="n">
-        <v>10.377584</v>
-      </c>
-      <c r="G174" t="n">
-        <v>5.5656</v>
-      </c>
-      <c r="H174" t="n">
-        <v>3.411422</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>(b) Final (672h) mass loss vs. SA/V ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="B177" s="1" t="inlineStr">
-        <is>
-          <t>Strut thickness (mm)</t>
-        </is>
-      </c>
-      <c r="C177" s="1" t="inlineStr">
-        <is>
-          <t>SA/V ratio (mm^-1)</t>
-        </is>
-      </c>
-      <c r="D177" s="1" t="inlineStr">
-        <is>
-          <t>Final (672h) mass loss (%)</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Final (672h) mass loss, scaled x1.4332 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>thin_sav</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="n">
-        <v>0.0825</v>
-      </c>
-      <c r="C178" s="1" t="n">
-        <v>48.2123</v>
-      </c>
-      <c r="D178" s="1" t="n">
-        <v>7.24102</v>
-      </c>
-      <c r="E178" t="n">
-        <v>10.37758</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="inlineStr">
-        <is>
-          <t>mid_sav</t>
-        </is>
-      </c>
-      <c r="B179" s="1" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="C179" s="1" t="n">
-        <v>24.1062</v>
-      </c>
-      <c r="D179" s="1" t="n">
-        <v>3.88343</v>
-      </c>
-      <c r="E179" t="n">
-        <v>5.5656</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="inlineStr">
-        <is>
-          <t>thick_sav</t>
-        </is>
-      </c>
-      <c r="B180" s="1" t="n">
-        <v>0.2475</v>
-      </c>
-      <c r="C180" s="1" t="n">
-        <v>16.0708</v>
-      </c>
-      <c r="D180" s="1" t="n">
-        <v>2.38034</v>
-      </c>
-      <c r="E180" t="n">
-        <v>3.41142</v>
       </c>
     </row>
   </sheetData>
@@ -23088,6 +19430,4056 @@
         <is>
           <t>global</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H180"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supplementary Figure 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study (Supplementary Figure 5a). Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>(a) Mass loss vs. time, raw simulation output</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Time (hours)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Thin strut t=0.0825mm (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Mid strut (baseline) t=0.165mm (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Thick strut t=0.2475mm (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Thin strut t=0.0825mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Mid strut t=0.165mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Thick strut t=0.2475mm, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.189357</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.109343</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.080549</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.156707</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.11544</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.253362</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.157841</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.115457</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.226212</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.165469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.310193</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.201633</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.148604</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.444558</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.288974</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.212974</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.333815</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.249848</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0.175336</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.478412</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.358074</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.251286</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.375187</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0.275296</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.190526</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.537705</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.394545</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.273055</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.407215</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.317775</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0.211982</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.583607</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.455424</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.303805</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.435107</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.350046</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.230155</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6235810000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.501674</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.32985</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.518921</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.412961</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0.262609</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.591842</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.376362</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.58073</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.473968</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.288579</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.832283</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.679275</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.413582</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.6893820000000001</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.530861</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0.308554</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.987999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.760812</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.442209</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.779559</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.5749840000000001</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.34109</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.117237</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.824048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.488839</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.8725889999999999</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.631798</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0.368947</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.250565</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.905471</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.528762</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.914041</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0.6641629999999999</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0.382127</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.309973</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.951856</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.547651</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1.01129</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0.726212</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.449346</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.040782</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.601973</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1.11756</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.7896339999999999</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0.456405</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.601649</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.131677</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.654104</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1.18753</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>0.820338</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.491695</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.701928</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.175681</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.704681</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1.27143</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0.518161</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.82217</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.245708</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.742611</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1.36776</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0.910593</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0.550017</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.960227</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.305031</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.788266</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1.46059</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>0.956944</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>0.572665</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.093268</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.37146</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.820724</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1.53696</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0.60609</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.202719</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.437895</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.868628</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1.61082</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>1.04893</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0.623081</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.308573</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.503291</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.892979</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1.69576</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>1.09325</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.652014</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.430306</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.566809</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9344440000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1.77361</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>1.13399</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0.680528</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.541878</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.625196</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.97531</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1.84992</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>1.17828</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0.713676</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.651243</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.688671</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.022816</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1.9361</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>1.20632</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0.7526350000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.774753</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.728857</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.078651</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>2.00236</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>1.24091</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>0.784246</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.869714</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.77843</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.123955</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>2.04977</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>1.28195</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>0.800565</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.937661</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.837247</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.147343</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>2.12737</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>1.31584</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0.81098</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.048874</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.885817</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.162269</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>2.20152</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>1.3493</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.825368</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.155144</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.933771</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.182889</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>2.24497</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>1.3873</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.847023</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.217415</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.988231</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.213925</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>2.3069</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>1.42109</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.870138</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.306171</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.036658</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.247052</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>2.35997</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>1.4737</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.906923</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.382229</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.112057</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.299771</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>2.40639</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>1.51029</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0.926669</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.448756</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.164496</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.328071</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>2.47157</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>1.54622</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>0.956117</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.54217</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.21599</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.370274</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>2.51772</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>1.55892</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0.971294</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.608311</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.234191</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.392026</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>2.5697</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>1.59332</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0.9946430000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.682807</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.283492</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.425489</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>2.60997</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>1.63703</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>1.01903</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.74052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.346136</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.460439</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>2.64519</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>1.67726</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>1.03921</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.790996</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.403792</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.48936</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>2.73652</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>1.70213</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>1.07658</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.921888</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.439435</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.542918</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>2.81032</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>1.75589</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>1.10228</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.027655</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.516482</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.57975</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>2.85819</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>1.78632</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>1.11116</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.096261</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.560093</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.592477</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>2.93332</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>1.80596</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>1.12241</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.203935</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.588241</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.6086</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>2.97887</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>1.82209</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>1.14546</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.269215</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.611358</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.641634</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>3.0428</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>1.83782</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>1.16656</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.360838</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.633901</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.671874</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>3.10458</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>1.87153</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>1.17928</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.449379</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.682213</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.690104</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>3.16055</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>1.90541</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>1.18637</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.529593</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.730769</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.700265</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>3.20415</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>1.93686</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>1.1889</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.592079</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.775842</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.703891</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>3.25327</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>1.95255</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>1.20113</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.662476</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.798328</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.721419</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>3.29648</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>1.98273</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>1.21171</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.724403</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.841581</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.736582</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>3.35562</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2.03153</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>1.24036</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.809161</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.91152</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.777642</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>3.41401</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2.0432</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>1.25048</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.892843</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.928245</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.792145</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>3.47832</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>2.08247</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>1.26765</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.98501</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.984525</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.816753</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>3.52782</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>2.11012</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>1.26886</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.055952</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.024152</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.818487</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>3.57283</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>2.13003</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>1.28162</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.120459</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.052687</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.836774</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>3.61967</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>2.15116</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>1.29374</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.187588</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.082969</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.854144</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>3.67807</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>2.17461</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>1.31956</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.271285</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3.116577</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.891149</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>3.73513</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>2.19348</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>1.33983</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.353061</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.143621</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.920199</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>3.77826</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>2.22389</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>1.35912</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.414874</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.187204</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.947845</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>3.82179</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>2.25158</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>1.36612</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5.47726</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.226888</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.957877</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>3.85541</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>2.28056</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>1.37803</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5.525443</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.268421</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.974946</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>3.8919</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>2.31218</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>1.38899</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5.577739</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.313738</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.990653</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>3.94026</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>2.3232</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>1.39966</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5.647047</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.329531</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.005945</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>3.97807</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>2.33756</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>1.41277</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5.701235</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.350112</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.024734</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>4.01066</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>2.35868</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>1.44189</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5.747942</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.38038</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.066468</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>4.04855</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>2.3649</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>1.47372</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5.802244</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3.389294</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.112085</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>4.09999</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>2.39099</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>1.48617</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5.875966</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.426686</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.129928</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>4.15291</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>2.40506</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>1.50328</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5.95181</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3.44685</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.15445</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>4.1983</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>2.42384</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>1.53038</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6.016861</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3.473765</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.193289</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>4.22692</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>2.4331</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>1.54369</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.057878</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.487036</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.212364</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>4.26155</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>2.45561</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>1.55269</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6.107509</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.519297</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.225263</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>4.30147</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>2.47113</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>1.56403</v>
+      </c>
+      <c r="F77" t="n">
+        <v>6.164721</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.54154</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.241515</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>4.33258</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>2.48888</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>1.57682</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6.209307</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3.566978</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.259845</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>4.37244</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>2.5148</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>1.58776</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6.266433</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3.604126</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.275524</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>4.40686</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>1.60776</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.315762</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3.635942</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.304187</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>4.46063</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>2.54754</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>1.62079</v>
+      </c>
+      <c r="F81" t="n">
+        <v>6.392823</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.651048</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.322861</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>4.50323</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>2.55997</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>1.63519</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.453876</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.668862</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.343499</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>4.53929</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>2.58923</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>1.64838</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6.505556</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3.710797</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.362402</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>4.57438</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>2.59812</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>1.65518</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6.555846</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3.723537</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.372148</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>4.61799</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>2.60935</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>1.66138</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6.618346</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.739632</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.381033</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>4.64786</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>2.62626</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>1.68286</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6.661155</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3.763867</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.411818</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>4.66595</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>2.63919</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>1.69482</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6.687081</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3.782397</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.428958</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>328</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>4.70034</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>2.6565</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>1.7099</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6.736368</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3.807206</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.450571</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>4.73066</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>2.6697</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>1.71279</v>
+      </c>
+      <c r="F89" t="n">
+        <v>6.779821</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3.826123</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.454712</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>4.74206</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>2.68034</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>1.72079</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.796159</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3.841372</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.466178</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>4.77161</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>2.69703</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>1.73029</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6.838509</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.865292</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.479793</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>344</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>4.79355</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>2.72335</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>1.73832</v>
+      </c>
+      <c r="F92" t="n">
+        <v>6.869953</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3.903013</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.491301</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>348</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>4.82584</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>2.73515</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>1.75096</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6.91623</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3.919924</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.509416</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>352</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>4.85182</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>2.75292</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>1.76108</v>
+      </c>
+      <c r="F94" t="n">
+        <v>6.953464</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.945391</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.52392</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>356</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>4.89659</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>2.79243</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>1.77134</v>
+      </c>
+      <c r="F95" t="n">
+        <v>7.017627</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.002016</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.538624</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>4.94155</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>2.81148</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>1.78018</v>
+      </c>
+      <c r="F96" t="n">
+        <v>7.082062</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4.029318</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.551294</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>364</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>4.97182</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>2.82915</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>1.78755</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7.125444</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4.054642</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.561856</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>368</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>4.99816</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>2.85956</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>1.79737</v>
+      </c>
+      <c r="F98" t="n">
+        <v>7.163193</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4.098224</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.57593</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>372</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>5.03552</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>2.8711</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>1.80363</v>
+      </c>
+      <c r="F99" t="n">
+        <v>7.216736</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4.114763</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.584901</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>5.08052</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>2.88517</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>1.80754</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7.281229</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4.134928</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.590505</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>5.11113</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>2.89351</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>1.81685</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7.325098</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4.14688</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.603848</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>5.12218</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>2.91007</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>1.82533</v>
+      </c>
+      <c r="F102" t="n">
+        <v>7.340934</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4.170614</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.616001</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>5.14714</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>2.91719</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>1.83871</v>
+      </c>
+      <c r="F103" t="n">
+        <v>7.376706</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.180818</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.635177</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>5.17286</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>2.92759</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>1.84555</v>
+      </c>
+      <c r="F104" t="n">
+        <v>7.413567</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4.195723</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.64498</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>396</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>5.20512</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>2.95142</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>1.85358</v>
+      </c>
+      <c r="F105" t="n">
+        <v>7.459801</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4.229875</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2.656488</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>5.22893</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>2.96825</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>1.86463</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7.493925</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4.253995</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2.672324</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>5.25092</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>2.97465</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>1.87113</v>
+      </c>
+      <c r="F107" t="n">
+        <v>7.52544</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4.263167</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.68164</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>5.27132</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>2.98175</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>1.88195</v>
+      </c>
+      <c r="F108" t="n">
+        <v>7.554677</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4.273343</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.697147</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>5.30532</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>2.99276</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>1.89103</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7.603404</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4.289122</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.71016</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>5.3332</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>3.00508</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>1.90702</v>
+      </c>
+      <c r="F110" t="n">
+        <v>7.643361</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4.306779</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.733076</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>5.36758</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>3.01138</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>1.91116</v>
+      </c>
+      <c r="F111" t="n">
+        <v>7.692633</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4.315808</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.73901</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>5.41861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>3.03621</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>1.92445</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7.765768</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4.351393</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2.758056</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>428</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>5.45465</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>3.04562</v>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>1.92549</v>
+      </c>
+      <c r="F113" t="n">
+        <v>7.817419</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.364879</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2.759547</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>432</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>5.50073</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>3.05595</v>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>1.92831</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7.883459</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4.379684</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.763588</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>436</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>5.52596</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>3.05928</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>1.94251</v>
+      </c>
+      <c r="F115" t="n">
+        <v>7.919618</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4.384456</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.783939</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>5.55298</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>3.06697</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>1.94991</v>
+      </c>
+      <c r="F116" t="n">
+        <v>7.958342</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4.395477</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2.794545</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>5.60693</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>3.08553</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>1.97145</v>
+      </c>
+      <c r="F117" t="n">
+        <v>8.035662</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4.422077</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.825415</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>448</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>5.65747</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>3.10812</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>1.98139</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8.108093999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4.454452</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.839661</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>452</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>5.67797</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>3.13272</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>1.99337</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8.137473999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4.489708</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2.85683</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>456</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>3.14554</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>1.99918</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8.164747</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4.508081</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.865157</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>5.73482</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>3.1531</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>2.0158</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8.218949</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4.518916</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2.888976</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>464</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>5.75743</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>3.17696</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>2.02218</v>
+      </c>
+      <c r="F122" t="n">
+        <v>8.251353</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4.553111</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.89812</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>468</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>5.79351</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>3.21039</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>2.02788</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8.303062000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4.601022</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.906289</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>472</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>5.82756</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>3.22596</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>2.0376</v>
+      </c>
+      <c r="F124" t="n">
+        <v>8.351861</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4.623336</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.920219</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>476</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>5.85759</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>3.26108</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>2.04163</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8.394899000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.673669</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.925995</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>5.88906</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>3.27706</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>2.05258</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8.440001000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4.696571</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.941688</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>484</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>5.91451</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>3.29017</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>2.0558</v>
+      </c>
+      <c r="F127" t="n">
+        <v>8.476475000000001</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.71536</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.946303</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>488</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>5.94948</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>3.30571</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>2.06382</v>
+      </c>
+      <c r="F128" t="n">
+        <v>8.526593</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.737631</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2.957797</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>492</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>5.98072</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>3.32532</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>2.07587</v>
+      </c>
+      <c r="F129" t="n">
+        <v>8.571365</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4.765736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.975066</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>496</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>6.0107</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>3.33743</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>2.07942</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8.614331</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4.783091</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.980154</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>6.03806</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>3.34429</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>2.0857</v>
+      </c>
+      <c r="F131" t="n">
+        <v>8.653543000000001</v>
+      </c>
+      <c r="G131" t="n">
+        <v>4.792923</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.989154</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>6.07544</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>3.34953</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>2.09229</v>
+      </c>
+      <c r="F132" t="n">
+        <v>8.707114000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4.800433</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.998599</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>508</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>6.1188</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>3.35795</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>2.09723</v>
+      </c>
+      <c r="F133" t="n">
+        <v>8.769256</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4.8125</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3.005679</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>6.15302</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>3.37021</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>2.10204</v>
+      </c>
+      <c r="F134" t="n">
+        <v>8.818299</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.830071</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3.012572</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>516</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>6.18416</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>3.38754</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>2.10633</v>
+      </c>
+      <c r="F135" t="n">
+        <v>8.862928</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4.854907</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3.018721</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>520</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>6.20527</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>3.40369</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>2.12309</v>
+      </c>
+      <c r="F136" t="n">
+        <v>8.893181999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4.878053</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3.04274</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>524</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>6.2356</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>3.42603</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>2.13156</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8.93665</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4.91007</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3.054879</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>528</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>6.27085</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>3.4389</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>2.13618</v>
+      </c>
+      <c r="F138" t="n">
+        <v>8.987169</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4.928515</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3.061501</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>532</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>6.28381</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>3.46211</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>2.14776</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9.005743000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4.961778</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3.078097</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>536</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>6.32791</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>3.48009</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>2.15405</v>
+      </c>
+      <c r="F140" t="n">
+        <v>9.068946</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4.987547</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3.087111</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>540</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>6.34313</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>3.49388</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>2.16547</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.090759</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5.00731</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3.103478</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>544</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>6.36937</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>3.50471</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>2.18451</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9.128365000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5.022831</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3.130766</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>548</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>6.38234</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>3.52631</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>2.19587</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9.146953</v>
+      </c>
+      <c r="G143" t="n">
+        <v>5.053788</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3.147046</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>552</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>6.41694</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>3.53858</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>2.19672</v>
+      </c>
+      <c r="F144" t="n">
+        <v>9.196540000000001</v>
+      </c>
+      <c r="G144" t="n">
+        <v>5.071373</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3.148265</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>556</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>6.45426</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>3.54395</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>2.19802</v>
+      </c>
+      <c r="F145" t="n">
+        <v>9.250026</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5.079069</v>
+      </c>
+      <c r="H145" t="n">
+        <v>3.150128</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>560</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>6.49832</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>3.56249</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>2.20926</v>
+      </c>
+      <c r="F146" t="n">
+        <v>9.313172</v>
+      </c>
+      <c r="G146" t="n">
+        <v>5.10564</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3.166236</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>564</v>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>6.51171</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>3.56633</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>2.21202</v>
+      </c>
+      <c r="F147" t="n">
+        <v>9.332362</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5.111143</v>
+      </c>
+      <c r="H147" t="n">
+        <v>3.170192</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>568</v>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>6.52668</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>3.59267</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>2.21616</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9.353816</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5.148893</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3.176125</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>572</v>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>6.55212</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>3.6038</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>2.21984</v>
+      </c>
+      <c r="F149" t="n">
+        <v>9.390276</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5.164844</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3.181399</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>576</v>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>6.58663</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>3.62273</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>2.22157</v>
+      </c>
+      <c r="F150" t="n">
+        <v>9.439734</v>
+      </c>
+      <c r="G150" t="n">
+        <v>5.191974</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3.183879</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>6.62781</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>3.63244</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>2.2274</v>
+      </c>
+      <c r="F151" t="n">
+        <v>9.498752</v>
+      </c>
+      <c r="G151" t="n">
+        <v>5.20589</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3.192234</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>584</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>6.65774</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>3.64573</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>2.23246</v>
+      </c>
+      <c r="F152" t="n">
+        <v>9.541646999999999</v>
+      </c>
+      <c r="G152" t="n">
+        <v>5.224936</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3.199486</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>588</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>6.67469</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>3.65642</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>2.23821</v>
+      </c>
+      <c r="F153" t="n">
+        <v>9.565939</v>
+      </c>
+      <c r="G153" t="n">
+        <v>5.240257</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3.207727</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>592</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>6.72658</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>3.67105</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>2.24165</v>
+      </c>
+      <c r="F154" t="n">
+        <v>9.640306000000001</v>
+      </c>
+      <c r="G154" t="n">
+        <v>5.261224</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3.212657</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>596</v>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>6.75674</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>3.68722</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>2.26331</v>
+      </c>
+      <c r="F155" t="n">
+        <v>9.683529999999999</v>
+      </c>
+      <c r="G155" t="n">
+        <v>5.284398</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3.243699</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>6.7944</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>3.69438</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>2.26769</v>
+      </c>
+      <c r="F156" t="n">
+        <v>9.737503</v>
+      </c>
+      <c r="G156" t="n">
+        <v>5.29466</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3.249976</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>604</v>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>6.81633</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>3.70234</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>2.26999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>9.768933000000001</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5.306068</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3.253273</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>608</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>6.84222</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>3.71284</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>2.27729</v>
+      </c>
+      <c r="F158" t="n">
+        <v>9.806037</v>
+      </c>
+      <c r="G158" t="n">
+        <v>5.321116</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.263735</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>612</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>6.85846</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>3.72527</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>2.28083</v>
+      </c>
+      <c r="F159" t="n">
+        <v>9.829312</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5.33893</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3.268808</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>616</v>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>6.899</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>3.73775</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>2.28603</v>
+      </c>
+      <c r="F160" t="n">
+        <v>9.887413</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5.356816</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.276261</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>620</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>6.91603</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>3.75859</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>2.29873</v>
+      </c>
+      <c r="F161" t="n">
+        <v>9.911818999999999</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5.386684</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3.294462</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>624</v>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>6.93709</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>3.75859</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>2.30178</v>
+      </c>
+      <c r="F162" t="n">
+        <v>9.942002</v>
+      </c>
+      <c r="G162" t="n">
+        <v>5.386684</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.298833</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>628</v>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>6.95773</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>3.77672</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>2.3095</v>
+      </c>
+      <c r="F163" t="n">
+        <v>9.971582</v>
+      </c>
+      <c r="G163" t="n">
+        <v>5.412667</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3.309897</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>632</v>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>6.98908</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>3.79122</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>2.3119</v>
+      </c>
+      <c r="F164" t="n">
+        <v>10.016512</v>
+      </c>
+      <c r="G164" t="n">
+        <v>5.433448</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.313337</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>636</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>7.01598</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>3.8009</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>2.31952</v>
+      </c>
+      <c r="F165" t="n">
+        <v>10.055064</v>
+      </c>
+      <c r="G165" t="n">
+        <v>5.447321</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3.324257</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>640</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>7.03678</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>3.81442</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="F166" t="n">
+        <v>10.084874</v>
+      </c>
+      <c r="G166" t="n">
+        <v>5.466697</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3.329402</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>644</v>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>7.06777</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>3.8163</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="F167" t="n">
+        <v>10.129288</v>
+      </c>
+      <c r="G167" t="n">
+        <v>5.469392</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3.329402</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>648</v>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>7.09127</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>3.82387</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>2.33373</v>
+      </c>
+      <c r="F168" t="n">
+        <v>10.162967</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5.480241</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3.344623</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>652</v>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>7.10701</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>3.82989</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>2.33651</v>
+      </c>
+      <c r="F169" t="n">
+        <v>10.185525</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5.488868</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3.348607</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>656</v>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>7.1384</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>3.8345</v>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>2.35189</v>
+      </c>
+      <c r="F170" t="n">
+        <v>10.230512</v>
+      </c>
+      <c r="G170" t="n">
+        <v>5.495475</v>
+      </c>
+      <c r="H170" t="n">
+        <v>3.370649</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>660</v>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>7.16067</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>3.85259</v>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>2.36081</v>
+      </c>
+      <c r="F171" t="n">
+        <v>10.262429</v>
+      </c>
+      <c r="G171" t="n">
+        <v>5.521401</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3.383433</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>7.19842</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>3.86081</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>2.3658</v>
+      </c>
+      <c r="F172" t="n">
+        <v>10.316531</v>
+      </c>
+      <c r="G172" t="n">
+        <v>5.533182</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3.390584</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>668</v>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>7.22158</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>3.87308</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>2.36887</v>
+      </c>
+      <c r="F173" t="n">
+        <v>10.349723</v>
+      </c>
+      <c r="G173" t="n">
+        <v>5.550767</v>
+      </c>
+      <c r="H173" t="n">
+        <v>3.394984</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>672</v>
+      </c>
+      <c r="B174" s="1" t="n">
+        <v>7.24102</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>3.88343</v>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>2.38034</v>
+      </c>
+      <c r="F174" t="n">
+        <v>10.377584</v>
+      </c>
+      <c r="G174" t="n">
+        <v>5.5656</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3.411422</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>(b) Final (672h) mass loss vs. SA/V ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>Strut thickness (mm)</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>SA/V ratio (mm^-1)</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>Final (672h) mass loss (%)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Final (672h) mass loss, scaled x1.4332 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>thin_sav</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>48.2123</v>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>7.24102</v>
+      </c>
+      <c r="E178" t="n">
+        <v>10.37758</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>mid_sav</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>24.1062</v>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>3.88343</v>
+      </c>
+      <c r="E179" t="n">
+        <v>5.5656</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>thick_sav</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>16.0708</v>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>2.38034</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3.41142</v>
       </c>
     </row>
   </sheetData>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -18,12 +18,12 @@
     <sheet name="Figure 8b" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Figure 8c" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Figure 8d" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Supplementary Figure 1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Supplementary Figure 3" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Supplementary Figure 4" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Supplementary Figure 5" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Supplementary Figure 3" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Supplementary Figure 5" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Supplementary Figure 6b" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Supplementary Figure 9c,d" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Supplementary Figure 7" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Supplementary Figure 9" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Supplementary Figure 9a,b" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7548,7 +7548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Figure 1</t>
+          <t>Supplementary Figure 3</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Figure 3</t>
+          <t>Supplementary Figure 5</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Figure 4</t>
+          <t>Supplementary Figure 6b</t>
         </is>
       </c>
     </row>
@@ -9043,11 +9043,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Note: this run has 32 total iterations, global optimum at iteration 22 (RMSE=0.0424%, matching Figure 3b / main text). The supplementary caption text referencing iterations 45-48 is from a different/earlier calibration run; revise the caption to match this dataset (or supply the 45-48-iteration run if that is the one intended for publication).</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9833,38 +9829,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5</t>
+          <t>Final (672 h) mass loss as a function of controlled geometric parameters: (c) wire curvature (1/R), (d) adjacent-strut center-to-center spacing. Rule A (hard minimum), BO-calibrated kinetics, coarse mesh, same protocol across both studies.</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Final (672 h) mass loss as a function of controlled geometric parameters: (a) disc surface-area-to-volume ratio, (b) wire curvature (1/R), (c) adjacent-strut center-to-center spacing. Rule A (hard minimum), BO-calibrated kinetics, coarse mesh, same protocol across all three studies.</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>(a) SA/V ratio study</t>
+          <t>(c) Wire curvature study</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>(b) Wire curvature study</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>(c) Adjacent-strut spacing study</t>
+          <t>(d) Adjacent-strut spacing study</t>
         </is>
       </c>
     </row>
@@ -9876,27 +9861,27 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>SA/V ratio (mm^-1)</t>
+          <t>Radius (mm)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Curvature 1/R (mm^-1)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Final (672h) mass loss (%)</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Radius (mm)</t>
-        </is>
-      </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>Curvature 1/R (mm^-1)</t>
+          <t>Center-to-center spacing (mm)</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
@@ -9904,136 +9889,88 @@
           <t>Final (672h) mass loss (%)</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>Center-to-center spacing (mm)</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>Final (672h) mass loss (%)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>low_sav</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1.0714</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0.249715</v>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
           <t>StraightWire</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>5.5656</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>CloseGap_CC0.30mm</t>
         </is>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>4.71794</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>mid_sav</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.333439</v>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
           <t>Arc30deg</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="B7" s="1" t="n">
         <v>3.15</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="C7" s="1" t="n">
         <v>0.31746</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>5.629654</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>FarGap_CC1.60mm</t>
         </is>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>5.2656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>high_sav</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>2.4889</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0.572428</v>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
           <t>Arc90deg</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="B8" s="1" t="n">
         <v>1.05</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="C8" s="1" t="n">
         <v>0.952381</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>5.858692</v>
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Arc150deg</t>
         </is>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="B9" s="1" t="n">
         <v>0.63</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="C9" s="1" t="n">
         <v>1.587302</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>5.981674</v>
       </c>
     </row>
@@ -15092,14 +15029,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9</t>
+          <t>Supplementary Figure 9a,b</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study (Supplementary Figure 5a). Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
+          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study. Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
         </is>
       </c>
     </row>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -9832,7 +9832,13 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Supplementary Figure 9c,d</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -9840,7 +9846,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -25671,7 +25671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD678"/>
+  <dimension ref="A1:AK678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="21" max="21"/>
@@ -25684,6 +25684,12 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
     <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25763,6 +25769,11 @@
           <t>Experimental replicates (measured specimens, n=3 per time point)</t>
         </is>
       </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Regime control: Damkohler number and regime classification</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -25872,6 +25883,36 @@
           <t>SD (mg)</t>
         </is>
       </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>vO2React (mm/h)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>vO2Diff (mm/h)</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>Damkohler number Da</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>O2-diffusion-limited surface (%)</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>Regime (surface share)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -25945,6 +25986,23 @@
       <c r="AD6" t="n">
         <v>0.153</v>
       </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>NotYetComputed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -26018,6 +26076,26 @@
       <c r="AD7" t="n">
         <v>0.4</v>
       </c>
+      <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.5e-05</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.00018082</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0829554</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.81168</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -26091,6 +26169,26 @@
       <c r="AD8" t="n">
         <v>0.764</v>
       </c>
+      <c r="AF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.48981e-05</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-4.02089e-05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.370518</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16.8586</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -26164,6 +26262,26 @@
       <c r="AD9" t="n">
         <v>0.737</v>
       </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.4797e-05</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-2.22254e-05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.665768</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18.9365</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -26222,6 +26340,26 @@
       <c r="AD10" t="n">
         <v>1.328</v>
       </c>
+      <c r="AF10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.46965e-05</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1.44487e-05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.01715</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>25.3998</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -26260,6 +26398,26 @@
           <t>Mass loss (%) = (initial - final weight)/initial weight x 100; SD = sample SD (n-1). Pure Zn disc, HBSS, 37 C. Matches Table 3.</t>
         </is>
       </c>
+      <c r="AF11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-1.45967e-05</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.02942e-05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.41795</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>33.1663</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -26289,6 +26447,26 @@
       <c r="P12" s="1" t="n">
         <v>0.0159</v>
       </c>
+      <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.44976e-05</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-7.82006e-06</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.85389</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>41.9713</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -26316,6 +26494,26 @@
       <c r="P13" s="1" t="n">
         <v>8.58</v>
       </c>
+      <c r="AF13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-1.43991e-05</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-6.24199e-06</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.30681</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>51.3187</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -26338,6 +26536,26 @@
       <c r="P14" s="1" t="n">
         <v>0.9734</v>
       </c>
+      <c r="AF14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-1.43013e-05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-5.18581e-06</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.75778</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>60.5738</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -26357,6 +26575,26 @@
           <t>Error (%) = (Sim - Exp)/Exp x 100 (signed). Relative RMSE = RMSE / mean(Exp) x 100. n = 5 time points.</t>
         </is>
       </c>
+      <c r="AF15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.42042e-05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-4.45297e-06</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.18983</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>69.1285</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -26371,6 +26609,26 @@
       <c r="D16" s="1" t="n">
         <v>0.1231313538342954</v>
       </c>
+      <c r="AF16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-1.41078e-05</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-3.9299e-06</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.58985</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>99.5321</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -26385,6 +26643,26 @@
       <c r="D17" s="1" t="n">
         <v>0.1235321314044198</v>
       </c>
+      <c r="AF17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-1.4012e-05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-3.54672e-06</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.95068</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>99.5685</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -26399,6 +26677,26 @@
       <c r="D18" s="1" t="n">
         <v>0.1238339079555154</v>
       </c>
+      <c r="AF18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-1.39168e-05</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-3.25304e-06</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.27809</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>99.61320000000001</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -26413,6 +26711,26 @@
       <c r="D19" s="1" t="n">
         <v>0.1240254217468656</v>
       </c>
+      <c r="AF19" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1.38223e-05</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-3.0276e-06</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.56543</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>99.65470000000001</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -26427,6 +26745,26 @@
       <c r="D20" s="1" t="n">
         <v>0.1240894832507529</v>
       </c>
+      <c r="AF20" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.37284e-05</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-2.85897e-06</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.80189</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>99.6913</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -26441,6 +26779,26 @@
       <c r="D21" s="1" t="n">
         <v>0.1240118522378651</v>
       </c>
+      <c r="AF21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.36352e-05</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-2.73556e-06</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.98443</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>99.7235</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -26455,6 +26813,26 @@
       <c r="D22" s="1" t="n">
         <v>0.1237820992815037</v>
       </c>
+      <c r="AF22" t="n">
+        <v>64</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-1.35426e-05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-2.64308e-06</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.12381</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>99.7525</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -26469,6 +26847,26 @@
       <c r="D23" s="1" t="n">
         <v>0.1233955996827052</v>
       </c>
+      <c r="AF23" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-1.34507e-05</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-2.57092e-06</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.23184</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>99.7804</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -26483,6 +26881,26 @@
       <c r="D24" s="1" t="n">
         <v>0.1228584881388688</v>
       </c>
+      <c r="AF24" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-1.33593e-05</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-2.5138e-06</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.31439</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>99.80670000000001</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -26497,6 +26915,26 @@
       <c r="D25" s="1" t="n">
         <v>0.1221787452775384</v>
       </c>
+      <c r="AF25" t="n">
+        <v>76</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-1.32686e-05</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-2.46799e-06</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.37629</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>99.82850000000001</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -26511,6 +26949,26 @@
       <c r="D26" s="1" t="n">
         <v>0.1213637245757375</v>
       </c>
+      <c r="AF26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-1.31785e-05</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-2.43081e-06</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.42144</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>99.84699999999999</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -26525,6 +26983,26 @@
       <c r="D27" s="1" t="n">
         <v>0.1204272510841864</v>
       </c>
+      <c r="AF27" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-1.3089e-05</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-2.40032e-06</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.45301</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>99.8647</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -26539,6 +27017,26 @@
       <c r="D28" s="1" t="n">
         <v>0.1194131562024102</v>
       </c>
+      <c r="AF28" t="n">
+        <v>88</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-1.30001e-05</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-2.37509e-06</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.47353</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>99.8776</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -26553,6 +27051,26 @@
       <c r="D29" s="1" t="n">
         <v>0.1183655353721301</v>
       </c>
+      <c r="AF29" t="n">
+        <v>92</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-1.29118e-05</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-2.35402e-06</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>5.48502</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>99.88849999999999</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -26567,6 +27085,26 @@
       <c r="D30" s="1" t="n">
         <v>0.1173216363539563</v>
       </c>
+      <c r="AF30" t="n">
+        <v>96</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-1.28242e-05</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-2.33629e-06</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.48911</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>99.90049999999999</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -26581,6 +27119,26 @@
       <c r="D31" s="1" t="n">
         <v>0.1163081869633094</v>
       </c>
+      <c r="AF31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-1.27371e-05</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-2.32126e-06</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.48714</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>99.9123</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -26595,6 +27153,26 @@
       <c r="D32" s="1" t="n">
         <v>0.1153302643339966</v>
       </c>
+      <c r="AF32" t="n">
+        <v>104</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-1.26506e-05</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-2.30844e-06</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.48015</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>99.92149999999999</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -26609,6 +27187,26 @@
       <c r="D33" s="1" t="n">
         <v>0.114388645785176</v>
       </c>
+      <c r="AF33" t="n">
+        <v>108</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-1.25647e-05</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-2.29743e-06</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>5.46902</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>99.93129999999999</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -26623,6 +27221,26 @@
       <c r="D34" s="1" t="n">
         <v>0.1134837162942553</v>
       </c>
+      <c r="AF34" t="n">
+        <v>112</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-1.24793e-05</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-2.28792e-06</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.45444</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>99.93899999999999</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -26637,6 +27255,26 @@
       <c r="D35" s="1" t="n">
         <v>0.1126178495617659</v>
       </c>
+      <c r="AF35" t="n">
+        <v>116</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-1.23946e-05</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-2.27967e-06</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5.43701</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>99.94750000000001</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -26651,6 +27289,26 @@
       <c r="D36" s="1" t="n">
         <v>0.1117997089875733</v>
       </c>
+      <c r="AF36" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-1.23104e-05</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-2.27248e-06</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.41718</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>99.95440000000001</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -26665,6 +27323,26 @@
       <c r="D37" s="1" t="n">
         <v>0.1110400528034714</v>
       </c>
+      <c r="AF37" t="n">
+        <v>124</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-1.22268e-05</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>-2.26618e-06</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.39536</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>99.9601</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -26679,6 +27357,26 @@
       <c r="D38" s="1" t="n">
         <v>0.1103466271593397</v>
       </c>
+      <c r="AF38" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-1.21438e-05</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-2.26063e-06</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.37187</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>99.9649</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -26693,6 +27391,26 @@
       <c r="D39" s="1" t="n">
         <v>0.1097205986317153</v>
       </c>
+      <c r="AF39" t="n">
+        <v>132</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-1.20613e-05</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-2.25573e-06</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.34698</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>99.9688</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -26707,6 +27425,26 @@
       <c r="D40" s="1" t="n">
         <v>0.1091328583492951</v>
       </c>
+      <c r="AF40" t="n">
+        <v>136</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>-1.19794e-05</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>-2.25138e-06</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.32092</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>99.971</v>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -26721,6 +27459,26 @@
       <c r="D41" s="1" t="n">
         <v>0.1085510121743906</v>
       </c>
+      <c r="AF41" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>-1.18981e-05</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>-2.24752e-06</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.29388</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>99.97239999999999</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -26735,6 +27493,26 @@
       <c r="D42" s="1" t="n">
         <v>0.1079458151702543</v>
       </c>
+      <c r="AF42" t="n">
+        <v>144</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>-1.18173e-05</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-2.24407e-06</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>5.26602</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>99.974</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -26749,6 +27527,26 @@
       <c r="D43" s="1" t="n">
         <v>0.1073001618543659</v>
       </c>
+      <c r="AF43" t="n">
+        <v>148</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>-1.1737e-05</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>-2.24097e-06</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>5.23748</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>99.9752</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -26763,6 +27561,26 @@
       <c r="D44" s="1" t="n">
         <v>0.1066290900331442</v>
       </c>
+      <c r="AF44" t="n">
+        <v>152</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>-1.16573e-05</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>-2.2382e-06</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>5.20837</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>99.9759</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -26777,6 +27595,26 @@
       <c r="D45" s="1" t="n">
         <v>0.1059546719306844</v>
       </c>
+      <c r="AF45" t="n">
+        <v>156</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>-1.15782e-05</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>-2.23569e-06</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>5.17879</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>99.9769</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -26791,6 +27629,26 @@
       <c r="D46" s="1" t="n">
         <v>0.1052963957719576</v>
       </c>
+      <c r="AF46" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>-1.14996e-05</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>-2.23343e-06</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>5.14883</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>99.9778</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -26805,6 +27663,26 @@
       <c r="D47" s="1" t="n">
         <v>0.1046694585321525</v>
       </c>
+      <c r="AF47" t="n">
+        <v>164</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>-1.14215e-05</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>-2.23138e-06</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>5.11855</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>99.9785</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -26819,6 +27697,26 @@
       <c r="D48" s="1" t="n">
         <v>0.1040735468549181</v>
       </c>
+      <c r="AF48" t="n">
+        <v>168</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-1.13439e-05</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>-2.22953e-06</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>5.08803</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>99.97920000000001</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -26833,6 +27731,26 @@
       <c r="D49" s="1" t="n">
         <v>0.1035060759143579</v>
       </c>
+      <c r="AF49" t="n">
+        <v>172</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>-1.12669e-05</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>-2.22784e-06</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>5.05732</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -26847,6 +27765,26 @@
       <c r="D50" s="1" t="n">
         <v>0.1029638654141289</v>
       </c>
+      <c r="AF50" t="n">
+        <v>176</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>-1.11904e-05</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>-2.22629e-06</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>5.02645</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>99.9806</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -26861,6 +27799,26 @@
       <c r="D51" s="1" t="n">
         <v>0.1024429444577545</v>
       </c>
+      <c r="AF51" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>-1.11144e-05</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>-2.22488e-06</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>4.99548</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>99.98180000000001</v>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -26875,6 +27833,26 @@
       <c r="D52" s="1" t="n">
         <v>0.1019289328018456</v>
       </c>
+      <c r="AF52" t="n">
+        <v>184</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>-1.10389e-05</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>-2.22359e-06</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>4.96444</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>99.9823</v>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -26889,6 +27867,26 @@
       <c r="D53" s="1" t="n">
         <v>0.1014080761625971</v>
       </c>
+      <c r="AF53" t="n">
+        <v>188</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-1.09639e-05</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>-2.22241e-06</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>4.93335</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>99.9828</v>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -26903,6 +27901,26 @@
       <c r="D54" s="1" t="n">
         <v>0.1008669688875111</v>
       </c>
+      <c r="AF54" t="n">
+        <v>192</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>-1.08895e-05</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>-2.22132e-06</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>4.90225</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>99.9832</v>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -26917,6 +27935,26 @@
       <c r="D55" s="1" t="n">
         <v>0.1002989122045029</v>
       </c>
+      <c r="AF55" t="n">
+        <v>196</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-1.08155e-05</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>-2.22032e-06</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>4.87116</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>99.9834</v>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -26931,6 +27969,26 @@
       <c r="D56" s="1" t="n">
         <v>0.09972222949425953</v>
       </c>
+      <c r="AF56" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-1.07421e-05</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>-2.2194e-06</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4.84009</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>99.9834</v>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -26945,6 +28003,26 @@
       <c r="D57" s="1" t="n">
         <v>0.09915923256847266</v>
       </c>
+      <c r="AF57" t="n">
+        <v>204</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-1.06691e-05</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>-2.21854e-06</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4.80908</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>99.9833</v>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -26959,6 +28037,26 @@
       <c r="D58" s="1" t="n">
         <v>0.098630942852046</v>
       </c>
+      <c r="AF58" t="n">
+        <v>208</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-1.05967e-05</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>-2.21775e-06</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>4.77812</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>99.9834</v>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -26973,6 +28071,26 @@
       <c r="D59" s="1" t="n">
         <v>0.0981508134539094</v>
       </c>
+      <c r="AF59" t="n">
+        <v>212</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-1.05247e-05</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>-2.21702e-06</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>4.74724</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>99.9833</v>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -26987,6 +28105,26 @@
       <c r="D60" s="1" t="n">
         <v>0.09771411145470539</v>
       </c>
+      <c r="AF60" t="n">
+        <v>216</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-1.04533e-05</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>-2.21634e-06</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>4.71645</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>99.9837</v>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -27001,6 +28139,26 @@
       <c r="D61" s="1" t="n">
         <v>0.0973106579992216</v>
       </c>
+      <c r="AF61" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>-1.03823e-05</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>-2.21571e-06</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>4.68575</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>99.98390000000001</v>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -27015,6 +28173,26 @@
       <c r="D62" s="1" t="n">
         <v>0.09693178568761178</v>
       </c>
+      <c r="AF62" t="n">
+        <v>224</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>-1.03118e-05</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>-2.21512e-06</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>4.65516</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>99.9841</v>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -27029,6 +28207,26 @@
       <c r="D63" s="1" t="n">
         <v>0.09656876836882189</v>
       </c>
+      <c r="AF63" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>-1.02417e-05</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>-2.21458e-06</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>4.62469</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>99.9842</v>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -27043,6 +28241,26 @@
       <c r="D64" s="1" t="n">
         <v>0.09621196842422147</v>
       </c>
+      <c r="AF64" t="n">
+        <v>232</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>-1.01722e-05</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>-2.21407e-06</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>4.59435</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>99.9841</v>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -27057,6 +28275,26 @@
       <c r="D65" s="1" t="n">
         <v>0.0958529072251585</v>
       </c>
+      <c r="AF65" t="n">
+        <v>236</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>-1.01031e-05</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>-2.21359e-06</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>4.56413</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>99.98399999999999</v>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -27071,6 +28309,26 @@
       <c r="D66" s="1" t="n">
         <v>0.09548368957349142</v>
       </c>
+      <c r="AF66" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>-1.00345e-05</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>-2.21315e-06</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>4.53405</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>99.9838</v>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -27085,6 +28343,26 @@
       <c r="D67" s="1" t="n">
         <v>0.09509904665700883</v>
       </c>
+      <c r="AF67" t="n">
+        <v>244</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>-9.96637e-06</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>-2.21273e-06</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>4.50411</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>99.9836</v>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -27099,6 +28377,26 @@
       <c r="D68" s="1" t="n">
         <v>0.09470579067421878</v>
       </c>
+      <c r="AF68" t="n">
+        <v>248</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>-9.89869e-06</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>-2.21234e-06</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>4.47431</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>99.9836</v>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -27113,6 +28411,26 @@
       <c r="D69" s="1" t="n">
         <v>0.09431310051574124</v>
       </c>
+      <c r="AF69" t="n">
+        <v>252</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>-9.83147e-06</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>-2.21197e-06</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>4.44466</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>99.9837</v>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -27127,6 +28445,26 @@
       <c r="D70" s="1" t="n">
         <v>0.09392997805670734</v>
       </c>
+      <c r="AF70" t="n">
+        <v>256</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>-9.764710000000001e-06</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>-2.21163e-06</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>4.41517</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>99.98390000000001</v>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -27141,6 +28479,26 @@
       <c r="D71" s="1" t="n">
         <v>0.09356137035534468</v>
       </c>
+      <c r="AF71" t="n">
+        <v>260</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>-9.6984e-06</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>-2.2113e-06</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>4.38583</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>99.98390000000001</v>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -27155,6 +28513,26 @@
       <c r="D72" s="1" t="n">
         <v>0.09320151171390739</v>
       </c>
+      <c r="AF72" t="n">
+        <v>264</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>-9.632540000000001e-06</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>-2.211e-06</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>4.35664</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>99.98399999999999</v>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -27169,6 +28547,26 @@
       <c r="D73" s="1" t="n">
         <v>0.09284271134072715</v>
       </c>
+      <c r="AF73" t="n">
+        <v>268</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>-9.567130000000001e-06</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>-2.21071e-06</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>4.32762</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>99.9841</v>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -27183,6 +28581,26 @@
       <c r="D74" s="1" t="n">
         <v>0.09247697085479535</v>
       </c>
+      <c r="AF74" t="n">
+        <v>272</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>-9.502159999999999e-06</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>-2.21044e-06</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>4.29876</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>99.9841</v>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -27197,6 +28615,26 @@
       <c r="D75" s="1" t="n">
         <v>0.09209961654602945</v>
       </c>
+      <c r="AF75" t="n">
+        <v>276</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>-9.43763e-06</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>-2.21019e-06</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>4.27006</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>99.98399999999999</v>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -27211,6 +28649,26 @@
       <c r="D76" s="1" t="n">
         <v>0.09171379883304261</v>
       </c>
+      <c r="AF76" t="n">
+        <v>280</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>-9.373549999999999e-06</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>-2.20995e-06</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>4.24152</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>99.98390000000001</v>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -27225,6 +28683,26 @@
       <c r="D77" s="1" t="n">
         <v>0.09132490757534896</v>
       </c>
+      <c r="AF77" t="n">
+        <v>284</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>-9.30989e-06</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>-2.20972e-06</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>4.21315</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>99.9836</v>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -27239,6 +28717,26 @@
       <c r="D78" s="1" t="n">
         <v>0.09093803483082658</v>
       </c>
+      <c r="AF78" t="n">
+        <v>288</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>-9.24667e-06</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>-2.20951e-06</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>4.18495</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>99.98269999999999</v>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -27253,6 +28751,26 @@
       <c r="D79" s="1" t="n">
         <v>0.09055845680085915</v>
       </c>
+      <c r="AF79" t="n">
+        <v>292</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>-9.183880000000001e-06</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>-2.2093e-06</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>4.15691</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>99.9823</v>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -27267,6 +28785,26 @@
       <c r="D80" s="1" t="n">
         <v>0.09019112662327873</v>
       </c>
+      <c r="AF80" t="n">
+        <v>296</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>-9.12151e-06</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>-2.20911e-06</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>4.12905</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>99.982</v>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -27281,6 +28819,26 @@
       <c r="D81" s="1" t="n">
         <v>0.08984043797640451</v>
       </c>
+      <c r="AF81" t="n">
+        <v>300</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>-9.05957e-06</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>-2.20893e-06</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>4.10135</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>99.98180000000001</v>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -27295,6 +28853,26 @@
       <c r="D82" s="1" t="n">
         <v>0.08951091532630005</v>
       </c>
+      <c r="AF82" t="n">
+        <v>304</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>-8.998049999999999e-06</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>-2.20875e-06</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>4.07381</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>99.9816</v>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -27309,6 +28887,26 @@
       <c r="D83" s="1" t="n">
         <v>0.08920468188120592</v>
       </c>
+      <c r="AF83" t="n">
+        <v>308</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>-8.936949999999999e-06</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>-2.20859e-06</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>4.04645</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>99.9813</v>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -27323,6 +28921,26 @@
       <c r="D84" s="1" t="n">
         <v>0.08891335992498277</v>
       </c>
+      <c r="AF84" t="n">
+        <v>312</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>-8.876260000000001e-06</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>-2.20843e-06</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>4.01926</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>99.9811</v>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -27337,6 +28955,26 @@
       <c r="D85" s="1" t="n">
         <v>0.08862614604751046</v>
       </c>
+      <c r="AF85" t="n">
+        <v>316</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>-8.81598e-06</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>-2.20828e-06</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>3.99223</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>99.9808</v>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -27351,6 +28989,26 @@
       <c r="D86" s="1" t="n">
         <v>0.08833387229966326</v>
       </c>
+      <c r="AF86" t="n">
+        <v>320</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>-8.75612e-06</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>-2.20814e-06</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>3.96537</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>99.9804</v>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -27365,6 +29023,26 @@
       <c r="D87" s="1" t="n">
         <v>0.08802800479848273</v>
       </c>
+      <c r="AF87" t="n">
+        <v>324</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>-8.69666e-06</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>-2.20801e-06</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>3.93869</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>99.9803</v>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -27379,6 +29057,26 @@
       <c r="D88" s="1" t="n">
         <v>0.08770758483141153</v>
       </c>
+      <c r="AF88" t="n">
+        <v>328</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>-8.6376e-06</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>-2.20788e-06</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>3.91217</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>99.9803</v>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -27393,6 +29091,26 @@
       <c r="D89" s="1" t="n">
         <v>0.08737402622344086</v>
       </c>
+      <c r="AF89" t="n">
+        <v>332</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>-8.57894e-06</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>-2.20776e-06</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>3.88581</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>99.98009999999999</v>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -27407,6 +29125,26 @@
       <c r="D90" s="1" t="n">
         <v>0.08702723974231855</v>
       </c>
+      <c r="AF90" t="n">
+        <v>336</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>-8.520690000000001e-06</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>-2.20764e-06</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>3.85963</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>99.9798</v>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -27421,6 +29159,26 @@
       <c r="D91" s="1" t="n">
         <v>0.08666988679736835</v>
       </c>
+      <c r="AF91" t="n">
+        <v>340</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>-8.462819999999999e-06</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>-2.20753e-06</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>3.83361</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>99.9794</v>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -27435,6 +29193,26 @@
       <c r="D92" s="1" t="n">
         <v>0.08631079314327535</v>
       </c>
+      <c r="AF92" t="n">
+        <v>344</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>-8.40536e-06</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>-2.20743e-06</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>3.80776</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>99.9796</v>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -27449,6 +29227,26 @@
       <c r="D93" s="1" t="n">
         <v>0.08595966027640642</v>
       </c>
+      <c r="AF93" t="n">
+        <v>348</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>-8.34828e-06</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>-2.20733e-06</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>3.78208</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>99.9796</v>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -27463,6 +29261,26 @@
       <c r="D94" s="1" t="n">
         <v>0.08562645772838749</v>
       </c>
+      <c r="AF94" t="n">
+        <v>352</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>-8.29159e-06</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>-2.20723e-06</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>3.75656</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>99.9794</v>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -27477,6 +29295,26 @@
       <c r="D95" s="1" t="n">
         <v>0.08531643816295487</v>
       </c>
+      <c r="AF95" t="n">
+        <v>356</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>-8.235279999999999e-06</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>-2.20714e-06</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>3.73121</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>99.9794</v>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -27491,6 +29329,26 @@
       <c r="D96" s="1" t="n">
         <v>0.0850215769850417</v>
       </c>
+      <c r="AF96" t="n">
+        <v>360</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>-8.179360000000001e-06</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>-2.20705e-06</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>3.70602</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>99.97920000000001</v>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -27505,6 +29363,26 @@
       <c r="D97" s="1" t="n">
         <v>0.08472931410638661</v>
       </c>
+      <c r="AF97" t="n">
+        <v>364</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>-8.123810000000001e-06</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>-2.20696e-06</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>3.68099</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>99.97920000000001</v>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -27519,6 +29397,26 @@
       <c r="D98" s="1" t="n">
         <v>0.08442867512139254</v>
       </c>
+      <c r="AF98" t="n">
+        <v>368</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>-8.068649999999999e-06</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>-2.20688e-06</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>3.65613</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>99.979</v>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -27533,6 +29431,26 @@
       <c r="D99" s="1" t="n">
         <v>0.08411169679232629</v>
       </c>
+      <c r="AF99" t="n">
+        <v>372</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>-8.01385e-06</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>-2.20681e-06</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>3.63143</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>99.9787</v>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -27547,6 +29465,26 @@
       <c r="D100" s="1" t="n">
         <v>0.08378216361978076</v>
       </c>
+      <c r="AF100" t="n">
+        <v>376</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>-7.959430000000001e-06</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>-2.20673e-06</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>3.60689</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>99.9783</v>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -27561,6 +29499,26 @@
       <c r="D101" s="1" t="n">
         <v>0.0834465237514761</v>
       </c>
+      <c r="AF101" t="n">
+        <v>380</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>-7.905379999999999e-06</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>-2.20666e-06</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>3.58251</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>99.97790000000001</v>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -27575,6 +29533,26 @@
       <c r="D102" s="1" t="n">
         <v>0.0831109574662191</v>
       </c>
+      <c r="AF102" t="n">
+        <v>384</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>-7.8517e-06</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>-2.20659e-06</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>3.55829</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>99.97750000000001</v>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -27589,6 +29567,26 @@
       <c r="D103" s="1" t="n">
         <v>0.08278135995956597</v>
       </c>
+      <c r="AF103" t="n">
+        <v>388</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>-7.79838e-06</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>-2.20653e-06</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>3.53423</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>99.9769</v>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -27603,6 +29601,26 @@
       <c r="D104" s="1" t="n">
         <v>0.08246291781169843</v>
       </c>
+      <c r="AF104" t="n">
+        <v>392</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>-7.74542e-06</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>-2.20646e-06</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>3.51033</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>99.9765</v>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -27617,6 +29635,26 @@
       <c r="D105" s="1" t="n">
         <v>0.08216160353758246</v>
       </c>
+      <c r="AF105" t="n">
+        <v>396</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>-7.692830000000001e-06</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>-2.2064e-06</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>3.48659</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>99.9764</v>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -27631,6 +29669,26 @@
       <c r="D106" s="1" t="n">
         <v>0.08188179523644272</v>
       </c>
+      <c r="AF106" t="n">
+        <v>400</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>-7.64059e-06</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>-2.20634e-06</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>3.46301</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>99.9757</v>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -27645,6 +29703,26 @@
       <c r="D107" s="1" t="n">
         <v>0.0816254210145958</v>
       </c>
+      <c r="AF107" t="n">
+        <v>404</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>-7.5887e-06</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>-2.20629e-06</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>3.43958</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>99.9753</v>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -27659,6 +29737,26 @@
       <c r="D108" s="1" t="n">
         <v>0.08138132546288539</v>
       </c>
+      <c r="AF108" t="n">
+        <v>408</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>-7.53717e-06</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>-2.20624e-06</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>3.4163</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>99.9747</v>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -27673,6 +29771,26 @@
       <c r="D109" s="1" t="n">
         <v>0.08113455019743158</v>
       </c>
+      <c r="AF109" t="n">
+        <v>412</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>-7.48599e-06</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>-2.20618e-06</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>3.39318</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>99.974</v>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -27687,6 +29805,26 @@
       <c r="D110" s="1" t="n">
         <v>0.08087137124245822</v>
       </c>
+      <c r="AF110" t="n">
+        <v>416</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>-7.43515e-06</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>-2.20613e-06</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>3.37022</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>99.9736</v>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -27701,6 +29839,26 @@
       <c r="D111" s="1" t="n">
         <v>0.08058331988090196</v>
       </c>
+      <c r="AF111" t="n">
+        <v>420</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>-7.38466e-06</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>-2.20609e-06</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>3.3474</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>99.9734</v>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -27715,6 +29873,26 @@
       <c r="D112" s="1" t="n">
         <v>0.08027732729997705</v>
       </c>
+      <c r="AF112" t="n">
+        <v>424</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>-7.33451e-06</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>-2.20604e-06</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>3.32474</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>99.9725</v>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -27729,6 +29907,26 @@
       <c r="D113" s="1" t="n">
         <v>0.07996437561390424</v>
       </c>
+      <c r="AF113" t="n">
+        <v>428</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>-7.28471e-06</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>-2.206e-06</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>3.30223</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>99.97199999999999</v>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -27743,6 +29941,26 @@
       <c r="D114" s="1" t="n">
         <v>0.07965504141184</v>
       </c>
+      <c r="AF114" t="n">
+        <v>432</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>-7.23524e-06</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>-2.20595e-06</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>3.27987</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>99.9712</v>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -27757,6 +29975,26 @@
       <c r="D115" s="1" t="n">
         <v>0.07935737192106723</v>
       </c>
+      <c r="AF115" t="n">
+        <v>436</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>-7.18611e-06</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>-2.20591e-06</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>3.25766</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>99.9716</v>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -27771,6 +30009,26 @@
       <c r="D116" s="1" t="n">
         <v>0.07907063059222802</v>
       </c>
+      <c r="AF116" t="n">
+        <v>440</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>-7.13731e-06</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>-2.20587e-06</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>3.23559</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>99.97110000000001</v>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -27785,6 +30043,26 @@
       <c r="D117" s="1" t="n">
         <v>0.07879200340939584</v>
       </c>
+      <c r="AF117" t="n">
+        <v>444</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>-7.08884e-06</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>-2.20583e-06</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>3.21368</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>99.9699</v>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -27799,6 +30077,26 @@
       <c r="D118" s="1" t="n">
         <v>0.07851877656387476</v>
       </c>
+      <c r="AF118" t="n">
+        <v>448</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>-7.0407e-06</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>-2.2058e-06</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>3.19191</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>99.9684</v>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -27813,6 +30111,26 @@
       <c r="D119" s="1" t="n">
         <v>0.07824795627706468</v>
       </c>
+      <c r="AF119" t="n">
+        <v>452</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>-6.99289e-06</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>-2.20576e-06</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>3.17028</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>99.9669</v>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -27827,6 +30145,26 @@
       <c r="D120" s="1" t="n">
         <v>0.0779774407055526</v>
       </c>
+      <c r="AF120" t="n">
+        <v>456</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>-6.9454e-06</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>-2.20573e-06</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>3.1488</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>99.96559999999999</v>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -27841,6 +30179,26 @@
       <c r="D121" s="1" t="n">
         <v>0.07770386354634869</v>
       </c>
+      <c r="AF121" t="n">
+        <v>460</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>-6.89824e-06</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>-2.20569e-06</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>3.12747</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>99.9644</v>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -27855,6 +30213,26 @@
       <c r="D122" s="1" t="n">
         <v>0.07742526079464357</v>
       </c>
+      <c r="AF122" t="n">
+        <v>464</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-6.85139e-06</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-2.20566e-06</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>3.10628</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>99.96259999999999</v>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -27869,6 +30247,26 @@
       <c r="D123" s="1" t="n">
         <v>0.07713942903919103</v>
       </c>
+      <c r="AF123" t="n">
+        <v>468</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>-6.80487e-06</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>-2.20563e-06</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>3.08522</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>99.96080000000001</v>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -27883,6 +30281,26 @@
       <c r="D124" s="1" t="n">
         <v>0.07684906541954119</v>
       </c>
+      <c r="AF124" t="n">
+        <v>472</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>-6.75866e-06</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>-2.2056e-06</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>3.06432</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>99.9593</v>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -27897,6 +30315,26 @@
       <c r="D125" s="1" t="n">
         <v>0.07655742104023924</v>
       </c>
+      <c r="AF125" t="n">
+        <v>476</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>-6.71276e-06</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-2.20557e-06</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>3.04355</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>99.9584</v>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -27911,6 +30349,26 @@
       <c r="D126" s="1" t="n">
         <v>0.07626763894907877</v>
       </c>
+      <c r="AF126" t="n">
+        <v>480</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>-6.66718e-06</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>-2.20554e-06</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>3.02292</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>99.9572</v>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -27925,6 +30383,26 @@
       <c r="D127" s="1" t="n">
         <v>0.07598251864268254</v>
       </c>
+      <c r="AF127" t="n">
+        <v>484</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>-6.6219e-06</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-2.20552e-06</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>3.00243</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>99.9551</v>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -27939,6 +30417,26 @@
       <c r="D128" s="1" t="n">
         <v>0.07570381612035583</v>
       </c>
+      <c r="AF128" t="n">
+        <v>488</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>-6.57693e-06</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>-2.20549e-06</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>2.98207</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>99.9538</v>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -27953,6 +30451,26 @@
       <c r="D129" s="1" t="n">
         <v>0.07543299439295768</v>
       </c>
+      <c r="AF129" t="n">
+        <v>492</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>-6.53227e-06</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>-2.20547e-06</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>2.96186</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>99.9521</v>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -27967,6 +30485,26 @@
       <c r="D130" s="1" t="n">
         <v>0.07517146943931527</v>
       </c>
+      <c r="AF130" t="n">
+        <v>496</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>-6.48791e-06</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>-2.20544e-06</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>2.94178</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>99.9507</v>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -27981,6 +30519,26 @@
       <c r="D131" s="1" t="n">
         <v>0.07491959096390317</v>
       </c>
+      <c r="AF131" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>-6.44386e-06</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>-2.20542e-06</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2.92183</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>99.9483</v>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -27995,6 +30553,26 @@
       <c r="D132" s="1" t="n">
         <v>0.07467582834172752</v>
       </c>
+      <c r="AF132" t="n">
+        <v>504</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>-6.4001e-06</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>-2.20539e-06</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2.90202</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>99.9465</v>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -28009,6 +30587,26 @@
       <c r="D133" s="1" t="n">
         <v>0.07443707764424058</v>
       </c>
+      <c r="AF133" t="n">
+        <v>508</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-6.35664e-06</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>-2.20537e-06</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2.88234</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>99.9443</v>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -28023,6 +30621,26 @@
       <c r="D134" s="1" t="n">
         <v>0.07420032586385963</v>
       </c>
+      <c r="AF134" t="n">
+        <v>512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>-6.31347e-06</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>-2.20535e-06</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.8628</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>99.94199999999999</v>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -28037,6 +30655,26 @@
       <c r="D135" s="1" t="n">
         <v>0.07396382794560923</v>
       </c>
+      <c r="AF135" t="n">
+        <v>516</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>-6.2706e-06</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-2.20533e-06</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.84338</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -28051,6 +30689,26 @@
       <c r="D136" s="1" t="n">
         <v>0.07372565302328093</v>
       </c>
+      <c r="AF136" t="n">
+        <v>520</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-6.22801e-06</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-2.20531e-06</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2.8241</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>99.9379</v>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -28065,6 +30723,26 @@
       <c r="D137" s="1" t="n">
         <v>0.07348539732740578</v>
       </c>
+      <c r="AF137" t="n">
+        <v>524</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-6.18572e-06</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-2.20529e-06</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.80495</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>99.9357</v>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -28079,6 +30757,26 @@
       <c r="D138" s="1" t="n">
         <v>0.073241449781997</v>
       </c>
+      <c r="AF138" t="n">
+        <v>528</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-6.14372e-06</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-2.20527e-06</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.78593</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>99.9335</v>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -28093,6 +30791,26 @@
       <c r="D139" s="1" t="n">
         <v>0.07299378654942464</v>
       </c>
+      <c r="AF139" t="n">
+        <v>532</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>-6.102e-06</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>-2.20525e-06</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.76703</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>99.9306</v>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -28107,6 +30825,26 @@
       <c r="D140" s="1" t="n">
         <v>0.07274245606748407</v>
       </c>
+      <c r="AF140" t="n">
+        <v>536</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>-6.06056e-06</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>-2.20523e-06</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.74826</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>99.9276</v>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -28121,6 +30859,26 @@
       <c r="D141" s="1" t="n">
         <v>0.07248903169380341</v>
       </c>
+      <c r="AF141" t="n">
+        <v>540</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>-6.0194e-06</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>-2.20521e-06</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.72962</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>99.9246</v>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -28135,6 +30893,26 @@
       <c r="D142" s="1" t="n">
         <v>0.0722338367551119</v>
       </c>
+      <c r="AF142" t="n">
+        <v>544</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>-5.97853e-06</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>-2.2052e-06</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.71111</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>99.923</v>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -28149,6 +30927,26 @@
       <c r="D143" s="1" t="n">
         <v>0.07197789797869525</v>
       </c>
+      <c r="AF143" t="n">
+        <v>548</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>-5.93793e-06</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-2.20518e-06</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.69272</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>99.9211</v>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -28163,6 +30961,26 @@
       <c r="D144" s="1" t="n">
         <v>0.07172148323675412</v>
       </c>
+      <c r="AF144" t="n">
+        <v>552</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>-5.89761e-06</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>-2.20517e-06</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.67445</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>99.9188</v>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -28177,6 +30995,26 @@
       <c r="D145" s="1" t="n">
         <v>0.07146377455220949</v>
       </c>
+      <c r="AF145" t="n">
+        <v>556</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>-5.85756e-06</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>-2.20515e-06</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.65631</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>99.9162</v>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -28191,6 +31029,26 @@
       <c r="D146" s="1" t="n">
         <v>0.07120516486028444</v>
       </c>
+      <c r="AF146" t="n">
+        <v>560</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>-5.81778e-06</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>-2.20513e-06</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.63829</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>99.9136</v>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -28205,6 +31063,26 @@
       <c r="D147" s="1" t="n">
         <v>0.07094537457178263</v>
       </c>
+      <c r="AF147" t="n">
+        <v>564</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>-5.77827e-06</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>-2.20512e-06</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.62039</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>99.91240000000001</v>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -28219,6 +31097,26 @@
       <c r="D148" s="1" t="n">
         <v>0.07068738501140739</v>
       </c>
+      <c r="AF148" t="n">
+        <v>568</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>-5.73903e-06</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>-2.20511e-06</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>2.60261</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>99.9105</v>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -28233,6 +31131,26 @@
       <c r="D149" s="1" t="n">
         <v>0.0704334339643997</v>
       </c>
+      <c r="AF149" t="n">
+        <v>572</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>-5.70006e-06</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>-2.20509e-06</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>2.58495</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>99.9084</v>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -28247,6 +31165,26 @@
       <c r="D150" s="1" t="n">
         <v>0.07018657358347999</v>
       </c>
+      <c r="AF150" t="n">
+        <v>576</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>-5.66135e-06</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>-2.20508e-06</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>2.56742</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>99.9062</v>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -28261,6 +31199,26 @@
       <c r="D151" s="1" t="n">
         <v>0.06994866717354301</v>
       </c>
+      <c r="AF151" t="n">
+        <v>580</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>-5.62291e-06</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>-2.20506e-06</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>99.90300000000001</v>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -28275,6 +31233,26 @@
       <c r="D152" s="1" t="n">
         <v>0.06971624730426294</v>
       </c>
+      <c r="AF152" t="n">
+        <v>584</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>-5.58473e-06</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>-2.20505e-06</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.5327</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>99.9007</v>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -28289,6 +31267,26 @@
       <c r="D153" s="1" t="n">
         <v>0.06948600598764205</v>
       </c>
+      <c r="AF153" t="n">
+        <v>588</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>-5.5468e-06</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>-2.20504e-06</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>2.51551</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>99.8999</v>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -28303,6 +31301,26 @@
       <c r="D154" s="1" t="n">
         <v>0.0692535687888145</v>
       </c>
+      <c r="AF154" t="n">
+        <v>592</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>-5.50913e-06</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>-2.20503e-06</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.49844</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>99.8978</v>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -28317,6 +31335,26 @@
       <c r="D155" s="1" t="n">
         <v>0.0690165264330737</v>
       </c>
+      <c r="AF155" t="n">
+        <v>596</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>-5.47172e-06</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>-2.20502e-06</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.48149</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>99.89570000000001</v>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -28331,6 +31369,26 @@
       <c r="D156" s="1" t="n">
         <v>0.06877616720064846</v>
       </c>
+      <c r="AF156" t="n">
+        <v>600</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>-5.43457e-06</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>-2.205e-06</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2.46465</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>99.89360000000001</v>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -28345,6 +31403,26 @@
       <c r="D157" s="1" t="n">
         <v>0.06853471851876157</v>
       </c>
+      <c r="AF157" t="n">
+        <v>604</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>-5.39766e-06</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>-2.20499e-06</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>2.44793</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>99.89109999999999</v>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -28359,6 +31437,26 @@
       <c r="D158" s="1" t="n">
         <v>0.06829434937854423</v>
       </c>
+      <c r="AF158" t="n">
+        <v>608</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>-5.36101e-06</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>-2.20498e-06</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>2.43132</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>99.8886</v>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -28373,6 +31471,26 @@
       <c r="D159" s="1" t="n">
         <v>0.06805657161169748</v>
       </c>
+      <c r="AF159" t="n">
+        <v>612</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>-5.3246e-06</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>-2.20497e-06</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2.41482</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>99.887</v>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -28387,6 +31505,26 @@
       <c r="D160" s="1" t="n">
         <v>0.06782047092812034</v>
       </c>
+      <c r="AF160" t="n">
+        <v>616</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>-5.28844e-06</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>-2.20496e-06</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2.39843</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>99.88630000000001</v>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -28401,6 +31539,26 @@
       <c r="D161" s="1" t="n">
         <v>0.06758456365234446</v>
       </c>
+      <c r="AF161" t="n">
+        <v>620</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>-5.25253e-06</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>-2.20495e-06</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>2.38215</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>99.8849</v>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -28415,6 +31573,26 @@
       <c r="D162" s="1" t="n">
         <v>0.06734740403070419</v>
       </c>
+      <c r="AF162" t="n">
+        <v>624</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>-5.21686e-06</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>-2.20494e-06</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2.36599</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>99.8826</v>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -28429,6 +31607,26 @@
       <c r="D163" s="1" t="n">
         <v>0.06710824623229301</v>
       </c>
+      <c r="AF163" t="n">
+        <v>628</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>-5.18144e-06</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>-2.20493e-06</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2.34993</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>99.881</v>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -28443,6 +31641,26 @@
       <c r="D164" s="1" t="n">
         <v>0.06686899934368876</v>
       </c>
+      <c r="AF164" t="n">
+        <v>632</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>-5.14625e-06</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>-2.20492e-06</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.33398</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>99.87730000000001</v>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -28457,6 +31675,26 @@
       <c r="D165" s="1" t="n">
         <v>0.06663217947431646</v>
       </c>
+      <c r="AF165" t="n">
+        <v>636</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>-5.1113e-06</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>-2.20491e-06</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2.31814</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>99.87560000000001</v>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -28471,6 +31709,26 @@
       <c r="D166" s="1" t="n">
         <v>0.06639996105175112</v>
       </c>
+      <c r="AF166" t="n">
+        <v>640</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>-5.0766e-06</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>-2.2049e-06</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>2.30241</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>99.87430000000001</v>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -28485,6 +31743,26 @@
       <c r="D167" s="1" t="n">
         <v>0.0661746765660404</v>
       </c>
+      <c r="AF167" t="n">
+        <v>644</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>-5.04212e-06</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>-2.20489e-06</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>2.28679</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>99.87090000000001</v>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -28499,6 +31777,26 @@
       <c r="D168" s="1" t="n">
         <v>0.06595531483318721</v>
       </c>
+      <c r="AF168" t="n">
+        <v>648</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>-5.00788e-06</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>-2.20489e-06</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.27127</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>99.8682</v>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -28513,6 +31811,26 @@
       <c r="D169" s="1" t="n">
         <v>0.06574055099377865</v>
       </c>
+      <c r="AF169" t="n">
+        <v>652</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>-4.97387e-06</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>-2.20488e-06</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2.25585</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>99.8663</v>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -28527,6 +31845,26 @@
       <c r="D170" s="1" t="n">
         <v>0.06552909240048935</v>
       </c>
+      <c r="AF170" t="n">
+        <v>656</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>-4.9401e-06</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>-2.20487e-06</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.24054</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>99.86320000000001</v>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -28541,6 +31879,26 @@
       <c r="D171" s="1" t="n">
         <v>0.06532003941520105</v>
       </c>
+      <c r="AF171" t="n">
+        <v>660</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>-4.90655e-06</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>-2.20486e-06</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.22533</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>99.86190000000001</v>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -28555,6 +31913,26 @@
       <c r="D172" s="1" t="n">
         <v>0.06511395241349904</v>
       </c>
+      <c r="AF172" t="n">
+        <v>664</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>-4.87323e-06</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>-2.20485e-06</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2.21023</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>99.8591</v>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -28569,6 +31947,26 @@
       <c r="D173" s="1" t="n">
         <v>0.06491146308099088</v>
       </c>
+      <c r="AF173" t="n">
+        <v>668</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>-4.84014e-06</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>-2.20485e-06</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>2.19523</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>99.85680000000001</v>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -28583,6 +31981,26 @@
       <c r="D174" s="1" t="n">
         <v>0.06471400079436644</v>
       </c>
+      <c r="AF174" t="n">
+        <v>672</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>-4.80727e-06</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>-2.20484e-06</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>2.18033</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>99.8544</v>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -28610,6 +32028,11 @@
       </c>
       <c r="D176" s="1" t="n">
         <v>0.06433106947369424</v>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>Da = |vO2React| / |vO2Diff| (ratio of interfacial O2-reaction to O2-diffusion velocities); Da&lt;1 reaction-controlled, Da&gt;=1 diffusion-controlled. Surface-share label: a regime is dominant when &gt;75% of the interface is limited by it, otherwise 'Transition'.</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -35953,8 +39376,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C677"/>
+  <dimension ref="A1:J677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -35976,6 +39407,11 @@
           <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Regime control: Damkohler number and regime classification</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -35991,6 +39427,36 @@
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t>CR (mm/yr)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>vO2React (mm/h)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>vO2Diff (mm/h)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Damkohler number Da</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>O2-diffusion-limited surface (%)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Regime (surface share)</t>
         </is>
       </c>
     </row>
@@ -36004,6 +39470,23 @@
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NotYetComputed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -36015,6 +39498,23 @@
       <c r="C6" s="1" t="n">
         <v>0.0138</v>
       </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ZnDiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -36026,6 +39526,26 @@
       <c r="C7" s="1" t="n">
         <v>0.0276</v>
       </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.55745e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.32982e-05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.467729</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.11212</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -36037,6 +39557,26 @@
       <c r="C8" s="1" t="n">
         <v>0.0414</v>
       </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.55491e-05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.07992e-05</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5048550000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.92247</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -36048,6 +39588,26 @@
       <c r="C9" s="1" t="n">
         <v>0.0552</v>
       </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.55237e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.84877e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.544928</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.8827</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -36059,6 +39619,26 @@
       <c r="C10" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.54984e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.63497e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.588181</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.01643</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -36070,6 +39650,26 @@
       <c r="C11" s="1" t="n">
         <v>0.0762</v>
       </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.54731e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.43722e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.634868</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.349270000000001</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -36081,6 +39681,26 @@
       <c r="C12" s="1" t="n">
         <v>0.0834</v>
       </c>
+      <c r="E12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.54479e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.25431e-05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.68526</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.90832</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -36092,6 +39712,26 @@
       <c r="C13" s="1" t="n">
         <v>0.0906</v>
       </c>
+      <c r="E13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.54227e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-2.08512e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.739652</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.7212</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -36103,6 +39743,26 @@
       <c r="C14" s="1" t="n">
         <v>0.0978</v>
       </c>
+      <c r="E14" t="n">
+        <v>36</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.53975e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.92863e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.798362</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13.815</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -36114,6 +39774,26 @@
       <c r="C15" s="1" t="n">
         <v>0.105</v>
       </c>
+      <c r="E15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.53724e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.78389e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8617320000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>16.2141</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -36125,6 +39805,26 @@
       <c r="C16" s="1" t="n">
         <v>0.108</v>
       </c>
+      <c r="E16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.53473e-05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.65001e-05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.930132</v>
+      </c>
+      <c r="I16" t="n">
+        <v>18.9383</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -36136,6 +39836,26 @@
       <c r="C17" s="1" t="n">
         <v>0.111</v>
       </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.53222e-05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.52618e-05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O2ReactionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -36147,6 +39867,26 @@
       <c r="C18" s="1" t="n">
         <v>0.114</v>
       </c>
+      <c r="E18" t="n">
+        <v>52</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.52972e-05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.41164e-05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.08365</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.4016</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -36158,6 +39898,26 @@
       <c r="C19" s="1" t="n">
         <v>0.117</v>
       </c>
+      <c r="E19" t="n">
+        <v>56</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.52722e-05</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.3057e-05</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.16966</v>
+      </c>
+      <c r="I19" t="n">
+        <v>29.1326</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -36169,6 +39929,26 @@
       <c r="C20" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="E20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.52473e-05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.2077e-05</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.26251</v>
+      </c>
+      <c r="I20" t="n">
+        <v>33.1681</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -36180,6 +39960,26 @@
       <c r="C21" s="1" t="n">
         <v>0.123</v>
       </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.52224e-05</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.11707e-05</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.36272</v>
+      </c>
+      <c r="I21" t="n">
+        <v>37.4669</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -36191,6 +39991,26 @@
       <c r="C22" s="1" t="n">
         <v>0.126</v>
       </c>
+      <c r="E22" t="n">
+        <v>68</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.51976e-05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.03323e-05</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.47088</v>
+      </c>
+      <c r="I22" t="n">
+        <v>41.9731</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -36202,6 +40022,26 @@
       <c r="C23" s="1" t="n">
         <v>0.129</v>
       </c>
+      <c r="E23" t="n">
+        <v>72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.51728e-05</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-9.556860000000001e-06</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.58763</v>
+      </c>
+      <c r="I23" t="n">
+        <v>46.6171</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -36213,6 +40053,26 @@
       <c r="C24" s="1" t="n">
         <v>0.132</v>
       </c>
+      <c r="E24" t="n">
+        <v>76</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.5148e-05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-8.83963e-06</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.71365</v>
+      </c>
+      <c r="I24" t="n">
+        <v>51.3206</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -36224,6 +40084,26 @@
       <c r="C25" s="1" t="n">
         <v>0.135</v>
       </c>
+      <c r="E25" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.51233e-05</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-8.17621e-06</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.84967</v>
+      </c>
+      <c r="I25" t="n">
+        <v>56.0008</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -36235,6 +40115,26 @@
       <c r="C26" s="1" t="n">
         <v>0.1366</v>
       </c>
+      <c r="E26" t="n">
+        <v>84</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.50986e-05</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-7.56259e-06</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.99649</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60.5766</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -36246,6 +40146,26 @@
       <c r="C27" s="1" t="n">
         <v>0.1382</v>
       </c>
+      <c r="E27" t="n">
+        <v>88</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.5074e-05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-6.99502e-06</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.15496</v>
+      </c>
+      <c r="I27" t="n">
+        <v>64.9743</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -36257,6 +40177,26 @@
       <c r="C28" s="1" t="n">
         <v>0.1398</v>
       </c>
+      <c r="E28" t="n">
+        <v>92</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.50494e-05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-6.47005e-06</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.32601</v>
+      </c>
+      <c r="I28" t="n">
+        <v>69.1313</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -36268,6 +40208,26 @@
       <c r="C29" s="1" t="n">
         <v>0.1414</v>
       </c>
+      <c r="E29" t="n">
+        <v>96</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.50248e-05</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-5.98447e-06</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.51063</v>
+      </c>
+      <c r="I29" t="n">
+        <v>73</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -36279,6 +40239,26 @@
       <c r="C30" s="1" t="n">
         <v>0.143</v>
       </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.50003e-05</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-5.53534e-06</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.70991</v>
+      </c>
+      <c r="I30" t="n">
+        <v>99.99939999999999</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -36290,6 +40270,26 @@
       <c r="C31" s="1" t="n">
         <v>0.1446</v>
       </c>
+      <c r="E31" t="n">
+        <v>104</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1.49703e-05</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-5.41571e-06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.76424</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -36301,6 +40301,26 @@
       <c r="C32" s="1" t="n">
         <v>0.1462</v>
       </c>
+      <c r="E32" t="n">
+        <v>108</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-1.49382e-05</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-5.26929e-06</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.83496</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -36312,6 +40332,26 @@
       <c r="C33" s="1" t="n">
         <v>0.1478</v>
       </c>
+      <c r="E33" t="n">
+        <v>112</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.49053e-05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-5.13894e-06</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.90046</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -36323,6 +40363,26 @@
       <c r="C34" s="1" t="n">
         <v>0.1494</v>
       </c>
+      <c r="E34" t="n">
+        <v>116</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-1.48715e-05</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-5.05165e-06</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.94389</v>
+      </c>
+      <c r="I34" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -36334,6 +40394,26 @@
       <c r="C35" s="1" t="n">
         <v>0.151</v>
       </c>
+      <c r="E35" t="n">
+        <v>120</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.48377e-05</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-5.01567e-06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.95827</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -36345,6 +40425,26 @@
       <c r="C36" s="1" t="n">
         <v>0.1514</v>
       </c>
+      <c r="E36" t="n">
+        <v>124</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.48034e-05</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-5.00325e-06</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.95876</v>
+      </c>
+      <c r="I36" t="n">
+        <v>99.9992</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -36356,6 +40456,26 @@
       <c r="C37" s="1" t="n">
         <v>0.1518</v>
       </c>
+      <c r="E37" t="n">
+        <v>128</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-1.47707e-05</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-4.99144e-06</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.9592</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -36367,6 +40487,26 @@
       <c r="C38" s="1" t="n">
         <v>0.1522</v>
       </c>
+      <c r="E38" t="n">
+        <v>132</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1.47359e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-4.98022e-06</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.95888</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -36378,6 +40518,26 @@
       <c r="C39" s="1" t="n">
         <v>0.1526</v>
       </c>
+      <c r="E39" t="n">
+        <v>136</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-1.47006e-05</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-4.96954e-06</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.95814</v>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -36389,6 +40549,26 @@
       <c r="C40" s="1" t="n">
         <v>0.153</v>
       </c>
+      <c r="E40" t="n">
+        <v>140</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-1.46648e-05</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-4.95937e-06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.95699</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -36400,6 +40580,26 @@
       <c r="C41" s="1" t="n">
         <v>0.1534</v>
       </c>
+      <c r="E41" t="n">
+        <v>144</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1.46287e-05</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-4.94966e-06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.95549</v>
+      </c>
+      <c r="I41" t="n">
+        <v>99.99890000000001</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -36411,6 +40611,26 @@
       <c r="C42" s="1" t="n">
         <v>0.1538</v>
       </c>
+      <c r="E42" t="n">
+        <v>148</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-1.45922e-05</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-4.9404e-06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.95365</v>
+      </c>
+      <c r="I42" t="n">
+        <v>99.99930000000001</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -36422,6 +40642,26 @@
       <c r="C43" s="1" t="n">
         <v>0.1542</v>
       </c>
+      <c r="E43" t="n">
+        <v>152</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-1.45572e-05</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-4.93155e-06</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.95185</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -36433,6 +40673,26 @@
       <c r="C44" s="1" t="n">
         <v>0.1546</v>
       </c>
+      <c r="E44" t="n">
+        <v>156</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-1.45207e-05</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-4.92309e-06</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.94951</v>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -36444,6 +40704,26 @@
       <c r="C45" s="1" t="n">
         <v>0.155</v>
       </c>
+      <c r="E45" t="n">
+        <v>160</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-1.44835e-05</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-4.91499e-06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.9468</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -36455,6 +40735,26 @@
       <c r="C46" s="1" t="n">
         <v>0.1546</v>
       </c>
+      <c r="E46" t="n">
+        <v>164</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.44461e-05</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-4.90723e-06</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.94384</v>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -36466,6 +40766,26 @@
       <c r="C47" s="1" t="n">
         <v>0.1542</v>
       </c>
+      <c r="E47" t="n">
+        <v>168</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-1.44083e-05</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-4.89979e-06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.94059</v>
+      </c>
+      <c r="I47" t="n">
+        <v>99.9988</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -36477,6 +40797,26 @@
       <c r="C48" s="1" t="n">
         <v>0.1538</v>
       </c>
+      <c r="E48" t="n">
+        <v>172</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-1.43702e-05</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-4.89266e-06</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.93709</v>
+      </c>
+      <c r="I48" t="n">
+        <v>99.99930000000001</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -36488,6 +40828,26 @@
       <c r="C49" s="1" t="n">
         <v>0.1534</v>
       </c>
+      <c r="E49" t="n">
+        <v>176</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-1.43338e-05</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-4.88581e-06</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.93376</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -36499,6 +40859,26 @@
       <c r="C50" s="1" t="n">
         <v>0.153</v>
       </c>
+      <c r="E50" t="n">
+        <v>180</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-1.4296e-05</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-4.87923e-06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.92997</v>
+      </c>
+      <c r="I50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -36510,6 +40890,26 @@
       <c r="C51" s="1" t="n">
         <v>0.1526</v>
       </c>
+      <c r="E51" t="n">
+        <v>184</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-1.42577e-05</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-4.87291e-06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.92591</v>
+      </c>
+      <c r="I51" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -36521,6 +40921,26 @@
       <c r="C52" s="1" t="n">
         <v>0.1522</v>
       </c>
+      <c r="E52" t="n">
+        <v>188</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1.42193e-05</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4.86682e-06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.92168</v>
+      </c>
+      <c r="I52" t="n">
+        <v>100</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -36532,6 +40952,26 @@
       <c r="C53" s="1" t="n">
         <v>0.1518</v>
       </c>
+      <c r="E53" t="n">
+        <v>192</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-1.41807e-05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-4.86097e-06</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.91726</v>
+      </c>
+      <c r="I53" t="n">
+        <v>99.99890000000001</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -36543,6 +40983,26 @@
       <c r="C54" s="1" t="n">
         <v>0.1514</v>
       </c>
+      <c r="E54" t="n">
+        <v>196</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.41419e-05</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-4.85533e-06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.91266</v>
+      </c>
+      <c r="I54" t="n">
+        <v>99.99939999999999</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -36554,6 +41014,26 @@
       <c r="C55" s="1" t="n">
         <v>0.151</v>
       </c>
+      <c r="E55" t="n">
+        <v>200</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-1.41048e-05</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-4.84989e-06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.90827</v>
+      </c>
+      <c r="I55" t="n">
+        <v>99.9986</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -36565,6 +41045,26 @@
       <c r="C56" s="1" t="n">
         <v>0.1506</v>
       </c>
+      <c r="E56" t="n">
+        <v>204</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1.40665e-05</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-4.84465e-06</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.90351</v>
+      </c>
+      <c r="I56" t="n">
+        <v>99.9988</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -36576,6 +41076,26 @@
       <c r="C57" s="1" t="n">
         <v>0.1502</v>
       </c>
+      <c r="E57" t="n">
+        <v>208</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1.40279e-05</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-4.83959e-06</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.89857</v>
+      </c>
+      <c r="I57" t="n">
+        <v>99.999</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -36587,6 +41107,26 @@
       <c r="C58" s="1" t="n">
         <v>0.1498</v>
       </c>
+      <c r="E58" t="n">
+        <v>212</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.39892e-05</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-4.83471e-06</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.89349</v>
+      </c>
+      <c r="I58" t="n">
+        <v>99.9991</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -36598,6 +41138,26 @@
       <c r="C59" s="1" t="n">
         <v>0.1494</v>
       </c>
+      <c r="E59" t="n">
+        <v>216</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-1.39505e-05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-4.82999e-06</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2.88831</v>
+      </c>
+      <c r="I59" t="n">
+        <v>99.99939999999999</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -36609,6 +41169,26 @@
       <c r="C60" s="1" t="n">
         <v>0.149</v>
       </c>
+      <c r="E60" t="n">
+        <v>220</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-1.39117e-05</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-4.82544e-06</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2.88299</v>
+      </c>
+      <c r="I60" t="n">
+        <v>99.9906</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -36620,6 +41200,26 @@
       <c r="C61" s="1" t="n">
         <v>0.1486</v>
       </c>
+      <c r="E61" t="n">
+        <v>224</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-1.38746e-05</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-4.82103e-06</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.87793</v>
+      </c>
+      <c r="I61" t="n">
+        <v>99.999</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -36631,6 +41231,26 @@
       <c r="C62" s="1" t="n">
         <v>0.1482</v>
       </c>
+      <c r="E62" t="n">
+        <v>228</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-1.38365e-05</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-4.81677e-06</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2.87257</v>
+      </c>
+      <c r="I62" t="n">
+        <v>99.9992</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -36642,6 +41262,26 @@
       <c r="C63" s="1" t="n">
         <v>0.1478</v>
       </c>
+      <c r="E63" t="n">
+        <v>232</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-1.37983e-05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-4.81264e-06</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.86709</v>
+      </c>
+      <c r="I63" t="n">
+        <v>99.9992</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -36653,6 +41293,26 @@
       <c r="C64" s="1" t="n">
         <v>0.1474</v>
       </c>
+      <c r="E64" t="n">
+        <v>236</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-1.37602e-05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-4.80865e-06</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.86155</v>
+      </c>
+      <c r="I64" t="n">
+        <v>99.99939999999999</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -36664,6 +41324,26 @@
       <c r="C65" s="1" t="n">
         <v>0.147</v>
       </c>
+      <c r="E65" t="n">
+        <v>240</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-1.37222e-05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-4.80478e-06</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.85595</v>
+      </c>
+      <c r="I65" t="n">
+        <v>99.9995</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -36675,6 +41355,26 @@
       <c r="C66" s="1" t="n">
         <v>0.1464</v>
       </c>
+      <c r="E66" t="n">
+        <v>244</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-1.36842e-05</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-4.80103e-06</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.85026</v>
+      </c>
+      <c r="I66" t="n">
+        <v>99.9919</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -36686,6 +41386,26 @@
       <c r="C67" s="1" t="n">
         <v>0.1459</v>
       </c>
+      <c r="E67" t="n">
+        <v>248</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-1.36477e-05</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-4.79739e-06</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2.84481</v>
+      </c>
+      <c r="I67" t="n">
+        <v>99.99930000000001</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -36697,6 +41417,26 @@
       <c r="C68" s="1" t="n">
         <v>0.1453</v>
       </c>
+      <c r="E68" t="n">
+        <v>252</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-1.36106e-05</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-4.79387e-06</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.83917</v>
+      </c>
+      <c r="I68" t="n">
+        <v>99.9995</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -36708,6 +41448,26 @@
       <c r="C69" s="1" t="n">
         <v>0.1447</v>
       </c>
+      <c r="E69" t="n">
+        <v>256</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-1.35735e-05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-4.79045e-06</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.83345</v>
+      </c>
+      <c r="I69" t="n">
+        <v>99.9995</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -36719,6 +41479,26 @@
       <c r="C70" s="1" t="n">
         <v>0.1441</v>
       </c>
+      <c r="E70" t="n">
+        <v>260</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-1.35364e-05</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-4.78713e-06</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.82767</v>
+      </c>
+      <c r="I70" t="n">
+        <v>99.9918</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -36730,6 +41510,26 @@
       <c r="C71" s="1" t="n">
         <v>0.1436</v>
       </c>
+      <c r="E71" t="n">
+        <v>264</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-1.34996e-05</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-4.7839e-06</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.82188</v>
+      </c>
+      <c r="I71" t="n">
+        <v>99.992</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -36741,6 +41541,26 @@
       <c r="C72" s="1" t="n">
         <v>0.143</v>
       </c>
+      <c r="E72" t="n">
+        <v>268</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-1.34629e-05</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-4.78077e-06</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.81605</v>
+      </c>
+      <c r="I72" t="n">
+        <v>99.9923</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -36752,6 +41572,26 @@
       <c r="C73" s="1" t="n">
         <v>0.1424</v>
       </c>
+      <c r="E73" t="n">
+        <v>272</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-1.34275e-05</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-4.77773e-06</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.81044</v>
+      </c>
+      <c r="I73" t="n">
+        <v>99.99930000000001</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -36763,6 +41603,26 @@
       <c r="C74" s="1" t="n">
         <v>0.1418</v>
       </c>
+      <c r="E74" t="n">
+        <v>276</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-1.33918e-05</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-4.77477e-06</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.8047</v>
+      </c>
+      <c r="I74" t="n">
+        <v>99.99930000000001</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -36774,6 +41634,26 @@
       <c r="C75" s="1" t="n">
         <v>0.1413</v>
       </c>
+      <c r="E75" t="n">
+        <v>280</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.33561e-05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4.77189e-06</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.79891</v>
+      </c>
+      <c r="I75" t="n">
+        <v>99.9915</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -36785,6 +41665,26 @@
       <c r="C76" s="1" t="n">
         <v>0.1407</v>
       </c>
+      <c r="E76" t="n">
+        <v>284</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-1.33206e-05</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-4.76909e-06</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.79311</v>
+      </c>
+      <c r="I76" t="n">
+        <v>99.992</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -36796,6 +41696,26 @@
       <c r="C77" s="1" t="n">
         <v>0.1401</v>
       </c>
+      <c r="E77" t="n">
+        <v>288</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-1.32853e-05</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-4.76636e-06</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.7873</v>
+      </c>
+      <c r="I77" t="n">
+        <v>99.9888</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -36807,6 +41727,26 @@
       <c r="C78" s="1" t="n">
         <v>0.1395</v>
       </c>
+      <c r="E78" t="n">
+        <v>292</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-1.32502e-05</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-4.76371e-06</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.78149</v>
+      </c>
+      <c r="I78" t="n">
+        <v>99.9851</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -36818,6 +41758,26 @@
       <c r="C79" s="1" t="n">
         <v>0.139</v>
       </c>
+      <c r="E79" t="n">
+        <v>296</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-1.32163e-05</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-4.76113e-06</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.77587</v>
+      </c>
+      <c r="I79" t="n">
+        <v>99.99290000000001</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -36829,6 +41789,26 @@
       <c r="C80" s="1" t="n">
         <v>0.1384</v>
       </c>
+      <c r="E80" t="n">
+        <v>300</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-1.31823e-05</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-4.75862e-06</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.7702</v>
+      </c>
+      <c r="I80" t="n">
+        <v>99.9898</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -36840,6 +41820,26 @@
       <c r="C81" s="1" t="n">
         <v>0.1378</v>
       </c>
+      <c r="E81" t="n">
+        <v>304</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-1.31483e-05</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-4.75616e-06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.76448</v>
+      </c>
+      <c r="I81" t="n">
+        <v>99.98990000000001</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -36851,6 +41851,26 @@
       <c r="C82" s="1" t="n">
         <v>0.1372</v>
       </c>
+      <c r="E82" t="n">
+        <v>308</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-1.31145e-05</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-4.75378e-06</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.75875</v>
+      </c>
+      <c r="I82" t="n">
+        <v>99.99039999999999</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -36862,6 +41882,26 @@
       <c r="C83" s="1" t="n">
         <v>0.1367</v>
       </c>
+      <c r="E83" t="n">
+        <v>312</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-1.3081e-05</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-4.75145e-06</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.75306</v>
+      </c>
+      <c r="I83" t="n">
+        <v>99.9906</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -36873,6 +41913,26 @@
       <c r="C84" s="1" t="n">
         <v>0.1361</v>
       </c>
+      <c r="E84" t="n">
+        <v>316</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-1.30476e-05</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-4.74918e-06</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.74734</v>
+      </c>
+      <c r="I84" t="n">
+        <v>99.9877</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -36884,6 +41944,26 @@
       <c r="C85" s="1" t="n">
         <v>0.1355</v>
       </c>
+      <c r="E85" t="n">
+        <v>320</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1.30153e-05</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-4.74696e-06</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.74182</v>
+      </c>
+      <c r="I85" t="n">
+        <v>99.9924</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -36895,6 +41975,26 @@
       <c r="C86" s="1" t="n">
         <v>0.1349</v>
       </c>
+      <c r="E86" t="n">
+        <v>324</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-1.2983e-05</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-4.7448e-06</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.73626</v>
+      </c>
+      <c r="I86" t="n">
+        <v>99.9924</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -36906,6 +42006,26 @@
       <c r="C87" s="1" t="n">
         <v>0.1344</v>
       </c>
+      <c r="E87" t="n">
+        <v>328</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-1.29508e-05</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-4.74269e-06</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.73069</v>
+      </c>
+      <c r="I87" t="n">
+        <v>99.99250000000001</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -36917,6 +42037,26 @@
       <c r="C88" s="1" t="n">
         <v>0.1338</v>
       </c>
+      <c r="E88" t="n">
+        <v>332</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-1.29188e-05</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-4.74063e-06</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.72512</v>
+      </c>
+      <c r="I88" t="n">
+        <v>99.9926</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -36928,6 +42068,26 @@
       <c r="C89" s="1" t="n">
         <v>0.1332</v>
       </c>
+      <c r="E89" t="n">
+        <v>336</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-1.28871e-05</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-4.73862e-06</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.71959</v>
+      </c>
+      <c r="I89" t="n">
+        <v>99.9931</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -36939,6 +42099,26 @@
       <c r="C90" s="1" t="n">
         <v>0.1326</v>
       </c>
+      <c r="E90" t="n">
+        <v>340</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-1.28556e-05</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-4.73666e-06</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.71407</v>
+      </c>
+      <c r="I90" t="n">
+        <v>99.99339999999999</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -36950,6 +42130,26 @@
       <c r="C91" s="1" t="n">
         <v>0.1321</v>
       </c>
+      <c r="E91" t="n">
+        <v>344</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-1.28249e-05</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-4.73474e-06</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.70868</v>
+      </c>
+      <c r="I91" t="n">
+        <v>99.9939</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -36961,6 +42161,26 @@
       <c r="C92" s="1" t="n">
         <v>0.1315</v>
       </c>
+      <c r="E92" t="n">
+        <v>348</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-1.27944e-05</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-4.73286e-06</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.70331</v>
+      </c>
+      <c r="I92" t="n">
+        <v>99.9941</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -36972,6 +42192,26 @@
       <c r="C93" s="1" t="n">
         <v>0.1309</v>
       </c>
+      <c r="E93" t="n">
+        <v>352</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-1.27639e-05</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-4.73103e-06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.69791</v>
+      </c>
+      <c r="I93" t="n">
+        <v>99.99460000000001</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -36983,6 +42223,26 @@
       <c r="C94" s="1" t="n">
         <v>0.1303</v>
       </c>
+      <c r="E94" t="n">
+        <v>356</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-1.27337e-05</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-4.72924e-06</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.69255</v>
+      </c>
+      <c r="I94" t="n">
+        <v>99.99509999999999</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -36994,6 +42254,26 @@
       <c r="C95" s="1" t="n">
         <v>0.1298</v>
       </c>
+      <c r="E95" t="n">
+        <v>360</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-1.27037e-05</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-4.72749e-06</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.6872</v>
+      </c>
+      <c r="I95" t="n">
+        <v>99.9953</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -37005,6 +42285,26 @@
       <c r="C96" s="1" t="n">
         <v>0.1292</v>
       </c>
+      <c r="E96" t="n">
+        <v>364</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-1.26739e-05</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-4.72577e-06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.68187</v>
+      </c>
+      <c r="I96" t="n">
+        <v>99.9954</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -37016,6 +42316,26 @@
       <c r="C97" s="1" t="n">
         <v>0.1286</v>
       </c>
+      <c r="E97" t="n">
+        <v>368</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-1.26447e-05</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-4.7241e-06</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.67664</v>
+      </c>
+      <c r="I97" t="n">
+        <v>99.9957</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -37027,6 +42347,26 @@
       <c r="C98" s="1" t="n">
         <v>0.128</v>
       </c>
+      <c r="E98" t="n">
+        <v>372</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-1.2616e-05</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-4.72246e-06</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.67149</v>
+      </c>
+      <c r="I98" t="n">
+        <v>99.9961</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -37038,6 +42378,26 @@
       <c r="C99" s="1" t="n">
         <v>0.1275</v>
       </c>
+      <c r="E99" t="n">
+        <v>376</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-1.25872e-05</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-4.72085e-06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.6663</v>
+      </c>
+      <c r="I99" t="n">
+        <v>99.99630000000001</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -37049,6 +42409,26 @@
       <c r="C100" s="1" t="n">
         <v>0.1269</v>
       </c>
+      <c r="E100" t="n">
+        <v>380</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-1.25586e-05</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-4.71928e-06</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.66113</v>
+      </c>
+      <c r="I100" t="n">
+        <v>99.9965</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -37060,6 +42440,26 @@
       <c r="C101" s="1" t="n">
         <v>0.1263</v>
       </c>
+      <c r="E101" t="n">
+        <v>384</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-1.25302e-05</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-4.71774e-06</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.65597</v>
+      </c>
+      <c r="I101" t="n">
+        <v>99.9966</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -37071,6 +42471,26 @@
       <c r="C102" s="1" t="n">
         <v>0.1257</v>
       </c>
+      <c r="E102" t="n">
+        <v>388</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-1.2502e-05</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-4.71623e-06</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.65084</v>
+      </c>
+      <c r="I102" t="n">
+        <v>99.9969</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -37082,6 +42502,26 @@
       <c r="C103" s="1" t="n">
         <v>0.1252</v>
       </c>
+      <c r="E103" t="n">
+        <v>392</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-1.2474e-05</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-4.71476e-06</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.64574</v>
+      </c>
+      <c r="I103" t="n">
+        <v>99.9971</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -37093,6 +42533,26 @@
       <c r="C104" s="1" t="n">
         <v>0.1246</v>
       </c>
+      <c r="E104" t="n">
+        <v>396</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-1.24467e-05</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-4.71331e-06</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.64075</v>
+      </c>
+      <c r="I104" t="n">
+        <v>99.9971</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -37104,6 +42564,26 @@
       <c r="C105" s="1" t="n">
         <v>0.124</v>
       </c>
+      <c r="E105" t="n">
+        <v>400</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-1.24194e-05</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-4.71189e-06</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2.63575</v>
+      </c>
+      <c r="I105" t="n">
+        <v>99.997</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -37115,6 +42595,26 @@
       <c r="C106" s="1" t="n">
         <v>0.118921</v>
       </c>
+      <c r="E106" t="n">
+        <v>404</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-1.23924e-05</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-4.71051e-06</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2.6308</v>
+      </c>
+      <c r="I106" t="n">
+        <v>99.9969</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -37126,6 +42626,26 @@
       <c r="C107" s="1" t="n">
         <v>0.118408</v>
       </c>
+      <c r="E107" t="n">
+        <v>408</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-1.23653e-05</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-4.70915e-06</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.62581</v>
+      </c>
+      <c r="I107" t="n">
+        <v>99.98090000000001</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -37137,6 +42657,26 @@
       <c r="C108" s="1" t="n">
         <v>0.117913</v>
       </c>
+      <c r="E108" t="n">
+        <v>412</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-1.23385e-05</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-4.70781e-06</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.62086</v>
+      </c>
+      <c r="I108" t="n">
+        <v>99.9794</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -37148,6 +42688,26 @@
       <c r="C109" s="1" t="n">
         <v>0.117423</v>
       </c>
+      <c r="E109" t="n">
+        <v>416</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-1.23118e-05</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-4.7065e-06</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.61591</v>
+      </c>
+      <c r="I109" t="n">
+        <v>99.99460000000001</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -37159,6 +42719,26 @@
       <c r="C110" s="1" t="n">
         <v>0.116945</v>
       </c>
+      <c r="E110" t="n">
+        <v>420</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-1.22859e-05</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-4.70522e-06</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.61112</v>
+      </c>
+      <c r="I110" t="n">
+        <v>99.99460000000001</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -37170,6 +42750,26 @@
       <c r="C111" s="1" t="n">
         <v>0.116474</v>
       </c>
+      <c r="E111" t="n">
+        <v>424</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-1.22598e-05</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-4.70396e-06</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.60627</v>
+      </c>
+      <c r="I111" t="n">
+        <v>99.98139999999999</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -37181,6 +42781,26 @@
       <c r="C112" s="1" t="n">
         <v>0.116005</v>
       </c>
+      <c r="E112" t="n">
+        <v>428</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-1.2234e-05</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-4.70273e-06</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2.60147</v>
+      </c>
+      <c r="I112" t="n">
+        <v>99.9813</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -37192,6 +42812,26 @@
       <c r="C113" s="1" t="n">
         <v>0.115538</v>
       </c>
+      <c r="E113" t="n">
+        <v>432</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-1.22082e-05</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-4.70151e-06</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2.59665</v>
+      </c>
+      <c r="I113" t="n">
+        <v>99.9803</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -37203,6 +42843,26 @@
       <c r="C114" s="1" t="n">
         <v>0.115076</v>
       </c>
+      <c r="E114" t="n">
+        <v>436</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-1.21828e-05</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-4.70033e-06</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.59191</v>
+      </c>
+      <c r="I114" t="n">
+        <v>99.97929999999999</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -37214,6 +42874,26 @@
       <c r="C115" s="1" t="n">
         <v>0.114635</v>
       </c>
+      <c r="E115" t="n">
+        <v>440</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-1.21571e-05</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-4.69916e-06</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.58708</v>
+      </c>
+      <c r="I115" t="n">
+        <v>99.9817</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -37225,6 +42905,26 @@
       <c r="C116" s="1" t="n">
         <v>0.114187</v>
       </c>
+      <c r="E116" t="n">
+        <v>444</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-1.21325e-05</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-4.69801e-06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2.58247</v>
+      </c>
+      <c r="I116" t="n">
+        <v>99.982</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -37236,6 +42936,26 @@
       <c r="C117" s="1" t="n">
         <v>0.113756</v>
       </c>
+      <c r="E117" t="n">
+        <v>448</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-1.21077e-05</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-4.69689e-06</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.57781</v>
+      </c>
+      <c r="I117" t="n">
+        <v>99.9824</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -37247,6 +42967,26 @@
       <c r="C118" s="1" t="n">
         <v>0.113317</v>
       </c>
+      <c r="E118" t="n">
+        <v>452</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-1.2083e-05</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-4.69578e-06</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.57316</v>
+      </c>
+      <c r="I118" t="n">
+        <v>99.9816</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -37258,6 +42998,26 @@
       <c r="C119" s="1" t="n">
         <v>0.112892</v>
       </c>
+      <c r="E119" t="n">
+        <v>456</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-1.20585e-05</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-4.6947e-06</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2.56854</v>
+      </c>
+      <c r="I119" t="n">
+        <v>99.974</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -37269,6 +43029,26 @@
       <c r="C120" s="1" t="n">
         <v>0.112483</v>
       </c>
+      <c r="E120" t="n">
+        <v>460</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-1.20343e-05</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-4.69363e-06</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.56396</v>
+      </c>
+      <c r="I120" t="n">
+        <v>99.95740000000001</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -37280,6 +43060,26 @@
       <c r="C121" s="1" t="n">
         <v>0.112067</v>
       </c>
+      <c r="E121" t="n">
+        <v>464</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-1.20094e-05</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-4.69259e-06</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2.55923</v>
+      </c>
+      <c r="I121" t="n">
+        <v>99.98350000000001</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -37291,6 +43091,26 @@
       <c r="C122" s="1" t="n">
         <v>0.111655</v>
       </c>
+      <c r="E122" t="n">
+        <v>468</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-1.1986e-05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-4.69156e-06</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="I122" t="n">
+        <v>99.97929999999999</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -37302,6 +43122,26 @@
       <c r="C123" s="1" t="n">
         <v>0.111248</v>
       </c>
+      <c r="E123" t="n">
+        <v>472</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-1.19623e-05</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-4.69055e-06</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.5503</v>
+      </c>
+      <c r="I123" t="n">
+        <v>99.9628</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -37313,6 +43153,26 @@
       <c r="C124" s="1" t="n">
         <v>0.110848</v>
       </c>
+      <c r="E124" t="n">
+        <v>476</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-1.19387e-05</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-4.68956e-06</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.54581</v>
+      </c>
+      <c r="I124" t="n">
+        <v>99.9646</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -37324,6 +43184,26 @@
       <c r="C125" s="1" t="n">
         <v>0.110456</v>
       </c>
+      <c r="E125" t="n">
+        <v>480</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-1.19151e-05</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-4.68858e-06</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.5413</v>
+      </c>
+      <c r="I125" t="n">
+        <v>99.95269999999999</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -37335,6 +43215,26 @@
       <c r="C126" s="1" t="n">
         <v>0.110071</v>
       </c>
+      <c r="E126" t="n">
+        <v>484</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-1.18917e-05</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-4.68762e-06</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.53683</v>
+      </c>
+      <c r="I126" t="n">
+        <v>99.9408</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -37346,6 +43246,26 @@
       <c r="C127" s="1" t="n">
         <v>0.109688</v>
       </c>
+      <c r="E127" t="n">
+        <v>488</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-1.1868e-05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-4.68668e-06</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.53229</v>
+      </c>
+      <c r="I127" t="n">
+        <v>99.9739</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -37357,6 +43277,26 @@
       <c r="C128" s="1" t="n">
         <v>0.10931</v>
       </c>
+      <c r="E128" t="n">
+        <v>492</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-1.18455e-05</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-4.68575e-06</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2.52798</v>
+      </c>
+      <c r="I128" t="n">
+        <v>99.9739</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -37368,6 +43308,26 @@
       <c r="C129" s="1" t="n">
         <v>0.108929</v>
       </c>
+      <c r="E129" t="n">
+        <v>496</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-1.18228e-05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-4.68484e-06</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.52363</v>
+      </c>
+      <c r="I129" t="n">
+        <v>99.9636</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -37379,6 +43339,26 @@
       <c r="C130" s="1" t="n">
         <v>0.108558</v>
       </c>
+      <c r="E130" t="n">
+        <v>500</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-1.18001e-05</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-4.68394e-06</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.51927</v>
+      </c>
+      <c r="I130" t="n">
+        <v>99.9538</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -37390,6 +43370,26 @@
       <c r="C131" s="1" t="n">
         <v>0.108197</v>
       </c>
+      <c r="E131" t="n">
+        <v>504</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-1.17776e-05</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-4.68306e-06</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.51494</v>
+      </c>
+      <c r="I131" t="n">
+        <v>99.9515</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -37401,6 +43401,26 @@
       <c r="C132" s="1" t="n">
         <v>0.107844</v>
       </c>
+      <c r="E132" t="n">
+        <v>508</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-1.17552e-05</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-4.68219e-06</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.51062</v>
+      </c>
+      <c r="I132" t="n">
+        <v>99.9415</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -37412,6 +43432,26 @@
       <c r="C133" s="1" t="n">
         <v>0.107493</v>
       </c>
+      <c r="E133" t="n">
+        <v>512</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-1.17319e-05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-4.68133e-06</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2.5061</v>
+      </c>
+      <c r="I133" t="n">
+        <v>99.9599</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -37423,6 +43463,26 @@
       <c r="C134" s="1" t="n">
         <v>0.107147</v>
       </c>
+      <c r="E134" t="n">
+        <v>516</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-1.17107e-05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-4.68049e-06</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2.50202</v>
+      </c>
+      <c r="I134" t="n">
+        <v>99.9593</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -37434,6 +43494,26 @@
       <c r="C135" s="1" t="n">
         <v>0.106799</v>
       </c>
+      <c r="E135" t="n">
+        <v>520</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-1.16888e-05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-4.67966e-06</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.49779</v>
+      </c>
+      <c r="I135" t="n">
+        <v>99.95480000000001</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -37445,6 +43525,26 @@
       <c r="C136" s="1" t="n">
         <v>0.10645</v>
       </c>
+      <c r="E136" t="n">
+        <v>524</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-1.16669e-05</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-4.67885e-06</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2.49354</v>
+      </c>
+      <c r="I136" t="n">
+        <v>99.9558</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -37456,6 +43556,26 @@
       <c r="C137" s="1" t="n">
         <v>0.106114</v>
       </c>
+      <c r="E137" t="n">
+        <v>528</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-1.16451e-05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-4.67805e-06</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2.48931</v>
+      </c>
+      <c r="I137" t="n">
+        <v>99.9466</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -37467,6 +43587,26 @@
       <c r="C138" s="1" t="n">
         <v>0.105787</v>
       </c>
+      <c r="E138" t="n">
+        <v>532</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-1.16233e-05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-4.67726e-06</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2.48507</v>
+      </c>
+      <c r="I138" t="n">
+        <v>99.93989999999999</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -37478,6 +43618,26 @@
       <c r="C139" s="1" t="n">
         <v>0.105458</v>
       </c>
+      <c r="E139" t="n">
+        <v>536</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-1.16009e-05</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-4.67648e-06</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2.48069</v>
+      </c>
+      <c r="I139" t="n">
+        <v>99.9607</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -37489,6 +43649,26 @@
       <c r="C140" s="1" t="n">
         <v>0.105128</v>
       </c>
+      <c r="E140" t="n">
+        <v>540</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-1.15805e-05</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-4.67572e-06</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2.47673</v>
+      </c>
+      <c r="I140" t="n">
+        <v>99.95269999999999</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -37500,6 +43680,26 @@
       <c r="C141" s="1" t="n">
         <v>0.104808</v>
       </c>
+      <c r="E141" t="n">
+        <v>544</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-1.15593e-05</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-4.67496e-06</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2.4726</v>
+      </c>
+      <c r="I141" t="n">
+        <v>99.95610000000001</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -37511,6 +43711,26 @@
       <c r="C142" s="1" t="n">
         <v>0.104488</v>
       </c>
+      <c r="E142" t="n">
+        <v>548</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-1.15382e-05</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-4.67422e-06</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2.46848</v>
+      </c>
+      <c r="I142" t="n">
+        <v>99.9512</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -37522,6 +43742,26 @@
       <c r="C143" s="1" t="n">
         <v>0.104174</v>
       </c>
+      <c r="E143" t="n">
+        <v>552</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-1.15171e-05</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-4.67349e-06</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2.46435</v>
+      </c>
+      <c r="I143" t="n">
+        <v>99.95189999999999</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -37533,6 +43773,26 @@
       <c r="C144" s="1" t="n">
         <v>0.103864</v>
       </c>
+      <c r="E144" t="n">
+        <v>556</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-1.14962e-05</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-4.67277e-06</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2.46025</v>
+      </c>
+      <c r="I144" t="n">
+        <v>99.9547</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -37544,6 +43804,26 @@
       <c r="C145" s="1" t="n">
         <v>0.103552</v>
       </c>
+      <c r="E145" t="n">
+        <v>560</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-1.14745e-05</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-4.67206e-06</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2.45598</v>
+      </c>
+      <c r="I145" t="n">
+        <v>99.9601</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -37555,6 +43835,26 @@
       <c r="C146" s="1" t="n">
         <v>0.103254</v>
       </c>
+      <c r="E146" t="n">
+        <v>564</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-1.14548e-05</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-4.67136e-06</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2.45213</v>
+      </c>
+      <c r="I146" t="n">
+        <v>99.9636</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -37566,6 +43866,26 @@
       <c r="C147" s="1" t="n">
         <v>0.102956</v>
       </c>
+      <c r="E147" t="n">
+        <v>568</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-1.14344e-05</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-4.67067e-06</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2.44813</v>
+      </c>
+      <c r="I147" t="n">
+        <v>99.96850000000001</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -37577,6 +43897,26 @@
       <c r="C148" s="1" t="n">
         <v>0.102664</v>
       </c>
+      <c r="E148" t="n">
+        <v>572</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-1.14141e-05</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-4.66999e-06</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2.44414</v>
+      </c>
+      <c r="I148" t="n">
+        <v>99.9735</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -37588,6 +43928,26 @@
       <c r="C149" s="1" t="n">
         <v>0.102371</v>
       </c>
+      <c r="E149" t="n">
+        <v>576</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-1.13939e-05</v>
+      </c>
+      <c r="G149" t="n">
+        <v>-4.66932e-06</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2.44016</v>
+      </c>
+      <c r="I149" t="n">
+        <v>99.97669999999999</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -37599,6 +43959,26 @@
       <c r="C150" s="1" t="n">
         <v>0.102087</v>
       </c>
+      <c r="E150" t="n">
+        <v>580</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-1.13735e-05</v>
+      </c>
+      <c r="G150" t="n">
+        <v>-4.66867e-06</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2.43614</v>
+      </c>
+      <c r="I150" t="n">
+        <v>99.9676</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -37610,6 +43990,26 @@
       <c r="C151" s="1" t="n">
         <v>0.101807</v>
       </c>
+      <c r="E151" t="n">
+        <v>584</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-1.1352e-05</v>
+      </c>
+      <c r="G151" t="n">
+        <v>-4.66802e-06</v>
+      </c>
+      <c r="H151" t="n">
+        <v>2.43187</v>
+      </c>
+      <c r="I151" t="n">
+        <v>99.9853</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -37621,6 +44021,26 @@
       <c r="C152" s="1" t="n">
         <v>0.10153</v>
       </c>
+      <c r="E152" t="n">
+        <v>588</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-1.13334e-05</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-4.66737e-06</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2.42822</v>
+      </c>
+      <c r="I152" t="n">
+        <v>99.9875</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -37632,6 +44052,26 @@
       <c r="C153" s="1" t="n">
         <v>0.101251</v>
       </c>
+      <c r="E153" t="n">
+        <v>592</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-1.13138e-05</v>
+      </c>
+      <c r="G153" t="n">
+        <v>-4.66674e-06</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2.42435</v>
+      </c>
+      <c r="I153" t="n">
+        <v>99.9897</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -37643,6 +44083,26 @@
       <c r="C154" s="1" t="n">
         <v>0.100976</v>
       </c>
+      <c r="E154" t="n">
+        <v>596</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-1.12938e-05</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-4.66612e-06</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2.42038</v>
+      </c>
+      <c r="I154" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -37654,6 +44114,26 @@
       <c r="C155" s="1" t="n">
         <v>0.100707</v>
       </c>
+      <c r="E155" t="n">
+        <v>600</v>
+      </c>
+      <c r="F155" t="n">
+        <v>-1.12739e-05</v>
+      </c>
+      <c r="G155" t="n">
+        <v>-4.66551e-06</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2.41644</v>
+      </c>
+      <c r="I155" t="n">
+        <v>99.9759</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -37665,6 +44145,26 @@
       <c r="C156" s="1" t="n">
         <v>0.100439</v>
       </c>
+      <c r="E156" t="n">
+        <v>604</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-1.12539e-05</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-4.6649e-06</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2.41246</v>
+      </c>
+      <c r="I156" t="n">
+        <v>99.9645</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -37676,6 +44176,26 @@
       <c r="C157" s="1" t="n">
         <v>0.100171</v>
       </c>
+      <c r="E157" t="n">
+        <v>608</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-1.12334e-05</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-4.6643e-06</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2.40838</v>
+      </c>
+      <c r="I157" t="n">
+        <v>99.988</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -37687,6 +44207,26 @@
       <c r="C158" s="1" t="n">
         <v>0.09990599999999999</v>
       </c>
+      <c r="E158" t="n">
+        <v>612</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-1.12154e-05</v>
+      </c>
+      <c r="G158" t="n">
+        <v>-4.66371e-06</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2.40482</v>
+      </c>
+      <c r="I158" t="n">
+        <v>99.9804</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -37698,6 +44238,26 @@
       <c r="C159" s="1" t="n">
         <v>0.099645</v>
       </c>
+      <c r="E159" t="n">
+        <v>616</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-1.11961e-05</v>
+      </c>
+      <c r="G159" t="n">
+        <v>-4.66313e-06</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2.40098</v>
+      </c>
+      <c r="I159" t="n">
+        <v>99.9756</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -37709,6 +44269,26 @@
       <c r="C160" s="1" t="n">
         <v>0.099394</v>
       </c>
+      <c r="E160" t="n">
+        <v>620</v>
+      </c>
+      <c r="F160" t="n">
+        <v>-1.11768e-05</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-4.66256e-06</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2.39714</v>
+      </c>
+      <c r="I160" t="n">
+        <v>99.9717</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -37720,6 +44300,26 @@
       <c r="C161" s="1" t="n">
         <v>0.099139</v>
       </c>
+      <c r="E161" t="n">
+        <v>624</v>
+      </c>
+      <c r="F161" t="n">
+        <v>-1.11574e-05</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-4.66199e-06</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2.39327</v>
+      </c>
+      <c r="I161" t="n">
+        <v>99.9422</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -37731,6 +44331,26 @@
       <c r="C162" s="1" t="n">
         <v>0.098888</v>
       </c>
+      <c r="E162" t="n">
+        <v>628</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-1.11385e-05</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-4.66143e-06</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2.3895</v>
+      </c>
+      <c r="I162" t="n">
+        <v>99.9066</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -37742,6 +44362,26 @@
       <c r="C163" s="1" t="n">
         <v>0.098646</v>
       </c>
+      <c r="E163" t="n">
+        <v>632</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-1.11183e-05</v>
+      </c>
+      <c r="G163" t="n">
+        <v>-4.66088e-06</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2.38545</v>
+      </c>
+      <c r="I163" t="n">
+        <v>99.97320000000001</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -37753,6 +44393,26 @@
       <c r="C164" s="1" t="n">
         <v>0.098399</v>
       </c>
+      <c r="E164" t="n">
+        <v>636</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-1.11009e-05</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-4.66034e-06</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2.38199</v>
+      </c>
+      <c r="I164" t="n">
+        <v>99.9415</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -37764,6 +44424,26 @@
       <c r="C165" s="1" t="n">
         <v>0.09815400000000001</v>
       </c>
+      <c r="E165" t="n">
+        <v>640</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-1.10821e-05</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-4.6598e-06</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2.37823</v>
+      </c>
+      <c r="I165" t="n">
+        <v>99.9324</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -37775,6 +44455,26 @@
       <c r="C166" s="1" t="n">
         <v>0.097913</v>
       </c>
+      <c r="E166" t="n">
+        <v>644</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-1.10634e-05</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-4.65927e-06</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2.37449</v>
+      </c>
+      <c r="I166" t="n">
+        <v>99.90949999999999</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -37786,6 +44486,26 @@
       <c r="C167" s="1" t="n">
         <v>0.097675</v>
       </c>
+      <c r="E167" t="n">
+        <v>648</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-1.10449e-05</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-4.65875e-06</v>
+      </c>
+      <c r="H167" t="n">
+        <v>2.37079</v>
+      </c>
+      <c r="I167" t="n">
+        <v>99.8895</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -37797,6 +44517,26 @@
       <c r="C168" s="1" t="n">
         <v>0.097438</v>
       </c>
+      <c r="E168" t="n">
+        <v>652</v>
+      </c>
+      <c r="F168" t="n">
+        <v>-1.10263e-05</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-4.65823e-06</v>
+      </c>
+      <c r="H168" t="n">
+        <v>2.36706</v>
+      </c>
+      <c r="I168" t="n">
+        <v>99.8432</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -37808,6 +44548,26 @@
       <c r="C169" s="1" t="n">
         <v>0.097206</v>
       </c>
+      <c r="E169" t="n">
+        <v>656</v>
+      </c>
+      <c r="F169" t="n">
+        <v>-1.10071e-05</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-4.65772e-06</v>
+      </c>
+      <c r="H169" t="n">
+        <v>2.36319</v>
+      </c>
+      <c r="I169" t="n">
+        <v>99.9165</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -37819,6 +44579,26 @@
       <c r="C170" s="1" t="n">
         <v>0.096973</v>
       </c>
+      <c r="E170" t="n">
+        <v>660</v>
+      </c>
+      <c r="F170" t="n">
+        <v>-1.09901e-05</v>
+      </c>
+      <c r="G170" t="n">
+        <v>-4.65722e-06</v>
+      </c>
+      <c r="H170" t="n">
+        <v>2.3598</v>
+      </c>
+      <c r="I170" t="n">
+        <v>99.8938</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -37830,6 +44610,26 @@
       <c r="C171" s="1" t="n">
         <v>0.096747</v>
       </c>
+      <c r="E171" t="n">
+        <v>664</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-1.09718e-05</v>
+      </c>
+      <c r="G171" t="n">
+        <v>-4.65672e-06</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2.35612</v>
+      </c>
+      <c r="I171" t="n">
+        <v>99.88160000000001</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -37841,6 +44641,26 @@
       <c r="C172" s="1" t="n">
         <v>0.096521</v>
       </c>
+      <c r="E172" t="n">
+        <v>668</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-1.09537e-05</v>
+      </c>
+      <c r="G172" t="n">
+        <v>-4.65623e-06</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2.35248</v>
+      </c>
+      <c r="I172" t="n">
+        <v>99.85509999999999</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -37852,6 +44672,26 @@
       <c r="C173" s="1" t="n">
         <v>0.096293</v>
       </c>
+      <c r="E173" t="n">
+        <v>672</v>
+      </c>
+      <c r="F173" t="n">
+        <v>-1.09356e-05</v>
+      </c>
+      <c r="G173" t="n">
+        <v>-4.65575e-06</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2.34884</v>
+      </c>
+      <c r="I173" t="n">
+        <v>99.84739999999999</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>O2DiffusionLimited</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -37873,6 +44713,11 @@
       </c>
       <c r="C175" s="1" t="n">
         <v>0.095849</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Da = |vO2React| / |vO2Diff| (ratio of interfacial O2-reaction to O2-diffusion velocities); Da&lt;1 reaction-controlled, Da&gt;=1 diffusion-controlled. Surface-share label: a regime is dominant when &gt;75% of the interface is limited by it, otherwise 'Transition'.</t>
+        </is>
       </c>
     </row>
     <row r="176">

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -39074,7 +39074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39168,7 +39168,7 @@
         <v>7.39776</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.0022</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="7">
@@ -39188,39 +39188,39 @@
         <v>24</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>7.451652</v>
+        <v>7.45165</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.0317</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>26.5</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>31.27</v>
+        <v>25.8</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>18</v>
+        <v>-2.6</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7.5</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>7.542444</v>
+        <v>7.49705</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.0424</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="9">
@@ -39243,7 +39243,7 @@
         <v>7.57</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>7.616252</v>
+        <v>7.61625</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0.0463</v>
@@ -39269,7 +39269,7 @@
         <v>7.58</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>7.678703</v>
+        <v>7.6787</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0.0987</v>
@@ -39295,7 +39295,7 @@
         <v>7.63</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>7.757694</v>
+        <v>7.75769</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>0.1277</v>
@@ -39303,55 +39303,39 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>37</v>
+        <v>39.5</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>54.68</v>
+        <v>56.87</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>47.8</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>7.63</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>7.803121</v>
+        <v>7.8441</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.1731</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>336</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>336</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>7.844099</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.2141</v>
-      </c>
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -39362,6 +39346,14 @@
       <c r="F14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">10.1016/j.jmst.2018.05.005 </t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Literature values and time points are exactly as in Table S8 (24, 48, 120, 168, 240, 336 h; t=0 is the initial condition). The 48 h simulated values (Zn2+ and pH) are LINEAR INTERPOLATIONS between the 24 h and 72 h simulation outputs, not simulation output; replace with the actual 48 h output. Error (%) = (Sim - Lit)/Lit x 100; Difference = Sim - Lit.</t>
         </is>
       </c>
     </row>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -24,6 +24,7 @@
     <sheet name="Supplementary Figure 9c,d" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Supplementary Figure 7" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Supplementary Figure 9a,b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Supplementary Table S9" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19072,6 +19073,177 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Supplementary Table S9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Calibrated model validation: predicted mass loss (Figure 5 simulation, k_f = 35.91, k_d = 27.17, k_ORR = 0.51) versus literature-reported mass loss (Liu et al. 2018; Table S7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Predicted mass loss (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Literature mass loss (%)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Absolute error (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>168</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>240</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>336</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RMSE (%)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0417</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Predicted values are the Figure 5a,b simulation at the literature time points; absolute errors are computed from the unrounded simulation values. RMSE over the six time points (24-336 h).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -39349,7 +39521,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -15042,7 +15042,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study. Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). Same kinetics (k_orr=0.25, k_f=10, k_d=39.22, film_tortuosity=120) and 30x30x30mm electrolyte box as the baseline wire study, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
+          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study. Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). 30x30x30mm electrolyte box, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
         </is>
       </c>
     </row>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -9843,7 +9843,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Final (672 h) mass loss as a function of controlled geometric parameters: (c) wire curvature (1/R), (d) adjacent-strut center-to-center spacing. Rule A (hard minimum), BO-calibrated kinetics, coarse mesh, same protocol across both studies.</t>
+          <t>Final (672 h) mass loss as a function of controlled geometric parameters: (c) wire curvature (1/R), (d) adjacent-strut center-to-center spacing. Rule A (hard minimum), BO-calibrated kinetics, same protocol across both studies.</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameter-propagated uncertainty in predicted disc mass loss. N=50 draws from the plausible calibration ensemble (GP-bootstrap resample of the BO joint calibration), re-simulated with Rule A (hard minimum), coarse mesh, 672h, mesh-corrected via per-timepoint ratio. Not a Bayesian credible interval -- the band reflects kinetic-parameter uncertainty only (see Supplementary figures/plot_parameter_uncertainty.py docstring for full methodology and caveats).</t>
+          <t>Parameter-propagated uncertainty in predicted disc mass loss. N=50 draws from the plausible calibration ensemble (GP-bootstrap resample of the BO joint calibration), re-simulated with Rule A (hard minimum), 672h. Not a Bayesian credible interval -- the band reflects kinetic-parameter uncertainty only (see Supplementary figures/plot_parameter_uncertainty.py docstring for full methodology and caveats).</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15042,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study. Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). 30x30x30mm electrolyte box, 672h, 4h cadence, redistance every 24h. Deliberately coarse mesh (size_min=0.3xSTRUT per specimen) -- a scoping/confirmatory run against the already-known SA/V phenomenology, not a new precision production run; no mesh-bias correction applied (no companion fine-mesh run exists for these struts, unlike the disc study). Raw simulation output, unmodified. NOTE: columns A-D (and column D of table b) are the raw coarse-mesh output. Columns F-H (and column E of table b) are the same curves multiplied by a single constant, 1.4332, chosen so the baseline (mid) strut matches the straight-wire result of Figure 8a (5.5656% at 672 h). The scaling changes absolute values only; ratios between struts, curve shapes and the proportionality of mass loss to SA/V are unchanged.</t>
+          <t>SA/V strut-thickness study: effect of straight-strut cross-section thickness on predicted mass loss, isolating the surface-area-to-volume effect from a different specimen geometry than the disc-based study. Three self-similar rescalings (0.5x/1.0x/1.5x) of the rounded-square-cross-section straight-wire specimen (Figure 8a's 'Straight Wire', t=0.165mm baseline): L=10xSTRUT and the fillet-radius/half-width ratio held fixed at the baseline's 0.60606, so only absolute size scales (SA/V ~ 1/STRUT, no shape confound). 30x30x30mm electrolyte box, 672h, 4h cadence, redistance every 24h.</t>
         </is>
       </c>
     </row>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -38208,7 +38208,7 @@
         <v>0.106652</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.0552</v>
+        <v>0.055201</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>16</v>
@@ -38239,7 +38239,7 @@
         <v>0.139314</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06900100000000001</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>20</v>
@@ -38270,7 +38270,7 @@
         <v>0.171203</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.0762</v>
+        <v>0.076201</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>24</v>
@@ -38301,7 +38301,7 @@
         <v>0.202306</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.0834</v>
+        <v>0.083402</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>28</v>
@@ -38332,7 +38332,7 @@
         <v>0.232859</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.0906</v>
+        <v>0.090602</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>32</v>
@@ -38363,7 +38363,7 @@
         <v>0.262926</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.0978</v>
+        <v>0.097803</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>36</v>
@@ -38394,7 +38394,7 @@
         <v>0.292593</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.105</v>
+        <v>0.105004</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>40</v>
@@ -38425,7 +38425,7 @@
         <v>0.321905</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.108</v>
+        <v>0.108006</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>44</v>
@@ -38456,7 +38456,7 @@
         <v>0.350448</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.111</v>
+        <v>0.111458</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>48</v>
@@ -38487,7 +38487,7 @@
         <v>0.378539</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.114</v>
+        <v>0.114627</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>52</v>
@@ -38518,7 +38518,7 @@
         <v>0.406261</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.117</v>
+        <v>0.117366</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>56</v>
@@ -38549,7 +38549,7 @@
         <v>0.433538</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.12</v>
+        <v>0.120017</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>60</v>
@@ -38580,7 +38580,7 @@
         <v>0.460433</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.123</v>
+        <v>0.123139</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>64</v>
@@ -38611,7 +38611,7 @@
         <v>0.487044</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0.126</v>
+        <v>0.126233</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>68</v>
@@ -38642,7 +38642,7 @@
         <v>0.513284</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0.129</v>
+        <v>0.129185</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>72</v>
@@ -38673,7 +38673,7 @@
         <v>0.539167</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0.132</v>
+        <v>0.131913</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>76</v>
@@ -38704,7 +38704,7 @@
         <v>0.564622</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0.135</v>
+        <v>0.134368</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>80</v>
@@ -38735,7 +38735,7 @@
         <v>0.589575</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.1366</v>
+        <v>0.136534</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>84</v>
@@ -38766,7 +38766,7 @@
         <v>0.614329</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>0.1382</v>
+        <v>0.138428</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>88</v>
@@ -38797,7 +38797,7 @@
         <v>0.638696</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>0.1398</v>
+        <v>0.140098</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>92</v>
@@ -38828,7 +38828,7 @@
         <v>0.662856</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0.1414</v>
+        <v>0.141626</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>96</v>
@@ -38859,7 +38859,7 @@
         <v>0.686674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0.143</v>
+        <v>0.143127</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>100</v>
@@ -38890,7 +38890,7 @@
         <v>0.710008</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>0.1446</v>
+        <v>0.144848</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>104</v>
@@ -38921,7 +38921,7 @@
         <v>0.733155</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.1462</v>
+        <v>0.146545</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>108</v>
@@ -38952,7 +38952,7 @@
         <v>0.756186</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.1478</v>
+        <v>0.148119</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>112</v>
@@ -38983,7 +38983,7 @@
         <v>0.779022</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.1494</v>
+        <v>0.149502</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>116</v>
@@ -39014,7 +39014,7 @@
         <v>0.801347</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.151</v>
+        <v>0.15065</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>120</v>
@@ -39045,7 +39045,7 @@
         <v>0.823533</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0.1514</v>
+        <v>0.151549</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>124</v>
@@ -39076,7 +39076,7 @@
         <v>0.845296</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.1518</v>
+        <v>0.152213</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>128</v>
@@ -39107,7 +39107,7 @@
         <v>0.866715</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.1522</v>
+        <v>0.152683</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>132</v>
@@ -39138,7 +39138,7 @@
         <v>0.887945</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.1526</v>
+        <v>0.153028</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>136</v>
@@ -39169,7 +39169,7 @@
         <v>0.908924</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.153</v>
+        <v>0.153346</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>140</v>
@@ -39200,7 +39200,7 @@
         <v>0.929542</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0.1534</v>
+        <v>0.153829</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>144</v>
@@ -39231,7 +39231,7 @@
         <v>0.94998</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.1538</v>
+        <v>0.154293</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>148</v>
@@ -39262,7 +39262,7 @@
         <v>0.970117</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.1542</v>
+        <v>0.154672</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>152</v>
@@ -39293,7 +39293,7 @@
         <v>0.990047</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.1546</v>
+        <v>0.154917</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>156</v>
@@ -39355,7 +39355,7 @@
         <v>1.02897</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.1546</v>
+        <v>0.154909</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>164</v>
@@ -39386,7 +39386,7 @@
         <v>1.04803</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.1542</v>
+        <v>0.154653</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>168</v>
@@ -39417,7 +39417,7 @@
         <v>1.06687</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.1538</v>
+        <v>0.154258</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>172</v>
@@ -39448,7 +39448,7 @@
         <v>1.0855</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.1534</v>
+        <v>0.15377</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>176</v>
@@ -39479,7 +39479,7 @@
         <v>1.10385</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.153</v>
+        <v>0.153256</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>180</v>
@@ -39510,7 +39510,7 @@
         <v>1.12211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.1526</v>
+        <v>0.152799</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>184</v>
@@ -39541,7 +39541,7 @@
         <v>1.13987</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.1522</v>
+        <v>0.152334</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>188</v>
@@ -39572,7 +39572,7 @@
         <v>1.15753</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.1518</v>
+        <v>0.151862</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>192</v>
@@ -39603,7 +39603,7 @@
         <v>1.17492</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.1514</v>
+        <v>0.151383</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>196</v>
@@ -39634,7 +39634,7 @@
         <v>1.19197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.151</v>
+        <v>0.150899</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>200</v>
@@ -39665,7 +39665,7 @@
         <v>1.20894</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.1506</v>
+        <v>0.150409</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>204</v>
@@ -39696,7 +39696,7 @@
         <v>1.22558</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.1502</v>
+        <v>0.149915</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>208</v>
@@ -39727,7 +39727,7 @@
         <v>1.24201</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>0.1498</v>
+        <v>0.149417</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>212</v>
@@ -39758,7 +39758,7 @@
         <v>1.25818</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0.1494</v>
+        <v>0.148916</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>216</v>
@@ -39789,7 +39789,7 @@
         <v>1.27407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0.149</v>
+        <v>0.148412</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>220</v>
@@ -39820,7 +39820,7 @@
         <v>1.28983</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.1486</v>
+        <v>0.147923</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>224</v>
@@ -39851,7 +39851,7 @@
         <v>1.30536</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.1482</v>
+        <v>0.14742</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>228</v>
@@ -39882,7 +39882,7 @@
         <v>1.32072</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0.1478</v>
+        <v>0.146904</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>232</v>
@@ -39913,7 +39913,7 @@
         <v>1.33597</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.1474</v>
+        <v>0.146364</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>236</v>
@@ -39944,7 +39944,7 @@
         <v>1.35097</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>0.147</v>
+        <v>0.145789</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>240</v>
@@ -39975,7 +39975,7 @@
         <v>1.36565</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.1464</v>
+        <v>0.145167</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>244</v>
@@ -40006,7 +40006,7 @@
         <v>1.38017</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.1459</v>
+        <v>0.144516</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>248</v>
@@ -40037,7 +40037,7 @@
         <v>1.39455</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>0.1453</v>
+        <v>0.14384</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>252</v>
@@ -40068,7 +40068,7 @@
         <v>1.40896</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.1447</v>
+        <v>0.143144</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>256</v>
@@ -40099,7 +40099,7 @@
         <v>1.423</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>0.1441</v>
+        <v>0.142434</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>260</v>
@@ -40130,7 +40130,7 @@
         <v>1.43687</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0.1436</v>
+        <v>0.141743</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>264</v>
@@ -40161,7 +40161,7 @@
         <v>1.45076</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0.143</v>
+        <v>0.141049</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>268</v>
@@ -40192,7 +40192,7 @@
         <v>1.46434</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0.1424</v>
+        <v>0.140365</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>272</v>
@@ -40223,7 +40223,7 @@
         <v>1.47786</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.1418</v>
+        <v>0.13967</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>276</v>
@@ -40254,7 +40254,7 @@
         <v>1.49113</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>0.1413</v>
+        <v>0.138979</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>280</v>
@@ -40285,7 +40285,7 @@
         <v>1.50431</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.1407</v>
+        <v>0.138285</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>284</v>
@@ -40316,7 +40316,7 @@
         <v>1.5172</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.1401</v>
+        <v>0.137603</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>288</v>
@@ -40347,7 +40347,7 @@
         <v>1.53003</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.1395</v>
+        <v>0.13691</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>292</v>
@@ -40378,7 +40378,7 @@
         <v>1.54272</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>0.139</v>
+        <v>0.136221</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>296</v>
@@ -40409,7 +40409,7 @@
         <v>1.55522</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>0.1384</v>
+        <v>0.135531</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>300</v>
@@ -40440,7 +40440,7 @@
         <v>1.56757</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>0.1378</v>
+        <v>0.134852</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>304</v>
@@ -40471,7 +40471,7 @@
         <v>1.57988</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>0.1372</v>
+        <v>0.134164</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>308</v>
@@ -40502,7 +40502,7 @@
         <v>1.59224</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>0.1367</v>
+        <v>0.133482</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>312</v>
@@ -40533,7 +40533,7 @@
         <v>1.60433</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.1361</v>
+        <v>0.132798</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>316</v>
@@ -40564,7 +40564,7 @@
         <v>1.61627</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>0.1355</v>
+        <v>0.132127</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>320</v>
@@ -40595,7 +40595,7 @@
         <v>1.6281</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>0.1349</v>
+        <v>0.131448</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>324</v>
@@ -40626,7 +40626,7 @@
         <v>1.63985</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>0.1344</v>
+        <v>0.130776</v>
       </c>
       <c r="F87" s="1" t="n">
         <v>328</v>
@@ -40657,7 +40657,7 @@
         <v>1.65158</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.1338</v>
+        <v>0.130103</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>332</v>
@@ -40688,7 +40688,7 @@
         <v>1.66322</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>0.1332</v>
+        <v>0.129444</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>336</v>
@@ -40719,7 +40719,7 @@
         <v>1.6746</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.1326</v>
+        <v>0.128777</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>340</v>
@@ -40750,7 +40750,7 @@
         <v>1.68597</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.1321</v>
+        <v>0.128118</v>
       </c>
       <c r="F91" s="1" t="n">
         <v>344</v>
@@ -40781,7 +40781,7 @@
         <v>1.69734</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>0.1315</v>
+        <v>0.12746</v>
       </c>
       <c r="F92" s="1" t="n">
         <v>348</v>
@@ -40812,7 +40812,7 @@
         <v>1.70861</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>0.1309</v>
+        <v>0.126817</v>
       </c>
       <c r="F93" s="1" t="n">
         <v>352</v>
@@ -40843,7 +40843,7 @@
         <v>1.71964</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.1303</v>
+        <v>0.126167</v>
       </c>
       <c r="F94" s="1" t="n">
         <v>356</v>
@@ -40874,7 +40874,7 @@
         <v>1.73058</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>0.1298</v>
+        <v>0.125526</v>
       </c>
       <c r="F95" s="1" t="n">
         <v>360</v>
@@ -40905,7 +40905,7 @@
         <v>1.74157</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>0.1292</v>
+        <v>0.124887</v>
       </c>
       <c r="F96" s="1" t="n">
         <v>364</v>
@@ -40936,7 +40936,7 @@
         <v>1.75258</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>0.1286</v>
+        <v>0.124263</v>
       </c>
       <c r="F97" s="1" t="n">
         <v>368</v>
@@ -40967,7 +40967,7 @@
         <v>1.76334</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>0.128</v>
+        <v>0.123635</v>
       </c>
       <c r="F98" s="1" t="n">
         <v>372</v>
@@ -40998,7 +40998,7 @@
         <v>1.77408</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>0.1275</v>
+        <v>0.123016</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>376</v>
@@ -41029,7 +41029,7 @@
         <v>1.78483</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>0.1269</v>
+        <v>0.122399</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>380</v>
@@ -41060,7 +41060,7 @@
         <v>1.79549</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.1263</v>
+        <v>0.121792</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>384</v>
@@ -41091,7 +41091,7 @@
         <v>1.80606</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>0.1257</v>
+        <v>0.121192</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>388</v>
@@ -41122,7 +41122,7 @@
         <v>1.81649</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.1252</v>
+        <v>0.1206</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>392</v>
@@ -41153,7 +41153,7 @@
         <v>1.8269</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.1246</v>
+        <v>0.120018</v>
       </c>
       <c r="F104" s="1" t="n">
         <v>396</v>
@@ -41184,7 +41184,7 @@
         <v>1.83724</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>0.124</v>
+        <v>0.119464</v>
       </c>
       <c r="F105" s="1" t="n">
         <v>400</v>
@@ -41215,7 +41215,7 @@
         <v>1.8475</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>0.118921</v>
+        <v>0.118929</v>
       </c>
       <c r="F106" s="1" t="n">
         <v>404</v>
@@ -41246,7 +41246,7 @@
         <v>1.85762</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0.118408</v>
+        <v>0.11841</v>
       </c>
       <c r="F107" s="1" t="n">
         <v>408</v>
@@ -41277,7 +41277,7 @@
         <v>1.86789</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.117913</v>
+        <v>0.117903</v>
       </c>
       <c r="F108" s="1" t="n">
         <v>412</v>
@@ -41308,7 +41308,7 @@
         <v>1.87808</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.117423</v>
+        <v>0.11742</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>416</v>
@@ -41370,7 +41370,7 @@
         <v>1.8985</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>0.116474</v>
+        <v>0.116469</v>
       </c>
       <c r="F111" s="1" t="n">
         <v>424</v>
@@ -41401,7 +41401,7 @@
         <v>1.90856</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.116005</v>
+        <v>0.116001</v>
       </c>
       <c r="F112" s="1" t="n">
         <v>428</v>
@@ -41432,7 +41432,7 @@
         <v>1.91854</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>0.115538</v>
+        <v>0.115539</v>
       </c>
       <c r="F113" s="1" t="n">
         <v>432</v>
@@ -41463,7 +41463,7 @@
         <v>1.92845</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.115076</v>
+        <v>0.115083</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>436</v>
@@ -41494,7 +41494,7 @@
         <v>1.93857</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.114635</v>
+        <v>0.114632</v>
       </c>
       <c r="F115" s="1" t="n">
         <v>440</v>
@@ -41525,7 +41525,7 @@
         <v>1.94844</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>0.114187</v>
+        <v>0.114188</v>
       </c>
       <c r="F116" s="1" t="n">
         <v>444</v>
@@ -41556,7 +41556,7 @@
         <v>1.95846</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.113756</v>
+        <v>0.113751</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>448</v>
@@ -41587,7 +41587,7 @@
         <v>1.96819</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.113317</v>
+        <v>0.113322</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>452</v>
@@ -41618,7 +41618,7 @@
         <v>1.97804</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.112892</v>
+        <v>0.112898</v>
       </c>
       <c r="F119" s="1" t="n">
         <v>456</v>
@@ -41649,7 +41649,7 @@
         <v>1.98804</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>0.112483</v>
+        <v>0.112477</v>
       </c>
       <c r="F120" s="1" t="n">
         <v>460</v>
@@ -41680,7 +41680,7 @@
         <v>1.99781</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0.112067</v>
+        <v>0.112063</v>
       </c>
       <c r="F121" s="1" t="n">
         <v>464</v>
@@ -41711,7 +41711,7 @@
         <v>2.00751</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>0.111655</v>
+        <v>0.111654</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>468</v>
@@ -41742,7 +41742,7 @@
         <v>2.01716</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>0.111248</v>
+        <v>0.11125</v>
       </c>
       <c r="F123" s="1" t="n">
         <v>472</v>
@@ -41773,7 +41773,7 @@
         <v>2.02681</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0.110848</v>
+        <v>0.110852</v>
       </c>
       <c r="F124" s="1" t="n">
         <v>476</v>
@@ -41804,7 +41804,7 @@
         <v>2.0365</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0.110456</v>
+        <v>0.110458</v>
       </c>
       <c r="F125" s="1" t="n">
         <v>480</v>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16017,7 +16018,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched experimental mass-loss measurements and was adopted in the final model.</t>
+          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched literature mass-loss measurements and was adopted in the final model.</t>
         </is>
       </c>
     </row>
@@ -16145,54 +16146,54 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Mass Loss (%)</t>
+          <t>Mass loss (%)</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Relative Error (%)</t>
+          <t>Relative error (%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>L1(Very Low)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+          <t>L1 (Very Low)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>182768</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1.439</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1465.6</v>
+        <v>1465.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>L2(Low)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+          <t>L2 (Low)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0.4977</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>441.4</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>L3(Medium)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+          <t>L3 (Medium)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>3454723</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -16205,10 +16206,10 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>L4(High)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
+          <t>L4 (High)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>4990080</v>
       </c>
       <c r="C8" s="6" t="n">
@@ -16221,33 +16222,33 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>L5(Very High)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
+          <t>L5 (Very High)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
         <v>11958220</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0.1002</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="8" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>L6(Ultra High)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
+          <t>L6 (Ultra High)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>18864900</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>0.0927</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="11">
@@ -16256,7 +16257,7 @@
           <t>Reference</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="9" t="n">
         <v>21245850</v>
       </c>
       <c r="C11" s="6" t="n">
@@ -16306,7 +16307,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Mesh Type</t>
+          <t>Mesh type</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -16316,12 +16317,12 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Mass Loss (%)</t>
+          <t>Mass loss (%)</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Error vs. Ref (%)</t>
+          <t>Error vs. reference (%)</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -16336,14 +16337,14 @@
           <t>Uniform Mesh</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="9" t="n">
         <v>799520</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>2.8561</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3011</v>
+        <v>3007.8</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -16357,7 +16358,7 @@
           <t>Adaptive Mesh</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -16376,7 +16377,7 @@
           <t>Reference Mesh</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="9" t="n">
         <v>21245850</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -16885,7 +16886,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>60,953</t>
+          <t>2,592</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -17027,17 +17028,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>FreeFEM++</t>
+          <t>FreeFEM (v4.14)</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>FreeFEM++</t>
+          <t>FreeFEM (v4.14)</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>FreeFEM++</t>
+          <t>FreeFEM (v4.14)</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17170,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameters included in the Morris sensitivity analysis</t>
+          <t>Parameters included in the Morris sensitivity analysis.</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17209,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>50-200</t>
+          <t>50–200</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -17230,12 +17231,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>1–50</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>mm^6g^-2h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17253,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>0.1-5.0</t>
+          <t>0.1–5.0</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -17274,12 +17275,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>5–20</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>mm^2h^-1</t>
+          <t>mm^2 h^-1</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17297,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1X10^-9 to 1X10^-7</t>
+          <t>1×10^-9 to 1×10^-7</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -17318,12 +17319,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1.5-5.0</t>
+          <t>1.5–5.0</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>mm^2h^-1</t>
+          <t>mm^2 h^-1</t>
         </is>
       </c>
     </row>
@@ -17340,12 +17341,12 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>5-15</t>
+          <t>5–15</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>mm^2h^-1</t>
+          <t>mm^2 h^-1</t>
         </is>
       </c>
     </row>
@@ -17362,12 +17363,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>15-35</t>
+          <t>15–35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>mm^2h^-1</t>
+          <t>mm^2 h^-1</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17400,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Morris design settings</t>
+          <t>Morris design settings.</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17521,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Literature mass-loss data used for Bayesian calibration (Liu et al. 2018)</t>
+          <t>Literature mass-loss data used for Bayesian calibration (Liu et al. 2018).</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17533,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -17637,7 +17638,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Literature Zn dissolution and pH data used for validation (Liu et al. 2018)</t>
+          <t>Literature Zn dissolution and pH data used for validation (Liu et al. 2018).</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17650,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -19684,14 +19685,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Calibrated model validation through comparison of predicted mass loss and literature-reported mass loss for Zn degradation</t>
+          <t>Final calibrated-model predictions of mass loss compared with the literature mass-loss data used for calibration (Liu et al. 2018).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -19920,7 +19921,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Main-text Table 2</t>
         </is>
       </c>
     </row>
@@ -19937,32 +19938,36 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>External probe points</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>9</v>
+          <t>Initial sampling</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>12-point Latin hypercube design (iterations 1–12)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Corner-point evaluations</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>8</v>
+          <t>Acquisition function</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Expected improvement</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Warm-start data</t>
+          <t>Total iterations</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Previous runs and training dataset</t>
+          <t>32 (optimum at iteration 22)</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20027,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Geometric and computational parameters of the controlled test structures used in Figure 8</t>
+          <t>Geometric and computational parameters of the controlled test structures used in Figure 8.</t>
         </is>
       </c>
     </row>
@@ -24202,7 +24207,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -24253,7 +24258,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -24273,7 +24278,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -24284,7 +24289,7 @@
       <c r="H5" s="1" t="n"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
@@ -24310,7 +24315,7 @@
       </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="V5" s="1" t="inlineStr">
@@ -24360,7 +24365,7 @@
       </c>
       <c r="AF5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="AG5" s="1" t="inlineStr">
@@ -37729,7 +37734,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Zn2+ Release - Simulation vs Experimental</t>
+          <t>Zn2+ Release - Simulation vs Literature</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -37741,7 +37746,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -37761,7 +37766,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -38036,7 +38041,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -38051,7 +38056,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Time (h)</t>
+          <t>Time (hours)</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -3659,7 +3659,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>L1 (VeryLow)</t>
+          <t>L1 (Very Low)</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -3672,7 +3672,7 @@
         <v>1.439</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1465.6</v>
+        <v>1465.8</v>
       </c>
     </row>
     <row r="6">
@@ -3691,7 +3691,7 @@
         <v>0.4977</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>441.4</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="7">
@@ -3735,7 +3735,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>L5 (VeryHigh)</t>
+          <t>L5 (Very High)</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -3754,7 +3754,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>L6 (UltraHigh)</t>
+          <t>L6 (Ultra High)</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -3767,7 +3767,7 @@
         <v>0.0927</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="11">
@@ -5113,8 +5113,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
-    </row>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Normalization: (value - min) / (max - min) over the 32 evaluated iterations (k_f: 1.213-83.562 h^-1; k_d: 5.0-100.0 mm^6 g^-2 h^-1; k_ORR: 0.0602-4.4933 mm h^-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -37731,6 +37736,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -37980,15 +37986,16 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.1016/j.jmst.2018.05.005 </t>
+          <t>Literature source: Liu et al. (2018), https://doi.org/10.1016/j.jmst.2018.05.005</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.1016/j.jmst.2018.05.005 </t>
-        </is>
-      </c>
-    </row>
+          <t>Literature source: Liu et al. (2018), https://doi.org/10.1016/j.jmst.2018.05.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="n"/>
     </row>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -6,18 +6,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3a" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3b" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4a-c" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4d-f" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4g-i" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 5a,b" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 5e,f" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 6a,b" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 8a" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 8b" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 8c" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 8d" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 2a" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 2b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3a-c" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3d-f" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3g-i" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4a,b" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4e,f" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 5a,b" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 7a" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 7b" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 7c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 7d" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 3a</t>
+          <t>Figure 2a</t>
         </is>
       </c>
     </row>
@@ -487,6 +487,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -654,7 +655,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 8b</t>
+          <t>Figure 7b</t>
         </is>
       </c>
     </row>
@@ -665,6 +666,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2561,7 +2563,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Figure 8c</t>
+          <t>Figure 7c</t>
         </is>
       </c>
     </row>
@@ -2572,6 +2574,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2722,7 +2725,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Figure 8d</t>
+          <t>Figure 7d</t>
         </is>
       </c>
     </row>
@@ -2733,6 +2736,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2960,6 +2964,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3384,6 +3389,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3499,6 +3505,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3629,6 +3636,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3819,6 +3827,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5921,6 +5930,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -10040,6 +10050,7 @@
       </c>
       <c r="H174" s="1" t="n"/>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -10941,7 +10952,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 3b</t>
+          <t>Figure 2b</t>
         </is>
       </c>
     </row>
@@ -11824,6 +11835,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -15755,6 +15767,7 @@
         <v>3.411422</v>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -15860,6 +15873,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -16027,6 +16041,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16138,6 +16153,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16309,6 +16325,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16431,6 +16448,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17179,6 +17197,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17409,6 +17428,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17530,6 +17550,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17647,6 +17668,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17770,7 +17792,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 4a-c</t>
+          <t>Figure 3a-c</t>
         </is>
       </c>
     </row>
@@ -17781,6 +17803,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17788,6 +17811,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -18412,6 +18436,7 @@
         <v>0.357907</v>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
@@ -19036,6 +19061,7 @@
         <v>0.405208</v>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
@@ -19694,6 +19720,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -19846,6 +19873,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20032,10 +20060,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Geometric and computational parameters of the controlled test structures used in Figure 8.</t>
-        </is>
-      </c>
-    </row>
+          <t>Geometric and computational parameters of the controlled test structures used in Figure 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20355,7 +20384,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 4d-f</t>
+          <t>Figure 3d-f</t>
         </is>
       </c>
     </row>
@@ -20366,6 +20395,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -20373,6 +20403,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -20997,6 +21028,7 @@
         <v>25.1378</v>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
@@ -21621,6 +21653,7 @@
         <v>11.827</v>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
@@ -22262,7 +22295,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 4g-i</t>
+          <t>Figure 3g-i</t>
         </is>
       </c>
     </row>
@@ -22273,6 +22306,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -22280,6 +22314,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -22904,6 +22939,7 @@
         <v>0.9999700000000008</v>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
@@ -23528,6 +23564,7 @@
         <v>1.328479999999997</v>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
@@ -24173,12 +24210,12 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 5a,b</t>
+          <t>Figure 4a,b</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Figure 5a,b - model validation statistics</t>
+          <t>Figure 4a,b - model validation statistics</t>
         </is>
       </c>
     </row>
@@ -24190,10 +24227,11 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Simulated vs. experimental mass loss by immersion day (supports Figure 5a; not a numbered manuscript table).</t>
-        </is>
-      </c>
-    </row>
+          <t>Simulated vs. experimental mass loss by immersion day (supports Figure 4a; not a numbered manuscript table).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -37725,7 +37763,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 5e,f</t>
+          <t>Figure 4e,f</t>
         </is>
       </c>
     </row>
@@ -38022,7 +38060,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 6a,b</t>
+          <t>Figure 5a,b</t>
         </is>
       </c>
     </row>
@@ -48888,7 +48926,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Figure 8a</t>
+          <t>Figure 7a</t>
         </is>
       </c>
     </row>
@@ -48899,6 +48937,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/Computational_results_-_SourceData_updated.xlsx
+++ b/Computational_results_-_SourceData_updated.xlsx
@@ -2941,431 +2941,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Model parameters used in the Zn biodegradation simulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Property/Parameter</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Magnitude</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Material properties</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Zn density</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>ρ_Zn</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>7.14 g cm^-3</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>[46]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Zn molar mass</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>M_Zn</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>65.38 g mol^-1</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>[46]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Diffusion coefficients (37 °C)</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ diffusivity</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>D_Zn^0</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>7.56 × 10^-4 mm^2 s^-1</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>[47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Cl- diffusivity</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>D_Cl^0</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>2.16 × 10^-3 mm^2 s^-1</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>[47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OH- diffusivity</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>D_OH^0</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>5.60 × 10^-3 mm^2 s^-1</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>[47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>O2 diffusivity</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>D_O2^0</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>2.60 × 10^-3 mm^2 s^-1</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>[48]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Film properties</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Film density</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>ρ_film</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>5.606 g cm^-3</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>[47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Film porosity</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>ε</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>[49]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Film tortuosity</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>τ</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>[50]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Film molar mass</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>M_film</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>81.38 g mol^-1</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>[46]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Interface conditions</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ sat. concentration</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>[Zn]_sat</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>10 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>[51]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Initial conditions</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ concentration</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>C_Zn^0</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Cl- concentration</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>C_Cl^0</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>142.3 mmol L^-1</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>[52]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>O2 concentration</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>C_O2^0</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>3.5 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>[29]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>[53]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3378,7 +2953,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3494,7 +3069,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 2</t>
         </is>
       </c>
     </row>
@@ -3605,6 +3180,431 @@
       <c r="C9" s="1" t="inlineStr">
         <is>
           <t>0.311±0.115</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Model parameters used in the Zn biodegradation simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Property/Parameter</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Magnitude</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Material properties</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Zn density</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ρ_Zn</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>7.14 g cm^-3</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>[46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Zn molar mass</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>M_Zn</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>65.38 g mol^-1</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>[46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Diffusion coefficients (37 °C)</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Zn2+ diffusivity</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>D_Zn^0</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>7.56 × 10^-4 mm^2 s^-1</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>[47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Cl- diffusivity</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>D_Cl^0</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>2.16 × 10^-3 mm^2 s^-1</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>[47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OH- diffusivity</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>D_OH^0</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>5.60 × 10^-3 mm^2 s^-1</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>[47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>O2 diffusivity</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>D_O2^0</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>2.60 × 10^-3 mm^2 s^-1</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>[48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Film properties</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Film density</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>ρ_film</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>5.606 g cm^-3</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>[47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Film porosity</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>ε</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>[49]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Film tortuosity</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>τ</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>[50]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Film molar mass</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>M_film</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>81.38 g mol^-1</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>[46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Interface conditions</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Zn2+ sat. concentration</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>[Zn]_sat</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>10 mg L^-1</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>[51]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Initial conditions</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
+      <c r="D20" s="1" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Zn2+ concentration</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>C_Zn^0</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Cl- concentration</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>C_Cl^0</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>142.3 mmol L^-1</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>[52]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>O2 concentration</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>C_O2^0</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>3.5 mg L^-1</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>[29]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
+          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 mm^6 g^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 1).</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Main-text Table 2</t>
+          <t>Main-text Table 1</t>
         </is>
       </c>
     </row>
